--- a/商品采集汇总.xlsx
+++ b/商品采集汇总.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3043,15 +3043,11 @@
           <t>兰蔻 极光乳液净澈焕肤亮白乳液 75ml</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>470.0</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>369.0</t>
-        </is>
+      <c r="D90" t="n">
+        <v>470</v>
+      </c>
+      <c r="E90" t="n">
+        <v>369</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -3078,24 +3074,1160 @@
           <t>兰蔻 极光乳液净澈焕肤亮白乳液 75ml</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D91" t="n">
+        <v>419</v>
+      </c>
+      <c r="E91" t="n">
+        <v>292</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>191</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>【正品行货】Clinique/倩碧小雏菊单色腮红提亮自然3.5g</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>倩碧小雏菊裸色阳光腮#05</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>228.8</v>
+      </c>
+      <c r="E92" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>191</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>【Clinique】倩碧小雏菊腮红#01#02#05#07#08#15提亮自然</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>倩碧小雏菊裸色阳光腮#05</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>170</v>
+      </c>
+      <c r="E93" t="n">
+        <v>94</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>198</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>【专柜礼盒】雅诗兰黛 第七代小棕瓶50ml特润修护紧致专柜原装</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>2388</v>
+      </c>
+      <c r="E94" t="n">
+        <v>312</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>199</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛净莹柔肤洗面奶深层清洁温和保湿专柜直售</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>雅诗兰黛 净莹柔肤洁面乳150ml（蓝洁面）</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>8072</v>
+      </c>
+      <c r="E95" t="n">
+        <v>128.8</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>200</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛DW持妆粉底液 油皮亲妈持久不脱妆遮瑕控油</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>雅诗兰黛DW  2c0</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>2130</v>
+      </c>
+      <c r="E96" t="n">
+        <v>228</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>201</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛小棕瓶系列 滋润修护 熬夜必选</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>雅诗兰黛大棕罐膜霜65ml</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>75</v>
+      </c>
+      <c r="E97" t="n">
+        <v>75</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>201</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Estee Lauder雅诗兰黛大棕罐封愈膜霜65ml紧致面霜</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>雅诗兰黛大棕罐膜霜65ml</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>458</v>
+      </c>
+      <c r="E98" t="n">
+        <v>369</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>201</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】大棕罐封愈膜霜65ml 修护紧致面霜 节日礼物</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>雅诗兰黛大棕罐膜霜65ml</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>428</v>
+      </c>
+      <c r="E99" t="n">
+        <v>428</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>202</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛红石榴洁面60ml支鲜活亮采二合一洁面乳</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴洁面60ml</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>62</v>
+      </c>
+      <c r="E100" t="n">
+        <v>62</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>202</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛红石榴60ml小样洁面清洁毛孔控油旅行必备款</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴洁面60ml</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>158</v>
+      </c>
+      <c r="E101" t="n">
+        <v>138</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>203</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛眼霜第七代小棕瓶特润修护紧致送礼盒礼物</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>雅诗兰黛第七代特润小棕瓶100ml*2（新款）</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>2680</v>
+      </c>
+      <c r="E102" t="n">
+        <v>312</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>203</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>【专柜礼盒】雅诗兰黛 第七代小棕瓶50ml特润修护紧致专柜原装</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>雅诗兰黛第七代特润小棕瓶100ml*2（新款）</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>312</v>
+      </c>
+      <c r="E103" t="n">
+        <v>312</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>204</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>EsteeLauder雅诗兰黛线雕精华50ml 淡纹抗皱</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>雅诗兰黛线雕精华50ml（新版）</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>379</v>
+      </c>
+      <c r="E104" t="n">
+        <v>379</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>205</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛眼霜小棕瓶15ml第五代修护抗蓝光熬夜淡化</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>雅诗兰黛小棕瓶眼霜15ml</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>699</v>
+      </c>
+      <c r="E105" t="n">
+        <v>313</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>205</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛小棕瓶系列 滋润修护 熬夜必选</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>雅诗兰黛小棕瓶眼霜15ml</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>75</v>
+      </c>
+      <c r="E106" t="n">
+        <v>75</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>162</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>【正品行货】兰蔻净澈焕肤亮白乳液 75MI滋润补水提亮油皮挚爱</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>兰蔻 极光乳液净澈焕肤亮白乳液 75ml</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>470.0</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>369.0</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>162</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>【兰蔻】极光乳液75ml提亮焕白改善暗沉</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>兰蔻 极光乳液净澈焕肤亮白乳液 75ml</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
         <is>
           <t>419.0</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E108" t="inlineStr">
         <is>
           <t>292.0</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
         <is>
           <t>2025-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>191</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>【正品行货】Clinique/倩碧小雏菊单色腮红提亮自然3.5g</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>倩碧小雏菊裸色阳光腮#05</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>228.8</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>191</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>【Clinique】倩碧小雏菊腮红#01#02#05#07#08#15提亮自然</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>倩碧小雏菊裸色阳光腮#05</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>170.0</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>198</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>【专柜礼盒】雅诗兰黛 第七代小棕瓶50ml特润修护紧致专柜原装</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2388.0</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>312.0</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>199</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛净莹柔肤洗面奶深层清洁温和保湿专柜直售</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>雅诗兰黛 净莹柔肤洁面乳150ml（蓝洁面）</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>8072.0</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>128.8</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>200</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛DW持妆粉底液 油皮亲妈持久不脱妆遮瑕控油</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>雅诗兰黛DW  2c0</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2130.0</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>228.0</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>201</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛小棕瓶系列 滋润修护 熬夜必选</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>雅诗兰黛大棕罐膜霜65ml</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>201</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Estee Lauder雅诗兰黛大棕罐封愈膜霜65ml紧致面霜</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>雅诗兰黛大棕罐膜霜65ml</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>458.0</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>369.0</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>201</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】大棕罐封愈膜霜65ml 修护紧致面霜 节日礼物</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>雅诗兰黛大棕罐膜霜65ml</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>428.0</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>428.0</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>202</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛红石榴洁面60ml支鲜活亮采二合一洁面乳</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴洁面60ml</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>202</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛红石榴60ml小样洁面清洁毛孔控油旅行必备款</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴洁面60ml</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>203</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛眼霜第七代小棕瓶特润修护紧致送礼盒礼物</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>雅诗兰黛第七代特润小棕瓶100ml*2（新款）</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2680.0</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>312.0</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>203</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>【专柜礼盒】雅诗兰黛 第七代小棕瓶50ml特润修护紧致专柜原装</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>雅诗兰黛第七代特润小棕瓶100ml*2（新款）</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>312.0</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>312.0</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>204</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>EsteeLauder雅诗兰黛线雕精华50ml 淡纹抗皱</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>雅诗兰黛线雕精华50ml（新版）</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>379.0</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>379.0</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>205</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛眼霜小棕瓶15ml第五代修护抗蓝光熬夜淡化</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>雅诗兰黛小棕瓶眼霜15ml</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>699.0</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>313.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>205</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛小棕瓶系列 滋润修护 熬夜必选</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>雅诗兰黛小棕瓶眼霜15ml</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>206</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】智妍夜胶原晚霜75ml淡纹紧致面霜化妆品礼盒套装生日礼物</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>雅诗兰黛智妍晚霜75ml</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>1299.0</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>837.0</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>206</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】多效智妍面霜(清爽版)75ml双支</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>雅诗兰黛智妍晚霜75ml</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>1050.0</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>757.0</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>206</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>EsteeLauder 雅诗兰黛智妍焕白乳霜 75ml</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>雅诗兰黛智妍晚霜75ml</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>638.0</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>471.0</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>206</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>双瓶 单品 雅诗兰黛多效智妍面霜滋润版75ml</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>雅诗兰黛智妍晚霜75ml</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>1169.0</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>774.0</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
         </is>
       </c>
     </row>

--- a/商品采集汇总.xlsx
+++ b/商品采集汇总.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3031,201 +3031,197 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>162</v>
+        <v>198</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>【正品行货】兰蔻净澈焕肤亮白乳液 75MI滋润补水提亮油皮挚爱</t>
+          <t>【专柜礼盒】雅诗兰黛 第七代小棕瓶50ml特润修护紧致专柜原装</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>兰蔻 极光乳液净澈焕肤亮白乳液 75ml</t>
+          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>470</v>
+        <v>2388</v>
       </c>
       <c r="E90" t="n">
-        <v>369</v>
+        <v>312</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>2025-02-01</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>162</v>
+        <v>199</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>【兰蔻】极光乳液75ml提亮焕白改善暗沉</t>
+          <t>【正品行货】雅诗兰黛净莹柔肤洗面奶深层清洁温和保湿专柜直售</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>兰蔻 极光乳液净澈焕肤亮白乳液 75ml</t>
+          <t>雅诗兰黛 净莹柔肤洁面乳150ml（蓝洁面）</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>419</v>
+        <v>8072</v>
       </c>
       <c r="E91" t="n">
-        <v>292</v>
+        <v>128.8</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>【正品行货】Clinique/倩碧小雏菊单色腮红提亮自然3.5g</t>
+          <t>【正品行货】雅诗兰黛DW持妆粉底液 油皮亲妈持久不脱妆遮瑕控油</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>倩碧小雏菊裸色阳光腮#05</t>
+          <t>雅诗兰黛DW  2c0</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>228.8</v>
+        <v>2130</v>
       </c>
       <c r="E92" t="n">
-        <v>90.5</v>
+        <v>228</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>【Clinique】倩碧小雏菊腮红#01#02#05#07#08#15提亮自然</t>
+          <t>【正品行货】雅诗兰黛小棕瓶系列 滋润修护 熬夜必选</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>倩碧小雏菊裸色阳光腮#05</t>
+          <t>雅诗兰黛大棕罐膜霜65ml</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="E93" t="n">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2023-10-01</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>【专柜礼盒】雅诗兰黛 第七代小棕瓶50ml特润修护紧致专柜原装</t>
+          <t>Estee Lauder雅诗兰黛大棕罐封愈膜霜65ml紧致面霜</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
+          <t>雅诗兰黛大棕罐膜霜65ml</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>2388</v>
+        <v>458</v>
       </c>
       <c r="E94" t="n">
-        <v>312</v>
+        <v>369</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>【正品行货】雅诗兰黛净莹柔肤洗面奶深层清洁温和保湿专柜直售</t>
+          <t>【雅诗兰黛】大棕罐封愈膜霜65ml 修护紧致面霜 节日礼物</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>雅诗兰黛 净莹柔肤洁面乳150ml（蓝洁面）</t>
+          <t>雅诗兰黛大棕罐膜霜65ml</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>8072</v>
+        <v>428</v>
       </c>
       <c r="E95" t="n">
-        <v>128.8</v>
+        <v>428</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>【正品行货】雅诗兰黛DW持妆粉底液 油皮亲妈持久不脱妆遮瑕控油</t>
+          <t>【正品行货】雅诗兰黛红石榴洁面60ml支鲜活亮采二合一洁面乳</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>雅诗兰黛DW  2c0</t>
+          <t>雅诗兰黛红石榴洁面60ml</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2130</v>
+        <v>62</v>
       </c>
       <c r="E96" t="n">
-        <v>228</v>
+        <v>62</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3236,295 +3232,295 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>【正品行货】雅诗兰黛小棕瓶系列 滋润修护 熬夜必选</t>
+          <t>【正品行货】雅诗兰黛红石榴60ml小样洁面清洁毛孔控油旅行必备款</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>雅诗兰黛大棕罐膜霜65ml</t>
+          <t>雅诗兰黛红石榴洁面60ml</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="E97" t="n">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>2023-10-01</t>
-        </is>
-      </c>
+      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Estee Lauder雅诗兰黛大棕罐封愈膜霜65ml紧致面霜</t>
+          <t>【正品行货】雅诗兰黛眼霜第七代小棕瓶特润修护紧致送礼盒礼物</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>雅诗兰黛大棕罐膜霜65ml</t>
+          <t>雅诗兰黛第七代特润小棕瓶100ml*2（新款）</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>458</v>
+        <v>2680</v>
       </c>
       <c r="E98" t="n">
-        <v>369</v>
+        <v>312</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
+      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>【雅诗兰黛】大棕罐封愈膜霜65ml 修护紧致面霜 节日礼物</t>
+          <t>【专柜礼盒】雅诗兰黛 第七代小棕瓶50ml特润修护紧致专柜原装</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>雅诗兰黛大棕罐膜霜65ml</t>
+          <t>雅诗兰黛第七代特润小棕瓶100ml*2（新款）</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>428</v>
+        <v>312</v>
       </c>
       <c r="E99" t="n">
-        <v>428</v>
+        <v>312</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
+      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>【正品行货】雅诗兰黛红石榴洁面60ml支鲜活亮采二合一洁面乳</t>
+          <t>EsteeLauder雅诗兰黛线雕精华50ml 淡纹抗皱</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴洁面60ml</t>
+          <t>雅诗兰黛线雕精华50ml（新版）</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>62</v>
+        <v>379</v>
       </c>
       <c r="E100" t="n">
-        <v>62</v>
+        <v>379</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>【正品行货】雅诗兰黛红石榴60ml小样洁面清洁毛孔控油旅行必备款</t>
+          <t>【正品行货】雅诗兰黛眼霜小棕瓶15ml第五代修护抗蓝光熬夜淡化</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴洁面60ml</t>
+          <t>雅诗兰黛小棕瓶眼霜15ml</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>158</v>
+        <v>699</v>
       </c>
       <c r="E101" t="n">
-        <v>138</v>
+        <v>313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>【正品行货】雅诗兰黛眼霜第七代小棕瓶特润修护紧致送礼盒礼物</t>
+          <t>【正品行货】雅诗兰黛小棕瓶系列 滋润修护 熬夜必选</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>雅诗兰黛第七代特润小棕瓶100ml*2（新款）</t>
+          <t>雅诗兰黛小棕瓶眼霜15ml</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2680</v>
+        <v>75</v>
       </c>
       <c r="E102" t="n">
-        <v>312</v>
+        <v>75</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>【专柜礼盒】雅诗兰黛 第七代小棕瓶50ml特润修护紧致专柜原装</t>
+          <t>【雅诗兰黛】智妍夜胶原晚霜75ml淡纹紧致面霜化妆品礼盒套装生日礼物</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>雅诗兰黛第七代特润小棕瓶100ml*2（新款）</t>
+          <t>雅诗兰黛智妍晚霜75ml</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>312</v>
+        <v>1299</v>
       </c>
       <c r="E103" t="n">
-        <v>312</v>
+        <v>837</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>EsteeLauder雅诗兰黛线雕精华50ml 淡纹抗皱</t>
+          <t>【雅诗兰黛】多效智妍面霜(清爽版)75ml双支</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>雅诗兰黛线雕精华50ml（新版）</t>
+          <t>雅诗兰黛智妍晚霜75ml</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>379</v>
+        <v>1050</v>
       </c>
       <c r="E104" t="n">
-        <v>379</v>
+        <v>757</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>2025-02-01</t>
-        </is>
-      </c>
+      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>【正品行货】雅诗兰黛眼霜小棕瓶15ml第五代修护抗蓝光熬夜淡化</t>
+          <t>EsteeLauder 雅诗兰黛智妍焕白乳霜 75ml</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>雅诗兰黛小棕瓶眼霜15ml</t>
+          <t>雅诗兰黛智妍晚霜75ml</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>699</v>
+        <v>638</v>
       </c>
       <c r="E105" t="n">
-        <v>313</v>
+        <v>471</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2024-08-01</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>【正品行货】雅诗兰黛小棕瓶系列 滋润修护 熬夜必选</t>
+          <t>双瓶 单品 雅诗兰黛多效智妍面霜滋润版75ml</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>雅诗兰黛小棕瓶眼霜15ml</t>
+          <t>雅诗兰黛智妍晚霜75ml</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>75</v>
+        <v>1169</v>
       </c>
       <c r="E106" t="n">
-        <v>75</v>
+        <v>774</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3530,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>【正品行货】兰蔻净澈焕肤亮白乳液 75MI滋润补水提亮油皮挚爱</t>
+          <t>【兰蔻】极光乳液75ml提亮焕白改善暗沉</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3542,15 +3538,11 @@
           <t>兰蔻 极光乳液净澈焕肤亮白乳液 75ml</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>470.0</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>369.0</t>
-        </is>
+      <c r="D107" t="n">
+        <v>399</v>
+      </c>
+      <c r="E107" t="n">
+        <v>315.91</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -3559,530 +3551,486 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>162</v>
+        <v>191</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>【兰蔻】极光乳液75ml提亮焕白改善暗沉</t>
+          <t>【Clinique】倩碧小雏菊腮红#01#02#05#07#08#15提亮自然</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>兰蔻 极光乳液净澈焕肤亮白乳液 75ml</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>419.0</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>292.0</t>
-        </is>
+          <t>倩碧小雏菊裸色阳光腮#05</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>170</v>
+      </c>
+      <c r="E108" t="n">
+        <v>94</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2024-08-01</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>【正品行货】Clinique/倩碧小雏菊单色腮红提亮自然3.5g</t>
+          <t>IPSA/茵芙莎三色遮瑕膏4.5g遮盖斑点遮痘黑眼圈保湿水润修饰肤色</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>倩碧小雏菊裸色阳光腮#05</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>228.8</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>90.5</t>
-        </is>
+          <t>茵芙纱 三色遮瑕4.5g</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>400</v>
+      </c>
+      <c r="E109" t="n">
+        <v>102.5</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
+      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>【Clinique】倩碧小雏菊腮红#01#02#05#07#08#15提亮自然</t>
+          <t>IPSA/茵芙莎 三色遮瑕膏4.5g 遮黑眼圈痘痘泪沟遮暇【5天内发货】</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>倩碧小雏菊裸色阳光腮#05</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>170.0</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
+          <t>茵芙纱 三色遮瑕4.5g</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>220</v>
+      </c>
+      <c r="E110" t="n">
+        <v>220</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-04-13</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>【专柜礼盒】雅诗兰黛 第七代小棕瓶50ml特润修护紧致专柜原装</t>
+          <t>【跨境原装】资生堂安耐晒防晒霜清爽不油面部防紫外线敏感肌正品</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>2388.0</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>312.0</t>
-        </is>
+          <t>资生堂安耐晒60ml新版</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>114.9</v>
+      </c>
+      <c r="E111" t="n">
+        <v>114.9</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>【正品行货】雅诗兰黛净莹柔肤洗面奶深层清洁温和保湿专柜直售</t>
+          <t>【资生堂】百优精纯面霜75ml保湿滋润补水紧致抗衰老乳霜</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>雅诗兰黛 净莹柔肤洁面乳150ml（蓝洁面）</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>8072.0</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>128.8</t>
-        </is>
+          <t>资生堂百优面霜 75ml</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>288</v>
+      </c>
+      <c r="E112" t="n">
+        <v>237.9</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>【正品行货】雅诗兰黛DW持妆粉底液 油皮亲妈持久不脱妆遮瑕控油</t>
+          <t>【资生堂】百优精华面霜75ml补水保湿</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>雅诗兰黛DW  2c0</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>2130.0</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>228.0</t>
-        </is>
+          <t>资生堂百优面霜 75ml</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>419</v>
+      </c>
+      <c r="E113" t="n">
+        <v>228</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>【正品行货】雅诗兰黛小棕瓶系列 滋润修护 熬夜必选</t>
+          <t>【SHISEIDO】资生堂新版欧版蓝胖子防晒霜150ml*2防晒乳防水防汗旅行</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>雅诗兰黛大棕罐膜霜65ml</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
+          <t>资生堂蓝胖子150ml 新版</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>269</v>
+      </c>
+      <c r="E114" t="n">
+        <v>208</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2024-06-01</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Estee Lauder雅诗兰黛大棕罐封愈膜霜65ml紧致面霜</t>
+          <t>【SHISEIDO】资生堂新版蓝胖子防晒霜150ml防水防汗不油腻防晒乳欧版</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>雅诗兰黛大棕罐膜霜65ml</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>458.0</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>369.0</t>
-        </is>
+          <t>资生堂蓝胖子150ml 新版</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>139</v>
+      </c>
+      <c r="E115" t="n">
+        <v>105</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-06-01</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>【雅诗兰黛】大棕罐封愈膜霜65ml 修护紧致面霜 节日礼物</t>
+          <t>【资生堂】蓝胖子防晒霜防晒乳新版 50ml/瓶</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>雅诗兰黛大棕罐膜霜65ml</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>428.0</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>428.0</t>
-        </is>
+          <t>资生堂蓝胖子防晒50ml</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>169</v>
+      </c>
+      <c r="E116" t="n">
+        <v>102</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-11-01</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>【正品行货】雅诗兰黛红石榴洁面60ml支鲜活亮采二合一洁面乳</t>
+          <t>【资生堂】蓝胖子防晒霜防晒乳新版 50ml/瓶</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴洁面60ml</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
+          <t>资生堂蓝胖子防晒50ml（新版）</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>169</v>
+      </c>
+      <c r="E117" t="n">
+        <v>102</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>202</v>
+        <v>162</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>【正品行货】雅诗兰黛红石榴60ml小样洁面清洁毛孔控油旅行必备款</t>
+          <t>【兰蔻】极光乳液75ml提亮焕白改善暗沉</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴洁面60ml</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>158.0</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>138.0</t>
-        </is>
+          <t>兰蔻 极光乳液净澈焕肤亮白乳液 75ml</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>419</v>
+      </c>
+      <c r="E118" t="n">
+        <v>292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>203</v>
+        <v>162</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>【正品行货】雅诗兰黛眼霜第七代小棕瓶特润修护紧致送礼盒礼物</t>
+          <t>【正品行货】兰蔻净澈焕肤亮白乳液 75MI滋润补水提亮油皮挚爱</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>雅诗兰黛第七代特润小棕瓶100ml*2（新款）</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>2680.0</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>312.0</t>
-        </is>
+          <t>兰蔻 极光乳液净澈焕肤亮白乳液 75ml</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>470</v>
+      </c>
+      <c r="E119" t="n">
+        <v>369</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>【专柜礼盒】雅诗兰黛 第七代小棕瓶50ml特润修护紧致专柜原装</t>
+          <t>【正品行货】Clinique/倩碧小雏菊单色腮红提亮自然3.5g</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>雅诗兰黛第七代特润小棕瓶100ml*2（新款）</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>312.0</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>312.0</t>
-        </is>
+          <t>倩碧小雏菊裸色阳光腮#05</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>228.8</v>
+      </c>
+      <c r="E120" t="n">
+        <v>90.5</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EsteeLauder雅诗兰黛线雕精华50ml 淡纹抗皱</t>
+          <t>【资生堂】时光琉璃洁面125ml深层清洁保湿补水洗面奶</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>雅诗兰黛线雕精华50ml（新版）</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>379.0</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>379.0</t>
-        </is>
+          <t>资生堂琉璃洁面125ml</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>159</v>
+      </c>
+      <c r="E121" t="n">
+        <v>110</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>2025-02-01</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>【正品行货】雅诗兰黛眼霜小棕瓶15ml第五代修护抗蓝光熬夜淡化</t>
+          <t>【资生堂】时光琉璃洁面125ml温和保湿补水深层清洁洗面奶</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>雅诗兰黛小棕瓶眼霜15ml</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>699.0</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>313.0</t>
-        </is>
+          <t>资生堂琉璃洁面125ml</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>141</v>
+      </c>
+      <c r="E122" t="n">
+        <v>109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2024-06-01</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>【正品行货】雅诗兰黛小棕瓶系列 滋润修护 熬夜必选</t>
+          <t>【正品行货】资生堂时光琉璃丰润洁颜乳 50ml清洁保湿</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>雅诗兰黛小棕瓶眼霜15ml</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
+          <t>资生堂琉璃洁面50ml新版</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>47</v>
+      </c>
+      <c r="E123" t="n">
+        <v>47</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -4091,33 +4039,29 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2024-09-02</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>【雅诗兰黛】智妍夜胶原晚霜75ml淡纹紧致面霜化妆品礼盒套装生日礼物</t>
+          <t>专柜 资生堂时光琉璃丰润洁面乳50ml小样温和深层清洁泡沫洗面奶</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>雅诗兰黛智妍晚霜75ml</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>1299.0</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>837.0</t>
-        </is>
+          <t>资生堂琉璃洁面50ml新版</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>51.226</v>
+      </c>
+      <c r="E124" t="n">
+        <v>51.2</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -4132,102 +4076,6655 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>【雅诗兰黛】多效智妍面霜(清爽版)75ml双支</t>
+          <t>【正品行货】资生堂时光琉璃丰润洁颜乳 50ml*2 清洁保湿 旅行装</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>雅诗兰黛智妍晚霜75ml</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>1050.0</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>757.0</t>
-        </is>
+          <t>资生堂琉璃洁面50ml新版</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>89</v>
+      </c>
+      <c r="E125" t="n">
+        <v>89</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EsteeLauder 雅诗兰黛智妍焕白乳霜 75ml</t>
+          <t>【海外直采】Shiseido/资生堂时光琉璃爽肤水74ml改善暗沉保湿</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>雅诗兰黛智妍晚霜75ml</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>638.0</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>471.0</t>
-        </is>
+          <t>资生堂琉璃爽肤水74ml新版</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>74.95999999999999</v>
+      </c>
+      <c r="E126" t="n">
+        <v>74.95999999999999</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-02-01</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
+        <v>215</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>【资生堂】时光琉璃水时光琉璃柔肤水保湿修复74ml补水保湿水</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>资生堂琉璃爽肤水74ml新版</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>77</v>
+      </c>
+      <c r="E127" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2024-04-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>216</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂男士活力均衡水 150ml*2瓶 国柜新款</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>资生堂男生爽肤水150ml</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>194.2</v>
+      </c>
+      <c r="E128" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>216</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂新男士活力均衡水 150ml修护保湿控油礼物送人</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>资生堂男生爽肤水150ml</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="E129" t="n">
+        <v>66.06</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>216</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂男士活力均衡水150ml   补水保湿</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>资生堂男生爽肤水150ml</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>315</v>
+      </c>
+      <c r="E130" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>216</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>【资生堂】男士活力均衡水150ml保湿补水</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>资生堂男生爽肤水150ml</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="E131" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>2024-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>217</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>【资生堂】时光琉璃洁面125ml深层清洁保湿补水洗面奶</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>资生堂男士洁面乳125ml</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>159</v>
+      </c>
+      <c r="E132" t="n">
+        <v>110</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>217</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Shiseido/资生堂肌活焕采洁面膏125ml深层清洁</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>资生堂男士洁面乳125ml</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>199</v>
+      </c>
+      <c r="E133" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>217</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>【资生堂】时光琉璃洁面125ml温和保湿补水深层清洁洗面奶</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>资生堂男士洁面乳125ml</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>141</v>
+      </c>
+      <c r="E134" t="n">
+        <v>109</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>218</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>资生堂UNO乳液脸部补水保湿控油滋润男士面霜秋冬</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>资生堂男士乳液100ml</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>35</v>
+      </c>
+      <c r="E135" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>218</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>日本资生堂UNO乳液男士护肤品三合一滋润控油润肤露</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>资生堂男士乳液100ml</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="E136" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>218</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂二代悦薇智感紧颜亮肤乳 100ml 清爽型</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>资生堂男士乳液100ml</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>185</v>
+      </c>
+      <c r="E137" t="n">
+        <v>185</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>219</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>两套 单品 资生堂悦薇清爽水乳 水150ml+乳液100ml</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>资生堂悦微清爽水150ml（新版）</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>719</v>
+      </c>
+      <c r="E138" t="n">
+        <v>550</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>219</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2套Shiseido/资生堂二代悦薇水150ml+乳液150ml清爽型</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>资生堂悦微清爽水150ml（新版）</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>1099</v>
+      </c>
+      <c r="E139" t="n">
+        <v>538</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>219</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>二代资生堂悦薇水乳清爽亮肤水150ml+乳液100ml保湿</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>资生堂悦微清爽水150ml（新版）</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>375</v>
+      </c>
+      <c r="E140" t="n">
+        <v>276</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>220</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>【全球购正品】资生堂悦薇珀翡紧颜亮肤水(滋润型)150ml</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>资生堂悦微滋润水150ml（新版）</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>359</v>
+      </c>
+      <c r="E141" t="n">
+        <v>359</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>221</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂悦薇智感视黄醇抗皱霜 20ml 新版小针管眼霜</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>资生堂悦薇纯A小针管眼霜20ml</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>511</v>
+      </c>
+      <c r="E142" t="n">
+        <v>256</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>222</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>【资生堂】新版悦薇珀翡紧颜亮肤乳液50ml滋润型保湿滋润补水</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>资生堂悦薇滋润乳100ml（新版）</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>187</v>
+      </c>
+      <c r="E143" t="n">
+        <v>52.11</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>222</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂二代悦薇智感紧颜亮肤乳 100ml 清爽型</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>资生堂悦薇滋润乳100ml（新版）</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>185</v>
+      </c>
+      <c r="E144" t="n">
+        <v>185</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>223</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂二代悦薇智感紧颜亮肤乳 100ml 清爽型</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>资生堂悦薇清爽乳100ml（新版）</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>185</v>
+      </c>
+      <c r="E145" t="n">
+        <v>185</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>224</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>祖玛珑蓝风铃香水100ml</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>祖玛珑 蓝风铃香水100ml</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>629</v>
+      </c>
+      <c r="E146" t="n">
+        <v>454</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>225</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>祖玛珑蓝风铃香水30ml清新持久留香</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>祖玛珑鼠尾草与海盐香水30ml</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>329</v>
+      </c>
+      <c r="E147" t="n">
+        <v>250</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>225</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>祖玛珑鼠尾草与海盐香水30ml</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>祖玛珑鼠尾草与海盐香水30ml</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>320</v>
+      </c>
+      <c r="E148" t="n">
+        <v>225.2</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>226</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>【正品行货】阿玛尼新款蓝标大师粉底液#1 #2 #3持久遮瑕细腻服帖</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>阿玛尼大师蓝标粉底液2#</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>289</v>
+      </c>
+      <c r="E149" t="n">
+        <v>185</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>226</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>正品行货|新版阿玛尼粉底液大师蓝标遮瑕持久不脱妆滋润干皮</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>阿玛尼大师蓝标粉底液2#</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>253</v>
+      </c>
+      <c r="E150" t="n">
+        <v>185</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>226</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>【阿玛尼】蓝标大师粉底液 2 号 30ml 保湿遮瑕持久干皮</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>阿玛尼大师蓝标粉底液2#</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>279</v>
+      </c>
+      <c r="E151" t="n">
+        <v>183</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>227</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>【GIORGIO ARMANI】乔治·阿玛尼 权力权利PRO粉底液30ml #2【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底 30m1#2</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>226</v>
+      </c>
+      <c r="E152" t="n">
+        <v>226</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>228</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>【GIORGIO ARMANI】乔治·阿玛尼 权力权利PRO粉底液30ml #3【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底 30m1 #3</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>225</v>
+      </c>
+      <c r="E153" t="n">
+        <v>225</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>229</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>【GIORGIO ARMANI】阿玛尼大师光采焕颜粉底液蓝标30ml#3轻薄持久自然</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>阿玛尼「大师」锁光粉底液#3</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>289</v>
+      </c>
+      <c r="E154" t="n">
+        <v>188</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>230</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>【累计热销129万+件】GIORGIO ARMANI/阿玛尼红气垫替换芯15g#3号色单双个控油持妆新款</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>阿玛尼气垫替换芯3号</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>188</v>
+      </c>
+      <c r="E155" t="n">
+        <v>84</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>231</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>【48.7万人回购该品牌】LANCOME/兰蔻菁纯裸唇釉275# 菁纯柔雾哑光唇釉 温柔气质显色【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>兰蔻水唇釉275#</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>270</v>
+      </c>
+      <c r="E156" t="n">
+        <v>188</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>232</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>【母亲节礼物】GUCCI/古驰绮梦栀子花浓香清新花香礼盒大牌正品</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>古驰绮梦栀子花香水50ml浓香型</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>600</v>
+      </c>
+      <c r="E157" t="n">
+        <v>188</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>232</v>
+      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>古驰绮梦栀子花香水50ml浓香型</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>529</v>
+      </c>
+      <c r="E158" t="n">
+        <v>188</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>233</v>
+      </c>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>POLA 黑BA洁面</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>678</v>
+      </c>
+      <c r="E159" t="n">
+        <v>188</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>234</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>【正品行货】赫莲娜绿宝瓶眼霜15ml淡化黑眼圈细纹熬夜眼精华护肤</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>HR赫莲娜绿宝瓶眼霜15ml</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>595</v>
+      </c>
+      <c r="E160" t="n">
+        <v>188</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>234</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>【累计热销99.6万+件】HR/赫莲娜 绿宝瓶眼霜15ml眼部修复淡化黑眼圈【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>HR赫莲娜绿宝瓶眼霜15ml</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>681</v>
+      </c>
+      <c r="E161" t="n">
+        <v>188</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>235</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>【旧街场】白咖啡马来西亚进口经典原味榛果咖啡三合一速溶咖啡粉*2袋</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>马来西亚旧街场三合一经典原味白咖啡525g</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>188</v>
+      </c>
+      <c r="E162" t="n">
+        <v>51</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>236</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>【旗舰店】旧街场马来西亚进口榛果味白咖啡三合一速溶40条盒装</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>马来西亚旧街场三合一榛果味白咖啡525g</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>188</v>
+      </c>
+      <c r="E163" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>236</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>【旗舰店】旧街场马来西亚进口榛果味三合一白咖啡速溶40条盒装</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>马来西亚旧街场三合一榛果味白咖啡525g</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>188</v>
+      </c>
+      <c r="E164" t="n">
+        <v>109</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>237</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>【旗舰店】旧街场马来西亚进口榛果味白咖啡三合一速溶40条盒装</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>马来西亚旧街场进口三合一速溶白咖啡低糖醇厚条装525g</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>188</v>
+      </c>
+      <c r="E165" t="n">
+        <v>188</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>238</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>【旗舰店】旧街场马来西亚进口榛果味白咖啡三合一速溶40条盒装</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>马来西亚进口OldTown旧街场白咖啡特浓浓醇三合一速溶白咖啡15条</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>188</v>
+      </c>
+      <c r="E166" t="n">
+        <v>188</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>239</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>【累计热销141.7万+件】进口马来西亚旧街场白咖啡二合一咖啡奶精速溶咖啡18条装450g原装</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>马来西亚进口旧街场白咖啡二合一375g</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>188</v>
+      </c>
+      <c r="E167" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>239</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>【9303人好评】原装进口 马来西亚旧街场二合一无蔗糖白咖啡正品15条装 375g</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>马来西亚进口旧街场白咖啡二合一375g</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>188</v>
+      </c>
+      <c r="E168" t="n">
+        <v>32.46</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>240</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>【旧街场】白咖啡二合一20条盒装500g马来西亚原装进口提神减糖学生</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>马来西亚旧街场进口白咖啡咸焦糖525g</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>188</v>
+      </c>
+      <c r="E169" t="n">
+        <v>188</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>241</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>【旧街场】咖啡马来西亚原装进口速溶白咖啡粉微研磨减少糖袋装正品</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>马来西亚旧街场进口白咖啡微研磨375g</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>188</v>
+      </c>
+      <c r="E170" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>241</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>【累计热销141.7万+件】马来西亚进口旧街场白咖啡3合1微研磨咖啡减少糖15条速溶3袋45条</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>马来西亚旧街场进口白咖啡微研磨375g</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>188</v>
+      </c>
+      <c r="E171" t="n">
+        <v>149</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>242</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>【累计热销141.7万+件】马来西亚进口速溶咖啡粉OLDTOWN旧街场二合一白咖啡无蔗糖3袋装</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>马来西亚OLDTOWN进口白咖啡天然庶糖540g</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>188</v>
+      </c>
+      <c r="E172" t="n">
+        <v>147</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>242</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>【品牌好评92.3万+条】马来西亚进口速溶咖啡粉OLDTOWN旧街场三合一蔗糖白咖啡3袋装45条</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>马来西亚OLDTOWN进口白咖啡天然庶糖540g</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>188</v>
+      </c>
+      <c r="E173" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>242</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>【旧街场】咖啡马来西亚进口二合一无添加蔗糖速溶白咖啡15条袋装正品</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>马来西亚OLDTOWN进口白咖啡天然庶糖540g</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>188</v>
+      </c>
+      <c r="E174" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>242</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>【9303人好评】原装进口 马来西亚旧街场二合一无蔗糖白咖啡正品15条装 375g</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>马来西亚OLDTOWN进口白咖啡天然庶糖540g</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>188</v>
+      </c>
+      <c r="E175" t="n">
+        <v>32.46</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>243</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>【正品行货】植村秀新品元气小红喷定妆喷雾持久控油保湿100ml</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>植村秀持久保湿定妆喷雾100ml</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>255</v>
+      </c>
+      <c r="E176" t="n">
+        <v>155.6</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>244</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>【SK-II】大红瓶面霜80g滋养保湿紧致肌肤清爽款</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>SK2大红瓶面霜80g滋润</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>899</v>
+      </c>
+      <c r="E177" t="n">
+        <v>188</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>245</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>【Embryolisse】 法国大宝妆前乳75ml 隔离霜女补水保湿打底不浮粉【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Embryolisse 大宝妆前乳75ml 法国进口</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="E178" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>246</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>【ESTEE LAUDER】雅诗兰黛新款红石榴洗面奶125ml</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴洁面125ml</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="E179" t="n">
+        <v>85.87</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>247</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>【百补品牌热销276.8万件】两瓶 单品 SHISEIDO资生堂第四代红腰子精华75ml</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO红腰子精华（新版）75ml</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>609</v>
+      </c>
+      <c r="E180" t="n">
+        <v>418</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>247</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>【】SHISEIDO资生堂第四代红腰子精华75ml</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO红腰子精华（新版）75ml</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>310</v>
+      </c>
+      <c r="E181" t="n">
+        <v>211.8</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>248</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>【SHISEIDO】资生堂时光琉璃御藏柔肤水170ml保湿滋润紧致肌肤爽肤水</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>资生堂/ SHISEIDO时光大琉璃水（新版）170ml</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>339</v>
+      </c>
+      <c r="E182" t="n">
+        <v>249.9</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>249</v>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO悦薇大抗糖面霜（清爽）50ml</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>389</v>
+      </c>
+      <c r="E183" t="n">
+        <v>306.89</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>250</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>【SHISEIDO】资生堂时光琉璃晚霜15ml保湿补水紧致面霜【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO琉璃晚霜15ml（新版）</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>225</v>
+      </c>
+      <c r="E184" t="n">
+        <v>225</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>250</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>新版!资生堂时光琉璃丰盈晚霜面霜奢养夜霜15ml保湿紧致淡纹抗皱</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO琉璃晚霜15ml（新版）</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="E185" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>251</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>【资生堂】百优精纯面霜50ml保湿滋润增弹紧致抗衰老乳霜</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO百优面霜50ml</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>239</v>
+      </c>
+      <c r="E186" t="n">
+        <v>166</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>252</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>VERSACE/范思哲 爱罗斯爱神红色烈爱男士EDP浓香水50ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>范思哲 爱罗斯爱神男士香水 50ml EDP</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>358</v>
+      </c>
+      <c r="E187" t="n">
+        <v>358</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>253</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>【100ml】爱罗斯爱神男士香水EDP简装100ml</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>范思哲 爱罗斯爱神男士香水 100ml EDP 简装</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>399</v>
+      </c>
+      <c r="E188" t="n">
+        <v>399</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>254</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>【4.1万人回购该品牌】范思哲(VERSACE) 追梦人男士淡香水100ML简装</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>范思哲 追梦人男士淡香水 100ml EDT</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>155</v>
+      </c>
+      <c r="E189" t="n">
+        <v>132.1</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>255</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>【50ml博柏利新伦敦男士淡香水EDT50ml</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>博柏利 新伦敦男士淡香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>259</v>
+      </c>
+      <c r="E190" t="n">
+        <v>259</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>2025-01-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>255</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>【品牌好评24.1万+条】博柏利(BURBERRY)伦敦男士淡香水EDT 50ML</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>博柏利 新伦敦男士淡香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>150</v>
+      </c>
+      <c r="E191" t="n">
+        <v>150</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>256</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>【50mlCK Man超凡男士淡香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>CK Man男士香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>160</v>
+      </c>
+      <c r="E192" t="n">
+        <v>160</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>256</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>【】Calvin Klein凯文克莱 CK 诱惑迷情男士香水EDT 50ML</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>CK Man男士香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>289</v>
+      </c>
+      <c r="E193" t="n">
+        <v>205</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>256</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>【Calvin Klein】凯文克莱 CK 诱惑迷情男士香水EDT 50ML</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>CK Man男士香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>289</v>
+      </c>
+      <c r="E194" t="n">
+        <v>205</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>257</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>【100mlCK绝色美丽女士香水EDP黄色100ml简装无盖</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>CK 绝色美丽女士香水 100ml EDP 黄色</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>999</v>
+      </c>
+      <c r="E195" t="n">
+        <v>299</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>258</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>【NOVO】希尔顿酒店高档香薰五星级同款卧室内家用持久卫生间香氛香水</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>杜鲁萨迪 雅逸玫瑰女士香水 30ml EDT</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E196" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>259</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>大卫杜夫(Davidoff)神秘水冷水男士香水持久淡香</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>大卫杜夫 冷水男士香水 75ml EDP 加强版</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>139</v>
+      </c>
+      <c r="E197" t="n">
+        <v>139</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>259</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>【Davidoff】大卫杜夫冷水男士淡香水EDT75ml</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>大卫杜夫 冷水男士香水 75ml EDP 加强版</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>129</v>
+      </c>
+      <c r="E198" t="n">
+        <v>129</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>259</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>【】大卫杜夫(Davidoff)冷水男士淡香水</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>大卫杜夫 冷水男士香水 75ml EDP 加强版</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>159</v>
+      </c>
+      <c r="E199" t="n">
+        <v>139</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>260</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>GUCCI/古驰竹韵女士50ml淡香水EDT木质花香调礼物清新留香</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>古驰 竹韵女士香水浓香型50ml</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>281</v>
+      </c>
+      <c r="E200" t="n">
+        <v>223</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>260</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰竹韵女士EDT淡香水50ml木质花香调送礼礼物</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>古驰 竹韵女士香水浓香型50ml</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>329</v>
+      </c>
+      <c r="E201" t="n">
+        <v>228</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>260</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰竹韵女士EDP50ml木质调花香调浓香水礼物</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>古驰 竹韵女士香水浓香型50ml</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>280</v>
+      </c>
+      <c r="E202" t="n">
+        <v>228</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>261</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>【正品行货】Clarins/娇韵诗双萃眼精华眼霜20ml*2焕亮紧致提拉</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃眼霜 20ml</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>1320</v>
+      </c>
+      <c r="E203" t="n">
+        <v>464</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>261</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>【正品行货】Clarins/娇韵诗双萃眼精华眼霜焕亮紧致提拉改善暗沉</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃眼霜 20ml</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>660</v>
+      </c>
+      <c r="E204" t="n">
+        <v>225</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>261</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>【原装正品】Clarins娇韵诗双萃焕活眼部精华眼霜焕亮紧致20ML【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃眼霜 20ml</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>299</v>
+      </c>
+      <c r="E205" t="n">
+        <v>207</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>262</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>CLARINS娇韵诗双萃精华滋润型第九代75ml/瓶</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃新版第9代 75ml</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>729</v>
+      </c>
+      <c r="E206" t="n">
+        <v>520</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>262</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>【Clarins】 娇韵诗双萃赋活精华液75ml 第九代</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃新版第9代 75ml</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>748</v>
+      </c>
+      <c r="E207" t="n">
+        <v>524</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>262</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>【正品行货】娇韵诗第九代油皮双萃精华液轻盈淡纹透亮清爽版50ml</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃新版第9代 75ml</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>1081</v>
+      </c>
+      <c r="E208" t="n">
+        <v>423</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>263</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>【娇韵诗】棉花籽洁面乳125ml清爽清洁洗面奶</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>娇韵诗 棉花籽洁面 125ml 新版</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>883</v>
+      </c>
+      <c r="E209" t="n">
+        <v>88</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>264</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>【娇韵诗】身体护理油100ml紧致提拉淡纹滋养</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>娇韵诗 抚纹油 100ml</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>319</v>
+      </c>
+      <c r="E210" t="n">
+        <v>202</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>264</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>【Clarins】娇韵诗身体护理油抚纹油100ml提拉紧致淡纹滋养</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>娇韵诗 抚纹油 100ml</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>269</v>
+      </c>
+      <c r="E211" t="n">
+        <v>217</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>265</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>【正品行货】Clarins/娇韵诗双萃精华液紧致抗皱淡纹熬夜面部精华</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃新版第9代 30ml</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>1580</v>
+      </c>
+      <c r="E212" t="n">
+        <v>514</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>265</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>【正品行货】Clarins/娇韵诗双萃精华液紧致抗皱淡纹面部精华30ml</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃新版第9代 30ml</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>790</v>
+      </c>
+      <c r="E213" t="n">
+        <v>254</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>265</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>【娇韵诗】双萃精华30ml双萃赋活修护精华露保湿提亮淡纹修护紧致【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃新版第9代 30ml</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>499</v>
+      </c>
+      <c r="E214" t="n">
+        <v>323</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>266</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>【欧舒丹】欧舒丹护手霜普罗旺玫瑰/乳木果/樱花护手霜30ML</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>欧舒丹樱花护手霜三支装</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>65</v>
+      </c>
+      <c r="E215" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>266</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>L'OCCITANE欧舒丹 樱花香氛护手霜 150ml保湿留香【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>欧舒丹樱花护手霜三支装</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>230</v>
+      </c>
+      <c r="E216" t="n">
+        <v>143</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>266</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>【正品行货】欧舒丹护手霜全新樱花香润手霜75ml持久留香保湿</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>欧舒丹樱花护手霜三支装</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>191.8</v>
+      </c>
+      <c r="E217" t="n">
+        <v>112</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>267</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>法国L'OCCITANE欧舒丹嫩肤沐浴露身体乳全系列</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>欧舒丹乳木果身体乳250ml</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>107</v>
+      </c>
+      <c r="E218" t="n">
+        <v>107</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>268</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>【正品行货】欧舒丹瑰香之心香氛身体乳250ml</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>欧舒丹玫瑰身体乳250ml</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>235</v>
+      </c>
+      <c r="E219" t="n">
+        <v>164</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>269</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>LAMER海蓝之谜璀璨泡沫洁面乳125ml</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>海蓝之谜洁面125ml</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>590</v>
+      </c>
+      <c r="E220" t="n">
+        <v>372</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>270</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>【正品行货】肌肤之钥净采洁面膏清爽型/湿润型125ml补水保湿滋润</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>CPB滋润洗面奶125ml</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>269</v>
+      </c>
+      <c r="E221" t="n">
+        <v>152</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>270</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>【正品行货】肌肤之钥净采洁面膏清爽型/湿润型125ml补水保湿滋润</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>CPB滋润洗面奶125ml</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>269</v>
+      </c>
+      <c r="E222" t="n">
+        <v>178</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>271</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>日本本土版CPB肌肤之钥防晒润色隔离妆前乳BB霜30ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>CPB美白短管隔离30ml</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>429</v>
+      </c>
+      <c r="E223" t="n">
+        <v>339.47</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>272</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>进口费列罗巧克力榛子正品高档礼盒情人节礼物送女友生日礼品闺蜜</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>FERRERO ROCHER 费列罗榛果巧克力制品T30</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>179</v>
+      </c>
+      <c r="E224" t="n">
+        <v>129</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>272</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>【费列罗】巧克力T3粒送女友情人节礼物盒装金沙婚庆喜糖果散装伴手礼</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>FERRERO ROCHER 费列罗榛果巧克力制品T30</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E225" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>273</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>【ESTEE LAUDER雅诗兰黛】红石榴面霜 鲜活亮采日霜50ml保湿补水</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>红石榴面霜50ml 旧版</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>470</v>
+      </c>
+      <c r="E226" t="n">
+        <v>119</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>273</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Estee Lauder雅诗兰黛红石榴光采能量保湿霜日霜旧版50ml</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>红石榴面霜50ml 旧版</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>189</v>
+      </c>
+      <c r="E227" t="n">
+        <v>131</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>274</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰爱心唇釉442 443 620限定浮雕黑管5.5ml</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>圣罗兰爱心黑管唇釉620</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>235</v>
+      </c>
+      <c r="E228" t="n">
+        <v>143.4</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>274</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰全新爱心七夕浮雕黑管唇釉610 620 442 443</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>圣罗兰爱心黑管唇釉620</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>153</v>
+      </c>
+      <c r="E229" t="n">
+        <v>153</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>274</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>YSL/圣罗兰爱心浮雕黑管唇釉416/622/440/610/620/234/442/443【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>圣罗兰爱心黑管唇釉620</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
         <v>206</v>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>双瓶 单品 雅诗兰黛多效智妍面霜滋润版75ml</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>雅诗兰黛智妍晚霜75ml</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>1169.0</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>774.0</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>2025-03-01</t>
+      <c r="E230" t="n">
+        <v>126</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>275</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL/圣罗兰新版粉皮革气垫替换芯B10 遮瑕替换装12g</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>圣罗兰黑色皮革气垫B10</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>300</v>
+      </c>
+      <c r="E231" t="n">
+        <v>183</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>2025-02-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>275</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>YSL/圣罗兰新版黑皮革气垫替换芯#B10 持妆自然服帖SPF23【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>圣罗兰黑色皮革气垫B10</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>400</v>
+      </c>
+      <c r="E232" t="n">
+        <v>137.9</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>275</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰皮革气垫羽毛气垫B10白皮B20自然肤色遮瑕</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>圣罗兰黑色皮革气垫B10</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>299</v>
+      </c>
+      <c r="E233" t="n">
+        <v>230.6</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>277</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>【正品行货】兰蔻菁纯臻颜精华粉底液100#/110#35ml 新版礼物送人</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>兰蔻菁纯粉底液100</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>640</v>
+      </c>
+      <c r="E234" t="n">
+        <v>357</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>277</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>【正品行货】兰蔻菁纯臻颜精华粉底液100 5ml*3小样细腻服帖滋润</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>兰蔻菁纯粉底液100</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>95</v>
+      </c>
+      <c r="E235" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>278</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II骨胶原晶致活肤修护乳液补水保湿抗皱紧致舒缓</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>SK2骨胶原乳液100g</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>600</v>
+      </c>
+      <c r="E236" t="n">
+        <v>424</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>279</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>【14.8万人回购该品牌】SK-II/sk2护肤精华露嫩肤清莹露保湿修护抗皱紧致嫩滑230ml化妆水</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>SK2清莹露230ml</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>408.99</v>
+      </c>
+      <c r="E237" t="n">
+        <v>408.99</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>280</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II大红瓶滋润保湿修护眼霜淡化眼纹细黑眼圈眼周</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>SK2立体修护眼霜15g两瓶装</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>580</v>
+      </c>
+      <c r="E238" t="n">
+        <v>381</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>281</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>【14.8万人回购该品牌】SKII/SK2小灯泡精华50ml新品光子瓶美白肌因光蕴环采钻白精华液【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>SK2小灯泡50ml两瓶装（25年款）</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E239" t="n">
+        <v>745</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>282</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>【碧欧泉】男士水动力保湿乳液100ml清爽提亮修护礼物</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>碧欧泉男士水动力乳液100ml</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>331</v>
+      </c>
+      <c r="E240" t="n">
+        <v>205.28</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>283</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>【6.8万人回购该品牌】植村秀(shu uemura)绿茶新肌卸妆油450ml保湿控油</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>植村秀绿茶卸妆油450ml两瓶装</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>488</v>
+      </c>
+      <c r="E241" t="n">
+        <v>309</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>284</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>【正品行货】圣罗兰女神逆龄自然透气轻薄粉底液B20控油遮瑕</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>圣罗兰女神逆龄粉底液B20</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>368</v>
+      </c>
+      <c r="E242" t="n">
+        <v>279</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>284</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>【6.38万人评价品牌正品】YSL/圣罗兰 逆龄女神粉底液30ml 恒久遮瑕#B20【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>圣罗兰女神逆龄粉底液B20</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>529</v>
+      </c>
+      <c r="E243" t="n">
+        <v>252.1</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>284</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>【YSL】圣罗兰逆龄女神粉底液恒久B20#遮瑕轻薄控油30ml</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>圣罗兰女神逆龄粉底液B20</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>399</v>
+      </c>
+      <c r="E244" t="n">
+        <v>285.7</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>285</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>【正品行货】兰蔻全新菁纯眼霜 20ml*2瓶  眼霜正品淡斑淡纹眼霜</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>兰蔻菁纯眼霜20ml两瓶装</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E245" t="n">
+        <v>760</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>285</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>【品牌好评297万+条】Lancome/兰蔻 菁纯眼霜20ml 淡纹紧致抗皱抗老化滋润保湿焕亮眼周【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>兰蔻菁纯眼霜20ml两瓶装</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>560</v>
+      </c>
+      <c r="E246" t="n">
+        <v>408</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>285</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>【兰蔻】菁纯臻颜眼霜20ml 淡纹滋润紧致眼周保湿抗皱抗老化【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>兰蔻菁纯眼霜20ml两瓶装</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>1165</v>
+      </c>
+      <c r="E247" t="n">
+        <v>410</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>286</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>【兰蔻】第三代小黑瓶肌底液100ml保湿修护维稳面部精华</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>兰蔻第三代肌底液100ml</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>616</v>
+      </c>
+      <c r="E248" t="n">
+        <v>480</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>286</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>兰蔻小黑瓶肌底液第三代超修精华100ml【5月6日发完】</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>兰蔻第三代肌底液100ml</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>659</v>
+      </c>
+      <c r="E249" t="n">
+        <v>486</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>287</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>【Urban Decay】衰败城市UD四色牛郎眼影 心动哑光细闪盘高光闪亮片【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>衰败城市牛郎眼影</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>453</v>
+      </c>
+      <c r="E250" t="n">
+        <v>245</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>288</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>【Guerlain】娇兰复原蜜50ML帝皇蜂精华液第三代保湿紧致修护肌肤白盒</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>娇兰帝皇蜂姿第三代黄金复原蜜50ML</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>680</v>
+      </c>
+      <c r="E251" t="n">
+        <v>468</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>289</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>【Guerlain】娇兰复原蜜50ML帝皇蜂精华液第三代保湿紧致修护肌肤白盒</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>娇兰帝皇蜂姿第三代黄金复原蜜50ML</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>680</v>
+      </c>
+      <c r="E252" t="n">
+        <v>468</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>290</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>【Hermes】爱马仕大地男士淡香水50ml经典淡香木质调正装男士香水</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>爱马仕大地淡香水50ml</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>429</v>
+      </c>
+      <c r="E253" t="n">
+        <v>429</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>290</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>【Hermes】爱马仕大地男士淡香水50ml正装有盒木质调</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>爱马仕大地淡香水50ml</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>439</v>
+      </c>
+      <c r="E254" t="n">
+        <v>439</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>290</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>【Hermes】爱马仕大地男士淡香水50ml经典淡香木质调正装男士香水</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>爱马仕大地淡香水50ml</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>450</v>
+      </c>
+      <c r="E255" t="n">
+        <v>450</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>290</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>【Hermes】爱马仕大地男士EDT淡香水50ml 经典木质调</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>爱马仕大地淡香水50ml</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>399</v>
+      </c>
+      <c r="E256" t="n">
+        <v>399</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>291</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>【累计热销13.8万+件】韩国SUM37°苏秘惊喜气垫BB霜粉底液提亮防晒清透1号色</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>苏秘气垫1号</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>127.9</v>
+      </c>
+      <c r="E257" t="n">
+        <v>87</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>292</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】红石榴水200ml滋润型 鲜活亮采精华水 补水保湿抗氧提亮</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>雅诗兰黛 鲜活亮采红石榴倍润水 200ml</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>211</v>
+      </c>
+      <c r="E258" t="n">
+        <v>129.2</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>293</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>【YSL】圣罗兰夜皇后面霜50ml轻盈版舒缓淡纹节日礼物</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰夜皇后50ml</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>589</v>
+      </c>
+      <c r="E259" t="n">
+        <v>506</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>294</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>YSL/圣罗兰25新品粉盖粉底液恒久#LC1 粉调最白 滋润持妆25ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC1</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>399</v>
+      </c>
+      <c r="E260" t="n">
+        <v>399</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>295</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>YSL/圣罗兰 粉盖恒久粉底液25ml #LC2 粉1白【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC2</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>278</v>
+      </c>
+      <c r="E261" t="n">
+        <v>278</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>295</v>
+      </c>
+      <c r="B262" t="inlineStr"/>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC2</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>399</v>
+      </c>
+      <c r="E262" t="n">
+        <v>399</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>296</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>【累计热销393.9万+件】两支 单品 兰蔻新版小白管轻透水漾防晒乳50ml</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>兰蔻小白管轻适水漾防晒乳 50ml*2</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>660</v>
+      </c>
+      <c r="E263" t="n">
+        <v>380</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>296</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>【累计热销393.9万+件】LANCOME兰蔻新版小白管轻透水漾防晒乳50ml</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>兰蔻小白管轻适水漾防晒乳 50ml*2</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>330</v>
+      </c>
+      <c r="E264" t="n">
+        <v>191</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>297</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>【YSL】圣罗兰粉皮革气垫 明彩粉光轻垫粉底液气 垫 保湿持久遮瑕</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>圣罗兰 明彩粉光轻垫粉底液 粉气垫 #B20 CN</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>470</v>
+      </c>
+      <c r="E265" t="n">
+        <v>352</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>297</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>【YSL】圣罗兰明彩轻垫粉底液B20 5g 皮气垫 遮瑕提亮 轻薄持妆</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>圣罗兰 明彩粉光轻垫粉底液 粉气垫 #B20 CN</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="E266" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>298</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>【保税原装】资生堂蓝胖子防晒霜高倍防晒军训户外防紫外线正品</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>资生堂蓝胖子防晒50ml对装</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="E267" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>298</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>【保税原装】资生堂蓝胖子防晒霜清爽防紫外线防水防汗高倍防晒乳</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>资生堂蓝胖子防晒50ml对装</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>329</v>
+      </c>
+      <c r="E268" t="n">
+        <v>166</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>299</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>【2.06万人评价品牌正品】Armani 阿玛尼权力PRO粉底液1.5号/2号色红标遮瑕控油滋润</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底1.5 30ml</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>298</v>
+      </c>
+      <c r="E269" t="n">
+        <v>298</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>300</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>【正品行货】兰蔻肌底焕活修护小黑瓶眼霜20ML</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>兰蔻小黑瓶眼霜20ml</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>225</v>
+      </c>
+      <c r="E270" t="n">
+        <v>225</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>299</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Armani 阿玛尼权力PRO粉底液1.5号/2号色红标遮瑕控油滋润</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底1.5 30ml</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>298</v>
+      </c>
+      <c r="E271" t="n">
+        <v>298</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>299</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>【阿玛尼】权力红标粉底液30ml#1.5pro 遮瑕控油持久</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底1.5 30ml</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>312</v>
+      </c>
+      <c r="E272" t="n">
+        <v>245</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>301</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>【正品行货】赫莲娜绿宝瓶眼霜15ml淡化黑眼圈细纹熬夜眼精华护肤</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>HR赫莲娜绿眼霜对装</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>595</v>
+      </c>
+      <c r="E273" t="n">
+        <v>375</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>301</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>HR/赫莲娜 绿宝瓶眼霜15ml眼部修复淡化黑眼圈【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>HR赫莲娜绿眼霜对装</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>681</v>
+      </c>
+      <c r="E274" t="n">
+        <v>332.15</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>302</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰女士花悦绽放淡香水50ml</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>古驰花悦绽放女士淡香型香水50ml</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>588</v>
+      </c>
+      <c r="E275" t="n">
+        <v>229</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>302</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰花悦绽放女士淡香水EDT50ml浪漫白花香调</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>古驰花悦绽放女士淡香型香水50ml</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>355</v>
+      </c>
+      <c r="E276" t="n">
+        <v>245</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>302</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>【古驰】花悦绽放女士香水EDP浓香50ml持久留香</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>古驰花悦绽放女士淡香型香水50ml</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>409</v>
+      </c>
+      <c r="E277" t="n">
+        <v>272</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>303</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>【MAC】魅可定制无暇粉底液2.0二代NC11持妆油皮控油持久</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液N11 2.0</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>229</v>
+      </c>
+      <c r="E278" t="n">
+        <v>139</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>304</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>【正品行货】MAC/魅可新版定制无暇粉底液2.0 N12持妆控油遮瑕N18</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液N18 2.0</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>350</v>
+      </c>
+      <c r="E279" t="n">
+        <v>156</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>305</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>【正品行货】MAC/魅可新版定制无暇粉底液2.0 N12持妆控油遮瑕N18</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液NC11 2.0</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>350</v>
+      </c>
+      <c r="E280" t="n">
+        <v>156</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>306</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>【Givenchy】纪梵希 四宫格柔雾散粉0号1号2号3号 12g</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>纪梵希四宫格散粉1号色（新版）</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>298</v>
+      </c>
+      <c r="E281" t="n">
+        <v>194.9</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>306</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>GIVENCHY纪梵希 四宫格散粉#1百搭滤镜 四色定妆蜜粉细腻轻盈【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>纪梵希四宫格散粉1号色（新版）</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>298</v>
+      </c>
+      <c r="E282" t="n">
+        <v>193</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>306</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>【正品行货】GIVENCHY纪梵希四宫格散粉 四色定妆粉 遮瑕控油</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>纪梵希四宫格散粉1号色（新版）</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>296</v>
+      </c>
+      <c r="E283" t="n">
+        <v>182.9</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>307</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>DECORTE黛珂 牛油果植萃乳液300ML 保湿紧致弹润控油</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>黛珂牛油果乳液300ml*2</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>199</v>
+      </c>
+      <c r="E284" t="n">
+        <v>140</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>308</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>【正品行货】肌肤之钥净采洁面膏清爽型/湿润型125ml洗面奶滋润</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>CPB肌肤之钥清爽洁面125ML</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>269</v>
+      </c>
+      <c r="E285" t="n">
+        <v>150</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>308</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>【正品行货】肌肤之钥净采洁面膏清爽型/湿润型125ml补水保湿滋润</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>CPB肌肤之钥清爽洁面125ML</t>
+        </is>
+      </c>
+      <c r="D286" t="n">
+        <v>269</v>
+      </c>
+      <c r="E286" t="n">
+        <v>152</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>308</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>【正品行货】CPB肌肤之钥洗面奶湿润型125ml 净采洁面膏</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>CPB肌肤之钥清爽洁面125ML</t>
+        </is>
+      </c>
+      <c r="D287" t="n">
+        <v>260</v>
+      </c>
+      <c r="E287" t="n">
+        <v>152</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>308</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>CPB肌肤之钥净采洗面奶(滋润型)125ml/支【5月2日发完】</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>CPB肌肤之钥清爽洁面125ML</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>289</v>
+      </c>
+      <c r="E288" t="n">
+        <v>151.9</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>309</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰绮梦栀子花女士浓香水EDP100ml520节日礼物</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦馥栀100ML</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>700</v>
+      </c>
+      <c r="E289" t="n">
+        <v>448</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>309</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Gucci古驰 绮梦馥栀女士EDP浓香水100ml 25年新品</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦馥栀100ML</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>1119</v>
+      </c>
+      <c r="E290" t="n">
+        <v>540</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>309</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰绮梦馥栀香水100ml简装正品持久留香节日礼物自用</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦馥栀100ML</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>699</v>
+      </c>
+      <c r="E291" t="n">
+        <v>490</v>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>310</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰花悦绽放浓香水100ml简装黑盖女士香氛正品持久留香</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>GUCCI花悦绽放100ML浓香</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>541</v>
+      </c>
+      <c r="E292" t="n">
+        <v>340.91</v>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>310</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰花悦绽放女士浓香水花香调持久留香送礼100ml</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>GUCCI花悦绽放100ML浓香</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>447</v>
+      </c>
+      <c r="E293" t="n">
+        <v>385</v>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>310</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Gucci古驰花悦绽放女士淡香水100ml 持久留香送女友</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>GUCCI花悦绽放100ML浓香</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>525</v>
+      </c>
+      <c r="E294" t="n">
+        <v>319</v>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>311</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>【全球购正品】古驰绮梦木兰香型女士香水100ml</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦木兰100ML浓香型</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>599</v>
+      </c>
+      <c r="E295" t="n">
+        <v>499</v>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>311</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>GUCCI/古驰绮梦香草兰女士浓香水水生美食调简装礼物</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦木兰100ML浓香型</t>
+        </is>
+      </c>
+      <c r="D296" t="n">
+        <v>499</v>
+      </c>
+      <c r="E296" t="n">
+        <v>438</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>311</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>【100ml】古驰 绮梦兰花浓香水EDP简装无盖</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦木兰100ML浓香型</t>
+        </is>
+      </c>
+      <c r="D297" t="n">
+        <v>999</v>
+      </c>
+      <c r="E297" t="n">
+        <v>888</v>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>312</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Gucci古驰绮梦馥栀女士EDP浓香水100ml 25年新品</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦栀子花100ML浓香型</t>
+        </is>
+      </c>
+      <c r="D298" t="n">
+        <v>799</v>
+      </c>
+      <c r="E298" t="n">
+        <v>569.1</v>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>312</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰绮梦栀子花女士浓香水EDP100ml520节日礼物</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦栀子花100ML浓香型</t>
+        </is>
+      </c>
+      <c r="D299" t="n">
+        <v>700</v>
+      </c>
+      <c r="E299" t="n">
+        <v>448</v>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>312</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI古驰绮梦花园系列馥栀女士香水花香调EDP100ml</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦栀子花100ML浓香型</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>1730</v>
+      </c>
+      <c r="E300" t="n">
+        <v>609</v>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>313</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>【全球购正品】古驰绮梦木兰香型女士香水100ml</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦香草兰香100ml</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>599</v>
+      </c>
+      <c r="E301" t="n">
+        <v>499</v>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>313</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>GUCCI/古驰绮梦香草兰女士浓香水水生美食调简装礼物</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦香草兰香100ml</t>
+        </is>
+      </c>
+      <c r="D302" t="n">
+        <v>499</v>
+      </c>
+      <c r="E302" t="n">
+        <v>438</v>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>314</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰绮梦木兰女士浓香香水50ML持久留香花香调</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦香草兰香50ml</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>390</v>
+      </c>
+      <c r="E303" t="n">
+        <v>328</v>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>315</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>【卡诗】黑钻钥源洗发水鱼子酱滋养受损干枯毛躁润泽保湿黑金洗发露</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Kerastase卡诗黑钻鱼子酱洗发水250ml</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>208</v>
+      </c>
+      <c r="E304" t="n">
+        <v>180</v>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>299</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Armani 阿玛尼权力PRO粉底液1.5号/2号色红标遮瑕控油滋润</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底1.5 30ml</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>298.0</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>298.0</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>299</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>【阿玛尼】权力红标粉底液30ml#1.5pro 遮瑕控油持久</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底1.5 30ml</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>312.0</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>245.0</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>301</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>【正品行货】赫莲娜绿宝瓶眼霜15ml淡化黑眼圈细纹熬夜眼精华护肤</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>HR赫莲娜绿眼霜对装</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>595.0</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>375.0</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>301</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>HR/赫莲娜 绿宝瓶眼霜15ml眼部修复淡化黑眼圈【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>HR赫莲娜绿眼霜对装</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>681.0</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>332.15</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>302</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰女士花悦绽放淡香水50ml</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>古驰花悦绽放女士淡香型香水50ml</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>588.0</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>229.0</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>302</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰花悦绽放女士淡香水EDT50ml浪漫白花香调</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>古驰花悦绽放女士淡香型香水50ml</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>355.0</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>245.0</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>302</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>【古驰】花悦绽放女士香水EDP浓香50ml持久留香</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>古驰花悦绽放女士淡香型香水50ml</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>409.0</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>272.0</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>303</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>【MAC】魅可定制无暇粉底液2.0二代NC11持妆油皮控油持久</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液N11 2.0</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>229.0</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>304</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>【正品行货】MAC/魅可新版定制无暇粉底液2.0 N12持妆控油遮瑕N18</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液N18 2.0</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>350.0</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>305</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>【正品行货】MAC/魅可新版定制无暇粉底液2.0 N12持妆控油遮瑕N18</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液NC11 2.0</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>350.0</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>306</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>【Givenchy】纪梵希 四宫格柔雾散粉0号1号2号3号 12g</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>纪梵希四宫格散粉1号色（新版）</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>298.0</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>194.9</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>306</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>GIVENCHY纪梵希 四宫格散粉#1百搭滤镜 四色定妆蜜粉细腻轻盈【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>纪梵希四宫格散粉1号色（新版）</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>298.0</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>193.0</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>306</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>【正品行货】GIVENCHY纪梵希四宫格散粉 四色定妆粉 遮瑕控油</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>纪梵希四宫格散粉1号色（新版）</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>296.0</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>182.9</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>307</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>DECORTE黛珂 牛油果植萃乳液300ML 保湿紧致弹润控油</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>黛珂牛油果乳液300ml*2</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>199.0</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>308</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>【正品行货】肌肤之钥净采洁面膏清爽型/湿润型125ml洗面奶滋润</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>CPB肌肤之钥清爽洁面125ML</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>269.0</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>308</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>【正品行货】肌肤之钥净采洁面膏清爽型/湿润型125ml补水保湿滋润</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>CPB肌肤之钥清爽洁面125ML</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>269.0</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>308</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>【正品行货】CPB肌肤之钥洗面奶湿润型125ml 净采洁面膏</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>CPB肌肤之钥清爽洁面125ML</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>260.0</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>308</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>CPB肌肤之钥净采洗面奶(滋润型)125ml/支【5月2日发完】</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>CPB肌肤之钥清爽洁面125ML</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>289.0</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>151.9</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>309</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰绮梦栀子花女士浓香水EDP100ml520节日礼物</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦馥栀100ML</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>700.0</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>448.0</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>309</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Gucci古驰 绮梦馥栀女士EDP浓香水100ml 25年新品</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦馥栀100ML</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>1119.0</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>540.0</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>309</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰绮梦馥栀香水100ml简装正品持久留香节日礼物自用</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦馥栀100ML</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>699.0</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>490.0</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>310</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰花悦绽放浓香水100ml简装黑盖女士香氛正品持久留香</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>GUCCI花悦绽放100ML浓香</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>541.0</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>340.91</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>310</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰花悦绽放女士浓香水花香调持久留香送礼100ml</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>GUCCI花悦绽放100ML浓香</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>447.0</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>385.0</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>310</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Gucci古驰花悦绽放女士淡香水100ml 持久留香送女友</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>GUCCI花悦绽放100ML浓香</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>525.0</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>319.0</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>311</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>【全球购正品】古驰绮梦木兰香型女士香水100ml</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦木兰100ML浓香型</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>599.0</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>499.0</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>311</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>GUCCI/古驰绮梦香草兰女士浓香水水生美食调简装礼物</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦木兰100ML浓香型</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>499.0</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>438.0</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>311</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>【100ml】古驰 绮梦兰花浓香水EDP简装无盖</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦木兰100ML浓香型</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>999.0</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>888.0</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>312</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Gucci古驰绮梦馥栀女士EDP浓香水100ml 25年新品</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦栀子花100ML浓香型</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>799.0</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>569.1</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>312</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰绮梦栀子花女士浓香水EDP100ml520节日礼物</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦栀子花100ML浓香型</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>700.0</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>448.0</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>312</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI古驰绮梦花园系列馥栀女士香水花香调EDP100ml</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦栀子花100ML浓香型</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>1730.0</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>609.0</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>313</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>【全球购正品】古驰绮梦木兰香型女士香水100ml</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦香草兰香100ml</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>599.0</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>499.0</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>313</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>GUCCI/古驰绮梦香草兰女士浓香水水生美食调简装礼物</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦香草兰香100ml</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>499.0</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>438.0</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>314</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰绮梦木兰女士浓香香水50ML持久留香花香调</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦香草兰香50ml</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>390.0</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>328.0</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>315</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>【卡诗】黑钻钥源洗发水鱼子酱滋养受损干枯毛躁润泽保湿黑金洗发露</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Kerastase卡诗黑钻鱼子酱洗发水250ml</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>208.0</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>316</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>【HR】赫莲娜绿宝瓶悦活蓄能新肌水400ml</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水400ml</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>819.0</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>642.0</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>316</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>HR/赫莲娜绿宝瓶新肌水200ml 精华爽肤水</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水400ml</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>600.0</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>456.0</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>316</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>两瓶 单品 HR赫莲娜绿宝瓶悦活蓄能新肌水400ml</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水400ml</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>1600.0</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>1254.0</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>316</v>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>【正品行货】赫莲娜绿宝瓶眼霜15ml淡化黑眼圈细纹熬夜眼精华护肤</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水400ml</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>595.0</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>375.0</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
         </is>
       </c>
     </row>

--- a/商品采集汇总.xlsx
+++ b/商品采集汇总.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G342"/>
+  <dimension ref="A1:G506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8450,23 +8450,23 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Armani 阿玛尼权力PRO粉底液1.5号/2号色红标遮瑕控油滋润</t>
+          <t>【正品行货】赫莲娜绿宝瓶眼霜15ml淡化黑眼圈细纹熬夜眼精华护肤</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>阿玛尼权力PR0粉底1.5 30ml</t>
+          <t>HR赫莲娜绿眼霜对装</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>298</v>
+        <v>595</v>
       </c>
       <c r="E271" t="n">
-        <v>298</v>
+        <v>375</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -8475,102 +8475,94 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>【阿玛尼】权力红标粉底液30ml#1.5pro 遮瑕控油持久</t>
+          <t>HR/赫莲娜 绿宝瓶眼霜15ml眼部修复淡化黑眼圈【5天内发货】</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>阿玛尼权力PR0粉底1.5 30ml</t>
+          <t>HR赫莲娜绿眼霜对装</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>312</v>
+        <v>681</v>
       </c>
       <c r="E272" t="n">
-        <v>245</v>
+        <v>332.15</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-19</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>【正品行货】赫莲娜绿宝瓶眼霜15ml淡化黑眼圈细纹熬夜眼精华护肤</t>
+          <t>【GUCCI】古驰女士花悦绽放淡香水50ml</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>HR赫莲娜绿眼霜对装</t>
+          <t>古驰花悦绽放女士淡香型香水50ml</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="E273" t="n">
-        <v>375</v>
+        <v>229</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>HR/赫莲娜 绿宝瓶眼霜15ml眼部修复淡化黑眼圈【5天内发货】</t>
+          <t>【GUCCI】古驰花悦绽放女士淡香水EDT50ml浪漫白花香调</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>HR赫莲娜绿眼霜对装</t>
+          <t>古驰花悦绽放女士淡香型香水50ml</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>681</v>
+        <v>355</v>
       </c>
       <c r="E274" t="n">
-        <v>332.15</v>
+        <v>245</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
+      <c r="G274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -8578,7 +8570,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>【GUCCI】古驰女士花悦绽放淡香水50ml</t>
+          <t>【古驰】花悦绽放女士香水EDP浓香50ml持久留香</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -8587,95 +8579,95 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>588</v>
+        <v>409</v>
       </c>
       <c r="E275" t="n">
-        <v>229</v>
+        <v>272</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr"/>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>【GUCCI】古驰花悦绽放女士淡香水EDT50ml浪漫白花香调</t>
+          <t>【MAC】魅可定制无暇粉底液2.0二代NC11持妆油皮控油持久</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>古驰花悦绽放女士淡香型香水50ml</t>
+          <t>MAC无瑕粉底液N11 2.0</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>355</v>
+        <v>229</v>
       </c>
       <c r="E276" t="n">
-        <v>245</v>
+        <v>139</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>【古驰】花悦绽放女士香水EDP浓香50ml持久留香</t>
+          <t>【正品行货】MAC/魅可新版定制无暇粉底液2.0 N12持妆控油遮瑕N18</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>古驰花悦绽放女士淡香型香水50ml</t>
+          <t>MAC无瑕粉底液N18 2.0</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>409</v>
+        <v>350</v>
       </c>
       <c r="E277" t="n">
-        <v>272</v>
+        <v>156</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>2025-07-05</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>【MAC】魅可定制无暇粉底液2.0二代NC11持妆油皮控油持久</t>
+          <t>【正品行货】MAC/魅可新版定制无暇粉底液2.0 N12持妆控油遮瑕N18</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>MAC无瑕粉底液N11 2.0</t>
+          <t>MAC无瑕粉底液NC11 2.0</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>229</v>
+        <v>350</v>
       </c>
       <c r="E278" t="n">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -8686,57 +8678,65 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>【正品行货】MAC/魅可新版定制无暇粉底液2.0 N12持妆控油遮瑕N18</t>
+          <t>【Givenchy】纪梵希 四宫格柔雾散粉0号1号2号3号 12g</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>MAC无瑕粉底液N18 2.0</t>
+          <t>纪梵希四宫格散粉1号色（新版）</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>350</v>
+        <v>298</v>
       </c>
       <c r="E279" t="n">
-        <v>156</v>
+        <v>194.9</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G279" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>【正品行货】MAC/魅可新版定制无暇粉底液2.0 N12持妆控油遮瑕N18</t>
+          <t>GIVENCHY纪梵希 四宫格散粉#1百搭滤镜 四色定妆蜜粉细腻轻盈【5天内发货】</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>MAC无瑕粉底液NC11 2.0</t>
+          <t>纪梵希四宫格散粉1号色（新版）</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>350</v>
+        <v>298</v>
       </c>
       <c r="E280" t="n">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr"/>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>【Givenchy】纪梵希 四宫格柔雾散粉0号1号2号3号 12g</t>
+          <t>【正品行货】GIVENCHY纪梵希四宫格散粉 四色定妆粉 遮瑕控油</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -8753,10 +8753,10 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E281" t="n">
-        <v>194.9</v>
+        <v>182.9</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -8765,102 +8765,94 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-08-01</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>GIVENCHY纪梵希 四宫格散粉#1百搭滤镜 四色定妆蜜粉细腻轻盈【5天内发货】</t>
+          <t>DECORTE黛珂 牛油果植萃乳液300ML 保湿紧致弹润控油</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>纪梵希四宫格散粉1号色（新版）</t>
+          <t>黛珂牛油果乳液300ml*2</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>298</v>
+        <v>199</v>
       </c>
       <c r="E282" t="n">
-        <v>193</v>
+        <v>140</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>【正品行货】GIVENCHY纪梵希四宫格散粉 四色定妆粉 遮瑕控油</t>
+          <t>【正品行货】肌肤之钥净采洁面膏清爽型/湿润型125ml洗面奶滋润</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>纪梵希四宫格散粉1号色（新版）</t>
+          <t>CPB肌肤之钥清爽洁面125ML</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>296</v>
+        <v>269</v>
       </c>
       <c r="E283" t="n">
-        <v>182.9</v>
+        <v>150</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
+      <c r="G283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>DECORTE黛珂 牛油果植萃乳液300ML 保湿紧致弹润控油</t>
+          <t>【正品行货】肌肤之钥净采洁面膏清爽型/湿润型125ml补水保湿滋润</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>黛珂牛油果乳液300ml*2</t>
+          <t>CPB肌肤之钥清爽洁面125ML</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>199</v>
+        <v>269</v>
       </c>
       <c r="E284" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -8868,7 +8860,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>【正品行货】肌肤之钥净采洁面膏清爽型/湿润型125ml洗面奶滋润</t>
+          <t>【正品行货】CPB肌肤之钥洗面奶湿润型125ml 净采洁面膏</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -8877,10 +8869,10 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="E285" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -8895,7 +8887,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>【正品行货】肌肤之钥净采洁面膏清爽型/湿润型125ml补水保湿滋润</t>
+          <t>CPB肌肤之钥净采洗面奶(滋润型)125ml/支【5月2日发完】</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -8904,64 +8896,72 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="E286" t="n">
-        <v>152</v>
+        <v>151.9</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G286" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>【正品行货】CPB肌肤之钥洗面奶湿润型125ml 净采洁面膏</t>
+          <t>【GUCCI】古驰绮梦栀子花女士浓香水EDP100ml520节日礼物</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>CPB肌肤之钥清爽洁面125ML</t>
+          <t>GUCCI绮梦馥栀100ML</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>260</v>
+        <v>700</v>
       </c>
       <c r="E287" t="n">
-        <v>152</v>
+        <v>448</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G287" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>CPB肌肤之钥净采洗面奶(滋润型)125ml/支【5月2日发完】</t>
+          <t>Gucci古驰 绮梦馥栀女士EDP浓香水100ml 25年新品</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>CPB肌肤之钥清爽洁面125ML</t>
+          <t>GUCCI绮梦馥栀100ML</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>289</v>
+        <v>1119</v>
       </c>
       <c r="E288" t="n">
-        <v>151.9</v>
+        <v>540</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-17</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>【GUCCI】古驰绮梦栀子花女士浓香水EDP100ml520节日礼物</t>
+          <t>【GUCCI】古驰绮梦馥栀香水100ml简装正品持久留香节日礼物自用</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -8989,83 +8989,79 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E289" t="n">
-        <v>448</v>
+        <v>490</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2023-04-01</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Gucci古驰 绮梦馥栀女士EDP浓香水100ml 25年新品</t>
+          <t>【GUCCI】古驰花悦绽放浓香水100ml简装黑盖女士香氛正品持久留香</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>GUCCI绮梦馥栀100ML</t>
+          <t>GUCCI花悦绽放100ML浓香</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>1119</v>
+        <v>541</v>
       </c>
       <c r="E290" t="n">
-        <v>540</v>
+        <v>340.91</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2023-09-01</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>【GUCCI】古驰绮梦馥栀香水100ml简装正品持久留香节日礼物自用</t>
+          <t>【GUCCI】古驰花悦绽放女士浓香水花香调持久留香送礼100ml</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>GUCCI绮梦馥栀100ML</t>
+          <t>GUCCI花悦绽放100ML浓香</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>699</v>
+        <v>447</v>
       </c>
       <c r="E291" t="n">
-        <v>490</v>
+        <v>385</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>2023-04-01</t>
-        </is>
-      </c>
+      <c r="G291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -9073,7 +9069,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>【GUCCI】古驰花悦绽放浓香水100ml简装黑盖女士香氛正品持久留香</t>
+          <t>Gucci古驰花悦绽放女士淡香水100ml 持久留香送女友</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -9082,75 +9078,75 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>541</v>
+        <v>525</v>
       </c>
       <c r="E292" t="n">
-        <v>340.91</v>
+        <v>319</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>2023-09-01</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>【GUCCI】古驰花悦绽放女士浓香水花香调持久留香送礼100ml</t>
+          <t>【全球购正品】古驰绮梦木兰香型女士香水100ml</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>GUCCI花悦绽放100ML浓香</t>
+          <t>GUCCI绮梦木兰100ML浓香型</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>447</v>
+        <v>599</v>
       </c>
       <c r="E293" t="n">
-        <v>385</v>
+        <v>499</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Gucci古驰花悦绽放女士淡香水100ml 持久留香送女友</t>
+          <t>GUCCI/古驰绮梦香草兰女士浓香水水生美食调简装礼物</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>GUCCI花悦绽放100ML浓香</t>
+          <t>GUCCI绮梦木兰100ML浓香型</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>525</v>
+        <v>499</v>
       </c>
       <c r="E294" t="n">
-        <v>319</v>
+        <v>438</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G294" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -9158,7 +9154,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>【全球购正品】古驰绮梦木兰香型女士香水100ml</t>
+          <t>【100ml】古驰 绮梦兰花浓香水EDP简装无盖</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -9167,68 +9163,68 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>599</v>
+        <v>999</v>
       </c>
       <c r="E295" t="n">
-        <v>499</v>
+        <v>888</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G295" t="inlineStr"/>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>GUCCI/古驰绮梦香草兰女士浓香水水生美食调简装礼物</t>
+          <t>Gucci古驰绮梦馥栀女士EDP浓香水100ml 25年新品</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>GUCCI绮梦木兰100ML浓香型</t>
+          <t>GUCCI绮梦栀子花100ML浓香型</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>499</v>
+        <v>799</v>
       </c>
       <c r="E296" t="n">
-        <v>438</v>
+        <v>569.1</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>2024-03-01</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>【100ml】古驰 绮梦兰花浓香水EDP简装无盖</t>
+          <t>【GUCCI】古驰绮梦栀子花女士浓香水EDP100ml520节日礼物</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>GUCCI绮梦木兰100ML浓香型</t>
+          <t>GUCCI绮梦栀子花100ML浓香型</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>999</v>
+        <v>700</v>
       </c>
       <c r="E297" t="n">
-        <v>888</v>
+        <v>448</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -9237,7 +9233,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-01-01</t>
         </is>
       </c>
     </row>
@@ -9247,7 +9243,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Gucci古驰绮梦馥栀女士EDP浓香水100ml 25年新品</t>
+          <t>【正品行货】GUCCI古驰绮梦花园系列馥栀女士香水花香调EDP100ml</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9256,68 +9252,68 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>799</v>
+        <v>1730</v>
       </c>
       <c r="E298" t="n">
-        <v>569.1</v>
+        <v>609</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G298" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>【GUCCI】古驰绮梦栀子花女士浓香水EDP100ml520节日礼物</t>
+          <t>【全球购正品】古驰绮梦木兰香型女士香水100ml</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>GUCCI绮梦栀子花100ML浓香型</t>
+          <t>GUCCI绮梦香草兰香100ml</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>700</v>
+        <v>599</v>
       </c>
       <c r="E299" t="n">
-        <v>448</v>
+        <v>499</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>2024-01-01</t>
-        </is>
-      </c>
+      <c r="G299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>【正品行货】GUCCI古驰绮梦花园系列馥栀女士香水花香调EDP100ml</t>
+          <t>GUCCI/古驰绮梦香草兰女士浓香水水生美食调简装礼物</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>GUCCI绮梦栀子花100ML浓香型</t>
+          <t>GUCCI绮梦香草兰香100ml</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>1730</v>
+        <v>499</v>
       </c>
       <c r="E300" t="n">
-        <v>609</v>
+        <v>438</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -9326,56 +9322,60 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2024-03-01</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>【全球购正品】古驰绮梦木兰香型女士香水100ml</t>
+          <t>【GUCCI】古驰绮梦木兰女士浓香香水50ML持久留香花香调</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>GUCCI绮梦香草兰香100ml</t>
+          <t>GUCCI绮梦香草兰香50ml</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>599</v>
+        <v>390</v>
       </c>
       <c r="E301" t="n">
-        <v>499</v>
+        <v>328</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G301" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>GUCCI/古驰绮梦香草兰女士浓香水水生美食调简装礼物</t>
+          <t>【卡诗】黑钻钥源洗发水鱼子酱滋养受损干枯毛躁润泽保湿黑金洗发露</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>GUCCI绮梦香草兰香100ml</t>
+          <t>Kerastase卡诗黑钻鱼子酱洗发水250ml</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>499</v>
+        <v>208</v>
       </c>
       <c r="E302" t="n">
-        <v>438</v>
+        <v>180</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -9384,29 +9384,29 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>【GUCCI】古驰绮梦木兰女士浓香香水50ML持久留香花香调</t>
+          <t>【HR】赫莲娜绿宝瓶悦活蓄能新肌水400ml</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>GUCCI绮梦香草兰香50ml</t>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水400ml</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>390</v>
+        <v>819</v>
       </c>
       <c r="E303" t="n">
-        <v>328</v>
+        <v>642</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -9415,99 +9415,91 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-11-01</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>【卡诗】黑钻钥源洗发水鱼子酱滋养受损干枯毛躁润泽保湿黑金洗发露</t>
+          <t>HR/赫莲娜绿宝瓶新肌水200ml 精华爽肤水</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Kerastase卡诗黑钻鱼子酱洗发水250ml</t>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水400ml</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>208</v>
+        <v>600</v>
       </c>
       <c r="E304" t="n">
-        <v>180</v>
+        <v>456</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Armani 阿玛尼权力PRO粉底液1.5号/2号色红标遮瑕控油滋润</t>
+          <t>两瓶 单品 HR赫莲娜绿宝瓶悦活蓄能新肌水400ml</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>阿玛尼权力PR0粉底1.5 30ml</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>298.0</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>298.0</t>
-        </is>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水400ml</t>
+        </is>
+      </c>
+      <c r="D305" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E305" t="n">
+        <v>1254</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2024-11-01</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>【阿玛尼】权力红标粉底液30ml#1.5pro 遮瑕控油持久</t>
+          <t>【正品行货】赫莲娜绿宝瓶眼霜15ml淡化黑眼圈细纹熬夜眼精华护肤</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>阿玛尼权力PR0粉底1.5 30ml</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>312.0</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>245.0</t>
-        </is>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水400ml</t>
+        </is>
+      </c>
+      <c r="D306" t="n">
+        <v>595</v>
+      </c>
+      <c r="E306" t="n">
+        <v>375</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -9516,68 +9508,60 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>【正品行货】赫莲娜绿宝瓶眼霜15ml淡化黑眼圈细纹熬夜眼精华护肤</t>
+          <t>两瓶 单品 HR赫莲娜绿宝瓶悦活蓄能新肌水400ml</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>HR赫莲娜绿眼霜对装</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>595.0</t>
-        </is>
-      </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>375.0</t>
-        </is>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水200ml</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E307" t="n">
+        <v>1244</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>HR/赫莲娜 绿宝瓶眼霜15ml眼部修复淡化黑眼圈【5天内发货】</t>
+          <t>HR/赫莲娜绿宝瓶新肌水200ml 精华爽肤水</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>HR赫莲娜绿眼霜对装</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>681.0</t>
-        </is>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>332.15</t>
-        </is>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水200ml</t>
+        </is>
+      </c>
+      <c r="D308" t="n">
+        <v>600</v>
+      </c>
+      <c r="E308" t="n">
+        <v>456</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -9586,95 +9570,91 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2025-07-01</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>【GUCCI】古驰女士花悦绽放淡香水50ml</t>
+          <t>【正品行货】HR赫莲娜绿宝瓶新肌水200ml保湿修护提亮补水精华水</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>古驰花悦绽放女士淡香型香水50ml</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>588.0</t>
-        </is>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>229.0</t>
-        </is>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水200ml</t>
+        </is>
+      </c>
+      <c r="D309" t="n">
+        <v>456</v>
+      </c>
+      <c r="E309" t="n">
+        <v>456</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G309" t="inlineStr"/>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>【GUCCI】古驰花悦绽放女士淡香水EDT50ml浪漫白花香调</t>
+          <t>双支HR赫莲娜绿宝瓶新肌水200ml保湿修护提亮精华水</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>古驰花悦绽放女士淡香型香水50ml</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>355.0</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>245.0</t>
-        </is>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水200ml</t>
+        </is>
+      </c>
+      <c r="D310" t="n">
+        <v>1399</v>
+      </c>
+      <c r="E310" t="n">
+        <v>909</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G310" t="inlineStr"/>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>【古驰】花悦绽放女士香水EDP浓香50ml持久留香</t>
+          <t>SKII/SK2小灯泡精华50ml新品光子瓶美白肌因光蕴环采钻白精华液【5天内发货】</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>古驰花悦绽放女士淡香型香水50ml</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>409.0</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>272.0</t>
-        </is>
+          <t>SK-II光子小灯泡精华露50ml</t>
+        </is>
+      </c>
+      <c r="D311" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E311" t="n">
+        <v>745</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -9683,95 +9663,91 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2024-10-01</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>【MAC】魅可定制无暇粉底液2.0二代NC11持妆油皮控油持久</t>
+          <t>【正品行货】SK-II光子小灯泡50ml美白护肤精华液淡斑提亮</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>MAC无瑕粉底液N11 2.0</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>229.0</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
+          <t>SK-II光子小灯泡精华露50ml</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>1890</v>
+      </c>
+      <c r="E312" t="n">
+        <v>850</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr"/>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>【正品行货】MAC/魅可新版定制无暇粉底液2.0 N12持妆控油遮瑕N18</t>
+          <t>【正品行货】SK-II骨胶原晶致活肤修护乳液补水保湿抗皱紧致舒缓</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>MAC无瑕粉底液N18 2.0</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>350.0</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>156.0</t>
-        </is>
+          <t>SK-II晶致美肤乳液100g</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>600</v>
+      </c>
+      <c r="E313" t="n">
+        <v>424</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G313" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>【正品行货】MAC/魅可新版定制无暇粉底液2.0 N12持妆控油遮瑕N18</t>
+          <t>【正品行货】SKII氨基酸洗面奶护肤洁面乳120g温和控油清洁不刺激</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>MAC无瑕粉底液NC11 2.0</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>350.0</t>
-        </is>
-      </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>156.0</t>
-        </is>
+          <t>SKII女士洗面奶120g/支</t>
+        </is>
+      </c>
+      <c r="D314" t="n">
+        <v>480</v>
+      </c>
+      <c r="E314" t="n">
+        <v>259</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -9782,97 +9758,77 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>【Givenchy】纪梵希 四宫格柔雾散粉0号1号2号3号 12g</t>
+          <t>【正品行货】SK-II氨基酸洗面奶20g*6小样温和洁面乳深层清洁控油</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>纪梵希四宫格散粉1号色（新版）</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>298.0</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>194.9</t>
-        </is>
+          <t>SKII女士洗面奶120g/支</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>433</v>
+      </c>
+      <c r="E315" t="n">
+        <v>160</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GIVENCHY纪梵希 四宫格散粉#1百搭滤镜 四色定妆蜜粉细腻轻盈【5天内发货】</t>
+          <t>【正品行货】SKII氨基酸洗面奶护肤洁面乳120g两瓶装温和控油清洁</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>纪梵希四宫格散粉1号色（新版）</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>298.0</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>193.0</t>
-        </is>
+          <t>SKII女士洗面奶120g/支</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>900</v>
+      </c>
+      <c r="E316" t="n">
+        <v>481</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
+      <c r="G316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>【正品行货】GIVENCHY纪梵希四宫格散粉 四色定妆粉 遮瑕控油</t>
+          <t>【原装正品】 SK-II/SK2前男友面膜补水保湿急救护肤3/4/6/10片装【5天内发货】</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>纪梵希四宫格散粉1号色（新版）</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>296.0</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>182.9</t>
-        </is>
+          <t>SK-II前男友面膜10片装</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>518</v>
+      </c>
+      <c r="E317" t="n">
+        <v>410</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -9881,33 +9837,29 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-06-01</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>DECORTE黛珂 牛油果植萃乳液300ML 保湿紧致弹润控油</t>
+          <t>海外直邮SK-IIsk2前男友贴片式面膜10片护肤补水装保湿舒缓提亮【5天内发货】</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>黛珂牛油果乳液300ml*2</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>199.0</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>140.0</t>
-        </is>
+          <t>SK-II前男友面膜10片装</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>799</v>
+      </c>
+      <c r="E318" t="n">
+        <v>511</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -9916,126 +9868,122 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2024-06-01</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>【正品行货】肌肤之钥净采洁面膏清爽型/湿润型125ml洗面奶滋润</t>
+          <t>【正品行货】SK-II前男友面膜贴片10片sk2补水保湿舒缓抗老提亮</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>CPB肌肤之钥清爽洁面125ML</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>269.0</t>
-        </is>
-      </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
+          <t>SK-II前男友面膜10片装</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>490</v>
+      </c>
+      <c r="E319" t="n">
+        <v>435</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G319" t="inlineStr"/>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>【正品行货】肌肤之钥净采洁面膏清爽型/湿润型125ml补水保湿滋润</t>
+          <t>【原装正品】 SK-II/SK2前男友面膜补水保湿急救护肤3/4/6/10片装【5天内发货】</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>CPB肌肤之钥清爽洁面125ML</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>269.0</t>
-        </is>
-      </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>152.0</t>
-        </is>
+          <t>SK-II前男友面膜10片装</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>518</v>
+      </c>
+      <c r="E320" t="n">
+        <v>410</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>【正品行货】CPB肌肤之钥洗面奶湿润型125ml 净采洁面膏</t>
+          <t>【正品行货】SK-II前男友面膜贴片10片sk2补水保湿舒缓抗老提亮</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>CPB肌肤之钥清爽洁面125ML</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>260.0</t>
-        </is>
-      </c>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>152.0</t>
-        </is>
+          <t>SK-II前男友面膜10片装</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>490</v>
+      </c>
+      <c r="E321" t="n">
+        <v>435</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G321" t="inlineStr"/>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>CPB肌肤之钥净采洗面奶(滋润型)125ml/支【5月2日发完】</t>
+          <t>海外直邮SK-IIsk2前男友贴片式面膜10片护肤补水装保湿舒缓提亮【5天内发货】</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>CPB肌肤之钥清爽洁面125ML</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>289.0</t>
-        </is>
-      </c>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>151.9</t>
-        </is>
+          <t>SK-II前男友面膜10片装</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>799</v>
+      </c>
+      <c r="E322" t="n">
+        <v>511</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -10044,68 +9992,60 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2024-06-01</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>【GUCCI】古驰绮梦栀子花女士浓香水EDP100ml520节日礼物</t>
+          <t>【SK-II】大红瓶面霜80g滋养保湿紧致肌肤滋润款</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>GUCCI绮梦馥栀100ML</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>700.0</t>
-        </is>
-      </c>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>448.0</t>
-        </is>
+          <t>SKII大红瓶面霜80g清爽</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>899</v>
+      </c>
+      <c r="E323" t="n">
+        <v>618</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2025-03-28</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Gucci古驰 绮梦馥栀女士EDP浓香水100ml 25年新品</t>
+          <t>【SK-II】 致臻赋能焕采精华霜轻盈型 80g紧致抗皱滋润</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>GUCCI绮梦馥栀100ML</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>1119.0</t>
-        </is>
-      </c>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>540.0</t>
-        </is>
+          <t>SKII大红瓶面霜80g清爽</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>799</v>
+      </c>
+      <c r="E324" t="n">
+        <v>595</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -10114,196 +10054,176 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-23</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>【GUCCI】古驰绮梦馥栀香水100ml简装正品持久留香节日礼物自用</t>
+          <t>【正品行货】SKII赋能焕采精华霜大红瓶面霜滋润轻盈保湿紧致养肤</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>GUCCI绮梦馥栀100ML</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>699.0</t>
-        </is>
-      </c>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>490.0</t>
-        </is>
+          <t>SKII大红瓶面霜80g清爽</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>1460</v>
+      </c>
+      <c r="E325" t="n">
+        <v>692</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2025-01-09</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>【GUCCI】古驰花悦绽放浓香水100ml简装黑盖女士香氛正品持久留香</t>
+          <t>【特价清仓】NARS纳斯哑光唇釉空气柔雾唇霜#684 Gipsy吉普赛玫瑰</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>GUCCI花悦绽放100ML浓香</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>541.0</t>
-        </is>
-      </c>
-      <c r="E326" t="inlineStr">
-        <is>
-          <t>340.91</t>
-        </is>
+          <t>NARS空气唇釉GIPSY吉普赛</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>199</v>
+      </c>
+      <c r="E326" t="n">
+        <v>118.99</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>2023-09-01</t>
-        </is>
-      </c>
+      <c r="G326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>【GUCCI】古驰花悦绽放女士浓香水花香调持久留香送礼100ml</t>
+          <t>【NARS】NARS娜斯空气唇釉#037 #361 #360 #684 7.5ml/支</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>GUCCI花悦绽放100ML浓香</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>447.0</t>
-        </is>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>385.0</t>
-        </is>
+          <t>NARS空气唇釉GIPSY吉普赛</t>
+        </is>
+      </c>
+      <c r="D327" t="n">
+        <v>210</v>
+      </c>
+      <c r="E327" t="n">
+        <v>59.9</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G327" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>310</v>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>Gucci古驰花悦绽放女士淡香水100ml 持久留香送女友</t>
-        </is>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="B328" t="inlineStr"/>
       <c r="C328" t="inlineStr">
         <is>
-          <t>GUCCI花悦绽放100ML浓香</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>525.0</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>319.0</t>
-        </is>
+          <t>NARS空气唇釉GIPSY吉普赛</t>
+        </is>
+      </c>
+      <c r="D328" t="n">
+        <v>129</v>
+      </c>
+      <c r="E328" t="n">
+        <v>129</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G328" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>【全球购正品】古驰绮梦木兰香型女士香水100ml</t>
+          <t>【母亲节礼物】韩国whoo后天气丹华泫水乳单品保湿抗皱护肤品正品</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>GUCCI绮梦木兰100ML浓香型</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>599.0</t>
-        </is>
-      </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>499.0</t>
-        </is>
+          <t>后Whoo天气丹PRO乳110ML</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>255</v>
+      </c>
+      <c r="E329" t="n">
+        <v>245</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G329" t="inlineStr"/>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>GUCCI/古驰绮梦香草兰女士浓香水水生美食调简装礼物</t>
+          <t>【母亲节礼物】韩国whoo后天气丹华泫爽肤水150ml保湿抗皱护肤</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>GUCCI绮梦木兰100ML浓香型</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>499.0</t>
-        </is>
-      </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>438.0</t>
-        </is>
+          <t>后Whoo天气丹PRO乳110ML</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>255</v>
+      </c>
+      <c r="E330" t="n">
+        <v>245</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -10312,99 +10232,83 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2025-09-04</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>【100ml】古驰 绮梦兰花浓香水EDP简装无盖</t>
+          <t>韩国whoo后天气丹华泫水乳套盒保湿抗皱护肤品光耀套装</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>GUCCI绮梦木兰100ML浓香型</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>999.0</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>888.0</t>
-        </is>
+          <t>后Whoo天气丹PRO乳110ML</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>252</v>
+      </c>
+      <c r="E331" t="n">
+        <v>242</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
+      <c r="G331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Gucci古驰绮梦馥栀女士EDP浓香水100ml 25年新品</t>
+          <t>韩国thewhoo后黄金气垫粉底液21号#一正两替换自然遮瑕提亮</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>GUCCI绮梦栀子花100ML浓香型</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>799.0</t>
-        </is>
-      </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>569.1</t>
-        </is>
+          <t>后拱辰享美黄金气垫13G+替换装13G</t>
+        </is>
+      </c>
+      <c r="D332" t="n">
+        <v>223</v>
+      </c>
+      <c r="E332" t="n">
+        <v>127</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>【GUCCI】古驰绮梦栀子花女士浓香水EDP100ml520节日礼物</t>
+          <t>【正品行货】TOM FORD汤姆福特 四色眼影盘 20 47 46 修饰眼部</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>GUCCI绮梦栀子花100ML浓香型</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>700.0</t>
-        </is>
-      </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>448.0</t>
-        </is>
+          <t>TOMFORD幻魅四色眼影盘 #35 玫瑰晶石</t>
+        </is>
+      </c>
+      <c r="D333" t="n">
+        <v>800</v>
+      </c>
+      <c r="E333" t="n">
+        <v>599</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -10413,33 +10317,29 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>【正品行货】GUCCI古驰绮梦花园系列馥栀女士香水花香调EDP100ml</t>
+          <t>SKII/SK2小灯泡精华50ml新品光子瓶美白肌因光蕴环采钻白精华液【5天内发货】</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>GUCCI绮梦栀子花100ML浓香型</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>1730.0</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>609.0</t>
-        </is>
+          <t>SK-II小灯泡新版50ml</t>
+        </is>
+      </c>
+      <c r="D334" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E334" t="n">
+        <v>780</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -10448,64 +10348,60 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2024-10-01</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>【全球购正品】古驰绮梦木兰香型女士香水100ml</t>
+          <t>【正品行货】SK-II光子小灯泡50ml美白护肤精华液淡斑提亮</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>GUCCI绮梦香草兰香100ml</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>599.0</t>
-        </is>
-      </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>499.0</t>
-        </is>
+          <t>SK-II小灯泡新版50ml</t>
+        </is>
+      </c>
+      <c r="D335" t="n">
+        <v>1890</v>
+      </c>
+      <c r="E335" t="n">
+        <v>850</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G335" t="inlineStr"/>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>GUCCI/古驰绮梦香草兰女士浓香水水生美食调简装礼物</t>
+          <t>【正品行货】SK-II光子小灯泡精华75ml套装礼盒礼物淡斑提亮紧致</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>GUCCI绮梦香草兰香100ml</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>499.0</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>438.0</t>
-        </is>
+          <t>SKII光子小灯泡75ml</t>
+        </is>
+      </c>
+      <c r="D336" t="n">
+        <v>1559</v>
+      </c>
+      <c r="E336" t="n">
+        <v>1266.2</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -10514,103 +10410,83 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>【GUCCI】古驰绮梦木兰女士浓香香水50ML持久留香花香调</t>
+          <t>瑞士进口Alivaya美白洁颜蜜深层清洁收缩毛孔控油洗面奶舒缓卸妆【5天内发货】</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>GUCCI绮梦香草兰香50ml</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>390.0</t>
-        </is>
-      </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>328.0</t>
-        </is>
+          <t>SKII洁面油250ml</t>
+        </is>
+      </c>
+      <c r="D337" t="n">
+        <v>169.9</v>
+      </c>
+      <c r="E337" t="n">
+        <v>65.8</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
+      <c r="G337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>【卡诗】黑钻钥源洗发水鱼子酱滋养受损干枯毛躁润泽保湿黑金洗发露</t>
+          <t>AM馥郁满铺洁颜蜜洗面奶温和清洁保湿舒缓氨基酸洁面洗卸二合一女</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Kerastase卡诗黑钻鱼子酱洗发水250ml</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>208.0</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
+          <t>SKII洁面油250ml</t>
+        </is>
+      </c>
+      <c r="D338" t="n">
+        <v>240</v>
+      </c>
+      <c r="E338" t="n">
+        <v>139</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>【HR】赫莲娜绿宝瓶悦活蓄能新肌水400ml</t>
+          <t>【悦芙媞】洁颜蜜囤货装氨基酸洗面奶油皮去油洁面深度清洁洗面奶女</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水400ml</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>819.0</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>642.0</t>
-        </is>
+          <t>SKII洁面油250ml</t>
+        </is>
+      </c>
+      <c r="D339" t="n">
+        <v>139</v>
+      </c>
+      <c r="E339" t="n">
+        <v>91</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -10619,33 +10495,29 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2026-01-07</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>HR/赫莲娜绿宝瓶新肌水200ml 精华爽肤水</t>
+          <t>【13.3万人回购该品牌】正品行货|新版pro阿玛尼粉底液权力红标油皮遮瑕控油持久不脱妆</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水400ml</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>600.0</t>
-        </is>
-      </c>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>456.0</t>
-        </is>
+          <t>阿玛尼权力PR0粉底1.5 30ml</t>
+        </is>
+      </c>
+      <c r="D340" t="n">
+        <v>248</v>
+      </c>
+      <c r="E340" t="n">
+        <v>192</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -10654,79 +10526,4987 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2024-09-01</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>两瓶 单品 HR赫莲娜绿宝瓶悦活蓄能新肌水400ml</t>
+          <t>【正品行货】纪梵希口红粉丝绒口红N37小羊皮N319双支口红大牌女</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水400ml</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>1600.0</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>1254.0</t>
-        </is>
+          <t>纪梵希粉丝绒N37</t>
+        </is>
+      </c>
+      <c r="D341" t="n">
+        <v>746</v>
+      </c>
+      <c r="E341" t="n">
+        <v>458</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>【正品行货】赫莲娜绿宝瓶眼霜15ml淡化黑眼圈细纹熬夜眼精华护肤</t>
+          <t>【原装正品】  YSL圣罗兰唇釉黑管爱心唇釉持久保湿滋润不掉色【5天内发货】</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水400ml</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>595.0</t>
-        </is>
-      </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>375.0</t>
-        </is>
+          <t>圣罗兰爱心黑管唇釉440</t>
+        </is>
+      </c>
+      <c r="D342" t="n">
+        <v>188</v>
+      </c>
+      <c r="E342" t="n">
+        <v>126.9</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>333</v>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>【8.58万人评价品牌正品】ESTĒE LAUDER雅诗兰黛红石榴洁面乳 125ml 两支</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴洁面125ml两支装</t>
+        </is>
+      </c>
+      <c r="D343" t="n">
+        <v>358</v>
+      </c>
+      <c r="E343" t="n">
+        <v>358</v>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>333</v>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>【】双支雅诗兰黛红石榴洁面新款125ml 清洁保湿洁面乳</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴洁面125ml两支装</t>
+        </is>
+      </c>
+      <c r="D344" t="n">
+        <v>359</v>
+      </c>
+      <c r="E344" t="n">
+        <v>359</v>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>333</v>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>【77.2万人回购该品牌】2支雅诗兰黛红石榴洁面新款125ml 清洁保湿洁面乳</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴洁面125ml两支装</t>
+        </is>
+      </c>
+      <c r="D345" t="n">
+        <v>288</v>
+      </c>
+      <c r="E345" t="n">
+        <v>288</v>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>333</v>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>【累计热销532.7万+件】两支 单品 雅诗兰黛新款红石榴洗面奶125ml</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴洁面125ml两支装</t>
+        </is>
+      </c>
+      <c r="D346" t="n">
+        <v>299</v>
+      </c>
+      <c r="E346" t="n">
+        <v>299</v>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>334</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】红石榴水200ml滋润型 鲜活亮采精华水 补水保湿抗氧提亮</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴水200ml两支装</t>
+        </is>
+      </c>
+      <c r="D347" t="n">
+        <v>211</v>
+      </c>
+      <c r="E347" t="n">
+        <v>129.2</v>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>299</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>【2.07万人评价品牌正品】Armani 阿玛尼权力PRO粉底液1.5号/2号色红标遮瑕控油滋润</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底1.5 30ml</t>
+        </is>
+      </c>
+      <c r="D348" t="n">
+        <v>298</v>
+      </c>
+      <c r="E348" t="n">
+        <v>298</v>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>335</v>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>【正品行货】SKII小银瓶肌因光蕴淡斑精华露50ml提亮淡斑淡痘印</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>SK2小银瓶50ml两瓶装</t>
+        </is>
+      </c>
+      <c r="D349" t="n">
+        <v>1530</v>
+      </c>
+      <c r="E349" t="n">
+        <v>782</v>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>336</v>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II/sk2大红瓶面霜50g面部护肤套装礼盒紧致提拉</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>SK2大红瓶滋润面霜50g</t>
+        </is>
+      </c>
+      <c r="D350" t="n">
+        <v>998</v>
+      </c>
+      <c r="E350" t="n">
+        <v>784</v>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>336</v>
+      </c>
+      <c r="B351" t="inlineStr"/>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>SK2大红瓶滋润面霜50g</t>
+        </is>
+      </c>
+      <c r="D351" t="n">
+        <v>784</v>
+      </c>
+      <c r="E351" t="n">
+        <v>784</v>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>337</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>【】Fresh馥蕾诗西柚果香瑰丽香皂250g</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>馥蕾诗西柚香皂</t>
+        </is>
+      </c>
+      <c r="D352" t="n">
+        <v>105</v>
+      </c>
+      <c r="E352" t="n">
+        <v>105</v>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>337</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗西柚/睡莲/小苍兰香皂250g 深层清洁香皂</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>馥蕾诗西柚香皂</t>
+        </is>
+      </c>
+      <c r="D353" t="n">
+        <v>119</v>
+      </c>
+      <c r="E353" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>338</v>
+      </c>
+      <c r="B354" t="inlineStr"/>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
+        </is>
+      </c>
+      <c r="D354" t="n">
+        <v>472</v>
+      </c>
+      <c r="E354" t="n">
+        <v>292.74</v>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>339</v>
+      </c>
+      <c r="B355" t="inlineStr"/>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>馥蕾诗红茶紧致面霜50ml</t>
+        </is>
+      </c>
+      <c r="D355" t="n">
+        <v>584</v>
+      </c>
+      <c r="E355" t="n">
+        <v>368.53</v>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>340</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗莲花青春保湿面霜日霜50ml提亮肤色滋养舒缓</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>馥蕾诗睡莲日霜50ml</t>
+        </is>
+      </c>
+      <c r="D356" t="n">
+        <v>269</v>
+      </c>
+      <c r="E356" t="n">
+        <v>217</v>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
           <t>2025-04-01</t>
         </is>
       </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>341</v>
+      </c>
+      <c r="B357" t="inlineStr"/>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>馥蕾诗玫瑰保湿面霜50ml两瓶装</t>
+        </is>
+      </c>
+      <c r="D357" t="n">
+        <v>230</v>
+      </c>
+      <c r="E357" t="n">
+        <v>230</v>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>342</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>【2.8万人回购该品牌】fresh馥蕾诗小苍兰瑰丽香皂250g</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>馥蕾诗小苍兰香皂</t>
+        </is>
+      </c>
+      <c r="D358" t="n">
+        <v>105</v>
+      </c>
+      <c r="E358" t="n">
+        <v>105</v>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>343</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛白金级养肤粉底液宝石粉底光感保湿透亮遮瑕</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>雅诗兰黛白金粉底液1W0</t>
+        </is>
+      </c>
+      <c r="D359" t="n">
+        <v>599</v>
+      </c>
+      <c r="E359" t="n">
+        <v>390</v>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>344</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Fresh/馥蕾诗红茶精华水250ml酵母透精华液补水保湿细腻改善暗沉【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>馥蕾诗红茶精粹水250ml</t>
+        </is>
+      </c>
+      <c r="D360" t="n">
+        <v>538</v>
+      </c>
+      <c r="E360" t="n">
+        <v>538</v>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>344</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Fresh/馥蕾诗 红茶精华水250ml酵母透精华液补水保湿细腻改善暗沉【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>馥蕾诗红茶精粹水250ml</t>
+        </is>
+      </c>
+      <c r="D361" t="n">
+        <v>800</v>
+      </c>
+      <c r="E361" t="n">
+        <v>534</v>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>345</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】白金级养肤粉底液30ml滋润持久抗氧化 1CO#【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>雅诗兰黛白金粉底液1CO</t>
+        </is>
+      </c>
+      <c r="D362" t="n">
+        <v>625</v>
+      </c>
+      <c r="E362" t="n">
+        <v>400.38</v>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>346</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Clarins/娇韵诗美白牛奶水200ml提亮淡斑 滋润款</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>娇韵诗美白滋润水200ml</t>
+        </is>
+      </c>
+      <c r="D363" t="n">
+        <v>395</v>
+      </c>
+      <c r="E363" t="n">
+        <v>395</v>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>346</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>【Clarins】 娇韵诗 牛奶水爽肤水美白淡斑补水透亮 滋润水200ml</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>娇韵诗美白滋润水200ml</t>
+        </is>
+      </c>
+      <c r="D364" t="n">
+        <v>35914</v>
+      </c>
+      <c r="E364" t="n">
+        <v>359</v>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>347</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>【正品】娇韵诗焕颜紧致弹簧日晚霜淡纹胶原回弹清爽抗皱面霜50ml</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="D365" t="n">
+        <v>339</v>
+      </c>
+      <c r="E365" t="n">
+        <v>335</v>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>348</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>双支雅诗兰黛智妍乳霜75ml/瓶清爽版 保湿补水</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>雅诗兰黛多效智妍乳霜75ml清爽</t>
+        </is>
+      </c>
+      <c r="D366" t="n">
+        <v>9263</v>
+      </c>
+      <c r="E366" t="n">
+        <v>754</v>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>299</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>【品牌好评101.6万+条】正品行货|新版pro阿玛尼粉底液权力红标油皮遮瑕控油持久不脱妆</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底1.5 30ml</t>
+        </is>
+      </c>
+      <c r="D367" t="n">
+        <v>248</v>
+      </c>
+      <c r="E367" t="n">
+        <v>192</v>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>349</v>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>【正品原装】Maison Margiela/梅森马吉拉慵懒周末身体乳200ml</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>马丁马吉拉慵懒周末身体乳200ml</t>
+        </is>
+      </c>
+      <c r="D368" t="n">
+        <v>248</v>
+      </c>
+      <c r="E368" t="n">
+        <v>248</v>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>349</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>【梅森马吉拉】慵懒周末身体乳200ml清洁去角质花香调保湿润肤乳</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>马丁马吉拉慵懒周末身体乳200ml</t>
+        </is>
+      </c>
+      <c r="D369" t="n">
+        <v>229</v>
+      </c>
+      <c r="E369" t="n">
+        <v>229</v>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>350</v>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>【正品行货】兰蔻全新持妆粉底液PO-01 持久控油透气遮瑕贴肤底妆</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>兰蔻养肤水粉底液 PO-01 30ml</t>
+        </is>
+      </c>
+      <c r="D370" t="n">
+        <v>1623</v>
+      </c>
+      <c r="E370" t="n">
+        <v>162</v>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>350</v>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>LANCOME兰蔻持妆粉底液P0-01黑盖30ml持久控油</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>兰蔻养肤水粉底液 PO-01 30ml</t>
+        </is>
+      </c>
+      <c r="D371" t="n">
+        <v>290</v>
+      </c>
+      <c r="E371" t="n">
+        <v>155</v>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>350</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>【正品行货】兰蔻全新持妆粉底液PO-01 30ml持久控油透气遮瑕贴肤</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>兰蔻养肤水粉底液 PO-01 30ml</t>
+        </is>
+      </c>
+      <c r="D372" t="n">
+        <v>260</v>
+      </c>
+      <c r="E372" t="n">
+        <v>169.9</v>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>351</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>KIEHL‘S科颜氏高保湿乳液125ml 补水保湿</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>科颜氏男士乳液125ml</t>
+        </is>
+      </c>
+      <c r="D373" t="n">
+        <v>200</v>
+      </c>
+      <c r="E373" t="n">
+        <v>131.98</v>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>351</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>【科颜氏】男士活力保湿乳液125ml补水保湿清爽控油SPF19</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>科颜氏男士乳液125ml</t>
+        </is>
+      </c>
+      <c r="D374" t="n">
+        <v>179</v>
+      </c>
+      <c r="E374" t="n">
+        <v>126</v>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>299</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>【阿玛尼】权力红标粉底液30ml#1.5pro 遮瑕控油持久</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底1.5 30ml</t>
+        </is>
+      </c>
+      <c r="D375" t="n">
+        <v>312</v>
+      </c>
+      <c r="E375" t="n">
+        <v>245</v>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>299</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Armani 阿玛尼权力PRO粉底液1.5号/2号色红标遮瑕控油滋润</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底1.5 30ml</t>
+        </is>
+      </c>
+      <c r="D376" t="n">
+        <v>29820</v>
+      </c>
+      <c r="E376" t="n">
+        <v>298</v>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>352</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>【科颜氏】清爽啫哩面霜50ml控油补水舒缓修复滋润</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>科颜氏果冻清爽高保湿霜50ml/瓶</t>
+        </is>
+      </c>
+      <c r="D377" t="n">
+        <v>189</v>
+      </c>
+      <c r="E377" t="n">
+        <v>125</v>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>353</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>两瓶 单品 娇韵诗第九代双萃赋活修护精华100ml</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>娇韵诗第九代全新双萃焕活修护精华 100ML</t>
+        </is>
+      </c>
+      <c r="D378" t="n">
+        <v>15463</v>
+      </c>
+      <c r="E378" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>353</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>修护效果好</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>娇韵诗第九代全新双萃焕活修护精华 100ML</t>
+        </is>
+      </c>
+      <c r="D379" t="n">
+        <v>15463</v>
+      </c>
+      <c r="E379" t="n">
+        <v>1546</v>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>353</v>
+      </c>
+      <c r="B380" t="inlineStr"/>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>娇韵诗第九代全新双萃焕活修护精华 100ML</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr"/>
+      <c r="E380" t="inlineStr"/>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>354</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>【保税原装】资生堂安耐晒防晒霜紫外线防水防汗防晒乳隔离霜正品</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>资生堂安耐晒90ml</t>
+        </is>
+      </c>
+      <c r="D381" t="n">
+        <v>114</v>
+      </c>
+      <c r="E381" t="n">
+        <v>114</v>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>354</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>【跨境原装】资生堂安耐晒防晒霜清爽不油面部防紫外线敏感肌正品</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>资生堂安耐晒90ml</t>
+        </is>
+      </c>
+      <c r="D382" t="n">
+        <v>115</v>
+      </c>
+      <c r="E382" t="n">
+        <v>115</v>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>355</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>【ANESSA】安耐晒安热沙面部防晒霜小金管防晒乳旅行军训</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>安耐晒金钻高效防晒90ml</t>
+        </is>
+      </c>
+      <c r="D383" t="n">
+        <v>159</v>
+      </c>
+      <c r="E383" t="n">
+        <v>91</v>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>355</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>【干皮挚爱】ANESSA安热沙安耐晒金啫喱高倍持久水润防晒防紫外线</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>安耐晒金钻高效防晒90ml</t>
+        </is>
+      </c>
+      <c r="D384" t="n">
+        <v>219</v>
+      </c>
+      <c r="E384" t="n">
+        <v>118.69</v>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>2024-11-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>356</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】原生液200ml樱花精华水肌初赋活收缩毛孔去闭口滋润干皮</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>雅诗兰黛樱花微精华原生液400ml</t>
+        </is>
+      </c>
+      <c r="D385" t="n">
+        <v>298</v>
+      </c>
+      <c r="E385" t="n">
+        <v>298</v>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>356</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】二代微精华肌底樱花原生液400ml赋活面部爽肤水收缩毛孔</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>雅诗兰黛樱花微精华原生液400ml</t>
+        </is>
+      </c>
+      <c r="D386" t="n">
+        <v>639</v>
+      </c>
+      <c r="E386" t="n">
+        <v>339</v>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>357</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL/圣罗兰口红小金条 21复古红显白大牌节日礼盒装</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>圣罗兰小金条细管口红21号复古正红色</t>
+        </is>
+      </c>
+      <c r="D387" t="n">
+        <v>128</v>
+      </c>
+      <c r="E387" t="n">
+        <v>128</v>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>357</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰口红小金条1966皮革哑光21杨树林416礼盒装</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>圣罗兰小金条细管口红21号复古正红色</t>
+        </is>
+      </c>
+      <c r="D388" t="n">
+        <v>1380</v>
+      </c>
+      <c r="E388" t="n">
+        <v>138</v>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>358</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>BOBBI BROWN/芭比波郎卸妆油200ml清透温和</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>芭比布朗舒缓卸妆洁面油200ml</t>
+        </is>
+      </c>
+      <c r="D389" t="n">
+        <v>298</v>
+      </c>
+      <c r="E389" t="n">
+        <v>182</v>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>358</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>芭比布朗清润舒盈新版卸妆油200ml/瓶 温和卸妆</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>芭比布朗舒缓卸妆洁面油200ml</t>
+        </is>
+      </c>
+      <c r="D390" t="n">
+        <v>270</v>
+      </c>
+      <c r="E390" t="n">
+        <v>177</v>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>358</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>芭比布朗清润舒盈新版卸妆油200ml 温和卸妆</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>芭比布朗舒缓卸妆洁面油200ml</t>
+        </is>
+      </c>
+      <c r="D391" t="n">
+        <v>1803</v>
+      </c>
+      <c r="E391" t="n">
+        <v>163</v>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>358</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>【BOBBI BROWN】芭比布朗卸妆油200ml清润洁肤油温和清洁卸妆不糊眼</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>芭比布朗舒缓卸妆洁面油200ml</t>
+        </is>
+      </c>
+      <c r="D392" t="n">
+        <v>323</v>
+      </c>
+      <c r="E392" t="n">
+        <v>200.71</v>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>359</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>【娇韵诗】第九代黄金双萃精华100ml/瓶滋润补水</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>娇韵诗双萃焕活修护精华露100ml</t>
+        </is>
+      </c>
+      <c r="D393" t="n">
+        <v>998</v>
+      </c>
+      <c r="E393" t="n">
+        <v>658</v>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>359</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>【娇韵诗】双萃精华 100ml清爽版控油修护维稳保湿面部精华【两瓶装】</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>娇韵诗双萃焕活修护精华露100ml</t>
+        </is>
+      </c>
+      <c r="D394" t="n">
+        <v>15303</v>
+      </c>
+      <c r="E394" t="n">
+        <v>1330</v>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>359</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>两瓶 单品 娇韵诗第九代双萃赋活修护精华100ml</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>娇韵诗双萃焕活修护精华露100ml</t>
+        </is>
+      </c>
+      <c r="D395" t="n">
+        <v>15463</v>
+      </c>
+      <c r="E395" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>359</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>【娇韵诗】第九代双萃精华露100ml清爽版 修护淡纹滋润</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>娇韵诗双萃焕活修护精华露100ml</t>
+        </is>
+      </c>
+      <c r="D396" t="n">
+        <v>969</v>
+      </c>
+      <c r="E396" t="n">
+        <v>715</v>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>360</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>【阿玛尼】口红权力哑雾红黑管口红410色号3.1g不掉色</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>阿玛尼权力口红410色</t>
+        </is>
+      </c>
+      <c r="D397" t="n">
+        <v>84162</v>
+      </c>
+      <c r="E397" t="n">
+        <v>84</v>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>361</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>【正品行货】ysl圣罗兰口红nm裸缪斯 rm黑金浮雕方管显白滋润唇膏</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰黑金方管13色</t>
+        </is>
+      </c>
+      <c r="D398" t="n">
+        <v>128</v>
+      </c>
+      <c r="E398" t="n">
+        <v>128</v>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>361</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰黑金浮雕口红方管唇膏裸色NM裸缪斯大牌</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰黑金方管13色</t>
+        </is>
+      </c>
+      <c r="D399" t="n">
+        <v>118</v>
+      </c>
+      <c r="E399" t="n">
+        <v>118</v>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>361</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>【正品行货】ysl/圣罗兰大牌口红nm裸缪斯黑金浮雕方管大牌礼盒装</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰黑金方管13色</t>
+        </is>
+      </c>
+      <c r="D400" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E400" t="n">
+        <v>128</v>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>362</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>【正品行货】圣罗兰/YSL方管口红黑金浮雕NM裸缪斯大牌正品礼盒装</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰黑金方管14色</t>
+        </is>
+      </c>
+      <c r="D401" t="n">
+        <v>128</v>
+      </c>
+      <c r="E401" t="n">
+        <v>128</v>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>362</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰黑金浮雕口红方管唇膏裸色NM裸缪斯大牌</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰黑金方管14色</t>
+        </is>
+      </c>
+      <c r="D402" t="n">
+        <v>118</v>
+      </c>
+      <c r="E402" t="n">
+        <v>118</v>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>363</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL/圣罗兰黑金浮雕方管唇膏大牌口红 1971流言礼盒</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰黑金方管1968</t>
+        </is>
+      </c>
+      <c r="D403" t="n">
+        <v>128</v>
+      </c>
+      <c r="E403" t="n">
+        <v>128</v>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>364</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL/圣罗兰啵啵唇冻镜面唇釉银管乌龙冻04唇蜜礼盒款</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰银管02色</t>
+        </is>
+      </c>
+      <c r="D404" t="n">
+        <v>208</v>
+      </c>
+      <c r="E404" t="n">
+        <v>208</v>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>365</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>两瓶 单品 Clinique倩碧黄油乳液滋润(有油)125ml</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>倩碧有油润肤乳125ml</t>
+        </is>
+      </c>
+      <c r="D405" t="n">
+        <v>1463</v>
+      </c>
+      <c r="E405" t="n">
+        <v>146</v>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>365</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>【正品行货】Clinique/倩碧黄油无油有油乳液保湿滋润滋养</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>倩碧有油润肤乳125ml</t>
+        </is>
+      </c>
+      <c r="D406" t="n">
+        <v>217.8</v>
+      </c>
+      <c r="E406" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>365</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>【Clinique】倩碧黄油润肤乳无油/有油125ml</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>倩碧有油润肤乳125ml</t>
+        </is>
+      </c>
+      <c r="D407" t="n">
+        <v>186</v>
+      </c>
+      <c r="E407" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>365</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>【正品行货】Clinique/倩碧黄油无油有油乳液保湿滋润滋养125ml*2</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>倩碧有油润肤乳125ml</t>
+        </is>
+      </c>
+      <c r="D408" t="n">
+        <v>547.8</v>
+      </c>
+      <c r="E408" t="n">
+        <v>148</v>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>366</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>La Mer/海蓝之谜 奇迹精华油30ml 臻璨焕活精华油</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>海蓝之谜 臻璨焕活精华油30ml （万能油）</t>
+        </is>
+      </c>
+      <c r="D409" t="n">
+        <v>8683</v>
+      </c>
+      <c r="E409" t="n">
+        <v>868</v>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>366</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>LA MER/海蓝之谜 再生万能油臻璨焕活精华油30ml</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>海蓝之谜 臻璨焕活精华油30ml （万能油）</t>
+        </is>
+      </c>
+      <c r="D410" t="n">
+        <v>1350</v>
+      </c>
+      <c r="E410" t="n">
+        <v>914.53</v>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>367</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>【SK-II】sk2全新大红瓶精华霜清爽面霜80g保湿补水护肤紧致</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>SK2大红瓶清爽版80g</t>
+        </is>
+      </c>
+      <c r="D411" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E411" t="n">
+        <v>721</v>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>368</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>【正品行货】SKII赋能焕采精华霜大红瓶面霜滋润轻盈保湿紧致养肤</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>SK2大红瓶滋润版80g</t>
+        </is>
+      </c>
+      <c r="D412" t="n">
+        <v>1460</v>
+      </c>
+      <c r="E412" t="n">
+        <v>692</v>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>368</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>【SK-II】大红瓶面霜80g滋润型保湿抗皱紧致修护舒缓提亮</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>SK2大红瓶滋润版80g</t>
+        </is>
+      </c>
+      <c r="D413" t="n">
+        <v>899</v>
+      </c>
+      <c r="E413" t="n">
+        <v>669.24</v>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>368</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>【SK-II】大红瓶面霜80g滋养保湿紧致肌肤滋润款</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>SK2大红瓶滋润版80g</t>
+        </is>
+      </c>
+      <c r="D414" t="n">
+        <v>6183</v>
+      </c>
+      <c r="E414" t="n">
+        <v>618</v>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>368</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>【SK-II】 致臻赋能焕采精华霜轻盈型 80g紧致抗皱滋润</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>SK2大红瓶滋润版80g</t>
+        </is>
+      </c>
+      <c r="D415" t="n">
+        <v>799</v>
+      </c>
+      <c r="E415" t="n">
+        <v>595</v>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>369</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】红石榴水200ml滋润型 鲜活亮采精华水 补水保湿抗氧提亮</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>雅诗兰黛ESTEE LAUDER新版红石榴能量水清爽型 200ML</t>
+        </is>
+      </c>
+      <c r="D416" t="n">
+        <v>211</v>
+      </c>
+      <c r="E416" t="n">
+        <v>129.2</v>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>370</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>海外直邮SK-II/SK2/SKII小银瓶肌因光蕴淡斑精华露50ml淡斑淡痘印</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>SK-II 小银瓶精华50ML</t>
+        </is>
+      </c>
+      <c r="D417" t="n">
+        <v>6453</v>
+      </c>
+      <c r="E417" t="n">
+        <v>645</v>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>370</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>【正品行货】SKII小银瓶肌因光蕴淡斑精华露50ml提亮淡斑淡痘印</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>SK-II 小银瓶精华50ML</t>
+        </is>
+      </c>
+      <c r="D418" t="n">
+        <v>7823</v>
+      </c>
+      <c r="E418" t="n">
+        <v>782</v>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>370</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>【14.8万人回购该品牌】海外直邮SK-II/SK2/SKII小银瓶肌因光蕴淡斑精华露50ml淡斑淡痘印</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>SK-II 小银瓶精华50ML</t>
+        </is>
+      </c>
+      <c r="D419" t="n">
+        <v>6453</v>
+      </c>
+      <c r="E419" t="n">
+        <v>645</v>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>370</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>SK-II该商品100%正品，假一赔十</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>SK-II 小银瓶精华50ML</t>
+        </is>
+      </c>
+      <c r="D420" t="n">
+        <v>1099</v>
+      </c>
+      <c r="E420" t="n">
+        <v>690</v>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>371</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>【阿玛尼】蓝标大师粉底液 2 号 30ml 保湿遮瑕持久干皮</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>阿玛尼大师粉底液2号</t>
+        </is>
+      </c>
+      <c r="D421" t="n">
+        <v>279</v>
+      </c>
+      <c r="E421" t="n">
+        <v>279</v>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>372</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>【Lancome】兰蔻美丽人生馥郁版女士浓香EDP 30-50-100ml【法国直发】</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Lancome兰蔻美丽人生馥郁版100ml</t>
+        </is>
+      </c>
+      <c r="D422" t="n">
+        <v>533</v>
+      </c>
+      <c r="E422" t="n">
+        <v>533</v>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>373</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>LANCOME兰蔻 美丽人生香水 馥郁版30ml</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Lancome兰蔻美丽人生馥郁版50ml</t>
+        </is>
+      </c>
+      <c r="D423" t="n">
+        <v>599</v>
+      </c>
+      <c r="E423" t="n">
+        <v>349</v>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>374</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>【专柜行货】兰蔻新品美丽人生香水50ml 浓香版EDP 女士香水</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>兰蔻 美丽人生香氛精华香水 50ml</t>
+        </is>
+      </c>
+      <c r="D424" t="n">
+        <v>1060</v>
+      </c>
+      <c r="E424" t="n">
+        <v>879.8</v>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>374</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>【Lancome】兰蔻美丽人生馥郁版女士浓香EDP 30-50-100ml【法国直发】</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>兰蔻 美丽人生香氛精华香水 50ml</t>
+        </is>
+      </c>
+      <c r="D425" t="n">
+        <v>533</v>
+      </c>
+      <c r="E425" t="n">
+        <v>533</v>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>375</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>【Lancome】兰蔻idole偶像是我淡香水50ml留香清新约会高级礼物</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Lancome/兰蔻是我IDOLE偶像香水 50ml</t>
+        </is>
+      </c>
+      <c r="D426" t="n">
+        <v>3733</v>
+      </c>
+      <c r="E426" t="n">
+        <v>373</v>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>376</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>【百补品牌热销225.2万件】Lancome/兰蔻 IDOLE是我香水100ml 女士EDP持久花香调浓香</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Lancome 兰蔻是我 浓情版 100ml</t>
+        </is>
+      </c>
+      <c r="D427" t="n">
+        <v>5393</v>
+      </c>
+      <c r="E427" t="n">
+        <v>539</v>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>377</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>【百补品牌热销36.5万件】GUCCI/古驰绮梦茉莉女士香水100ml节日香氛礼物</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>GUCCI 香水 茉莉100ML</t>
+        </is>
+      </c>
+      <c r="D428" t="n">
+        <v>700</v>
+      </c>
+      <c r="E428" t="n">
+        <v>419</v>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>377</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>【1.23万人评价品牌正品】GUCCI/古驰绮梦茉莉女士香水100ml浓香水简装礼物</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>GUCCI 香水 茉莉100ML</t>
+        </is>
+      </c>
+      <c r="D429" t="n">
+        <v>599</v>
+      </c>
+      <c r="E429" t="n">
+        <v>404.49</v>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>378</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>【Hermes】爱马仕香水李先生花园淡香水100mlEDT芳香柑橘调 持久留香</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>李先生的花园(Le Jardin de Monsieur Li)，淡香水，100 ml</t>
+        </is>
+      </c>
+      <c r="D430" t="n">
+        <v>537</v>
+      </c>
+      <c r="E430" t="n">
+        <v>338.4</v>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>379</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>【Hermes】爱马仕绯红火参/血色大黄古龙水中性香水100ml</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>绯红火参古龙水（Eau de rhubarbe écarlate）, 古龍水, 100 ml</t>
+        </is>
+      </c>
+      <c r="D431" t="n">
+        <v>39945</v>
+      </c>
+      <c r="E431" t="n">
+        <v>399</v>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>380</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>【正品行货】BOBBI BROWN芭比波朗 水唇冻 奢金缎光唇膏 云朵唇霜</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>NARS小粉金细管唇膏1.5G #321 Turned on</t>
+        </is>
+      </c>
+      <c r="D432" t="n">
+        <v>375</v>
+      </c>
+      <c r="E432" t="n">
+        <v>166</v>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>381</v>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>【原装正品】MAC魅可新经典大子弹头口红唇膏哑光3.5g显色显白</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>MAC 丝柔哑光唇膏 #646 MARRAKESH 肉桂红茶</t>
+        </is>
+      </c>
+      <c r="D433" t="n">
+        <v>127.9</v>
+      </c>
+      <c r="E433" t="n">
+        <v>87</v>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>382</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>【海蓝之谜】调理焕肤液100ml 补水控油保湿改善闭口</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>LAMER海蓝之谜调理焕肤液100ml</t>
+        </is>
+      </c>
+      <c r="D434" t="n">
+        <v>809</v>
+      </c>
+      <c r="E434" t="n">
+        <v>629</v>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>383</v>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>【】MAC魅可定妆喷雾100ml补水保湿控提亮持久控油</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>MAC魅可保湿定妆喷雾Fix+100mL</t>
+        </is>
+      </c>
+      <c r="D435" t="n">
+        <v>289</v>
+      </c>
+      <c r="E435" t="n">
+        <v>135</v>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>384</v>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>MAC/魅可盈润妆前保湿精华乳50ml打底隔离帖服提亮妆前乳</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>MAC妆前保湿精华乳100ML</t>
+        </is>
+      </c>
+      <c r="D436" t="n">
+        <v>336</v>
+      </c>
+      <c r="E436" t="n">
+        <v>336</v>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>384</v>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>MAC/魅可白芍妆前精华乳 养合一水润打底服帖保湿清透焕颜精华</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>MAC妆前保湿精华乳100ML</t>
+        </is>
+      </c>
+      <c r="D437" t="n">
+        <v>165</v>
+      </c>
+      <c r="E437" t="n">
+        <v>165</v>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>385</v>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>【MAC】魅可 新升级定制无瑕粉底液NC12#30ml</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>MAC 无暇粉底液NC12 30ML</t>
+        </is>
+      </c>
+      <c r="D438" t="n">
+        <v>245</v>
+      </c>
+      <c r="E438" t="n">
+        <v>137</v>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>386</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>【ESTEE LAUDER雅诗兰黛】红石榴面霜 鲜活亮采日霜50ml保湿补水</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>雅诗兰黛 红石榴面霜50ml</t>
+        </is>
+      </c>
+      <c r="D439" t="n">
+        <v>1193</v>
+      </c>
+      <c r="E439" t="n">
+        <v>119</v>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>387</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>【累计热销532.7万+件】正品行货雅诗兰黛红石榴洗面奶泡沫深清洁去油去黄提亮125ml</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>雅诗兰黛 红石榴洁面125ml</t>
+        </is>
+      </c>
+      <c r="D440" t="n">
+        <v>1093</v>
+      </c>
+      <c r="E440" t="n">
+        <v>109</v>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>387</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>【ESTEE LAUDER】雅诗兰黛新款红石榴洗面奶125ml</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>雅诗兰黛 红石榴洁面125ml</t>
+        </is>
+      </c>
+      <c r="D441" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="E441" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>388</v>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>【跨境原装】资生堂红腰子洗面奶女洁面乳膏氨基酸清洁保湿旗舰店</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO红腰子洁面125ml</t>
+        </is>
+      </c>
+      <c r="D442" t="n">
+        <v>65</v>
+      </c>
+      <c r="E442" t="n">
+        <v>65</v>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>389</v>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>【资生堂】红妍洗面奶+悦薇水乳+眼霜+红腰子精华+抗糖面霜护肤套装</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO悦薇抗糖眼霜（新版）15ml</t>
+        </is>
+      </c>
+      <c r="D443" t="n">
+        <v>1429</v>
+      </c>
+      <c r="E443" t="n">
+        <v>1429</v>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>2024-02-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>389</v>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>【资生堂】悦薇智感紧塑焕白眼霜15ml 抗糖紧致淡黑眼圈细纹 小熨斗</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO悦薇抗糖眼霜（新版）15ml</t>
+        </is>
+      </c>
+      <c r="D444" t="n">
+        <v>153</v>
+      </c>
+      <c r="E444" t="n">
+        <v>109</v>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>390</v>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>【4.44万人评价品牌正品】SHISEIDO/资生堂 盼丽风姿眼霜15ml抗皱抚痕皱修护小雷达眼霜</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO盼丽风姿眼霜（新款）15ml</t>
+        </is>
+      </c>
+      <c r="D445" t="n">
+        <v>199</v>
+      </c>
+      <c r="E445" t="n">
+        <v>121</v>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>390</v>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂盼丽风姿智感抚纹眼霜15ml小雷达眼霜抗皱紧致</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO盼丽风姿眼霜（新款）15ml</t>
+        </is>
+      </c>
+      <c r="D446" t="n">
+        <v>147</v>
+      </c>
+      <c r="E446" t="n">
+        <v>147</v>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>391</v>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】DW持妆粉底液30ml油皮遮瑕控油无泵头1C1</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1C1 30ML 新版 2026年</t>
+        </is>
+      </c>
+      <c r="D447" t="n">
+        <v>259</v>
+      </c>
+      <c r="E447" t="n">
+        <v>239</v>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>392</v>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】DW持妆粉底液油皮亲妈持久遮瑕控油服帖防晒1N2#</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N2 30ML 新版 2026</t>
+        </is>
+      </c>
+      <c r="D448" t="n">
+        <v>29932</v>
+      </c>
+      <c r="E448" t="n">
+        <v>299</v>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>393</v>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】DW二代持妆粉底液 #1N1 30ML遮瑕持久控油提亮肌肤</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N1 30ML 新版 2026</t>
+        </is>
+      </c>
+      <c r="D449" t="n">
+        <v>299</v>
+      </c>
+      <c r="E449" t="n">
+        <v>299</v>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>394</v>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>【正品行货】MAC/魅可大子弹头口红哑光柔雾666大宠粉602大辣椒</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>MAC魅可 丝柔哑光唇膏 大子弹口红#666 Sweet Deal 玫瑰冷萃</t>
+        </is>
+      </c>
+      <c r="D450" t="n">
+        <v>112</v>
+      </c>
+      <c r="E450" t="n">
+        <v>112</v>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>394</v>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>【正品行货】MAC/魅可大子弹头口红哑光柔雾666大宠粉602大辣椒</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>MAC魅可 丝柔哑光唇膏 大子弹口红#666 Sweet Deal 玫瑰冷萃</t>
+        </is>
+      </c>
+      <c r="D451" t="n">
+        <v>88</v>
+      </c>
+      <c r="E451" t="n">
+        <v>88</v>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>395</v>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>【LAN】兰气泡油2.0保湿修护抗皱精华油水油同补</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Laneige Skin Veil Base_EX No.40 30ml紫色</t>
+        </is>
+      </c>
+      <c r="D452" t="n">
+        <v>500</v>
+      </c>
+      <c r="E452" t="n">
+        <v>299</v>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>395</v>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>韩国LANEIGE兰芝新款马卡龙防晒隔离霜遮瑕三合一妆前乳打底</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Laneige Skin Veil Base_EX No.40 30ml紫色</t>
+        </is>
+      </c>
+      <c r="D453" t="n">
+        <v>111</v>
+      </c>
+      <c r="E453" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>395</v>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>韩国Laneige兰芝新款雪纱防晒隔离霜遮瑕三合一妆前乳</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Laneige Skin Veil Base_EX No.40 30ml紫色</t>
+        </is>
+      </c>
+      <c r="D454" t="n">
+        <v>111</v>
+      </c>
+      <c r="E454" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>396</v>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>韩国Laneige兰芝新款雪纱防晒隔离霜遮瑕三合一妆前乳</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Laneige Skin Veil Base_EX No.60 30ml绿色</t>
+        </is>
+      </c>
+      <c r="D455" t="n">
+        <v>111</v>
+      </c>
+      <c r="E455" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>396</v>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>韩国LANEIGE兰芝新款马卡龙防晒隔离霜遮瑕三合一妆前乳打底</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Laneige Skin Veil Base_EX No.60 30ml绿色</t>
+        </is>
+      </c>
+      <c r="D456" t="n">
+        <v>111</v>
+      </c>
+      <c r="E456" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>396</v>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>【兰芝】隔离霜雪纱丝柔隔离乳妆前防晒遮瑕30ml#40紫色60绿色新升级</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Laneige Skin Veil Base_EX No.60 30ml绿色</t>
+        </is>
+      </c>
+      <c r="D457" t="n">
+        <v>99</v>
+      </c>
+      <c r="E457" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>2025-04-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>397</v>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>【资生堂】悦薇面霜抗糖抗初老补水紧致智感紧塑焕白霜</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>资生堂 悦薇大抗糖滋润面霜（新款）50mL</t>
+        </is>
+      </c>
+      <c r="D458" t="n">
+        <v>359</v>
+      </c>
+      <c r="E458" t="n">
+        <v>275.07</v>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>398</v>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>【NARS】娜斯5894大白饼粉饼控油磨皮持妆蜜粉饼【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>NARS蜜粉饼5894 效期24年</t>
+        </is>
+      </c>
+      <c r="D459" t="n">
+        <v>251</v>
+      </c>
+      <c r="E459" t="n">
+        <v>128</v>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>398</v>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>正品行货NARS粉饼娜斯蜜粉饼散粉大白饼控油清爽定妆持久</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>NARS蜜粉饼5894 效期24年</t>
+        </is>
+      </c>
+      <c r="D460" t="n">
+        <v>288</v>
+      </c>
+      <c r="E460" t="n">
+        <v>130</v>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>399</v>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>韩国Whoo后拱辰享雪玉凝美白洁面洗面奶180ml*2</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>WHOO/后拱辰享洁面泡沫180ml/支 （新条码）</t>
+        </is>
+      </c>
+      <c r="D461" t="n">
+        <v>199</v>
+      </c>
+      <c r="E461" t="n">
+        <v>122</v>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>399</v>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>韩国Whoo后拱辰享雪玉凝美白洁面洗面奶180ml</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>WHOO/后拱辰享洁面泡沫180ml/支 （新条码）</t>
+        </is>
+      </c>
+      <c r="D462" t="n">
+        <v>159</v>
+      </c>
+      <c r="E462" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>399</v>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>韩国Whoo后拱辰享雪玉凝美白洁面洗面奶180ml</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>WHOO/后拱辰享洁面泡沫180ml/支 （新条码）</t>
+        </is>
+      </c>
+      <c r="D463" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="E463" t="n">
+        <v>63</v>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>400</v>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>【资生堂】第四代红腰子红妍肌活精华露抗皱紧致保湿补水100ml</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>SHISEIDO资生堂红腰子精华100ml</t>
+        </is>
+      </c>
+      <c r="D464" t="n">
+        <v>398</v>
+      </c>
+      <c r="E464" t="n">
+        <v>325</v>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>400</v>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>【SHISEIDO】资生堂第四代红腰子50ml 补水保湿</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>SHISEIDO资生堂红腰子精华100ml</t>
+        </is>
+      </c>
+      <c r="D465" t="n">
+        <v>280</v>
+      </c>
+      <c r="E465" t="n">
+        <v>160</v>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>400</v>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>【资生堂】四代红腰子精华100ml*2面部精华露保湿滋润</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>SHISEIDO资生堂红腰子精华100ml</t>
+        </is>
+      </c>
+      <c r="D466" t="n">
+        <v>1209</v>
+      </c>
+      <c r="E466" t="n">
+        <v>640</v>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>400</v>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>【资生堂】四代红腰子精华100ml面部精华露补水保湿滋润</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>SHISEIDO资生堂红腰子精华100ml</t>
+        </is>
+      </c>
+      <c r="D467" t="n">
+        <v>1209</v>
+      </c>
+      <c r="E467" t="n">
+        <v>635</v>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>401</v>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>诺沃品牌官方正品，100%保障</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>古驰炼金师花园香草颂香水100ML</t>
+        </is>
+      </c>
+      <c r="D468" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E468" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>401</v>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>GUCCI/古驰炼金士花园系列香水100ml简装正品留香</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>古驰炼金师花园香草颂香水100ML</t>
+        </is>
+      </c>
+      <c r="D469" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E469" t="n">
+        <v>700</v>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>402</v>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>诺沃品牌官方正品，100%保障</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>古驰炼金师花园沐光橙香水100ML</t>
+        </is>
+      </c>
+      <c r="D470" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E470" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>403</v>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>【Maison Margiela】 梅森马吉拉 爵士酒廊淡香水EDT 100毫升【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>马丁马吉拉-爵士酒廊淡香100ml</t>
+        </is>
+      </c>
+      <c r="D471" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E471" t="n">
+        <v>545</v>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>403</v>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>MAISON MAUGUELA/梅森马吉拉 爵士酒廊EDT淡香水100ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>马丁马吉拉-爵士酒廊淡香100ml</t>
+        </is>
+      </c>
+      <c r="D472" t="n">
+        <v>545</v>
+      </c>
+      <c r="E472" t="n">
+        <v>545</v>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>404</v>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰全新爱心唇釉440 610 416 622限定浮雕黑管</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>YSL新款爱心唇釉610#</t>
+        </is>
+      </c>
+      <c r="D473" t="n">
+        <v>212</v>
+      </c>
+      <c r="E473" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>404</v>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL/圣罗兰全新黑管唇釉610 416 442 443爱心限量版</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>YSL新款爱心唇釉610#</t>
+        </is>
+      </c>
+      <c r="D474" t="n">
+        <v>250</v>
+      </c>
+      <c r="E474" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>404</v>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰全新爱心唇釉610 416 622 440限定浮雕黑管</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>YSL新款爱心唇釉610#</t>
+        </is>
+      </c>
+      <c r="D475" t="n">
+        <v>248</v>
+      </c>
+      <c r="E475" t="n">
+        <v>152.1</v>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>404</v>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>【原装正品】  YSL圣罗兰唇釉黑管爱心唇釉持久保湿滋润不掉色【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>YSL新款爱心唇釉610#</t>
+        </is>
+      </c>
+      <c r="D476" t="n">
+        <v>188</v>
+      </c>
+      <c r="E476" t="n">
+        <v>126.9</v>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>405</v>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Bvlgari宝格丽新版白茶香150ml 清新香水 自然茶香【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>宝格丽白茶淡香150ml</t>
+        </is>
+      </c>
+      <c r="D477" t="n">
+        <v>999</v>
+      </c>
+      <c r="E477" t="n">
+        <v>768</v>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>406</v>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>【正品行货】植村秀绿茶卸妆洁颜油  温和深层清洁彩妆保湿</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>植村秀绿茶卸妆油150ml</t>
+        </is>
+      </c>
+      <c r="D478" t="n">
+        <v>380</v>
+      </c>
+      <c r="E478" t="n">
+        <v>304</v>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>406</v>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>【正品行货】植村秀绿茶新肌洁颜油卸妆油150ml 去黄抗氧化</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>植村秀绿茶卸妆油150ml</t>
+        </is>
+      </c>
+      <c r="D479" t="n">
+        <v>380</v>
+      </c>
+      <c r="E479" t="n">
+        <v>380</v>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>407</v>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>液体腮红高光饱和修容氛围膨胀收缩气色学生自然提亮防水丝绒防汗</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>NARS 水光绚色液体腮红 西柚奶桃 BRAZEN 7ml</t>
+        </is>
+      </c>
+      <c r="D480" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="E480" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>407</v>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Nars纳斯小粉金液体腮红7ml光感自然#BEHAVE烟粉豆沙</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>NARS 水光绚色液体腮红 西柚奶桃 BRAZEN 7ml</t>
+        </is>
+      </c>
+      <c r="D481" t="n">
+        <v>139</v>
+      </c>
+      <c r="E481" t="n">
+        <v>95</v>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>408</v>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Nars纳斯小粉金液体腮红7ml光感自然#BEHAVE烟粉豆沙</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>NARS 水光绚色液体腮红 烟粉豆沙色 BEHAVE 7ml</t>
+        </is>
+      </c>
+      <c r="D482" t="n">
+        <v>139</v>
+      </c>
+      <c r="E482" t="n">
+        <v>95</v>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>409</v>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>【正品行货】祖玛珑香水持久留香香水英国梨与香豌豆香型清新30ml</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Jo Malone祖玛珑英国梨与豌豆花香水30ml</t>
+        </is>
+      </c>
+      <c r="D483" t="n">
+        <v>501</v>
+      </c>
+      <c r="E483" t="n">
+        <v>315.74</v>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>410</v>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>【Lancome】兰蔻轻透水漾防晒清爽隔离50ml/瓶</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>兰蔻清爽防晒双支装50ml*2 新版</t>
+        </is>
+      </c>
+      <c r="D484" t="n">
+        <v>342</v>
+      </c>
+      <c r="E484" t="n">
+        <v>183</v>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>410</v>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>两支 单品 兰蔻新版小白管轻透水漾防晒乳50ml</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>兰蔻清爽防晒双支装50ml*2 新版</t>
+        </is>
+      </c>
+      <c r="D485" t="n">
+        <v>659</v>
+      </c>
+      <c r="E485" t="n">
+        <v>382</v>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>410</v>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>双支 单品 Lancome兰蔻清透水漾防晒清爽隔离50ml</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>兰蔻清爽防晒双支装50ml*2 新版</t>
+        </is>
+      </c>
+      <c r="D486" t="n">
+        <v>614</v>
+      </c>
+      <c r="E486" t="n">
+        <v>360</v>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>411</v>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>日本快美特新款车载香薰汽车车用香水高档男士香氛除异味持久摆件</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>古驰炼金师花园狮之心香水100ML</t>
+        </is>
+      </c>
+      <c r="D487" t="n">
+        <v>128</v>
+      </c>
+      <c r="E487" t="n">
+        <v>62.22</v>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>411</v>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>GUCCI/古驰炼金士花园系列香水100ML正品香氛送礼</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>古驰炼金师花园狮之心香水100ML</t>
+        </is>
+      </c>
+      <c r="D488" t="n">
+        <v>1099</v>
+      </c>
+      <c r="E488" t="n">
+        <v>736.36</v>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>411</v>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>诺沃品牌官方正品，100%保障</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>古驰炼金师花园狮之心香水100ML</t>
+        </is>
+      </c>
+      <c r="D489" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E489" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>412</v>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>【百补品牌热销36.6万件】GUCCI/古驰炼金士花园系列香水100ml简装正品留香</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>古驰炼金师花园桂之舞香水100ML</t>
+        </is>
+      </c>
+      <c r="D490" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E490" t="n">
+        <v>700</v>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>413</v>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>新色!NARS纳斯新版腮红膨胀色氛围色显嫩细腻4.8g爱欲沉溺慢热</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>NARS AFTERGLOW LIQUID BLUSH - INSATIABLE</t>
+        </is>
+      </c>
+      <c r="D491" t="n">
+        <v>330</v>
+      </c>
+      <c r="E491" t="n">
+        <v>208</v>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>414</v>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>【NARS】纳斯裸黑管囗红#865哑光丝滑显白不拔干节日礼物</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>NARS THE MULTIPLE TRANCE 8G</t>
+        </is>
+      </c>
+      <c r="D492" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="E492" t="n">
+        <v>79</v>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>415</v>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>NARS娜斯大白饼1.8g持久定妆防水细腻控油粉饼便携</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>NARS THE MULTIPLE HOT TAKE 8G</t>
+        </is>
+      </c>
+      <c r="D493" t="n">
+        <v>43</v>
+      </c>
+      <c r="E493" t="n">
+        <v>35</v>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>415</v>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>【NARS】娜斯新品柔滑多功能棒腮红棒眼颊唇三用swing,sex appeal 8g</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>NARS THE MULTIPLE HOT TAKE 8G</t>
+        </is>
+      </c>
+      <c r="D494" t="n">
+        <v>199</v>
+      </c>
+      <c r="E494" t="n">
+        <v>199</v>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>416</v>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>【正品行货】NARS/纳斯新款腮红盘920sex appeal爱欲沉溺专柜直售</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>NARS THE MULTIPLE SEX APPEAL 8G</t>
+        </is>
+      </c>
+      <c r="D495" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E495" t="n">
+        <v>129</v>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>417</v>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>【2.31万人评价品牌正品】Nars纳斯小粉金液体腮红7ml光感自然#BEHAVE烟粉豆沙</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>NARS AFTER GLOW LIQUID BLUSH -WANDERLUST 7ML</t>
+        </is>
+      </c>
+      <c r="D496" t="n">
+        <v>139</v>
+      </c>
+      <c r="E496" t="n">
+        <v>95</v>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>418</v>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>【6.1万人回购该品牌】Gucci/古驰竹韵女士浓香水75ml花香木质生日礼物简装</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>古驰竹韵浓香75ml</t>
+        </is>
+      </c>
+      <c r="D497" t="n">
+        <v>700</v>
+      </c>
+      <c r="E497" t="n">
+        <v>290.2</v>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>412</v>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>【百补品牌热销36.6万件】GUCCI/古驰炼金士花园系列香水100ml简装正品留香</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>古驰炼金师花园桂之舞香水100ML</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>700.0</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>413</v>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>新色!NARS纳斯新版腮红膨胀色氛围色显嫩细腻4.8g爱欲沉溺慢热</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>NARS AFTERGLOW LIQUID BLUSH - INSATIABLE</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>330.0</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>208.0</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>414</v>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>【NARS】纳斯裸黑管囗红#865哑光丝滑显白不拔干节日礼物</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>NARS THE MULTIPLE TRANCE 8G</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>117.9</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>415</v>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>NARS娜斯大白饼1.8g持久定妆防水细腻控油粉饼便携</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>NARS THE MULTIPLE HOT TAKE 8G</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>43.0</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>415</v>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>【NARS】娜斯新品柔滑多功能棒腮红棒眼颊唇三用swing,sex appeal 8g</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>NARS THE MULTIPLE HOT TAKE 8G</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>199.0</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>199.0</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" t="n">
+        <v>416</v>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>【正品行货】NARS/纳斯新款腮红盘920sex appeal爱欲沉溺专柜直售</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>NARS THE MULTIPLE SEX APPEAL 8G</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>1600.0</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" t="n">
+        <v>417</v>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>【2.31万人评价品牌正品】Nars纳斯小粉金液体腮红7ml光感自然#BEHAVE烟粉豆沙</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>NARS AFTER GLOW LIQUID BLUSH -WANDERLUST 7ML</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="n">
+        <v>418</v>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>【6.1万人回购该品牌】Gucci/古驰竹韵女士浓香水75ml花香木质生日礼物简装</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>古驰竹韵浓香75ml</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>700.0</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>290.2</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="n">
+        <v>419</v>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>【欧莱雅】第三代紫熨斗眼霜玻色因抗皱提拉紧致抗老咖啡因淡化细纹女</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>欧莱雅紫熨斗30ml 第三代</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>33.9</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>20.88</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/商品采集汇总.xlsx
+++ b/商品采集汇总.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G506"/>
+  <dimension ref="A1:G539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15215,62 +15215,50 @@
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>【百补品牌热销36.6万件】GUCCI/古驰炼金士花园系列香水100ml简装正品留香</t>
+          <t>【欧莱雅】第三代紫熨斗眼霜玻色因抗皱提拉紧致抗老咖啡因淡化细纹女</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>古驰炼金师花园桂之舞香水100ML</t>
-        </is>
-      </c>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="E498" t="inlineStr">
-        <is>
-          <t>700.0</t>
-        </is>
+          <t>欧莱雅紫熨斗30ml 第三代</t>
+        </is>
+      </c>
+      <c r="D498" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E498" t="n">
+        <v>20.88</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G498" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>413</v>
+        <v>1</v>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>新色!NARS纳斯新版腮红膨胀色氛围色显嫩细腻4.8g爱欲沉溺慢热</t>
+          <t>CPB/肌肤之钥 御龄防晒霜防晒乳50ml【5天内发货】</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>NARS AFTERGLOW LIQUID BLUSH - INSATIABLE</t>
-        </is>
-      </c>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>330.0</t>
-        </is>
-      </c>
-      <c r="E499" t="inlineStr">
-        <is>
-          <t>208.0</t>
-        </is>
+          <t>CPB防晒霜50g</t>
+        </is>
+      </c>
+      <c r="D499" t="n">
+        <v>981</v>
+      </c>
+      <c r="E499" t="n">
+        <v>981</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -15281,155 +15269,143 @@
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>414</v>
+        <v>1</v>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>【NARS】纳斯裸黑管囗红#865哑光丝滑显白不拔干节日礼物</t>
+          <t>原装正品CPB肌肤之钥御龄防晒霜50ml高倍防晒隔离乳面部防护SPF50【5天内发货】</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>NARS THE MULTIPLE TRANCE 8G</t>
-        </is>
-      </c>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>117.9</t>
-        </is>
-      </c>
-      <c r="E500" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
+          <t>CPB防晒霜50g</t>
+        </is>
+      </c>
+      <c r="D500" t="n">
+        <v>380</v>
+      </c>
+      <c r="E500" t="n">
+        <v>380</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G500" t="inlineStr">
-        <is>
-          <t>2024-07-06</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>415</v>
+        <v>2</v>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>NARS娜斯大白饼1.8g持久定妆防水细腻控油粉饼便携</t>
+          <t>【CPB】肌肤之钥净采洗面奶(滋润型)125ml/支</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>NARS THE MULTIPLE HOT TAKE 8G</t>
-        </is>
-      </c>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>43.0</t>
-        </is>
-      </c>
-      <c r="E501" t="inlineStr">
-        <is>
-          <t>35.0</t>
-        </is>
+          <t>CPB滋润洁面125ml</t>
+        </is>
+      </c>
+      <c r="D501" t="n">
+        <v>289</v>
+      </c>
+      <c r="E501" t="n">
+        <v>152</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G501" t="inlineStr"/>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>415</v>
+        <v>3</v>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>【NARS】娜斯新品柔滑多功能棒腮红棒眼颊唇三用swing,sex appeal 8g</t>
+          <t>【肌肤之钥】CPB长管隔离霜37ml保湿滋润款控油提亮肤色</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>NARS THE MULTIPLE HOT TAKE 8G</t>
-        </is>
-      </c>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>199.0</t>
-        </is>
-      </c>
-      <c r="E502" t="inlineStr">
-        <is>
-          <t>199.0</t>
-        </is>
+          <t>CPB长管隔离38ml 清爽</t>
+        </is>
+      </c>
+      <c r="D502" t="n">
+        <v>225</v>
+      </c>
+      <c r="E502" t="n">
+        <v>165</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G502" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>416</v>
+        <v>4</v>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>【正品行货】NARS/纳斯新款腮红盘920sex appeal爱欲沉溺专柜直售</t>
+          <t>【CPB】肌肤之钥光透妆前乳长管隔离37ml/支</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>NARS THE MULTIPLE SEX APPEAL 8G</t>
-        </is>
-      </c>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>1600.0</t>
-        </is>
-      </c>
-      <c r="E503" t="inlineStr">
-        <is>
-          <t>129.0</t>
-        </is>
+          <t>CPB长管隔离新款37ml滋润</t>
+        </is>
+      </c>
+      <c r="D503" t="n">
+        <v>303</v>
+      </c>
+      <c r="E503" t="n">
+        <v>164.9</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G503" t="inlineStr"/>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>417</v>
+        <v>4</v>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>【2.31万人评价品牌正品】Nars纳斯小粉金液体腮红7ml光感自然#BEHAVE烟粉豆沙</t>
+          <t>【肌肤之钥】CPB长管隔离霜37ml保湿滋润款控油提亮肤色</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>NARS AFTER GLOW LIQUID BLUSH -WANDERLUST 7ML</t>
-        </is>
-      </c>
-      <c r="D504" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
-      <c r="E504" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
+          <t>CPB长管隔离新款37ml滋润</t>
+        </is>
+      </c>
+      <c r="D504" t="n">
+        <v>225</v>
+      </c>
+      <c r="E504" t="n">
+        <v>165</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -15438,33 +15414,29 @@
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-06-01</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>418</v>
+        <v>4</v>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>【6.1万人回购该品牌】Gucci/古驰竹韵女士浓香水75ml花香木质生日礼物简装</t>
+          <t>【肌肤之钥】CPB长管隔离 黑隔离 37ml 妆前乳 提亮肤色</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>古驰竹韵浓香75ml</t>
-        </is>
-      </c>
-      <c r="D505" t="inlineStr">
-        <is>
-          <t>700.0</t>
-        </is>
-      </c>
-      <c r="E505" t="inlineStr">
-        <is>
-          <t>290.2</t>
-        </is>
+          <t>CPB长管隔离新款37ml滋润</t>
+        </is>
+      </c>
+      <c r="D505" t="n">
+        <v>289</v>
+      </c>
+      <c r="E505" t="n">
+        <v>162</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -15473,40 +15445,999 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2025-08-18</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
+        <v>4</v>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>【正品行货】 CPB长管隔离37ml *2光凝润采妆前霜 防晒保湿</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>CPB长管隔离新款37ml滋润</t>
+        </is>
+      </c>
+      <c r="D506" t="n">
+        <v>499</v>
+      </c>
+      <c r="E506" t="n">
+        <v>335</v>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="n">
+        <v>5</v>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>MAC/魅可 尤雾弹口红唇膏#923 暖粉豆沙 哑光雾面显白【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>MAC 子弹头口红 923# STAY CURIOUS</t>
+        </is>
+      </c>
+      <c r="D507" t="n">
+        <v>150</v>
+      </c>
+      <c r="E507" t="n">
+        <v>102.63</v>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="n">
+        <v>5</v>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>【MAC】魅可尤雾弹子弹头唇膏口红925 316 314 923正品显色显白【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>MAC 子弹头口红 923# STAY CURIOUS</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>116</v>
+      </c>
+      <c r="E508" t="n">
+        <v>116</v>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>5</v>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>【MAC】魅可子弹头唇膏哑光滋润316/923显色尤雾弹显白口红正装</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>MAC 子弹头口红 923# STAY CURIOUS</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>199</v>
+      </c>
+      <c r="E509" t="n">
+        <v>199</v>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" t="n">
+        <v>5</v>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>【520礼物】MAC/魅可全新轻尤雾弹子弹头口红唇膏316 314 923 930</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>MAC 子弹头口红 923# STAY CURIOUS</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E510" t="n">
+        <v>148</v>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" t="n">
+        <v>5</v>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>【MAC】魅可口红哑光602/707/923/916泫雅色柔雾子弹头素颜口红送礼盒【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>MAC 子弹头口红 923# STAY CURIOUS</t>
+        </is>
+      </c>
+      <c r="D511" t="n">
+        <v>88</v>
+      </c>
+      <c r="E511" t="n">
+        <v>88</v>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>5</v>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>MAC/魅可子弹头口红哑光小辣椒显白橘红色#316#923#925#666【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>MAC 子弹头口红 923# STAY CURIOUS</t>
+        </is>
+      </c>
+      <c r="D512" t="n">
+        <v>398</v>
+      </c>
+      <c r="E512" t="n">
+        <v>398</v>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" t="n">
+        <v>6</v>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>【520情人节】MAC/魅可热吻棒唇膏口红显色哑光滋润不掉色67/69</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>MAC热吻棒67</t>
+        </is>
+      </c>
+      <c r="D513" t="n">
+        <v>81</v>
+      </c>
+      <c r="E513" t="n">
+        <v>81</v>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>2024-12-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>7</v>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>MAC/魅可 新品紫白饼粉饼7g 绝绝紫双色去黄提亮柔焦控油【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>MAC紫白饼</t>
+        </is>
+      </c>
+      <c r="D514" t="n">
+        <v>214</v>
+      </c>
+      <c r="E514" t="n">
+        <v>131</v>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>7</v>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>【MAC】魅可新品紫白饼粉饼双色去黄提亮柔焦控油轻薄【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>MAC紫白饼</t>
+        </is>
+      </c>
+      <c r="D515" t="n">
+        <v>143</v>
+      </c>
+      <c r="E515" t="n">
+        <v>143</v>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>8</v>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>MIUMIU缪缪同名女士香水EDP50ml</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>MiuMiu粉漾女士淡香氛50ml</t>
+        </is>
+      </c>
+      <c r="D516" t="n">
+        <v>588</v>
+      </c>
+      <c r="E516" t="n">
+        <v>438</v>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>8</v>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>缪缪(MiuMiu) 同名女士香水 莹铃滢蓝粉漾幻境游转【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>MiuMiu粉漾女士淡香氛50ml</t>
+        </is>
+      </c>
+      <c r="D517" t="n">
+        <v>355</v>
+      </c>
+      <c r="E517" t="n">
+        <v>355</v>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>8</v>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>正品Miu Miu缪缪同名游转幻境粉黛Twist黑盖五代女士浓香水简装【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>MiuMiu粉漾女士淡香氛50ml</t>
+        </is>
+      </c>
+      <c r="D518" t="n">
         <v>419</v>
       </c>
-      <c r="B506" t="inlineStr">
-        <is>
-          <t>【欧莱雅】第三代紫熨斗眼霜玻色因抗皱提拉紧致抗老咖啡因淡化细纹女</t>
-        </is>
-      </c>
-      <c r="C506" t="inlineStr">
-        <is>
-          <t>欧莱雅紫熨斗30ml 第三代</t>
-        </is>
-      </c>
-      <c r="D506" t="inlineStr">
-        <is>
-          <t>33.9</t>
-        </is>
-      </c>
-      <c r="E506" t="inlineStr">
-        <is>
-          <t>20.88</t>
-        </is>
-      </c>
-      <c r="F506" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G506" t="inlineStr"/>
+      <c r="E518" t="n">
+        <v>419</v>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>8</v>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>【MIU MIU】缪缪女士玫瑰之水粉漾EDT淡香水100ml花香调</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>MiuMiu粉漾女士淡香氛50ml</t>
+        </is>
+      </c>
+      <c r="D519" t="n">
+        <v>650</v>
+      </c>
+      <c r="E519" t="n">
+        <v>533</v>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>9</v>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>MIUMIU缪缪同名女士香水EDP50ml</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>MiuMiu紅蓋同名女士濃香水50ml</t>
+        </is>
+      </c>
+      <c r="D520" t="n">
+        <v>588</v>
+      </c>
+      <c r="E520" t="n">
+        <v>438</v>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>9</v>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>【MIU MIU】 缪缪同名女士香水100ml红盖EDP</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>MiuMiu紅蓋同名女士濃香水50ml</t>
+        </is>
+      </c>
+      <c r="D521" t="n">
+        <v>699</v>
+      </c>
+      <c r="E521" t="n">
+        <v>699</v>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>9</v>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>正品Miu Miu缪缪 经典同名 女士淡香精浓香水EDP一代 简装 意大利【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>MiuMiu紅蓋同名女士濃香水50ml</t>
+        </is>
+      </c>
+      <c r="D522" t="n">
+        <v>448</v>
+      </c>
+      <c r="E522" t="n">
+        <v>433</v>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>9</v>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>缪缪(MiuMiu) 同名女士香水 莹铃滢蓝粉漾幻境游转【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>MiuMiu紅蓋同名女士濃香水50ml</t>
+        </is>
+      </c>
+      <c r="D523" t="n">
+        <v>355</v>
+      </c>
+      <c r="E523" t="n">
+        <v>355</v>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>10</v>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>【NARS】超方瓶流光美肌粉底液#L2持妆水润30ml</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>NARS 超方瓶-L2</t>
+        </is>
+      </c>
+      <c r="D524" t="n">
+        <v>319</v>
+      </c>
+      <c r="E524" t="n">
+        <v>180</v>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>11</v>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>【NARS】流光美肌粉底液 L4超方瓶DEAUVILLE 黄1.5白 健康小麦色 30ml</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>NARS超方瓶粉底液L4</t>
+        </is>
+      </c>
+      <c r="D525" t="n">
+        <v>319</v>
+      </c>
+      <c r="E525" t="n">
+        <v>236</v>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>12</v>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>【NARS】纳斯/娜斯超方瓶粉底液L0/L1/L2持妆遮瑕30ml</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>NARS 超方瓶粉底液 L3#</t>
+        </is>
+      </c>
+      <c r="D526" t="n">
+        <v>289</v>
+      </c>
+      <c r="E526" t="n">
+        <v>169.5</v>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>12</v>
+      </c>
+      <c r="B527" t="inlineStr"/>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>NARS 超方瓶粉底液 L3#</t>
+        </is>
+      </c>
+      <c r="D527" t="n">
+        <v>201.5</v>
+      </c>
+      <c r="E527" t="n">
+        <v>201.5</v>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>12</v>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>【原装正品】NARS/娜斯超方瓶流光美肌粉底液#L3持妆遮瑕不暗沉【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>NARS 超方瓶粉底液 L3#</t>
+        </is>
+      </c>
+      <c r="D528" t="n">
+        <v>220</v>
+      </c>
+      <c r="E528" t="n">
+        <v>220</v>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" t="n">
+        <v>13</v>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>【NARS】纳斯/娜斯超方瓶粉底液L0/L1/L2持妆遮瑕30ml</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>NARS 超方瓶粉底液#L1</t>
+        </is>
+      </c>
+      <c r="D529" t="n">
+        <v>289</v>
+      </c>
+      <c r="E529" t="n">
+        <v>169.5</v>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" t="n">
+        <v>13</v>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>【NARS】超方瓶流光美肌粉底液L1 30ml保湿滋润持久遮瑕</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>NARS 超方瓶粉底液#L1</t>
+        </is>
+      </c>
+      <c r="D530" t="n">
+        <v>240</v>
+      </c>
+      <c r="E530" t="n">
+        <v>164</v>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="n">
+        <v>14</v>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>【NARS】纳斯/娜斯超方瓶粉底液L0/L1/L2持妆遮瑕30ml</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>NARS 粉底液 LO色</t>
+        </is>
+      </c>
+      <c r="D531" t="n">
+        <v>289</v>
+      </c>
+      <c r="E531" t="n">
+        <v>169.5</v>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" t="n">
+        <v>15</v>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>【原装正品】NARS纳斯新版定妆散粉控油定妆持久隐形毛孔提亮11g</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>NARS纳斯定妆散粉</t>
+        </is>
+      </c>
+      <c r="D532" t="n">
+        <v>206</v>
+      </c>
+      <c r="E532" t="n">
+        <v>142.15</v>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="n">
+        <v>15</v>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>【NARS】纳斯流光美肌轻透持久定妆散粉新版11g</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>NARS纳斯定妆散粉</t>
+        </is>
+      </c>
+      <c r="D533" t="n">
+        <v>245</v>
+      </c>
+      <c r="E533" t="n">
+        <v>168.1</v>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>15</v>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>【NARS】纳斯流光美肌轻透持久定妆散粉新版11g 提亮肤色【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>NARS纳斯定妆散粉</t>
+        </is>
+      </c>
+      <c r="D534" t="n">
+        <v>199</v>
+      </c>
+      <c r="E534" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>15</v>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>【NARS】娜斯新版定妆大白散粉11g持久定妆</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>NARS纳斯定妆散粉</t>
+        </is>
+      </c>
+      <c r="D535" t="n">
+        <v>229</v>
+      </c>
+      <c r="E535" t="n">
+        <v>146</v>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>16</v>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>【正品行货】NARS超方瓶超雾瓶粉底持妆控油油皮柔雾遮瑕自然服帖</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>NARS 柔哑净瑕持妆粉底液45ml L3 GOBI</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>248.0</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>248.0</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>16</v>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>【NARS】纳斯超方瓶持妆粉底液流光美肌养肤遮瑕持久不脱妆干皮女L1L2</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>NARS 柔哑净瑕持妆粉底液45ml L3 GOBI</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>198.0</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>16</v>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>NARS/娜斯超方瓶持妆粉底液#L2#L0#L1#L1.25#L3细腻服帖遮瑕30ML【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>NARS 柔哑净瑕持妆粉底液45ml L3 GOBI</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>199.0</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>199.0</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>16</v>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>【现货正品】NARS超方瓶粉底液 轻薄润贴持妆不卡粉遮瑕混干皮</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>NARS 柔哑净瑕持妆粉底液45ml L3 GOBI</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>245.0</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>235.0</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/商品采集汇总.xlsx
+++ b/商品采集汇总.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G539"/>
+  <dimension ref="A1:G572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16325,15 +16325,11 @@
           <t>NARS 柔哑净瑕持妆粉底液45ml L3 GOBI</t>
         </is>
       </c>
-      <c r="D536" t="inlineStr">
-        <is>
-          <t>248.0</t>
-        </is>
-      </c>
-      <c r="E536" t="inlineStr">
-        <is>
-          <t>248.0</t>
-        </is>
+      <c r="D536" t="n">
+        <v>248</v>
+      </c>
+      <c r="E536" t="n">
+        <v>248</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -16360,15 +16356,11 @@
           <t>NARS 柔哑净瑕持妆粉底液45ml L3 GOBI</t>
         </is>
       </c>
-      <c r="D537" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="E537" t="inlineStr">
-        <is>
-          <t>198.0</t>
-        </is>
+      <c r="D537" t="n">
+        <v>300</v>
+      </c>
+      <c r="E537" t="n">
+        <v>198</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -16391,15 +16383,11 @@
           <t>NARS 柔哑净瑕持妆粉底液45ml L3 GOBI</t>
         </is>
       </c>
-      <c r="D538" t="inlineStr">
-        <is>
-          <t>199.0</t>
-        </is>
-      </c>
-      <c r="E538" t="inlineStr">
-        <is>
-          <t>199.0</t>
-        </is>
+      <c r="D538" t="n">
+        <v>199</v>
+      </c>
+      <c r="E538" t="n">
+        <v>199</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -16422,15 +16410,11 @@
           <t>NARS 柔哑净瑕持妆粉底液45ml L3 GOBI</t>
         </is>
       </c>
-      <c r="D539" t="inlineStr">
-        <is>
-          <t>245.0</t>
-        </is>
-      </c>
-      <c r="E539" t="inlineStr">
-        <is>
-          <t>235.0</t>
-        </is>
+      <c r="D539" t="n">
+        <v>245</v>
+      </c>
+      <c r="E539" t="n">
+        <v>235</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -16438,6 +16422,941 @@
         </is>
       </c>
       <c r="G539" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>18</v>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>【原装正品】Nars/娜斯光透感蜜粉5894大白粉饼10g正品【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>NARS5894蜜粉饼10G</t>
+        </is>
+      </c>
+      <c r="D540" t="n">
+        <v>148</v>
+      </c>
+      <c r="E540" t="n">
+        <v>148</v>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" t="n">
+        <v>19</v>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>【NARS】娜斯纳斯空气唇釉空气柔雾唇霜唇釉Gipsy#684玫瑰豆沙色口红</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>NARS空气唇釉686 lose control</t>
+        </is>
+      </c>
+      <c r="D541" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="E541" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" t="n">
+        <v>19</v>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>【NARS】娜斯纳斯空气唇釉空气柔雾唇霜唇釉Gipsy#684玫瑰豆沙色口红</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>NARS空气唇釉686 lose control</t>
+        </is>
+      </c>
+      <c r="D542" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="E542" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>21</v>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>【特价清仓】NARS纳斯口红细管哑光唇膏101#No Angel奶咖土棕1.5g</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>NARS细管101 NO ANGEL</t>
+        </is>
+      </c>
+      <c r="D543" t="n">
+        <v>148</v>
+      </c>
+      <c r="E543" t="n">
+        <v>79.86</v>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" t="n">
+        <v>17</v>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>原装正品NARS娜斯遮瑕蜜#1232Vanilla香草粉遮斑点痘印遮瑕膏6ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>NARS 遮瑕膏 VANILLA色号</t>
+        </is>
+      </c>
+      <c r="D544" t="n">
+        <v>128</v>
+      </c>
+      <c r="E544" t="n">
+        <v>128</v>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" t="n">
+        <v>18</v>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>NARS/纳斯蜜粉饼定妆修容高光散粉提亮持久遮瑕裸光【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>NARS5894蜜粉饼10G</t>
+        </is>
+      </c>
+      <c r="D545" t="n">
+        <v>222</v>
+      </c>
+      <c r="E545" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="n">
+        <v>18</v>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>【NARS】娜斯 流光美肌轻透蜜粉饼5894大白饼粉饼10g【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>NARS5894蜜粉饼10G</t>
+        </is>
+      </c>
+      <c r="D546" t="n">
+        <v>220</v>
+      </c>
+      <c r="E546" t="n">
+        <v>220</v>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="n">
+        <v>18</v>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>NARS/娜斯5894大白饼粉饼控油持妆蜜粉饼10g【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>NARS5894蜜粉饼10G</t>
+        </is>
+      </c>
+      <c r="D547" t="n">
+        <v>260</v>
+      </c>
+      <c r="E547" t="n">
+        <v>145</v>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="n">
+        <v>18</v>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>【原装正品】Nars/娜斯光透感蜜粉5894大白粉饼10g正品【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>NARS5894蜜粉饼10G</t>
+        </is>
+      </c>
+      <c r="D548" t="n">
+        <v>160</v>
+      </c>
+      <c r="E548" t="n">
+        <v>160</v>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" t="n">
+        <v>18</v>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>【NARS】娜斯流光美肌轻透蜜粉饼#5894大白粉饼10g细腻遮瑕含原装粉扑【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>NARS5894蜜粉饼10G</t>
+        </is>
+      </c>
+      <c r="D549" t="n">
+        <v>199</v>
+      </c>
+      <c r="E549" t="n">
+        <v>145</v>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" t="n">
+        <v>53</v>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>【YSL】圣罗兰粉皮革气垫 明彩粉光轻垫粉底液气 垫 保湿持久遮瑕</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰皮气垫新明彩亮润轻垫粉底液 #B20</t>
+        </is>
+      </c>
+      <c r="D550" t="n">
+        <v>470</v>
+      </c>
+      <c r="E550" t="n">
+        <v>352</v>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" t="n">
+        <v>53</v>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>【YSL】圣罗兰明彩轻垫粉底液B20 5g 皮气垫 遮瑕提亮 轻薄持妆</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰皮气垫新明彩亮润轻垫粉底液 #B20</t>
+        </is>
+      </c>
+      <c r="D551" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="E551" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr"/>
+    </row>
+    <row r="552">
+      <c r="A552" t="n">
+        <v>53</v>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>YSL/圣罗兰黑皮革气垫5g#B20新明彩轻垫粉底液遮瑕</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰皮气垫新明彩亮润轻垫粉底液 #B20</t>
+        </is>
+      </c>
+      <c r="D552" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="E552" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr"/>
+    </row>
+    <row r="553">
+      <c r="A553" t="n">
+        <v>53</v>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>【正品行货】圣罗兰新明彩轻垫粉底液 20 SPF35 遮瑕轻薄透气正装</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰皮气垫新明彩亮润轻垫粉底液 #B20</t>
+        </is>
+      </c>
+      <c r="D553" t="n">
+        <v>289</v>
+      </c>
+      <c r="E553" t="n">
+        <v>289</v>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr"/>
+    </row>
+    <row r="554">
+      <c r="A554" t="n">
+        <v>53</v>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰新明彩柔雾B20轻气垫5g持久不脱妆服帖细腻</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰皮气垫新明彩亮润轻垫粉底液 #B20</t>
+        </is>
+      </c>
+      <c r="D554" t="n">
+        <v>149</v>
+      </c>
+      <c r="E554" t="n">
+        <v>148</v>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>53</v>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>【正品行货】圣罗兰新明彩柔雾轻垫粉底液B20 14g皮气垫混油挚爱</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰皮气垫新明彩亮润轻垫粉底液 #B20</t>
+        </is>
+      </c>
+      <c r="D555" t="n">
+        <v>309</v>
+      </c>
+      <c r="E555" t="n">
+        <v>309</v>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>20</v>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>【特价清仓】NARS纳斯唇釉空气柔雾唇霜352#Thrust 奶咖玫瑰7.5ml</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>NARS空气唇釉thrust</t>
+        </is>
+      </c>
+      <c r="D556" t="n">
+        <v>179</v>
+      </c>
+      <c r="E556" t="n">
+        <v>99</v>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>20</v>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>【NARS】NARS娜斯空气唇釉#037 #361 #360 #684 7.5ml/支</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>NARS空气唇釉thrust</t>
+        </is>
+      </c>
+      <c r="D557" t="n">
+        <v>210</v>
+      </c>
+      <c r="E557" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>19</v>
+      </c>
+      <c r="B558" t="inlineStr"/>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>NARS空气唇釉686 lose control</t>
+        </is>
+      </c>
+      <c r="D558" t="n">
+        <v>129</v>
+      </c>
+      <c r="E558" t="n">
+        <v>129</v>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="n">
+        <v>19</v>
+      </c>
+      <c r="B559" t="inlineStr"/>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>NARS空气唇釉686 lose control</t>
+        </is>
+      </c>
+      <c r="D559" t="n">
+        <v>89</v>
+      </c>
+      <c r="E559" t="n">
+        <v>89</v>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>19</v>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>【NARS】娜斯纳斯空气唇釉空气柔雾唇霜唇釉Gipsy#684玫瑰豆沙色口红</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>NARS空气唇釉686 lose control</t>
+        </is>
+      </c>
+      <c r="D560" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="E560" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>21</v>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>【特价清仓】NARS纳斯口红细管哑光唇膏101#No Angel奶咖土棕1.5g</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>NARS细管101 NO ANGEL</t>
+        </is>
+      </c>
+      <c r="D561" t="n">
+        <v>178</v>
+      </c>
+      <c r="E561" t="n">
+        <v>99</v>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>21</v>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>【NARS】NARS娜斯细管口红#102 #116  #135 #133 #1011.5g/支</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>NARS细管101 NO ANGEL</t>
+        </is>
+      </c>
+      <c r="D562" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="E562" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>2023-03-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>22</v>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>【特价清仓】NARS纳斯细管口红哑光唇膏1.5g#116烟杏START ME UP</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>NARS细管116 START ME UP</t>
+        </is>
+      </c>
+      <c r="D563" t="n">
+        <v>188</v>
+      </c>
+      <c r="E563" t="n">
+        <v>108.96</v>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>22</v>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>【NARS】NARS娜斯细管口红#102 #116  #135 #133 #1011.5g/支</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>NARS细管116 START ME UP</t>
+        </is>
+      </c>
+      <c r="D564" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="E564" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>2023-03-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="n">
+        <v>23</v>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>【特价清仓】NARS纳斯细管口红#133日烧赤粽TOO HOT TO HOLD 1.5g</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>NARS细管133 TOO HOT TO HOLD</t>
+        </is>
+      </c>
+      <c r="D565" t="n">
+        <v>148</v>
+      </c>
+      <c r="E565" t="n">
+        <v>79.86</v>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>24</v>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Nature BOBO/漾然澳洲番木瓜膏16g*3瓶润唇膏保湿女唇膜霜油</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Nature BOBO澳洲木瓜膏唇膜润唇1</t>
+        </is>
+      </c>
+      <c r="D566" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="E566" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>24</v>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Nature BOBO/澳洲番木瓜膏16g*5瓶润唇膏保湿女唇膜霜油</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Nature BOBO澳洲木瓜膏唇膜润唇1</t>
+        </is>
+      </c>
+      <c r="D567" t="n">
+        <v>59</v>
+      </c>
+      <c r="E567" t="n">
+        <v>59</v>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" t="n">
+        <v>25</v>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Nature BOBO澳洲原装进口番木瓜膏创伤湿疹膏孕妇婴儿修复唇部</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Nature BOBO澳洲木瓜膏唇膜润唇2</t>
+        </is>
+      </c>
+      <c r="D568" t="n">
+        <v>26</v>
+      </c>
+      <c r="E568" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" t="n">
+        <v>25</v>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Nature BOBO/澳洲番木瓜膏16g*5瓶润唇膏保湿女唇膜霜油</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Nature BOBO澳洲木瓜膏唇膜润唇2</t>
+        </is>
+      </c>
+      <c r="D569" t="n">
+        <v>59</v>
+      </c>
+      <c r="E569" t="n">
+        <v>59</v>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>25</v>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Nature BOBO/漾然澳洲番木瓜膏16g*1瓶润唇膏保湿女唇膜霜油</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Nature BOBO澳洲木瓜膏唇膜润唇2</t>
+        </is>
+      </c>
+      <c r="D570" t="n">
+        <v>28.69</v>
+      </c>
+      <c r="E570" t="n">
+        <v>19</v>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>26</v>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>【正品行货】SKII男士神仙水精华露护肤补水紧致抗皱晶透保湿舒缓</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>SK2 神仙水230ml</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>1245.0</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>847.0</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>2025-01-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="n">
+        <v>26</v>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>SKII/SK2/skll男士神仙水精华露控油爽肤水230ml控油收毛孔正品</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>SK2 神仙水230ml</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>968.0</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>2025-01-16</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/商品采集汇总.xlsx
+++ b/商品采集汇总.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G572"/>
+  <dimension ref="A1:G587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17302,15 +17302,11 @@
           <t>SK2 神仙水230ml</t>
         </is>
       </c>
-      <c r="D571" t="inlineStr">
-        <is>
-          <t>1245.0</t>
-        </is>
-      </c>
-      <c r="E571" t="inlineStr">
-        <is>
-          <t>847.0</t>
-        </is>
+      <c r="D571" t="n">
+        <v>1245</v>
+      </c>
+      <c r="E571" t="n">
+        <v>847</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -17337,15 +17333,11 @@
           <t>SK2 神仙水230ml</t>
         </is>
       </c>
-      <c r="D572" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
-      <c r="E572" t="inlineStr">
-        <is>
-          <t>968.0</t>
-        </is>
+      <c r="D572" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E572" t="n">
+        <v>968</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -17355,6 +17347,467 @@
       <c r="G572" t="inlineStr">
         <is>
           <t>2025-01-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="n">
+        <v>27</v>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II赋能焕彩精华霜100g全新大红瓶滋润紧致保湿sk2</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>SK2大红瓶滋润面霜100g</t>
+        </is>
+      </c>
+      <c r="D573" t="n">
+        <v>1380</v>
+      </c>
+      <c r="E573" t="n">
+        <v>858</v>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="n">
+        <v>28</v>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>【SK-II】神仙水330ml抗皱精华液sk2化妆品护肤品水乳生日礼物女</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>SK2神仙水330ML</t>
+        </is>
+      </c>
+      <c r="D574" t="n">
+        <v>1098</v>
+      </c>
+      <c r="E574" t="n">
+        <v>1086</v>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="n">
+        <v>29</v>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>SK-Ⅱ男士保湿焕活洁面霜120g</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>SK-II 男士保湿焕活洁面霜120g</t>
+        </is>
+      </c>
+      <c r="D575" t="n">
+        <v>319</v>
+      </c>
+      <c r="E575" t="n">
+        <v>319</v>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>29</v>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>【专柜行货】SKII男士保湿焕活洁面霜 120g氨基酸洗面奶</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>SK-II 男士保湿焕活洁面霜120g</t>
+        </is>
+      </c>
+      <c r="D576" t="n">
+        <v>500</v>
+      </c>
+      <c r="E576" t="n">
+        <v>500</v>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr"/>
+    </row>
+    <row r="577">
+      <c r="A577" t="n">
+        <v>29</v>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II男士焕活保湿洁面霜120g</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>SK-II 男士保湿焕活洁面霜120g</t>
+        </is>
+      </c>
+      <c r="D577" t="n">
+        <v>560</v>
+      </c>
+      <c r="E577" t="n">
+        <v>420</v>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>30</v>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>SK-II/SK2 男士神仙水焕活护肤精华露 230ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>SK-II 男士焕活护肤精华露 230ml</t>
+        </is>
+      </c>
+      <c r="D578" t="n">
+        <v>798</v>
+      </c>
+      <c r="E578" t="n">
+        <v>798</v>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>30</v>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>【SK-II】 男士焕活护肤精华露230ml 保湿补水 提亮肌肤【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>SK-II 男士焕活护肤精华露 230ml</t>
+        </is>
+      </c>
+      <c r="D579" t="n">
+        <v>900</v>
+      </c>
+      <c r="E579" t="n">
+        <v>900</v>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>31</v>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>【正品行货】SKII小银瓶肌因光蕴淡斑精华露50ml提亮淡斑淡痘印</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>SK-II 小银瓶淡斑精华露75ml</t>
+        </is>
+      </c>
+      <c r="D580" t="n">
+        <v>1530</v>
+      </c>
+      <c r="E580" t="n">
+        <v>782</v>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>31</v>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>【SK-II】SK2小银瓶淡斑精华液美白提亮肌因光蕴祛斑精华露50ml正品</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>SK-II 小银瓶淡斑精华露75ml</t>
+        </is>
+      </c>
+      <c r="D581" t="n">
+        <v>1688</v>
+      </c>
+      <c r="E581" t="n">
+        <v>958</v>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>31</v>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>【SK-II】小银瓶面部精华露50ml 肌因光蕴美白提亮祛斑淡痘印【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>SK-II 小银瓶淡斑精华露75ml</t>
+        </is>
+      </c>
+      <c r="D582" t="n">
+        <v>898</v>
+      </c>
+      <c r="E582" t="n">
+        <v>898</v>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>31</v>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>【新年礼物】SK-II小银瓶精华液肌因光蕴情人节保湿补水淡斑送礼</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>SK-II 小银瓶淡斑精华露75ml</t>
+        </is>
+      </c>
+      <c r="D583" t="n">
+        <v>2290</v>
+      </c>
+      <c r="E583" t="n">
+        <v>2290</v>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="n">
+        <v>32</v>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>【正品行货】SKII小银瓶肌因光蕴淡斑精华露50ml提亮淡斑淡痘印</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>SK-II 小银瓶淡斑精华露75ml</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>1530.0</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>782.0</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="n">
+        <v>32</v>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>【SK-II】SK2小银瓶淡斑精华液美白提亮肌因光蕴祛斑精华露50ml正品</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>SK-II 小银瓶淡斑精华露75ml</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>1688.0</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>958.0</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>32</v>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>【SK-II】小银瓶面部精华露50ml 肌因光蕴美白提亮祛斑淡痘印【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>SK-II 小银瓶淡斑精华露75ml</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>898.0</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>898.0</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr"/>
+    </row>
+    <row r="587">
+      <c r="A587" t="n">
+        <v>32</v>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>【新年礼物】SK-II小银瓶精华液肌因光蕴情人节保湿补水淡斑送礼</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>SK-II 小银瓶淡斑精华露75ml</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>2290.0</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>2290.0</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
         </is>
       </c>
     </row>

--- a/商品采集汇总.xlsx
+++ b/商品采集汇总.xlsx
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I536"/>
+  <dimension ref="A1:I541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -16525,63 +16525,61 @@
     </row>
     <row r="435">
       <c r="A435" s="2" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
-          <t>【Murad】慕拉得a醇面部精华30ml视黄醇紧致抗初老提亮肤色A醇抗氧化</t>
+          <t>【1.2万人回购该品牌】马丁梅森马吉拉慵懒周末100ml 持久留香</t>
         </is>
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>慕拉得塑颜修复A醇精华30ml</t>
+          <t>马丁马吉拉-慵懒周末100ml</t>
         </is>
       </c>
       <c r="D435" s="2" t="inlineStr"/>
-      <c r="E435" s="2" t="n">
-        <v>469</v>
-      </c>
+      <c r="E435" s="2" t="inlineStr"/>
       <c r="F435" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G435" s="2" t="inlineStr"/>
+      <c r="G435" s="2" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
       <c r="H435" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I435" s="2" t="inlineStr">
-        <is>
-          <t>品名相似不足(ratio=33.3%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I435" s="2" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n">
-        <v>177</v>
-      </c>
-      <c r="B436" s="2" t="inlineStr"/>
+        <v>176</v>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
+          <t>【Murad】慕拉得a醇面部精华30ml视黄醇紧致抗初老提亮肤色A醇抗氧化</t>
+        </is>
+      </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>欧珑赤霞橘光护手霜30ML</t>
+          <t>慕拉得塑颜修复A醇精华30ml</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr"/>
       <c r="E436" s="2" t="n">
-        <v>75</v>
+        <v>469</v>
       </c>
       <c r="F436" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G436" s="2" t="inlineStr">
-        <is>
-          <t>2024-06-01</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="inlineStr"/>
       <c r="H436" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -16589,7 +16587,7 @@
       </c>
       <c r="I436" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>品名相似不足(ratio=33.3%)</t>
         </is>
       </c>
     </row>
@@ -16597,11 +16595,7 @@
       <c r="A437" s="2" t="n">
         <v>177</v>
       </c>
-      <c r="B437" s="2" t="inlineStr">
-        <is>
-          <t>【欧珑】莹润护手霜赤霞橘光无极乌龙30ml两款可选择持久留香清新体验</t>
-        </is>
-      </c>
+      <c r="B437" s="2" t="inlineStr"/>
       <c r="C437" s="2" t="inlineStr">
         <is>
           <t>欧珑赤霞橘光护手霜30ML</t>
@@ -16609,45 +16603,51 @@
       </c>
       <c r="D437" s="2" t="inlineStr"/>
       <c r="E437" s="2" t="n">
-        <v>68.67</v>
+        <v>75</v>
       </c>
       <c r="F437" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G437" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G437" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
       <c r="H437" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I437" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I437" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n">
-        <v>178</v>
-      </c>
-      <c r="B438" s="2" t="inlineStr"/>
+        <v>177</v>
+      </c>
+      <c r="B438" s="2" t="inlineStr">
+        <is>
+          <t>大牌清仓欧珑无极莹润身体乳滋润保湿香体留香持久可做护手霜15ml</t>
+        </is>
+      </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精  赤霞橘光 100ML</t>
+          <t>欧珑赤霞橘光护手霜30ML</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr"/>
-      <c r="E438" s="2" t="n">
-        <v>521</v>
-      </c>
+      <c r="E438" s="2" t="inlineStr"/>
       <c r="F438" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G438" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G438" s="2" t="inlineStr"/>
       <c r="H438" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -16655,69 +16655,65 @@
       </c>
       <c r="I438" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>规格不匹配；品名相似不足(ratio=42.9%)</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n">
-        <v>179</v>
-      </c>
-      <c r="B439" s="2" t="inlineStr"/>
+        <v>177</v>
+      </c>
+      <c r="B439" s="2" t="inlineStr">
+        <is>
+          <t>【欧珑】莹润护手霜赤霞橘光无极乌龙30ml两款可选择持久留香清新体验</t>
+        </is>
+      </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精  无极乌龙 100ML</t>
+          <t>欧珑赤霞橘光护手霜30ML</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr"/>
       <c r="E439" s="2" t="n">
-        <v>236</v>
+        <v>68.67</v>
       </c>
       <c r="F439" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G439" s="2" t="inlineStr">
-        <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
+      <c r="G439" s="2" t="inlineStr"/>
       <c r="H439" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I439" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I439" s="2" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n">
-        <v>179</v>
-      </c>
-      <c r="B440" s="2" t="inlineStr">
-        <is>
-          <t>【欧珑】淡香精9ml 赤霞橘光无极乌龙浓香水EDP持久留香Q版 带喷头</t>
-        </is>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="B440" s="2" t="inlineStr"/>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精  无极乌龙 100ML</t>
+          <t>欧珑淡香精  赤霞橘光 100ML</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr"/>
       <c r="E440" s="2" t="n">
-        <v>82.40000000000001</v>
+        <v>521</v>
       </c>
       <c r="F440" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G440" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G440" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
       <c r="H440" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -16725,7 +16721,7 @@
       </c>
       <c r="I440" s="2" t="inlineStr">
         <is>
-          <t>规格不匹配</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
@@ -16733,11 +16729,7 @@
       <c r="A441" s="2" t="n">
         <v>179</v>
       </c>
-      <c r="B441" s="2" t="inlineStr">
-        <is>
-          <t>【欧珑】无极乌龙香水赤霞橘光香氛持久生日礼物中性香</t>
-        </is>
-      </c>
+      <c r="B441" s="2" t="inlineStr"/>
       <c r="C441" s="2" t="inlineStr">
         <is>
           <t>欧珑淡香精  无极乌龙 100ML</t>
@@ -16745,7 +16737,7 @@
       </c>
       <c r="D441" s="2" t="inlineStr"/>
       <c r="E441" s="2" t="n">
-        <v>350</v>
+        <v>236</v>
       </c>
       <c r="F441" s="2" t="inlineStr">
         <is>
@@ -16754,7 +16746,7 @@
       </c>
       <c r="G441" s="2" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H441" s="2" t="inlineStr">
@@ -16764,93 +16756,101 @@
       </c>
       <c r="I441" s="2" t="inlineStr">
         <is>
-          <t>规格不匹配</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B442" s="2" t="inlineStr">
         <is>
-          <t>【Atelier Cologne】欧珑淡香水赤霞橘光30ml持久留香</t>
+          <t>【欧珑】淡香精9ml 赤霞橘光无极乌龙浓香水EDP持久留香Q版 带喷头</t>
         </is>
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 赤霞橘光 30ML</t>
+          <t>欧珑淡香精  无极乌龙 100ML</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr"/>
       <c r="E442" s="2" t="n">
-        <v>285</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F442" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G442" s="2" t="inlineStr">
-        <is>
-          <t>2023-11-01</t>
-        </is>
-      </c>
+      <c r="G442" s="2" t="inlineStr"/>
       <c r="H442" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I442" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I442" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B443" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】欧珑情柚独钟30ml香氛持久留香礼物送女友赠礼</t>
+          <t>【欧珑】无极乌龙香水赤霞橘光香氛持久生日礼物中性香</t>
         </is>
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 情柚独钟 30ML</t>
+          <t>欧珑淡香精  无极乌龙 100ML</t>
         </is>
       </c>
       <c r="D443" s="2" t="inlineStr"/>
       <c r="E443" s="2" t="n">
-        <v>399</v>
+        <v>350</v>
       </c>
       <c r="F443" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G443" s="2" t="inlineStr"/>
+      <c r="G443" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
       <c r="H443" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I443" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I443" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B444" s="2" t="inlineStr">
         <is>
-          <t>咕噜噜、丁香瓜马上拼</t>
+          <t>【Atelier Cologne】欧珑淡香水赤霞橘光30ml持久留香</t>
         </is>
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 无极乌龙 30ML</t>
+          <t>欧珑淡香精 赤霞橘光 30ML</t>
         </is>
       </c>
       <c r="D444" s="2" t="inlineStr"/>
       <c r="E444" s="2" t="n">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="F444" s="2" t="inlineStr">
         <is>
@@ -16859,48 +16859,38 @@
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I444" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I444" s="2" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B445" s="2" t="inlineStr">
         <is>
-          <t>【Atelier Cologne】欧珑淡香水无极乌龙30ml持久留香</t>
+          <t>【正品行货】欧珑赤霞橘光无极乌龙情柚独钟30ml香水高级感</t>
         </is>
       </c>
       <c r="C445" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 无极乌龙 30ML</t>
+          <t>欧珑淡香精 情柚独钟 30ML</t>
         </is>
       </c>
       <c r="D445" s="2" t="inlineStr"/>
-      <c r="E445" s="2" t="n">
-        <v>258</v>
-      </c>
+      <c r="E445" s="2" t="inlineStr"/>
       <c r="F445" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G445" s="2" t="inlineStr">
-        <is>
-          <t>2023-02-01</t>
-        </is>
-      </c>
+      <c r="G445" s="2" t="inlineStr"/>
       <c r="H445" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -16910,56 +16900,52 @@
     </row>
     <row r="446">
       <c r="A446" s="2" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B446" s="2" t="inlineStr">
         <is>
-          <t>不支持7天无理由退换</t>
+          <t>【正品行货】欧珑情柚独钟30ml香氛持久留香礼物送女友赠礼</t>
         </is>
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 无极乌龙 30ML</t>
+          <t>欧珑淡香精 情柚独钟 30ML</t>
         </is>
       </c>
       <c r="D446" s="2" t="inlineStr"/>
       <c r="E446" s="2" t="n">
-        <v>258</v>
+        <v>399</v>
       </c>
       <c r="F446" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G446" s="2" t="inlineStr">
-        <is>
-          <t>2023-02-01</t>
-        </is>
-      </c>
+      <c r="G446" s="2" t="inlineStr"/>
       <c r="H446" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I446" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=20.0%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I446" s="2" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="n">
-        <v>183</v>
-      </c>
-      <c r="B447" s="2" t="inlineStr"/>
+        <v>182</v>
+      </c>
+      <c r="B447" s="2" t="inlineStr">
+        <is>
+          <t>咕噜噜、丁香瓜马上拼</t>
+        </is>
+      </c>
       <c r="C447" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 雪松之恋 30ML</t>
+          <t>欧珑淡香精 无极乌龙 30ML</t>
         </is>
       </c>
       <c r="D447" s="2" t="inlineStr"/>
       <c r="E447" s="2" t="n">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="F447" s="2" t="inlineStr">
         <is>
@@ -16968,7 +16954,7 @@
       </c>
       <c r="G447" s="2" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="H447" s="2" t="inlineStr">
@@ -16984,57 +16970,65 @@
     </row>
     <row r="448">
       <c r="A448" s="2" t="n">
-        <v>183</v>
-      </c>
-      <c r="B448" s="2" t="inlineStr"/>
+        <v>182</v>
+      </c>
+      <c r="B448" s="2" t="inlineStr">
+        <is>
+          <t>【Atelier Cologne】欧珑淡香水无极乌龙30ml持久留香</t>
+        </is>
+      </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 雪松之恋 30ML</t>
+          <t>欧珑淡香精 无极乌龙 30ML</t>
         </is>
       </c>
       <c r="D448" s="2" t="inlineStr"/>
       <c r="E448" s="2" t="n">
-        <v>399</v>
+        <v>258</v>
       </c>
       <c r="F448" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G448" s="2" t="inlineStr"/>
+      <c r="G448" s="2" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
       <c r="H448" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I448" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I448" s="2" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n">
-        <v>184</v>
-      </c>
-      <c r="B449" s="2" t="inlineStr"/>
+        <v>182</v>
+      </c>
+      <c r="B449" s="2" t="inlineStr">
+        <is>
+          <t>不支持7天无理由退换</t>
+        </is>
+      </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>潘婷奇迹发膜胶原护发素损伤修护150ml</t>
+          <t>欧珑淡香精 无极乌龙 30ML</t>
         </is>
       </c>
       <c r="D449" s="2" t="inlineStr"/>
       <c r="E449" s="2" t="n">
-        <v>14.39</v>
+        <v>258</v>
       </c>
       <c r="F449" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G449" s="2" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="H449" s="2" t="inlineStr">
@@ -17044,27 +17038,23 @@
       </c>
       <c r="I449" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=20.0%)</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n">
-        <v>184</v>
-      </c>
-      <c r="B450" s="2" t="inlineStr">
-        <is>
-          <t>【潘婷】三分钟奇迹护发素发膜胶原蛋白强效护发素450ml</t>
-        </is>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="B450" s="2" t="inlineStr"/>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>潘婷奇迹发膜胶原护发素损伤修护150ml</t>
+          <t>欧珑淡香精 雪松之恋 30ML</t>
         </is>
       </c>
       <c r="D450" s="2" t="inlineStr"/>
       <c r="E450" s="2" t="n">
-        <v>39.9</v>
+        <v>236</v>
       </c>
       <c r="F450" s="2" t="inlineStr">
         <is>
@@ -17073,7 +17063,7 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -17083,102 +17073,96 @@
       </c>
       <c r="I450" s="2" t="inlineStr">
         <is>
-          <t>规格不匹配</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>Clinique倩碧紫胖子卸妆膏125ml*2 眼唇深层清洁温和</t>
+          <t>【正品行货】欧珑赤霞橘光无极乌龙情柚独钟30ml香水高级感</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>倩碧 紫胖子卸妆膏125ml</t>
+          <t>欧珑淡香精 雪松之恋 30ML</t>
         </is>
       </c>
       <c r="D451" s="2" t="inlineStr"/>
-      <c r="E451" s="2" t="n">
-        <v>209</v>
-      </c>
+      <c r="E451" s="2" t="inlineStr"/>
       <c r="F451" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G451" s="2" t="inlineStr">
-        <is>
-          <t>2025-03-31</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G451" s="2" t="inlineStr"/>
       <c r="H451" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I451" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I451" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n">
-        <v>186</v>
-      </c>
-      <c r="B452" s="2" t="inlineStr">
-        <is>
-          <t>【Clinique】倩碧小雏菊腮红#01#02#05#07#08#15提亮自然</t>
-        </is>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="B452" s="2" t="inlineStr"/>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>倩碧小雏菊裸色阳光腮#05</t>
+          <t>欧珑淡香精 雪松之恋 30ML</t>
         </is>
       </c>
       <c r="D452" s="2" t="inlineStr"/>
       <c r="E452" s="2" t="n">
-        <v>94</v>
+        <v>399</v>
       </c>
       <c r="F452" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G452" s="2" t="inlineStr">
-        <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G452" s="2" t="inlineStr"/>
       <c r="H452" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I452" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I452" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B453" s="2" t="inlineStr"/>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>倩碧小雏菊裸色阳光腮#05</t>
+          <t>潘婷奇迹发膜胶原护发素损伤修护150ml</t>
         </is>
       </c>
       <c r="D453" s="2" t="inlineStr"/>
       <c r="E453" s="2" t="n">
-        <v>90.5</v>
+        <v>14.39</v>
       </c>
       <c r="F453" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G453" s="2" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="H453" s="2" t="inlineStr">
@@ -17194,26 +17178,30 @@
     </row>
     <row r="454">
       <c r="A454" s="2" t="n">
-        <v>187</v>
-      </c>
-      <c r="B454" s="2" t="inlineStr"/>
+        <v>184</v>
+      </c>
+      <c r="B454" s="2" t="inlineStr">
+        <is>
+          <t>【潘婷】三分钟奇迹护发素发膜胶原蛋白强效护发素450ml</t>
+        </is>
+      </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>薇迪薇奇净颜美肌洁面乳</t>
+          <t>潘婷奇迹发膜胶原护发素损伤修护150ml</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr"/>
       <c r="E454" s="2" t="n">
-        <v>119</v>
+        <v>39.9</v>
       </c>
       <c r="F454" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G454" s="2" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H454" s="2" t="inlineStr">
@@ -17223,36 +17211,36 @@
       </c>
       <c r="I454" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；品名相似不足(ratio=0.0%)</t>
+          <t>规格不匹配</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B455" s="2" t="inlineStr">
         <is>
-          <t>VIDIVICI女神洗面奶净颜美肌洁面乳氨基酸温和保湿卸妆120ml正品</t>
+          <t>Clinique倩碧紫胖子卸妆膏125ml*2 眼唇深层清洁温和</t>
         </is>
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>薇迪薇奇净颜美肌洁面乳</t>
+          <t>倩碧 紫胖子卸妆膏125ml</t>
         </is>
       </c>
       <c r="D455" s="2" t="inlineStr"/>
       <c r="E455" s="2" t="n">
-        <v>66</v>
+        <v>209</v>
       </c>
       <c r="F455" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
@@ -17264,30 +17252,30 @@
     </row>
     <row r="456">
       <c r="A456" s="2" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
-          <t>【薇姿】绿标洗发水390ml二硫化硒去头屑控油深层清洁舒缓头皮洗发露</t>
+          <t>【Clinique】倩碧小雏菊腮红#01#02#05#07#08#15提亮自然</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>薇姿VICHY洗发水绿标硫化硒去屑止痒控油洗发乳390ml</t>
+          <t>倩碧小雏菊裸色阳光腮#05</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr"/>
       <c r="E456" s="2" t="n">
-        <v>78.59999999999999</v>
+        <v>94</v>
       </c>
       <c r="F456" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -17299,21 +17287,17 @@
     </row>
     <row r="457">
       <c r="A457" s="2" t="n">
-        <v>189</v>
-      </c>
-      <c r="B457" s="2" t="inlineStr">
-        <is>
-          <t>现货伟博深海鱼油Omega3 Webber三倍增强浓缩鱼油DHA900mg200粒</t>
-        </is>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="B457" s="2" t="inlineStr"/>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>伟博金萃高纯度鱼油1100</t>
+          <t>倩碧小雏菊裸色阳光腮#05</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr"/>
       <c r="E457" s="2" t="n">
-        <v>191.36</v>
+        <v>90.5</v>
       </c>
       <c r="F457" s="2" t="inlineStr">
         <is>
@@ -17322,7 +17306,7 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -17332,32 +17316,32 @@
       </c>
       <c r="I457" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=28.6%)</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B458" s="2" t="inlineStr"/>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>伟博金萃高纯度鱼油1100</t>
+          <t>薇迪薇奇净颜美肌洁面乳</t>
         </is>
       </c>
       <c r="D458" s="2" t="inlineStr"/>
       <c r="E458" s="2" t="n">
-        <v>205</v>
+        <v>119</v>
       </c>
       <c r="F458" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -17367,27 +17351,27 @@
       </c>
       <c r="I458" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>品牌不一致；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B459" s="2" t="inlineStr">
         <is>
-          <t>Webber Naturals伟博深海鱼油Omega-3高浓度三倍浓缩DHA成人200粒</t>
+          <t>VIDIVICI女神洗面奶净颜美肌洁面乳氨基酸温和保湿卸妆120ml正品</t>
         </is>
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>伟博金萃高纯度鱼油1100</t>
+          <t>薇迪薇奇净颜美肌洁面乳</t>
         </is>
       </c>
       <c r="D459" s="2" t="inlineStr"/>
       <c r="E459" s="2" t="n">
-        <v>200</v>
+        <v>66</v>
       </c>
       <c r="F459" s="2" t="inlineStr">
         <is>
@@ -17396,33 +17380,33 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I459" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=28.6%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I459" s="2" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n">
-        <v>189</v>
-      </c>
-      <c r="B460" s="2" t="inlineStr"/>
+        <v>188</v>
+      </c>
+      <c r="B460" s="2" t="inlineStr">
+        <is>
+          <t>【薇姿】绿标洗发水390ml二硫化硒去头屑控油深层清洁舒缓头皮洗发露</t>
+        </is>
+      </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>伟博金萃高纯度鱼油1100</t>
+          <t>薇姿VICHY洗发水绿标硫化硒去屑止痒控油洗发乳390ml</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr"/>
       <c r="E460" s="2" t="n">
-        <v>392</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F460" s="2" t="inlineStr">
         <is>
@@ -17431,25 +17415,25 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I460" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I460" s="2" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="n">
         <v>189</v>
       </c>
-      <c r="B461" s="2" t="inlineStr"/>
+      <c r="B461" s="2" t="inlineStr">
+        <is>
+          <t>现货伟博深海鱼油Omega3 Webber三倍增强浓缩鱼油DHA900mg200粒</t>
+        </is>
+      </c>
       <c r="C461" s="2" t="inlineStr">
         <is>
           <t>伟博金萃高纯度鱼油1100</t>
@@ -17457,7 +17441,7 @@
       </c>
       <c r="D461" s="2" t="inlineStr"/>
       <c r="E461" s="2" t="n">
-        <v>172</v>
+        <v>191.36</v>
       </c>
       <c r="F461" s="2" t="inlineStr">
         <is>
@@ -17466,7 +17450,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -17476,27 +17460,23 @@
       </c>
       <c r="I461" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=28.6%)</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n">
-        <v>190</v>
-      </c>
-      <c r="B462" s="2" t="inlineStr">
-        <is>
-          <t>3瓶 伟博天然硫酸氨糖软骨素180粒强效MSM缓疼痛中老年人维骨力D3</t>
-        </is>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="B462" s="2" t="inlineStr"/>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
+          <t>伟博金萃高纯度鱼油1100</t>
         </is>
       </c>
       <c r="D462" s="2" t="inlineStr"/>
       <c r="E462" s="2" t="n">
-        <v>486</v>
+        <v>205</v>
       </c>
       <c r="F462" s="2" t="inlineStr">
         <is>
@@ -17505,7 +17485,7 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -17515,27 +17495,27 @@
       </c>
       <c r="I462" s="2" t="inlineStr">
         <is>
-          <t>规格不匹配</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B463" s="2" t="inlineStr">
         <is>
-          <t>伟博硫酸氨糖软骨素 中老年成人维骨力D3促吸收 加拿大进口 180粒</t>
+          <t>Webber Naturals伟博深海鱼油Omega-3高浓度三倍浓缩DHA成人200粒</t>
         </is>
       </c>
       <c r="C463" s="2" t="inlineStr">
         <is>
-          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
+          <t>伟博金萃高纯度鱼油1100</t>
         </is>
       </c>
       <c r="D463" s="2" t="inlineStr"/>
       <c r="E463" s="2" t="n">
-        <v>328</v>
+        <v>200</v>
       </c>
       <c r="F463" s="2" t="inlineStr">
         <is>
@@ -17544,7 +17524,7 @@
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
@@ -17554,23 +17534,23 @@
       </c>
       <c r="I463" s="2" t="inlineStr">
         <is>
-          <t>规格不匹配；品名相似不足(ratio=45.5%)</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=28.6%)</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B464" s="2" t="inlineStr"/>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
+          <t>伟博金萃高纯度鱼油1100</t>
         </is>
       </c>
       <c r="D464" s="2" t="inlineStr"/>
       <c r="E464" s="2" t="n">
-        <v>167</v>
+        <v>392</v>
       </c>
       <c r="F464" s="2" t="inlineStr">
         <is>
@@ -17579,7 +17559,7 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -17595,21 +17575,17 @@
     </row>
     <row r="465">
       <c r="A465" s="2" t="n">
-        <v>190</v>
-      </c>
-      <c r="B465" s="2" t="inlineStr">
-        <is>
-          <t>加拿大伟博氨糖软骨素180粒中老年成人天然维骨力D3促钙吸收关节</t>
-        </is>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="B465" s="2" t="inlineStr"/>
       <c r="C465" s="2" t="inlineStr">
         <is>
-          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
+          <t>伟博金萃高纯度鱼油1100</t>
         </is>
       </c>
       <c r="D465" s="2" t="inlineStr"/>
       <c r="E465" s="2" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="F465" s="2" t="inlineStr">
         <is>
@@ -17618,7 +17594,7 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -17628,34 +17604,38 @@
       </c>
       <c r="I465" s="2" t="inlineStr">
         <is>
-          <t>规格不匹配；品名相似不足(ratio=45.5%)</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B466" s="2" t="inlineStr">
         <is>
-          <t>【520礼物】CHANEL/香奈儿山茶花洗面奶清爽控油净肤泡沫洁面乳</t>
+          <t>3瓶 伟博天然硫酸氨糖软骨素180粒强效MSM缓疼痛中老年人维骨力D3</t>
         </is>
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
+          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
         </is>
       </c>
       <c r="D466" s="2" t="inlineStr"/>
       <c r="E466" s="2" t="n">
-        <v>408</v>
+        <v>486</v>
       </c>
       <c r="F466" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G466" s="2" t="inlineStr"/>
+      <c r="G466" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
       <c r="H466" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -17669,24 +17649,32 @@
     </row>
     <row r="467">
       <c r="A467" s="2" t="n">
-        <v>191</v>
-      </c>
-      <c r="B467" s="2" t="inlineStr"/>
+        <v>190</v>
+      </c>
+      <c r="B467" s="2" t="inlineStr">
+        <is>
+          <t>伟博硫酸氨糖软骨素 中老年成人维骨力D3促吸收 加拿大进口 180粒</t>
+        </is>
+      </c>
       <c r="C467" s="2" t="inlineStr">
         <is>
-          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
+          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
         </is>
       </c>
       <c r="D467" s="2" t="inlineStr"/>
       <c r="E467" s="2" t="n">
-        <v>378</v>
+        <v>328</v>
       </c>
       <c r="F467" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G467" s="2" t="inlineStr"/>
+      <c r="G467" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
       <c r="H467" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -17694,96 +17682,108 @@
       </c>
       <c r="I467" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>规格不匹配；品名相似不足(ratio=45.5%)</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n">
-        <v>191</v>
-      </c>
-      <c r="B468" s="2" t="inlineStr">
-        <is>
-          <t>【原装正品】CHANEL香奈儿柔和净肤泡沫洁清洁 山茶花洁面 150ml</t>
-        </is>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="B468" s="2" t="inlineStr"/>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
+          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
         </is>
       </c>
       <c r="D468" s="2" t="inlineStr"/>
       <c r="E468" s="2" t="n">
-        <v>403</v>
+        <v>167</v>
       </c>
       <c r="F468" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G468" s="2" t="inlineStr"/>
+      <c r="G468" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
       <c r="H468" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I468" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I468" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B469" s="2" t="inlineStr">
         <is>
-          <t>Chanel香奈儿山茶花洗面奶150ml柔和净肤泡沫洁面乳</t>
+          <t>加拿大伟博氨糖软骨素180粒中老年成人天然维骨力D3促钙吸收关节</t>
         </is>
       </c>
       <c r="C469" s="2" t="inlineStr">
         <is>
-          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
+          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
         </is>
       </c>
       <c r="D469" s="2" t="inlineStr"/>
       <c r="E469" s="2" t="n">
-        <v>628</v>
+        <v>167</v>
       </c>
       <c r="F469" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G469" s="2" t="inlineStr"/>
+      <c r="G469" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
       <c r="H469" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I469" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I469" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=45.5%)</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="n">
-        <v>192</v>
-      </c>
-      <c r="B470" s="2" t="inlineStr"/>
+        <v>191</v>
+      </c>
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <t>【520礼物】CHANEL/香奈儿山茶花洗面奶清爽控油净肤泡沫洁面乳</t>
+        </is>
+      </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
+          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
         </is>
       </c>
       <c r="D470" s="2" t="inlineStr"/>
       <c r="E470" s="2" t="n">
-        <v>453</v>
+        <v>408</v>
       </c>
       <c r="F470" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G470" s="2" t="inlineStr">
-        <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
+      <c r="G470" s="2" t="inlineStr"/>
       <c r="H470" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -17791,27 +17791,23 @@
       </c>
       <c r="I470" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>规格不匹配</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="n">
-        <v>192</v>
-      </c>
-      <c r="B471" s="2" t="inlineStr">
-        <is>
-          <t>【雅诗兰黛】小棕瓶精华100ml第七代特润促进夜间修复抗衰香港仓发【5天内发货】</t>
-        </is>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="B471" s="2" t="inlineStr"/>
       <c r="C471" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
+          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
         </is>
       </c>
       <c r="D471" s="2" t="inlineStr"/>
       <c r="E471" s="2" t="n">
-        <v>407.99</v>
+        <v>378</v>
       </c>
       <c r="F471" s="2" t="inlineStr">
         <is>
@@ -17821,24 +17817,32 @@
       <c r="G471" s="2" t="inlineStr"/>
       <c r="H471" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I471" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I471" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n">
-        <v>192</v>
-      </c>
-      <c r="B472" s="2" t="inlineStr"/>
+        <v>191</v>
+      </c>
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <t>【原装正品】CHANEL香奈儿柔和净肤泡沫洁清洁 山茶花洁面 150ml</t>
+        </is>
+      </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
+          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
         </is>
       </c>
       <c r="D472" s="2" t="inlineStr"/>
       <c r="E472" s="2" t="n">
-        <v>448</v>
+        <v>403</v>
       </c>
       <c r="F472" s="2" t="inlineStr">
         <is>
@@ -17848,72 +17852,64 @@
       <c r="G472" s="2" t="inlineStr"/>
       <c r="H472" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I472" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I472" s="2" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n">
-        <v>192</v>
-      </c>
-      <c r="B473" s="2" t="inlineStr"/>
+        <v>191</v>
+      </c>
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <t>Chanel香奈儿山茶花洗面奶150ml柔和净肤泡沫洁面乳</t>
+        </is>
+      </c>
       <c r="C473" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
+          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
         </is>
       </c>
       <c r="D473" s="2" t="inlineStr"/>
       <c r="E473" s="2" t="n">
-        <v>499</v>
+        <v>628</v>
       </c>
       <c r="F473" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G473" s="2" t="inlineStr">
-        <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G473" s="2" t="inlineStr"/>
       <c r="H473" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I473" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I473" s="2" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B474" s="2" t="inlineStr"/>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛 净莹柔肤洁面乳150ml（蓝洁面）</t>
+          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
         </is>
       </c>
       <c r="D474" s="2" t="inlineStr"/>
       <c r="E474" s="2" t="n">
-        <v>112</v>
+        <v>453</v>
       </c>
       <c r="F474" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G474" s="2" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H474" s="2" t="inlineStr">
@@ -17929,32 +17925,28 @@
     </row>
     <row r="475">
       <c r="A475" s="2" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B475" s="2" t="inlineStr">
         <is>
-          <t>【品牌好评451.2万+条】EsteeLauder雅诗兰黛净莹柔肤洁面乳蓝洁面150ml</t>
+          <t>【雅诗兰黛】小棕瓶精华100ml第七代特润促进夜间修复抗衰香港仓发【5天内发货】</t>
         </is>
       </c>
       <c r="C475" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛 净莹柔肤洁面乳150ml（蓝洁面）</t>
+          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
         </is>
       </c>
       <c r="D475" s="2" t="inlineStr"/>
       <c r="E475" s="2" t="n">
-        <v>198</v>
+        <v>407.99</v>
       </c>
       <c r="F475" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G475" s="2" t="inlineStr">
-        <is>
-          <t>2025-02-02</t>
-        </is>
-      </c>
+      <c r="G475" s="2" t="inlineStr"/>
       <c r="H475" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -17964,57 +17956,57 @@
     </row>
     <row r="476">
       <c r="A476" s="2" t="n">
-        <v>194</v>
-      </c>
-      <c r="B476" s="2" t="inlineStr">
-        <is>
-          <t>【正品行货】雅诗兰黛DW方气垫2C0 持久遮瑕控油服帖</t>
-        </is>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="B476" s="2" t="inlineStr"/>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛DW  2c0</t>
+          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
         </is>
       </c>
       <c r="D476" s="2" t="inlineStr"/>
       <c r="E476" s="2" t="n">
-        <v>188</v>
+        <v>448</v>
       </c>
       <c r="F476" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G476" s="2" t="inlineStr"/>
       <c r="H476" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I476" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I476" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B477" s="2" t="inlineStr"/>
       <c r="C477" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛大棕罐膜霜65ml</t>
+          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
         </is>
       </c>
       <c r="D477" s="2" t="inlineStr"/>
       <c r="E477" s="2" t="n">
-        <v>239</v>
+        <v>499</v>
       </c>
       <c r="F477" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G477" s="2" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="H477" s="2" t="inlineStr">
@@ -18030,26 +18022,26 @@
     </row>
     <row r="478">
       <c r="A478" s="2" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B478" s="2" t="inlineStr"/>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛大棕罐膜霜65ml</t>
+          <t>雅诗兰黛 净莹柔肤洁面乳150ml（蓝洁面）</t>
         </is>
       </c>
       <c r="D478" s="2" t="inlineStr"/>
       <c r="E478" s="2" t="n">
-        <v>247</v>
+        <v>112</v>
       </c>
       <c r="F478" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G478" s="2" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="H478" s="2" t="inlineStr">
@@ -18065,21 +18057,21 @@
     </row>
     <row r="479">
       <c r="A479" s="2" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B479" s="2" t="inlineStr">
         <is>
-          <t>【78.6万人回购该品牌】Estee Lauder雅诗兰黛大棕罐封愈膜霜65ml紧致面霜</t>
+          <t>【品牌好评451.2万+条】EsteeLauder雅诗兰黛净莹柔肤洁面乳蓝洁面150ml</t>
         </is>
       </c>
       <c r="C479" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛大棕罐膜霜65ml</t>
+          <t>雅诗兰黛 净莹柔肤洁面乳150ml（蓝洁面）</t>
         </is>
       </c>
       <c r="D479" s="2" t="inlineStr"/>
       <c r="E479" s="2" t="n">
-        <v>369</v>
+        <v>198</v>
       </c>
       <c r="F479" s="2" t="inlineStr">
         <is>
@@ -18088,7 +18080,7 @@
       </c>
       <c r="G479" s="2" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="H479" s="2" t="inlineStr">
@@ -18100,54 +18092,48 @@
     </row>
     <row r="480">
       <c r="A480" s="2" t="n">
-        <v>195</v>
-      </c>
-      <c r="B480" s="2" t="inlineStr"/>
+        <v>194</v>
+      </c>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛DW方气垫2C0 持久遮瑕控油服帖</t>
+        </is>
+      </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛大棕罐膜霜65ml</t>
+          <t>雅诗兰黛DW  2c0</t>
         </is>
       </c>
       <c r="D480" s="2" t="inlineStr"/>
       <c r="E480" s="2" t="n">
-        <v>399</v>
+        <v>188</v>
       </c>
       <c r="F480" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G480" s="2" t="inlineStr">
-        <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G480" s="2" t="inlineStr"/>
       <c r="H480" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I480" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I480" s="2" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" s="2" t="n">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="B481" s="2" t="inlineStr"/>
       <c r="C481" s="2" t="inlineStr">
         <is>
-          <t>罗拉散粉经典款29G</t>
+          <t>雅诗兰黛大棕罐膜霜65ml</t>
         </is>
       </c>
       <c r="D481" s="2" t="inlineStr"/>
-      <c r="E481" s="2" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
+      <c r="E481" s="2" t="n">
+        <v>239</v>
       </c>
       <c r="F481" s="2" t="inlineStr">
         <is>
@@ -18156,7 +18142,7 @@
       </c>
       <c r="G481" s="2" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H481" s="2" t="inlineStr">
@@ -18172,30 +18158,28 @@
     </row>
     <row r="482">
       <c r="A482" s="2" t="n">
-        <v>174</v>
-      </c>
-      <c r="B482" s="2" t="inlineStr">
-        <is>
-          <t>Laura Mercier罗拉散粉新版Translucent柔光透明哑光控油定妆29g</t>
-        </is>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="B482" s="2" t="inlineStr"/>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>罗拉散粉经典款29G</t>
+          <t>雅诗兰黛大棕罐膜霜65ml</t>
         </is>
       </c>
       <c r="D482" s="2" t="inlineStr"/>
-      <c r="E482" s="2" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
+      <c r="E482" s="2" t="n">
+        <v>247</v>
       </c>
       <c r="F482" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G482" s="2" t="inlineStr"/>
+      <c r="G482" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
       <c r="H482" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -18203,26 +18187,28 @@
       </c>
       <c r="I482" s="2" t="inlineStr">
         <is>
-          <t>品名相似不足(ratio=50.0%)</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="n">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="B483" s="2" t="inlineStr">
         <is>
-          <t>【1.2万人回购该品牌】马丁梅森马吉拉慵懒周末100ml 持久留香</t>
+          <t>【78.6万人回购该品牌】Estee Lauder雅诗兰黛大棕罐封愈膜霜65ml紧致面霜</t>
         </is>
       </c>
       <c r="C483" s="2" t="inlineStr">
         <is>
-          <t>马丁马吉拉-慵懒周末100ml</t>
+          <t>雅诗兰黛大棕罐膜霜65ml</t>
         </is>
       </c>
       <c r="D483" s="2" t="inlineStr"/>
-      <c r="E483" s="2" t="inlineStr"/>
+      <c r="E483" s="2" t="n">
+        <v>369</v>
+      </c>
       <c r="F483" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -18230,7 +18216,7 @@
       </c>
       <c r="G483" s="2" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="H483" s="2" t="inlineStr">
@@ -18242,30 +18228,28 @@
     </row>
     <row r="484">
       <c r="A484" s="2" t="n">
-        <v>176</v>
-      </c>
-      <c r="B484" s="2" t="inlineStr">
-        <is>
-          <t>【Murad】慕拉得a醇面部精华30ml视黄醇紧致抗初老提亮肤色A醇抗氧化</t>
-        </is>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="B484" s="2" t="inlineStr"/>
       <c r="C484" s="2" t="inlineStr">
         <is>
-          <t>慕拉得塑颜修复A醇精华30ml</t>
+          <t>雅诗兰黛大棕罐膜霜65ml</t>
         </is>
       </c>
       <c r="D484" s="2" t="inlineStr"/>
-      <c r="E484" s="2" t="inlineStr">
-        <is>
-          <t>469.0</t>
-        </is>
+      <c r="E484" s="2" t="n">
+        <v>399</v>
       </c>
       <c r="F484" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G484" s="2" t="inlineStr"/>
+      <c r="G484" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
       <c r="H484" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -18273,34 +18257,32 @@
       </c>
       <c r="I484" s="2" t="inlineStr">
         <is>
-          <t>品名相似不足(ratio=33.3%)</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="n">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="B485" s="2" t="inlineStr"/>
       <c r="C485" s="2" t="inlineStr">
         <is>
-          <t>欧珑赤霞橘光护手霜30ML</t>
+          <t>雅诗兰黛红石榴洁面60ml</t>
         </is>
       </c>
       <c r="D485" s="2" t="inlineStr"/>
-      <c r="E485" s="2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
+      <c r="E485" s="2" t="n">
+        <v>111</v>
       </c>
       <c r="F485" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="H485" s="2" t="inlineStr">
@@ -18316,26 +18298,28 @@
     </row>
     <row r="486">
       <c r="A486" s="2" t="n">
-        <v>177</v>
-      </c>
-      <c r="B486" s="2" t="inlineStr">
-        <is>
-          <t>大牌清仓欧珑无极莹润身体乳滋润保湿香体留香持久可做护手霜15ml</t>
-        </is>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="B486" s="2" t="inlineStr"/>
       <c r="C486" s="2" t="inlineStr">
         <is>
-          <t>欧珑赤霞橘光护手霜30ML</t>
+          <t>雅诗兰黛红石榴洁面60ml</t>
         </is>
       </c>
       <c r="D486" s="2" t="inlineStr"/>
-      <c r="E486" s="2" t="inlineStr"/>
+      <c r="E486" s="2" t="n">
+        <v>165</v>
+      </c>
       <c r="F486" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G486" s="2" t="inlineStr"/>
+      <c r="G486" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
       <c r="H486" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -18343,29 +18327,27 @@
       </c>
       <c r="I486" s="2" t="inlineStr">
         <is>
-          <t>规格不匹配；品名相似不足(ratio=42.9%)</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="n">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="B487" s="2" t="inlineStr">
         <is>
-          <t>【欧珑】莹润护手霜赤霞橘光无极乌龙30ml两款可选择持久留香清新体验</t>
+          <t>【正品行货】雅诗兰黛红石榴洁面洗面奶60ml  细致毛孔深层清洁</t>
         </is>
       </c>
       <c r="C487" s="2" t="inlineStr">
         <is>
-          <t>欧珑赤霞橘光护手霜30ML</t>
+          <t>雅诗兰黛红石榴洁面60ml</t>
         </is>
       </c>
       <c r="D487" s="2" t="inlineStr"/>
-      <c r="E487" s="2" t="inlineStr">
-        <is>
-          <t>68.67</t>
-        </is>
+      <c r="E487" s="2" t="n">
+        <v>50.4</v>
       </c>
       <c r="F487" s="2" t="inlineStr">
         <is>
@@ -18382,30 +18364,28 @@
     </row>
     <row r="488">
       <c r="A488" s="2" t="n">
-        <v>178</v>
-      </c>
-      <c r="B488" s="2" t="inlineStr"/>
+        <v>196</v>
+      </c>
+      <c r="B488" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛鲜活亮采红石榴洗面奶60ml深层清洁</t>
+        </is>
+      </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精  赤霞橘光 100ML</t>
+          <t>雅诗兰黛红石榴洁面60ml</t>
         </is>
       </c>
       <c r="D488" s="2" t="inlineStr"/>
-      <c r="E488" s="2" t="inlineStr">
-        <is>
-          <t>521.0</t>
-        </is>
+      <c r="E488" s="2" t="n">
+        <v>49.9</v>
       </c>
       <c r="F488" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G488" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G488" s="2" t="inlineStr"/>
       <c r="H488" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -18413,25 +18393,23 @@
       </c>
       <c r="I488" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>品名相似不足(ratio=50.0%)</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="n">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="B489" s="2" t="inlineStr"/>
       <c r="C489" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精  无极乌龙 100ML</t>
+          <t>雅诗兰黛第七代特润小棕瓶100ml*2（新款）</t>
         </is>
       </c>
       <c r="D489" s="2" t="inlineStr"/>
-      <c r="E489" s="2" t="inlineStr">
-        <is>
-          <t>236.0</t>
-        </is>
+      <c r="E489" s="2" t="n">
+        <v>429</v>
       </c>
       <c r="F489" s="2" t="inlineStr">
         <is>
@@ -18456,23 +18434,21 @@
     </row>
     <row r="490">
       <c r="A490" s="2" t="n">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>【欧珑】淡香精9ml 赤霞橘光无极乌龙浓香水EDP持久留香Q版 带喷头</t>
+          <t>【专柜礼盒】雅诗兰黛眼霜第七代小棕瓶特润修护紧致送礼盒礼物</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精  无极乌龙 100ML</t>
+          <t>雅诗兰黛第七代特润小棕瓶100ml*2（新款）</t>
         </is>
       </c>
       <c r="D490" s="2" t="inlineStr"/>
-      <c r="E490" s="2" t="inlineStr">
-        <is>
-          <t>82.4</t>
-        </is>
+      <c r="E490" s="2" t="n">
+        <v>308</v>
       </c>
       <c r="F490" s="2" t="inlineStr">
         <is>
@@ -18493,34 +18469,22 @@
     </row>
     <row r="491">
       <c r="A491" s="2" t="n">
-        <v>179</v>
-      </c>
-      <c r="B491" s="2" t="inlineStr">
-        <is>
-          <t>【欧珑】无极乌龙香水赤霞橘光香氛持久生日礼物中性香</t>
-        </is>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="B491" s="2" t="inlineStr"/>
       <c r="C491" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精  无极乌龙 100ML</t>
+          <t>雅诗兰黛第七代特润小棕瓶100ml*2（新款）</t>
         </is>
       </c>
       <c r="D491" s="2" t="inlineStr"/>
-      <c r="E491" s="2" t="inlineStr">
-        <is>
-          <t>350.0</t>
-        </is>
-      </c>
+      <c r="E491" s="2" t="inlineStr"/>
       <c r="F491" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G491" s="2" t="inlineStr">
-        <is>
-          <t>2023-09-01</t>
-        </is>
-      </c>
+      <c r="G491" s="2" t="inlineStr"/>
       <c r="H491" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -18528,139 +18492,143 @@
       </c>
       <c r="I491" s="2" t="inlineStr">
         <is>
-          <t>规格不匹配</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="n">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="B492" s="2" t="inlineStr">
         <is>
-          <t>【Atelier Cologne】欧珑淡香水赤霞橘光30ml持久留香</t>
+          <t>【雅诗兰黛】第七代小棕瓶特润修护肌活精华液淡纹舒缓提亮紧致保湿</t>
         </is>
       </c>
       <c r="C492" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 赤霞橘光 30ML</t>
+          <t>雅诗兰黛第七代特润小棕瓶100ml*2（新款）</t>
         </is>
       </c>
       <c r="D492" s="2" t="inlineStr"/>
-      <c r="E492" s="2" t="inlineStr">
-        <is>
-          <t>285.0</t>
-        </is>
+      <c r="E492" s="2" t="n">
+        <v>300</v>
       </c>
       <c r="F492" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G492" s="2" t="inlineStr">
-        <is>
-          <t>2023-11-01</t>
-        </is>
-      </c>
+      <c r="G492" s="2" t="inlineStr"/>
       <c r="H492" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I492" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I492" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="n">
-        <v>181</v>
-      </c>
-      <c r="B493" s="2" t="inlineStr">
-        <is>
-          <t>【正品行货】欧珑赤霞橘光无极乌龙情柚独钟30ml香水高级感</t>
-        </is>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="B493" s="2" t="inlineStr"/>
       <c r="C493" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 情柚独钟 30ML</t>
+          <t>雅诗兰黛线雕精华50ml（新版）</t>
         </is>
       </c>
       <c r="D493" s="2" t="inlineStr"/>
-      <c r="E493" s="2" t="inlineStr"/>
+      <c r="E493" s="2" t="n">
+        <v>635</v>
+      </c>
       <c r="F493" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G493" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G493" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
       <c r="H493" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I493" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I493" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="n">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="B494" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】欧珑情柚独钟30ml香氛持久留香礼物送女友赠礼</t>
+          <t>【正品行货】雅诗兰黛紧塑线雕精华液面部提拉祛黄提亮100ML淡纹</t>
         </is>
       </c>
       <c r="C494" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 情柚独钟 30ML</t>
+          <t>雅诗兰黛线雕精华50ml（新版）</t>
         </is>
       </c>
       <c r="D494" s="2" t="inlineStr"/>
-      <c r="E494" s="2" t="inlineStr">
-        <is>
-          <t>399.0</t>
-        </is>
+      <c r="E494" s="2" t="n">
+        <v>775</v>
       </c>
       <c r="F494" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G494" s="2" t="inlineStr"/>
+      <c r="G494" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
       <c r="H494" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I494" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I494" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="n">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="B495" s="2" t="inlineStr">
         <is>
-          <t>咕噜噜、丁香瓜马上拼</t>
+          <t>雅诗兰黛紧塑线雕精华面部提拉紧致淡法令纹100ML小银瓶抗衰老</t>
         </is>
       </c>
       <c r="C495" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 无极乌龙 30ML</t>
+          <t>雅诗兰黛线雕精华50ml（新版）</t>
         </is>
       </c>
       <c r="D495" s="2" t="inlineStr"/>
-      <c r="E495" s="2" t="inlineStr">
-        <is>
-          <t>258.0</t>
-        </is>
+      <c r="E495" s="2" t="n">
+        <v>735</v>
       </c>
       <c r="F495" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G495" s="2" t="inlineStr">
-        <is>
-          <t>2023-02-01</t>
-        </is>
-      </c>
+      <c r="G495" s="2" t="inlineStr"/>
       <c r="H495" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -18668,75 +18636,63 @@
       </c>
       <c r="I495" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>规格不匹配</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="n">
-        <v>182</v>
-      </c>
-      <c r="B496" s="2" t="inlineStr">
-        <is>
-          <t>【Atelier Cologne】欧珑淡香水无极乌龙30ml持久留香</t>
-        </is>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="B496" s="2" t="inlineStr"/>
       <c r="C496" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 无极乌龙 30ML</t>
+          <t>雅诗兰黛线雕精华50ml（新版）</t>
         </is>
       </c>
       <c r="D496" s="2" t="inlineStr"/>
-      <c r="E496" s="2" t="inlineStr">
-        <is>
-          <t>258.0</t>
-        </is>
+      <c r="E496" s="2" t="n">
+        <v>370</v>
       </c>
       <c r="F496" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G496" s="2" t="inlineStr">
-        <is>
-          <t>2023-02-01</t>
-        </is>
-      </c>
+      <c r="G496" s="2" t="inlineStr"/>
       <c r="H496" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I496" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I496" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="n">
-        <v>182</v>
-      </c>
-      <c r="B497" s="2" t="inlineStr">
-        <is>
-          <t>不支持7天无理由退换</t>
-        </is>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="B497" s="2" t="inlineStr"/>
       <c r="C497" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 无极乌龙 30ML</t>
+          <t>雅诗兰黛小棕瓶眼霜15ml</t>
         </is>
       </c>
       <c r="D497" s="2" t="inlineStr"/>
-      <c r="E497" s="2" t="inlineStr">
-        <is>
-          <t>258.0</t>
-        </is>
+      <c r="E497" s="2" t="n">
+        <v>427</v>
       </c>
       <c r="F497" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G497" s="2" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H497" s="2" t="inlineStr">
@@ -18746,25 +18702,23 @@
       </c>
       <c r="I497" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=20.0%)</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="n">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="B498" s="2" t="inlineStr"/>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 雪松之恋 30ML</t>
+          <t>雅诗兰黛小棕瓶眼霜15ml</t>
         </is>
       </c>
       <c r="D498" s="2" t="inlineStr"/>
-      <c r="E498" s="2" t="inlineStr">
-        <is>
-          <t>236.0</t>
-        </is>
+      <c r="E498" s="2" t="n">
+        <v>400</v>
       </c>
       <c r="F498" s="2" t="inlineStr">
         <is>
@@ -18773,7 +18727,7 @@
       </c>
       <c r="G498" s="2" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="H498" s="2" t="inlineStr">
@@ -18789,96 +18743,94 @@
     </row>
     <row r="499">
       <c r="A499" s="2" t="n">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="B499" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】欧珑赤霞橘光无极乌龙情柚独钟30ml香水高级感</t>
+          <t>【雅诗兰黛】抗蓝光小棕瓶眼霜15ml/瓶</t>
         </is>
       </c>
       <c r="C499" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 雪松之恋 30ML</t>
+          <t>雅诗兰黛小棕瓶眼霜15ml</t>
         </is>
       </c>
       <c r="D499" s="2" t="inlineStr"/>
-      <c r="E499" s="2" t="inlineStr"/>
+      <c r="E499" s="2" t="n">
+        <v>279</v>
+      </c>
       <c r="F499" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G499" s="2" t="inlineStr"/>
+      <c r="G499" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
       <c r="H499" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I499" s="2" t="inlineStr">
-        <is>
-          <t>品名相似不足(ratio=0.0%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I499" s="2" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="n">
-        <v>183</v>
-      </c>
-      <c r="B500" s="2" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="B500" s="2" t="inlineStr">
+        <is>
+          <t>【ESTEE LAUDER】雅诗兰黛智妍夜晚霜75ml抗老修护</t>
+        </is>
+      </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>欧珑淡香精 雪松之恋 30ML</t>
+          <t>雅诗兰黛智妍晚霜75ml</t>
         </is>
       </c>
       <c r="D500" s="2" t="inlineStr"/>
-      <c r="E500" s="2" t="inlineStr">
-        <is>
-          <t>399.0</t>
-        </is>
+      <c r="E500" s="2" t="n">
+        <v>508</v>
       </c>
       <c r="F500" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G500" s="2" t="inlineStr"/>
+      <c r="G500" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
       <c r="H500" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I500" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I500" s="2" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" s="2" t="n">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="B501" s="2" t="inlineStr"/>
       <c r="C501" s="2" t="inlineStr">
         <is>
-          <t>潘婷奇迹发膜胶原护发素损伤修护150ml</t>
+          <t>雅诗兰黛智妍晚霜75ml</t>
         </is>
       </c>
       <c r="D501" s="2" t="inlineStr"/>
-      <c r="E501" s="2" t="inlineStr">
-        <is>
-          <t>14.39</t>
-        </is>
+      <c r="E501" s="2" t="n">
+        <v>499</v>
       </c>
       <c r="F501" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G501" s="2" t="inlineStr">
-        <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G501" s="2" t="inlineStr"/>
       <c r="H501" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -18892,23 +18844,21 @@
     </row>
     <row r="502">
       <c r="A502" s="2" t="n">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="B502" s="2" t="inlineStr">
         <is>
-          <t>【潘婷】三分钟奇迹护发素发膜胶原蛋白强效护发素450ml</t>
+          <t>【8.81万人评价品牌正品】ESTEELAUDER雅诗兰黛智妍夜胶原晚霜75ml 淡纹紧致</t>
         </is>
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>潘婷奇迹发膜胶原护发素损伤修护150ml</t>
+          <t>雅诗兰黛智妍晚霜75ml</t>
         </is>
       </c>
       <c r="D502" s="2" t="inlineStr"/>
-      <c r="E502" s="2" t="inlineStr">
-        <is>
-          <t>39.9</t>
-        </is>
+      <c r="E502" s="2" t="n">
+        <v>532</v>
       </c>
       <c r="F502" s="2" t="inlineStr">
         <is>
@@ -18917,50 +18867,40 @@
       </c>
       <c r="G502" s="2" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="H502" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I502" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I502" s="2" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" s="2" t="n">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="B503" s="2" t="inlineStr">
         <is>
-          <t>Clinique倩碧紫胖子卸妆膏125ml*2 眼唇深层清洁温和</t>
+          <t>【IPSA】茵芙莎三色遮瑕盘4.5g 遮瑕膏遮痘印痘痘黑眼圈持久妆效【5天内发货】</t>
         </is>
       </c>
       <c r="C503" s="2" t="inlineStr">
         <is>
-          <t>倩碧 紫胖子卸妆膏125ml</t>
+          <t>茵芙纱 三色遮瑕4.5g</t>
         </is>
       </c>
       <c r="D503" s="2" t="inlineStr"/>
-      <c r="E503" s="2" t="inlineStr">
-        <is>
-          <t>209.0</t>
-        </is>
+      <c r="E503" s="2" t="n">
+        <v>135</v>
       </c>
       <c r="F503" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G503" s="2" t="inlineStr">
-        <is>
-          <t>2025-03-31</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G503" s="2" t="inlineStr"/>
       <c r="H503" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -18970,32 +18910,32 @@
     </row>
     <row r="504">
       <c r="A504" s="2" t="n">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>【Clinique】倩碧小雏菊腮红#01#02#05#07#08#15提亮自然</t>
+          <t>【IPSA】茵芙莎三色遮瑕膏4.5g遮黑眼圈痘痘泪沟修饰肤色【5天内发货】</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
         <is>
-          <t>倩碧小雏菊裸色阳光腮#05</t>
-        </is>
-      </c>
-      <c r="D504" s="2" t="inlineStr"/>
-      <c r="E504" s="2" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
+          <t>茵芙纱 三色遮瑕4.5g</t>
+        </is>
+      </c>
+      <c r="D504" s="2" t="n">
+        <v>29913</v>
+      </c>
+      <c r="E504" s="2" t="n">
+        <v>299</v>
       </c>
       <c r="F504" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G504" s="2" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="H504" s="2" t="inlineStr">
@@ -19007,65 +18947,63 @@
     </row>
     <row r="505">
       <c r="A505" s="2" t="n">
-        <v>186</v>
-      </c>
-      <c r="B505" s="2" t="inlineStr"/>
+        <v>202</v>
+      </c>
+      <c r="B505" s="2" t="inlineStr">
+        <is>
+          <t>正品Shiseido资生堂新款安耐晒防晒霜60ml高度防晒防水防汗SPF50+【5天内发货】</t>
+        </is>
+      </c>
       <c r="C505" s="2" t="inlineStr">
         <is>
-          <t>倩碧小雏菊裸色阳光腮#05</t>
+          <t>资生堂安耐晒60ml新版</t>
         </is>
       </c>
       <c r="D505" s="2" t="inlineStr"/>
-      <c r="E505" s="2" t="inlineStr">
-        <is>
-          <t>90.5</t>
-        </is>
+      <c r="E505" s="2" t="n">
+        <v>75</v>
       </c>
       <c r="F505" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G505" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
+      <c r="G505" s="2" t="inlineStr"/>
       <c r="H505" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I505" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I505" s="2" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" s="2" t="n">
-        <v>187</v>
-      </c>
-      <c r="B506" s="2" t="inlineStr"/>
+        <v>202</v>
+      </c>
+      <c r="B506" s="2" t="inlineStr">
+        <is>
+          <t>【4.55万人评价品牌正品】安耐晒小金瓶防晒霜24年新版60ML 防水防晒高倍防晒</t>
+        </is>
+      </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>薇迪薇奇净颜美肌洁面乳</t>
-        </is>
-      </c>
-      <c r="D506" s="2" t="inlineStr"/>
-      <c r="E506" s="2" t="inlineStr">
-        <is>
-          <t>119.0</t>
-        </is>
+          <t>资生堂安耐晒60ml新版</t>
+        </is>
+      </c>
+      <c r="D506" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="E506" s="2" t="n">
+        <v>88.90000000000001</v>
       </c>
       <c r="F506" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G506" s="2" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="H506" s="2" t="inlineStr">
@@ -19075,75 +19013,69 @@
       </c>
       <c r="I506" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；品名相似不足(ratio=0.0%)</t>
+          <t>品牌不一致；品名相似不足(ratio=50.0%)</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="n">
-        <v>187</v>
-      </c>
-      <c r="B507" s="2" t="inlineStr">
-        <is>
-          <t>VIDIVICI女神洗面奶净颜美肌洁面乳氨基酸温和保湿卸妆120ml正品</t>
-        </is>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="B507" s="2" t="inlineStr"/>
       <c r="C507" s="2" t="inlineStr">
         <is>
-          <t>薇迪薇奇净颜美肌洁面乳</t>
+          <t>资生堂安耐晒60ml新版</t>
         </is>
       </c>
       <c r="D507" s="2" t="inlineStr"/>
-      <c r="E507" s="2" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
+      <c r="E507" s="2" t="n">
+        <v>69</v>
       </c>
       <c r="F507" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G507" s="2" t="inlineStr">
-        <is>
-          <t>2024-05-02</t>
-        </is>
-      </c>
+      <c r="G507" s="2" t="inlineStr"/>
       <c r="H507" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I507" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I507" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="n">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="B508" s="2" t="inlineStr">
         <is>
-          <t>【薇姿】绿标洗发水390ml二硫化硒去头屑控油深层清洁舒缓头皮洗发露</t>
+          <t>【资生堂】百优精华面霜75ml补水保湿</t>
         </is>
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>薇姿VICHY洗发水绿标硫化硒去屑止痒控油洗发乳390ml</t>
-        </is>
-      </c>
-      <c r="D508" s="2" t="inlineStr"/>
-      <c r="E508" s="2" t="inlineStr">
-        <is>
-          <t>78.6</t>
-        </is>
+          <t>资生堂百优面霜 75ml</t>
+        </is>
+      </c>
+      <c r="D508" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="E508" s="2" t="n">
+        <v>245</v>
       </c>
       <c r="F508" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G508" s="2" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="H508" s="2" t="inlineStr">
@@ -19155,294 +19087,260 @@
     </row>
     <row r="509">
       <c r="A509" s="2" t="n">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="B509" s="2" t="inlineStr">
         <is>
-          <t>现货伟博深海鱼油Omega3 Webber三倍增强浓缩鱼油DHA900mg200粒</t>
+          <t>【SHISEIDO】资生堂新版蓝胖子防晒霜150ml防晒乳防水防汗不油腻</t>
         </is>
       </c>
       <c r="C509" s="2" t="inlineStr">
         <is>
-          <t>伟博金萃高纯度鱼油1100</t>
-        </is>
-      </c>
-      <c r="D509" s="2" t="inlineStr"/>
-      <c r="E509" s="2" t="inlineStr">
-        <is>
-          <t>191.36</t>
-        </is>
+          <t>资生堂蓝胖子150ml 新版</t>
+        </is>
+      </c>
+      <c r="D509" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="E509" s="2" t="n">
+        <v>99.90000000000001</v>
       </c>
       <c r="F509" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G509" s="2" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H509" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I509" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=28.6%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I509" s="2" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" s="2" t="n">
-        <v>189</v>
-      </c>
-      <c r="B510" s="2" t="inlineStr"/>
+        <v>204</v>
+      </c>
+      <c r="B510" s="2" t="inlineStr">
+        <is>
+          <t>资生堂蓝胖子新艳阳夏臻效水动力防晒乳150ml 超强防护力新版防水【6月18日发完】</t>
+        </is>
+      </c>
       <c r="C510" s="2" t="inlineStr">
         <is>
-          <t>伟博金萃高纯度鱼油1100</t>
+          <t>资生堂蓝胖子150ml 新版</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr"/>
-      <c r="E510" s="2" t="inlineStr">
-        <is>
-          <t>205.0</t>
-        </is>
+      <c r="E510" s="2" t="n">
+        <v>99.68000000000001</v>
       </c>
       <c r="F510" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G510" s="2" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
+      <c r="G510" s="2" t="inlineStr"/>
       <c r="H510" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I510" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I510" s="2" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" s="2" t="n">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="B511" s="2" t="inlineStr">
         <is>
-          <t>Webber Naturals伟博深海鱼油Omega-3高浓度三倍浓缩DHA成人200粒</t>
+          <t>【累计热销429.6万+件】2支资生堂新版蓝胖子防晒霜50ml隔离防紫外线</t>
         </is>
       </c>
       <c r="C511" s="2" t="inlineStr">
         <is>
-          <t>伟博金萃高纯度鱼油1100</t>
+          <t>资生堂蓝胖子防晒50ml</t>
         </is>
       </c>
       <c r="D511" s="2" t="inlineStr"/>
-      <c r="E511" s="2" t="inlineStr">
-        <is>
-          <t>200.0</t>
-        </is>
+      <c r="E511" s="2" t="n">
+        <v>359</v>
       </c>
       <c r="F511" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G511" s="2" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="H511" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I511" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=28.6%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I511" s="2" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" s="2" t="n">
-        <v>189</v>
-      </c>
-      <c r="B512" s="2" t="inlineStr"/>
+        <v>206</v>
+      </c>
+      <c r="B512" s="2" t="inlineStr">
+        <is>
+          <t>资生堂蓝胖子防晒霜50ml新版不油腻防水防晒乳艳阳清爽隔离SPF50+【6月18日发完】</t>
+        </is>
+      </c>
       <c r="C512" s="2" t="inlineStr">
         <is>
-          <t>伟博金萃高纯度鱼油1100</t>
+          <t>资生堂蓝胖子防晒50ml（新版）</t>
         </is>
       </c>
       <c r="D512" s="2" t="inlineStr"/>
-      <c r="E512" s="2" t="inlineStr">
-        <is>
-          <t>392.0</t>
-        </is>
+      <c r="E512" s="2" t="n">
+        <v>91.5</v>
       </c>
       <c r="F512" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G512" s="2" t="inlineStr">
-        <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
+      <c r="G512" s="2" t="inlineStr"/>
       <c r="H512" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I512" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I512" s="2" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" s="2" t="n">
-        <v>189</v>
-      </c>
-      <c r="B513" s="2" t="inlineStr"/>
+        <v>207</v>
+      </c>
+      <c r="B513" s="2" t="inlineStr">
+        <is>
+          <t>【资生堂】时光琉璃洁面125ml深层清洁保湿补水洗面奶</t>
+        </is>
+      </c>
       <c r="C513" s="2" t="inlineStr">
         <is>
-          <t>伟博金萃高纯度鱼油1100</t>
-        </is>
-      </c>
-      <c r="D513" s="2" t="inlineStr"/>
-      <c r="E513" s="2" t="inlineStr">
-        <is>
-          <t>172.0</t>
-        </is>
+          <t>资生堂琉璃洁面125ml</t>
+        </is>
+      </c>
+      <c r="D513" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="E513" s="2" t="n">
+        <v>110</v>
       </c>
       <c r="F513" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G513" s="2" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="H513" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I513" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I513" s="2" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" s="2" t="n">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="B514" s="2" t="inlineStr">
         <is>
-          <t>3瓶 伟博天然硫酸氨糖软骨素180粒强效MSM缓疼痛中老年人维骨力D3</t>
+          <t>【资生堂】时光琉璃洁面125ml温和保湿补水深层清洁洗面奶</t>
         </is>
       </c>
       <c r="C514" s="2" t="inlineStr">
         <is>
-          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
-        </is>
-      </c>
-      <c r="D514" s="2" t="inlineStr"/>
-      <c r="E514" s="2" t="inlineStr">
-        <is>
-          <t>486.0</t>
-        </is>
+          <t>资生堂琉璃洁面125ml</t>
+        </is>
+      </c>
+      <c r="D514" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="E514" s="2" t="n">
+        <v>109</v>
       </c>
       <c r="F514" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="H514" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I514" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I514" s="2" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" s="2" t="n">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="B515" s="2" t="inlineStr">
         <is>
-          <t>伟博硫酸氨糖软骨素 中老年成人维骨力D3促吸收 加拿大进口 180粒</t>
+          <t>【正品行货】资生堂时光琉璃洁面50ml</t>
         </is>
       </c>
       <c r="C515" s="2" t="inlineStr">
         <is>
-          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
+          <t>资生堂琉璃洁面50ml新版</t>
         </is>
       </c>
       <c r="D515" s="2" t="inlineStr"/>
-      <c r="E515" s="2" t="inlineStr">
-        <is>
-          <t>328.0</t>
-        </is>
+      <c r="E515" s="2" t="n">
+        <v>45.6</v>
       </c>
       <c r="F515" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G515" s="2" t="inlineStr">
-        <is>
-          <t>2025-09-12</t>
-        </is>
-      </c>
+      <c r="G515" s="2" t="inlineStr"/>
       <c r="H515" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I515" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；品名相似不足(ratio=45.5%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I515" s="2" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" s="2" t="n">
-        <v>190</v>
-      </c>
-      <c r="B516" s="2" t="inlineStr"/>
+        <v>209</v>
+      </c>
+      <c r="B516" s="2" t="inlineStr">
+        <is>
+          <t>【品牌好评340.2万+条】Shiseido/资生堂时光琉璃爽肤水74ml改善暗沉保湿紧致修复提亮</t>
+        </is>
+      </c>
       <c r="C516" s="2" t="inlineStr">
         <is>
-          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
+          <t>资生堂琉璃爽肤水74ml新版</t>
         </is>
       </c>
       <c r="D516" s="2" t="inlineStr"/>
-      <c r="E516" s="2" t="inlineStr">
-        <is>
-          <t>167.0</t>
-        </is>
+      <c r="E516" s="2" t="n">
+        <v>78.90000000000001</v>
       </c>
       <c r="F516" s="2" t="inlineStr">
         <is>
@@ -19451,39 +19349,33 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I516" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I516" s="2" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" s="2" t="n">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="B517" s="2" t="inlineStr">
         <is>
-          <t>加拿大伟博氨糖软骨素180粒中老年成人天然维骨力D3促钙吸收关节</t>
+          <t>【累计热销429.6万+件】Shiseido/资生堂时光琉璃爽肤水74ml补水保湿滋润紧致透亮修复</t>
         </is>
       </c>
       <c r="C517" s="2" t="inlineStr">
         <is>
-          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
+          <t>资生堂琉璃爽肤水74ml新版</t>
         </is>
       </c>
       <c r="D517" s="2" t="inlineStr"/>
-      <c r="E517" s="2" t="inlineStr">
-        <is>
-          <t>167.0</t>
-        </is>
+      <c r="E517" s="2" t="n">
+        <v>78.90000000000001</v>
       </c>
       <c r="F517" s="2" t="inlineStr">
         <is>
@@ -19492,113 +19384,111 @@
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="H517" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I517" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；品名相似不足(ratio=45.5%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I517" s="2" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" s="2" t="n">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="B518" s="2" t="inlineStr">
         <is>
-          <t>【520礼物】CHANEL/香奈儿山茶花洗面奶清爽控油净肤泡沫洁面乳</t>
+          <t>【正品行货】资生堂男士活力均衡水150ml修护保湿清爽控油爽肤水</t>
         </is>
       </c>
       <c r="C518" s="2" t="inlineStr">
         <is>
-          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
-        </is>
-      </c>
-      <c r="D518" s="2" t="inlineStr"/>
-      <c r="E518" s="2" t="inlineStr">
-        <is>
-          <t>408.0</t>
-        </is>
+          <t>资生堂男生爽肤水150ml</t>
+        </is>
+      </c>
+      <c r="D518" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="E518" s="2" t="n">
+        <v>72</v>
       </c>
       <c r="F518" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G518" s="2" t="inlineStr"/>
+      <c r="G518" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
       <c r="H518" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I518" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I518" s="2" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" s="2" t="n">
-        <v>191</v>
-      </c>
-      <c r="B519" s="2" t="inlineStr"/>
+        <v>210</v>
+      </c>
+      <c r="B519" s="2" t="inlineStr">
+        <is>
+          <t>【资生堂】男士活力均衡水150ml 男士补水保湿爽肤水</t>
+        </is>
+      </c>
       <c r="C519" s="2" t="inlineStr">
         <is>
-          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
+          <t>资生堂男生爽肤水150ml</t>
         </is>
       </c>
       <c r="D519" s="2" t="inlineStr"/>
-      <c r="E519" s="2" t="inlineStr">
-        <is>
-          <t>378.0</t>
-        </is>
+      <c r="E519" s="2" t="n">
+        <v>78.09999999999999</v>
       </c>
       <c r="F519" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G519" s="2" t="inlineStr"/>
+      <c r="G519" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
       <c r="H519" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I519" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I519" s="2" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" s="2" t="n">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="B520" s="2" t="inlineStr">
         <is>
-          <t>【原装正品】CHANEL香奈儿柔和净肤泡沫洁清洁 山茶花洁面 150ml</t>
+          <t>【资生堂】时光琉璃洁面125ml温和保湿补水深层清洁洗面奶</t>
         </is>
       </c>
       <c r="C520" s="2" t="inlineStr">
         <is>
-          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
-        </is>
-      </c>
-      <c r="D520" s="2" t="inlineStr"/>
-      <c r="E520" s="2" t="inlineStr">
-        <is>
-          <t>403.0</t>
-        </is>
+          <t>资生堂男士洁面乳125ml</t>
+        </is>
+      </c>
+      <c r="D520" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="E520" s="2" t="n">
+        <v>109</v>
       </c>
       <c r="F520" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G520" s="2" t="inlineStr"/>
@@ -19611,27 +19501,27 @@
     </row>
     <row r="521">
       <c r="A521" s="2" t="n">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="B521" s="2" t="inlineStr">
         <is>
-          <t>Chanel香奈儿山茶花洗面奶150ml柔和净肤泡沫洁面乳</t>
+          <t>【资生堂】时光琉璃洁面125ml深层清洁保湿补水洗面奶</t>
         </is>
       </c>
       <c r="C521" s="2" t="inlineStr">
         <is>
-          <t>香奈儿山茶花柔和净肤泡沫 洁面 女款 清爽 150ml</t>
-        </is>
-      </c>
-      <c r="D521" s="2" t="inlineStr"/>
-      <c r="E521" s="2" t="inlineStr">
-        <is>
-          <t>628.0</t>
-        </is>
+          <t>资生堂男士洁面乳125ml</t>
+        </is>
+      </c>
+      <c r="D521" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="E521" s="2" t="n">
+        <v>110</v>
       </c>
       <c r="F521" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G521" s="2" t="inlineStr"/>
@@ -19644,19 +19534,23 @@
     </row>
     <row r="522">
       <c r="A522" s="2" t="n">
-        <v>192</v>
-      </c>
-      <c r="B522" s="2" t="inlineStr"/>
+        <v>212</v>
+      </c>
+      <c r="B522" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂男士焕能肌活滋润乳 100ml</t>
+        </is>
+      </c>
       <c r="C522" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
-        </is>
-      </c>
-      <c r="D522" s="2" t="inlineStr"/>
-      <c r="E522" s="2" t="inlineStr">
-        <is>
-          <t>453.0</t>
-        </is>
+          <t>资生堂男士乳液100ml</t>
+        </is>
+      </c>
+      <c r="D522" s="2" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="E522" s="2" t="n">
+        <v>88.29000000000001</v>
       </c>
       <c r="F522" s="2" t="inlineStr">
         <is>
@@ -19665,7 +19559,7 @@
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="H522" s="2" t="inlineStr">
@@ -19675,36 +19569,38 @@
       </c>
       <c r="I522" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>品名相似不足(ratio=50.0%)</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="n">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="B523" s="2" t="inlineStr">
         <is>
-          <t>【雅诗兰黛】小棕瓶精华100ml第七代特润促进夜间修复抗衰香港仓发【5天内发货】</t>
+          <t>【跨境原装】资生堂悦薇水颜亮肤滋润乳液老款滋润亮肤紧颜100ml</t>
         </is>
       </c>
       <c r="C523" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
+          <t>资生堂男士乳液100ml</t>
         </is>
       </c>
       <c r="D523" s="2" t="inlineStr"/>
-      <c r="E523" s="2" t="inlineStr">
-        <is>
-          <t>407.99</t>
-        </is>
+      <c r="E523" s="2" t="n">
+        <v>134.55</v>
       </c>
       <c r="F523" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G523" s="2" t="inlineStr"/>
+      <c r="G523" s="2" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
       <c r="H523" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -19714,26 +19610,32 @@
     </row>
     <row r="524">
       <c r="A524" s="2" t="n">
-        <v>192</v>
-      </c>
-      <c r="B524" s="2" t="inlineStr"/>
+        <v>212</v>
+      </c>
+      <c r="B524" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂二代悦薇智感紧颜亮肤乳 100ml 清爽型</t>
+        </is>
+      </c>
       <c r="C524" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
+          <t>资生堂男士乳液100ml</t>
         </is>
       </c>
       <c r="D524" s="2" t="inlineStr"/>
-      <c r="E524" s="2" t="inlineStr">
-        <is>
-          <t>448.0</t>
-        </is>
+      <c r="E524" s="2" t="n">
+        <v>185</v>
       </c>
       <c r="F524" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G524" s="2" t="inlineStr"/>
+      <c r="G524" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
       <c r="H524" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -19741,36 +19643,34 @@
       </c>
       <c r="I524" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>品名相似不足(ratio=50.0%)</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="2" t="n">
-        <v>192</v>
-      </c>
-      <c r="B525" s="2" t="inlineStr"/>
+        <v>213</v>
+      </c>
+      <c r="B525" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂第二代悦薇水+乳(清爽 /滋润)</t>
+        </is>
+      </c>
       <c r="C525" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛 第七代 小棕瓶100ml</t>
+          <t>资生堂悦微清爽水150ml（新版）</t>
         </is>
       </c>
       <c r="D525" s="2" t="inlineStr"/>
-      <c r="E525" s="2" t="inlineStr">
-        <is>
-          <t>499.0</t>
-        </is>
+      <c r="E525" s="2" t="n">
+        <v>210</v>
       </c>
       <c r="F525" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G525" s="2" t="inlineStr">
-        <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G525" s="2" t="inlineStr"/>
       <c r="H525" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -19778,36 +19678,34 @@
       </c>
       <c r="I525" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="n">
-        <v>193</v>
-      </c>
-      <c r="B526" s="2" t="inlineStr"/>
+        <v>213</v>
+      </c>
+      <c r="B526" s="2" t="inlineStr">
+        <is>
+          <t>【特价清仓】资生堂悦薇水乳套装补水保湿清爽亮肤抗衰老滋润正装</t>
+        </is>
+      </c>
       <c r="C526" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛 净莹柔肤洁面乳150ml（蓝洁面）</t>
+          <t>资生堂悦微清爽水150ml（新版）</t>
         </is>
       </c>
       <c r="D526" s="2" t="inlineStr"/>
-      <c r="E526" s="2" t="inlineStr">
-        <is>
-          <t>112.0</t>
-        </is>
+      <c r="E526" s="2" t="n">
+        <v>195</v>
       </c>
       <c r="F526" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G526" s="2" t="inlineStr">
-        <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G526" s="2" t="inlineStr"/>
       <c r="H526" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -19815,106 +19713,104 @@
       </c>
       <c r="I526" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="2" t="n">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="B527" s="2" t="inlineStr">
         <is>
-          <t>【品牌好评451.2万+条】EsteeLauder雅诗兰黛净莹柔肤洁面乳蓝洁面150ml</t>
+          <t>【特价清仓】资生堂悦薇水乳套装补水保湿清爽亮肤抗衰老滋润正装</t>
         </is>
       </c>
       <c r="C527" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛 净莹柔肤洁面乳150ml（蓝洁面）</t>
+          <t>资生堂悦微滋润水150ml（新版）</t>
         </is>
       </c>
       <c r="D527" s="2" t="inlineStr"/>
-      <c r="E527" s="2" t="inlineStr">
-        <is>
-          <t>198.0</t>
-        </is>
+      <c r="E527" s="2" t="n">
+        <v>195</v>
       </c>
       <c r="F527" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G527" s="2" t="inlineStr">
-        <is>
-          <t>2025-02-02</t>
-        </is>
-      </c>
+      <c r="G527" s="2" t="inlineStr"/>
       <c r="H527" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I527" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I527" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="n">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="B528" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】雅诗兰黛DW方气垫2C0 持久遮瑕控油服帖</t>
+          <t>【特价清仓】资生堂悦薇水乳套装补水保湿清爽亮肤抗衰老滋润正装</t>
         </is>
       </c>
       <c r="C528" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛DW  2c0</t>
+          <t>资生堂悦微滋润水150ml（新版）</t>
         </is>
       </c>
       <c r="D528" s="2" t="inlineStr"/>
-      <c r="E528" s="2" t="inlineStr">
-        <is>
-          <t>188.0</t>
-        </is>
+      <c r="E528" s="2" t="n">
+        <v>146</v>
       </c>
       <c r="F528" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G528" s="2" t="inlineStr"/>
       <c r="H528" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I528" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I528" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="n">
-        <v>195</v>
-      </c>
-      <c r="B529" s="2" t="inlineStr"/>
+        <v>214</v>
+      </c>
+      <c r="B529" s="2" t="inlineStr">
+        <is>
+          <t>【全球购正品】资生堂悦薇珀翡紧颜亮肤水(滋润型)150ml</t>
+        </is>
+      </c>
       <c r="C529" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛大棕罐膜霜65ml</t>
+          <t>资生堂悦微滋润水150ml（新版）</t>
         </is>
       </c>
       <c r="D529" s="2" t="inlineStr"/>
-      <c r="E529" s="2" t="inlineStr">
-        <is>
-          <t>239.0</t>
-        </is>
+      <c r="E529" s="2" t="n">
+        <v>299</v>
       </c>
       <c r="F529" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G529" s="2" t="inlineStr">
-        <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
+      <c r="G529" s="2" t="inlineStr"/>
       <c r="H529" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -19922,36 +19818,36 @@
       </c>
       <c r="I529" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>品名相似不足(ratio=66.7%)</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="n">
-        <v>195</v>
-      </c>
-      <c r="B530" s="2" t="inlineStr"/>
+        <v>214</v>
+      </c>
+      <c r="B530" s="2" t="inlineStr">
+        <is>
+          <t>【SHISEIDO】资生堂第二代悦薇智感紧颜亮肤水150ml  补水提亮清爽版</t>
+        </is>
+      </c>
       <c r="C530" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛大棕罐膜霜65ml</t>
-        </is>
-      </c>
-      <c r="D530" s="2" t="inlineStr"/>
-      <c r="E530" s="2" t="inlineStr">
-        <is>
-          <t>247.0</t>
-        </is>
+          <t>资生堂悦微滋润水150ml（新版）</t>
+        </is>
+      </c>
+      <c r="D530" s="2" t="n">
+        <v>309</v>
+      </c>
+      <c r="E530" s="2" t="n">
+        <v>200.85</v>
       </c>
       <c r="F530" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G530" s="2" t="inlineStr">
-        <is>
-          <t>2024-09-30</t>
-        </is>
-      </c>
+      <c r="G530" s="2" t="inlineStr"/>
       <c r="H530" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -19959,29 +19855,27 @@
       </c>
       <c r="I530" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>品名相似不足(ratio=66.7%)</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="n">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="B531" s="2" t="inlineStr">
         <is>
-          <t>【78.6万人回购该品牌】Estee Lauder雅诗兰黛大棕罐封愈膜霜65ml紧致面霜</t>
+          <t>【正品行货】资生堂悦薇智感视黄醇抗皱霜 20ml 新版小针管眼霜</t>
         </is>
       </c>
       <c r="C531" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛大棕罐膜霜65ml</t>
+          <t>资生堂悦薇纯A小针管眼霜20ml</t>
         </is>
       </c>
       <c r="D531" s="2" t="inlineStr"/>
-      <c r="E531" s="2" t="inlineStr">
-        <is>
-          <t>369.0</t>
-        </is>
+      <c r="E531" s="2" t="n">
+        <v>256</v>
       </c>
       <c r="F531" s="2" t="inlineStr">
         <is>
@@ -19990,7 +19884,7 @@
       </c>
       <c r="G531" s="2" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="H531" s="2" t="inlineStr">
@@ -20002,19 +19896,21 @@
     </row>
     <row r="532">
       <c r="A532" s="2" t="n">
-        <v>195</v>
-      </c>
-      <c r="B532" s="2" t="inlineStr"/>
+        <v>216</v>
+      </c>
+      <c r="B532" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂二代悦薇智感紧颜亮肤乳 100ml 清爽型</t>
+        </is>
+      </c>
       <c r="C532" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛大棕罐膜霜65ml</t>
+          <t>资生堂悦薇滋润乳100ml（新版）</t>
         </is>
       </c>
       <c r="D532" s="2" t="inlineStr"/>
-      <c r="E532" s="2" t="inlineStr">
-        <is>
-          <t>399.0</t>
-        </is>
+      <c r="E532" s="2" t="n">
+        <v>185</v>
       </c>
       <c r="F532" s="2" t="inlineStr">
         <is>
@@ -20023,35 +19919,33 @@
       </c>
       <c r="G532" s="2" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H532" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I532" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I532" s="2" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" s="2" t="n">
-        <v>196</v>
-      </c>
-      <c r="B533" s="2" t="inlineStr"/>
+        <v>216</v>
+      </c>
+      <c r="B533" s="2" t="inlineStr">
+        <is>
+          <t>【跨境原装】资生堂悦薇水颜亮肤滋润乳液老款滋润亮肤紧颜100ml</t>
+        </is>
+      </c>
       <c r="C533" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴洁面60ml</t>
+          <t>资生堂悦薇滋润乳100ml（新版）</t>
         </is>
       </c>
       <c r="D533" s="2" t="inlineStr"/>
-      <c r="E533" s="2" t="inlineStr">
-        <is>
-          <t>111.0</t>
-        </is>
+      <c r="E533" s="2" t="n">
+        <v>134.55</v>
       </c>
       <c r="F533" s="2" t="inlineStr">
         <is>
@@ -20060,34 +19954,34 @@
       </c>
       <c r="G533" s="2" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="H533" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I533" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I533" s="2" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" s="2" t="n">
-        <v>196</v>
-      </c>
-      <c r="B534" s="2" t="inlineStr"/>
+        <v>214</v>
+      </c>
+      <c r="B534" s="2" t="inlineStr">
+        <is>
+          <t>【特价清仓】资生堂悦薇水乳套装补水保湿清爽亮肤抗衰老滋润正装</t>
+        </is>
+      </c>
       <c r="C534" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴洁面60ml</t>
+          <t>资生堂悦微滋润水150ml（新版）</t>
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr"/>
       <c r="E534" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="F534" s="2" t="inlineStr">
@@ -20095,11 +19989,7 @@
           <t>否</t>
         </is>
       </c>
-      <c r="G534" s="2" t="inlineStr">
-        <is>
-          <t>2024-07-31</t>
-        </is>
-      </c>
+      <c r="G534" s="2" t="inlineStr"/>
       <c r="H534" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -20107,28 +19997,28 @@
       </c>
       <c r="I534" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="n">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="B535" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】雅诗兰黛红石榴洁面洗面奶60ml  细致毛孔深层清洁</t>
+          <t>【特价清仓】资生堂悦薇水乳套装补水保湿清爽亮肤抗衰老滋润正装</t>
         </is>
       </c>
       <c r="C535" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴洁面60ml</t>
+          <t>资生堂悦微滋润水150ml（新版）</t>
         </is>
       </c>
       <c r="D535" s="2" t="inlineStr"/>
       <c r="E535" s="2" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="F535" s="2" t="inlineStr">
@@ -20139,29 +20029,33 @@
       <c r="G535" s="2" t="inlineStr"/>
       <c r="H535" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I535" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I535" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" s="2" t="n">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="B536" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】雅诗兰黛鲜活亮采红石榴洗面奶60ml深层清洁</t>
+          <t>【全球购正品】资生堂悦薇珀翡紧颜亮肤水(滋润型)150ml</t>
         </is>
       </c>
       <c r="C536" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴洁面60ml</t>
+          <t>资生堂悦微滋润水150ml（新版）</t>
         </is>
       </c>
       <c r="D536" s="2" t="inlineStr"/>
       <c r="E536" s="2" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="F536" s="2" t="inlineStr">
@@ -20177,9 +20071,198 @@
       </c>
       <c r="I536" s="2" t="inlineStr">
         <is>
-          <t>品名相似不足(ratio=50.0%)</t>
-        </is>
-      </c>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="B537" s="2" t="inlineStr">
+        <is>
+          <t>【SHISEIDO】资生堂第二代悦薇智感紧颜亮肤水150ml  补水提亮清爽版</t>
+        </is>
+      </c>
+      <c r="C537" s="2" t="inlineStr">
+        <is>
+          <t>资生堂悦微滋润水150ml（新版）</t>
+        </is>
+      </c>
+      <c r="D537" s="2" t="inlineStr">
+        <is>
+          <t>309.0</t>
+        </is>
+      </c>
+      <c r="E537" s="2" t="inlineStr">
+        <is>
+          <t>200.85</t>
+        </is>
+      </c>
+      <c r="F537" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G537" s="2" t="inlineStr"/>
+      <c r="H537" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I537" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="B538" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂悦薇智感视黄醇抗皱霜 20ml 新版小针管眼霜</t>
+        </is>
+      </c>
+      <c r="C538" s="2" t="inlineStr">
+        <is>
+          <t>资生堂悦薇纯A小针管眼霜20ml</t>
+        </is>
+      </c>
+      <c r="D538" s="2" t="inlineStr"/>
+      <c r="E538" s="2" t="inlineStr">
+        <is>
+          <t>256.0</t>
+        </is>
+      </c>
+      <c r="F538" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G538" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="H538" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I538" s="2" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="B539" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂二代悦薇智感紧颜亮肤乳 100ml 清爽型</t>
+        </is>
+      </c>
+      <c r="C539" s="2" t="inlineStr">
+        <is>
+          <t>资生堂悦薇滋润乳100ml（新版）</t>
+        </is>
+      </c>
+      <c r="D539" s="2" t="inlineStr"/>
+      <c r="E539" s="2" t="inlineStr">
+        <is>
+          <t>185.0</t>
+        </is>
+      </c>
+      <c r="F539" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G539" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="H539" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I539" s="2" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="B540" s="2" t="inlineStr">
+        <is>
+          <t>【跨境原装】资生堂悦薇水颜亮肤滋润乳液老款滋润亮肤紧颜100ml</t>
+        </is>
+      </c>
+      <c r="C540" s="2" t="inlineStr">
+        <is>
+          <t>资生堂悦薇滋润乳100ml（新版）</t>
+        </is>
+      </c>
+      <c r="D540" s="2" t="inlineStr"/>
+      <c r="E540" s="2" t="inlineStr">
+        <is>
+          <t>134.55</t>
+        </is>
+      </c>
+      <c r="F540" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G540" s="2" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="H540" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I540" s="2" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="B541" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂二代悦薇智感紧颜亮肤乳 100ml 清爽型</t>
+        </is>
+      </c>
+      <c r="C541" s="2" t="inlineStr">
+        <is>
+          <t>资生堂悦薇清爽乳100ml（新版）</t>
+        </is>
+      </c>
+      <c r="D541" s="2" t="inlineStr"/>
+      <c r="E541" s="2" t="inlineStr">
+        <is>
+          <t>185.0</t>
+        </is>
+      </c>
+      <c r="F541" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G541" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="H541" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I541" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/商品采集汇总.xlsx
+++ b/商品采集汇总.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I541"/>
+  <dimension ref="A1:I581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -19966,184 +19966,176 @@
     </row>
     <row r="534">
       <c r="A534" s="2" t="n">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B534" s="2" t="inlineStr">
         <is>
-          <t>【特价清仓】资生堂悦薇水乳套装补水保湿清爽亮肤抗衰老滋润正装</t>
+          <t>【正品行货】资生堂二代悦薇智感紧颜亮肤乳 100ml 清爽型</t>
         </is>
       </c>
       <c r="C534" s="2" t="inlineStr">
         <is>
-          <t>资生堂悦微滋润水150ml（新版）</t>
+          <t>资生堂悦薇清爽乳100ml（新版）</t>
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr"/>
-      <c r="E534" s="2" t="inlineStr">
-        <is>
-          <t>195.0</t>
-        </is>
+      <c r="E534" s="2" t="n">
+        <v>185</v>
       </c>
       <c r="F534" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G534" s="2" t="inlineStr"/>
+      <c r="G534" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
       <c r="H534" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I534" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I534" s="2" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" s="2" t="n">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B535" s="2" t="inlineStr">
         <is>
-          <t>【特价清仓】资生堂悦薇水乳套装补水保湿清爽亮肤抗衰老滋润正装</t>
+          <t>Jo Malone/祖玛珑蓝风铃100ml清新留香</t>
         </is>
       </c>
       <c r="C535" s="2" t="inlineStr">
         <is>
-          <t>资生堂悦微滋润水150ml（新版）</t>
+          <t>祖玛珑 蓝风铃香水100ml</t>
         </is>
       </c>
       <c r="D535" s="2" t="inlineStr"/>
-      <c r="E535" s="2" t="inlineStr">
-        <is>
-          <t>146.0</t>
-        </is>
+      <c r="E535" s="2" t="n">
+        <v>598</v>
       </c>
       <c r="F535" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G535" s="2" t="inlineStr"/>
+      <c r="G535" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
       <c r="H535" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I535" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I535" s="2" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" s="2" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B536" s="2" t="inlineStr">
         <is>
-          <t>【全球购正品】资生堂悦薇珀翡紧颜亮肤水(滋润型)150ml</t>
+          <t>祖玛珑鼠尾草与海盐香水30ml清新持久留香</t>
         </is>
       </c>
       <c r="C536" s="2" t="inlineStr">
         <is>
-          <t>资生堂悦微滋润水150ml（新版）</t>
-        </is>
-      </c>
-      <c r="D536" s="2" t="inlineStr"/>
-      <c r="E536" s="2" t="inlineStr">
-        <is>
-          <t>299.0</t>
-        </is>
+          <t>祖玛珑鼠尾草与海盐香水30ml</t>
+        </is>
+      </c>
+      <c r="D536" s="2" t="n">
+        <v>318</v>
+      </c>
+      <c r="E536" s="2" t="n">
+        <v>250.2</v>
       </c>
       <c r="F536" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G536" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G536" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
       <c r="H536" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I536" s="2" t="inlineStr">
-        <is>
-          <t>品名相似不足(ratio=66.7%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I536" s="2" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" s="2" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B537" s="2" t="inlineStr">
         <is>
-          <t>【SHISEIDO】资生堂第二代悦薇智感紧颜亮肤水150ml  补水提亮清爽版</t>
+          <t>【正品行货】JO MALONE/祖.玛珑鼠尾草与海盐30ml清新持久留香</t>
         </is>
       </c>
       <c r="C537" s="2" t="inlineStr">
         <is>
-          <t>资生堂悦微滋润水150ml（新版）</t>
-        </is>
-      </c>
-      <c r="D537" s="2" t="inlineStr">
-        <is>
-          <t>309.0</t>
-        </is>
-      </c>
-      <c r="E537" s="2" t="inlineStr">
-        <is>
-          <t>200.85</t>
-        </is>
+          <t>祖玛珑鼠尾草与海盐香水30ml</t>
+        </is>
+      </c>
+      <c r="D537" s="2" t="n">
+        <v>390</v>
+      </c>
+      <c r="E537" s="2" t="n">
+        <v>277.5</v>
       </c>
       <c r="F537" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G537" s="2" t="inlineStr"/>
+      <c r="G537" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
       <c r="H537" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I537" s="2" t="inlineStr">
-        <is>
-          <t>品名相似不足(ratio=66.7%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I537" s="2" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" s="2" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B538" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】资生堂悦薇智感视黄醇抗皱霜 20ml 新版小针管眼霜</t>
+          <t>【阿玛尼】蓝标大师粉底液 2 号 30ml 保湿遮瑕持久干皮</t>
         </is>
       </c>
       <c r="C538" s="2" t="inlineStr">
         <is>
-          <t>资生堂悦薇纯A小针管眼霜20ml</t>
-        </is>
-      </c>
-      <c r="D538" s="2" t="inlineStr"/>
-      <c r="E538" s="2" t="inlineStr">
-        <is>
-          <t>256.0</t>
-        </is>
+          <t>阿玛尼大师蓝标粉底液2#</t>
+        </is>
+      </c>
+      <c r="D538" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="E538" s="2" t="n">
+        <v>179.2</v>
       </c>
       <c r="F538" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G538" s="2" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="H538" s="2" t="inlineStr">
@@ -20155,34 +20147,30 @@
     </row>
     <row r="539">
       <c r="A539" s="2" t="n">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B539" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】资生堂二代悦薇智感紧颜亮肤乳 100ml 清爽型</t>
+          <t>【正品行货】阿玛尼新款蓝标大师粉底液#1 #2 #3持久遮瑕细腻服帖</t>
         </is>
       </c>
       <c r="C539" s="2" t="inlineStr">
         <is>
-          <t>资生堂悦薇滋润乳100ml（新版）</t>
-        </is>
-      </c>
-      <c r="D539" s="2" t="inlineStr"/>
-      <c r="E539" s="2" t="inlineStr">
-        <is>
-          <t>185.0</t>
-        </is>
+          <t>阿玛尼大师蓝标粉底液2#</t>
+        </is>
+      </c>
+      <c r="D539" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="E539" s="2" t="n">
+        <v>185</v>
       </c>
       <c r="F539" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G539" s="2" t="inlineStr">
-        <is>
-          <t>2024-05-22</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G539" s="2" t="inlineStr"/>
       <c r="H539" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -20192,23 +20180,21 @@
     </row>
     <row r="540">
       <c r="A540" s="2" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B540" s="2" t="inlineStr">
         <is>
-          <t>【跨境原装】资生堂悦薇水颜亮肤滋润乳液老款滋润亮肤紧颜100ml</t>
+          <t>【正品保证】阿玛尼权力PRO粉底液2# 绒雾质感混油肌粉底遮瑕【5天内发货】</t>
         </is>
       </c>
       <c r="C540" s="2" t="inlineStr">
         <is>
-          <t>资生堂悦薇滋润乳100ml（新版）</t>
+          <t>阿玛尼权力PR0粉底30ml#2</t>
         </is>
       </c>
       <c r="D540" s="2" t="inlineStr"/>
-      <c r="E540" s="2" t="inlineStr">
-        <is>
-          <t>134.55</t>
-        </is>
+      <c r="E540" s="2" t="n">
+        <v>227</v>
       </c>
       <c r="F540" s="2" t="inlineStr">
         <is>
@@ -20217,52 +20203,1578 @@
       </c>
       <c r="G540" s="2" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H540" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I540" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I540" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="B541" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】阿玛尼权力无瑕持妆PRO粉底液(红标)30ml 绒雾感遮瑕</t>
+        </is>
+      </c>
+      <c r="C541" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底30ml#2</t>
+        </is>
+      </c>
+      <c r="D541" s="2" t="inlineStr"/>
+      <c r="E541" s="2" t="n">
+        <v>255</v>
+      </c>
+      <c r="F541" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G541" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="H541" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I541" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="B542" s="2" t="inlineStr">
+        <is>
+          <t>【阿玛尼】权力粉底液 3 号新款 30ml 持妆控油遮瑕油皮亲妈持久</t>
+        </is>
+      </c>
+      <c r="C542" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底30ml#3</t>
+        </is>
+      </c>
+      <c r="D542" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="E542" s="2" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="F542" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G542" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="H542" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I542" s="2" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="2" t="n">
+        <v>223</v>
+      </c>
+      <c r="B543" s="2" t="inlineStr">
+        <is>
+          <t>【阿玛尼】蓝标大师粉底液3#新版遮瑕轻薄透气持久30ml</t>
+        </is>
+      </c>
+      <c r="C543" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼「大师」锁光粉底液#3</t>
+        </is>
+      </c>
+      <c r="D543" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="E543" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="F543" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G543" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="H543" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I543" s="2" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="B544" s="2" t="inlineStr">
+        <is>
+          <t>GIORGIO ARMANI/阿玛尼红气垫替换芯15g#3号色单双个控油持妆新款</t>
+        </is>
+      </c>
+      <c r="C544" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼气垫替换芯3号</t>
+        </is>
+      </c>
+      <c r="D544" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="E544" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="F544" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G544" s="2" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="H544" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I544" s="2" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="B545" s="2" t="inlineStr">
+        <is>
+          <t>【特价清仓】ARMANI阿玛尼红气垫替换芯3号15g新版 遮瑕养肤持久</t>
+        </is>
+      </c>
+      <c r="C545" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼气垫替换芯3号</t>
+        </is>
+      </c>
+      <c r="D545" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="E545" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="F545" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G545" s="2" t="inlineStr"/>
+      <c r="H545" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I545" s="2" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="B546" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】兰蔻全新菁纯柔雾哑光唇釉  275# 单支礼盒装</t>
+        </is>
+      </c>
+      <c r="C546" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻水唇釉275#</t>
+        </is>
+      </c>
+      <c r="D546" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="E546" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="F546" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G546" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="H546" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I546" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="B547" s="2" t="inlineStr">
+        <is>
+          <t>【兰蔻】菁纯裸唇釉小蛮腰275 279 313 281 274哑光丝绒柔雾口红正品</t>
+        </is>
+      </c>
+      <c r="C547" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻水唇釉275#</t>
+        </is>
+      </c>
+      <c r="D547" s="2" t="inlineStr"/>
+      <c r="E547" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="F547" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G547" s="2" t="inlineStr"/>
+      <c r="H547" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I547" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="B548" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】Lancome/兰蔻菁纯裸唇釉哑光丝绒轻盈质地显白有气色</t>
+        </is>
+      </c>
+      <c r="C548" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻水唇釉275#</t>
+        </is>
+      </c>
+      <c r="D548" s="2" t="inlineStr"/>
+      <c r="E548" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="F548" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G548" s="2" t="inlineStr"/>
+      <c r="H548" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I548" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="B549" s="2" t="inlineStr">
+        <is>
+          <t>【现货直发】兰蔻菁纯裸唇釉6ml  粉盖柔雾丝滑浓郁口红女生礼物</t>
+        </is>
+      </c>
+      <c r="C549" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻水唇釉275#</t>
+        </is>
+      </c>
+      <c r="D549" s="2" t="inlineStr"/>
+      <c r="E549" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="F549" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G549" s="2" t="inlineStr"/>
+      <c r="H549" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I549" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="n">
+        <v>226</v>
+      </c>
+      <c r="B550" s="2" t="inlineStr">
+        <is>
+          <t>Gucci古驰绮梦馥栀女士EDP浓香水50ml 25年新品</t>
+        </is>
+      </c>
+      <c r="C550" s="2" t="inlineStr">
+        <is>
+          <t>古驰绮梦栀子花香水50ml浓香型</t>
+        </is>
+      </c>
+      <c r="D550" s="2" t="n">
+        <v>537</v>
+      </c>
+      <c r="E550" s="2" t="n">
+        <v>338.52</v>
+      </c>
+      <c r="F550" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G550" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="H550" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I550" s="2" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="2" t="n">
+        <v>226</v>
+      </c>
+      <c r="B551" s="2" t="inlineStr">
+        <is>
+          <t>【全球购正品】古驰绮梦馥栀香型女士香水50ml</t>
+        </is>
+      </c>
+      <c r="C551" s="2" t="inlineStr">
+        <is>
+          <t>古驰绮梦栀子花香水50ml浓香型</t>
+        </is>
+      </c>
+      <c r="D551" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="E551" s="2" t="n">
+        <v>357</v>
+      </c>
+      <c r="F551" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G551" s="2" t="inlineStr"/>
+      <c r="H551" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I551" s="2" t="inlineStr"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="n">
+        <v>226</v>
+      </c>
+      <c r="B552" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI古驰绮梦馥栀女士香水红瓶馥郁版EDP 50ml</t>
+        </is>
+      </c>
+      <c r="C552" s="2" t="inlineStr">
+        <is>
+          <t>古驰绮梦栀子花香水50ml浓香型</t>
+        </is>
+      </c>
+      <c r="D552" s="2" t="inlineStr"/>
+      <c r="E552" s="2" t="n">
+        <v>743</v>
+      </c>
+      <c r="F552" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G552" s="2" t="inlineStr"/>
+      <c r="H552" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I552" s="2" t="inlineStr"/>
+    </row>
+    <row r="553">
+      <c r="A553" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="B553" s="2" t="inlineStr">
+        <is>
+          <t>【特价清仓】资生堂悦薇水乳套装补水保湿清爽亮肤抗衰老滋润正装</t>
+        </is>
+      </c>
+      <c r="C553" s="2" t="inlineStr">
+        <is>
+          <t>资生堂悦微滋润水150ml（新版）</t>
+        </is>
+      </c>
+      <c r="D553" s="2" t="inlineStr"/>
+      <c r="E553" s="2" t="inlineStr">
+        <is>
+          <t>195.0</t>
+        </is>
+      </c>
+      <c r="F553" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G553" s="2" t="inlineStr"/>
+      <c r="H553" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I553" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="B554" s="2" t="inlineStr">
+        <is>
+          <t>【特价清仓】资生堂悦薇水乳套装补水保湿清爽亮肤抗衰老滋润正装</t>
+        </is>
+      </c>
+      <c r="C554" s="2" t="inlineStr">
+        <is>
+          <t>资生堂悦微滋润水150ml（新版）</t>
+        </is>
+      </c>
+      <c r="D554" s="2" t="inlineStr"/>
+      <c r="E554" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="F554" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G554" s="2" t="inlineStr"/>
+      <c r="H554" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I554" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="B555" s="2" t="inlineStr">
+        <is>
+          <t>【全球购正品】资生堂悦薇珀翡紧颜亮肤水(滋润型)150ml</t>
+        </is>
+      </c>
+      <c r="C555" s="2" t="inlineStr">
+        <is>
+          <t>资生堂悦微滋润水150ml（新版）</t>
+        </is>
+      </c>
+      <c r="D555" s="2" t="inlineStr"/>
+      <c r="E555" s="2" t="inlineStr">
+        <is>
+          <t>299.0</t>
+        </is>
+      </c>
+      <c r="F555" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G555" s="2" t="inlineStr"/>
+      <c r="H555" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I555" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="B556" s="2" t="inlineStr">
+        <is>
+          <t>【SHISEIDO】资生堂第二代悦薇智感紧颜亮肤水150ml  补水提亮清爽版</t>
+        </is>
+      </c>
+      <c r="C556" s="2" t="inlineStr">
+        <is>
+          <t>资生堂悦微滋润水150ml（新版）</t>
+        </is>
+      </c>
+      <c r="D556" s="2" t="inlineStr">
+        <is>
+          <t>309.0</t>
+        </is>
+      </c>
+      <c r="E556" s="2" t="inlineStr">
+        <is>
+          <t>200.85</t>
+        </is>
+      </c>
+      <c r="F556" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G556" s="2" t="inlineStr"/>
+      <c r="H556" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I556" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="B557" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂悦薇智感视黄醇抗皱霜 20ml 新版小针管眼霜</t>
+        </is>
+      </c>
+      <c r="C557" s="2" t="inlineStr">
+        <is>
+          <t>资生堂悦薇纯A小针管眼霜20ml</t>
+        </is>
+      </c>
+      <c r="D557" s="2" t="inlineStr"/>
+      <c r="E557" s="2" t="inlineStr">
+        <is>
+          <t>256.0</t>
+        </is>
+      </c>
+      <c r="F557" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G557" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="H557" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I557" s="2" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="B558" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂二代悦薇智感紧颜亮肤乳 100ml 清爽型</t>
+        </is>
+      </c>
+      <c r="C558" s="2" t="inlineStr">
+        <is>
+          <t>资生堂悦薇滋润乳100ml（新版）</t>
+        </is>
+      </c>
+      <c r="D558" s="2" t="inlineStr"/>
+      <c r="E558" s="2" t="inlineStr">
+        <is>
+          <t>185.0</t>
+        </is>
+      </c>
+      <c r="F558" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G558" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="H558" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I558" s="2" t="inlineStr"/>
+    </row>
+    <row r="559">
+      <c r="A559" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="B559" s="2" t="inlineStr">
+        <is>
+          <t>【跨境原装】资生堂悦薇水颜亮肤滋润乳液老款滋润亮肤紧颜100ml</t>
+        </is>
+      </c>
+      <c r="C559" s="2" t="inlineStr">
+        <is>
+          <t>资生堂悦薇滋润乳100ml（新版）</t>
+        </is>
+      </c>
+      <c r="D559" s="2" t="inlineStr"/>
+      <c r="E559" s="2" t="inlineStr">
+        <is>
+          <t>134.55</t>
+        </is>
+      </c>
+      <c r="F559" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G559" s="2" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="H559" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I559" s="2" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" s="2" t="n">
         <v>217</v>
       </c>
-      <c r="B541" s="2" t="inlineStr">
+      <c r="B560" s="2" t="inlineStr">
         <is>
           <t>【正品行货】资生堂二代悦薇智感紧颜亮肤乳 100ml 清爽型</t>
         </is>
       </c>
-      <c r="C541" s="2" t="inlineStr">
+      <c r="C560" s="2" t="inlineStr">
         <is>
           <t>资生堂悦薇清爽乳100ml（新版）</t>
         </is>
       </c>
-      <c r="D541" s="2" t="inlineStr"/>
-      <c r="E541" s="2" t="inlineStr">
+      <c r="D560" s="2" t="inlineStr"/>
+      <c r="E560" s="2" t="inlineStr">
         <is>
           <t>185.0</t>
         </is>
       </c>
-      <c r="F541" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G541" s="2" t="inlineStr">
+      <c r="F560" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G560" s="2" t="inlineStr">
         <is>
           <t>2024-05-22</t>
         </is>
       </c>
-      <c r="H541" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I541" s="2" t="inlineStr"/>
+      <c r="H560" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I560" s="2" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="B561" s="2" t="inlineStr">
+        <is>
+          <t>Jo Malone/祖玛珑蓝风铃100ml清新留香</t>
+        </is>
+      </c>
+      <c r="C561" s="2" t="inlineStr">
+        <is>
+          <t>祖玛珑 蓝风铃香水100ml</t>
+        </is>
+      </c>
+      <c r="D561" s="2" t="inlineStr"/>
+      <c r="E561" s="2" t="inlineStr">
+        <is>
+          <t>598.0</t>
+        </is>
+      </c>
+      <c r="F561" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G561" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="H561" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I561" s="2" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="B562" s="2" t="inlineStr">
+        <is>
+          <t>祖玛珑鼠尾草与海盐香水30ml清新持久留香</t>
+        </is>
+      </c>
+      <c r="C562" s="2" t="inlineStr">
+        <is>
+          <t>祖玛珑鼠尾草与海盐香水30ml</t>
+        </is>
+      </c>
+      <c r="D562" s="2" t="inlineStr">
+        <is>
+          <t>318.0</t>
+        </is>
+      </c>
+      <c r="E562" s="2" t="inlineStr">
+        <is>
+          <t>250.2</t>
+        </is>
+      </c>
+      <c r="F562" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G562" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="H562" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I562" s="2" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="B563" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】JO MALONE/祖.玛珑鼠尾草与海盐30ml清新持久留香</t>
+        </is>
+      </c>
+      <c r="C563" s="2" t="inlineStr">
+        <is>
+          <t>祖玛珑鼠尾草与海盐香水30ml</t>
+        </is>
+      </c>
+      <c r="D563" s="2" t="inlineStr">
+        <is>
+          <t>390.0</t>
+        </is>
+      </c>
+      <c r="E563" s="2" t="inlineStr">
+        <is>
+          <t>277.5</t>
+        </is>
+      </c>
+      <c r="F563" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G563" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="H563" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I563" s="2" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="B564" s="2" t="inlineStr">
+        <is>
+          <t>【阿玛尼】蓝标大师粉底液 2 号 30ml 保湿遮瑕持久干皮</t>
+        </is>
+      </c>
+      <c r="C564" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼大师蓝标粉底液2#</t>
+        </is>
+      </c>
+      <c r="D564" s="2" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="E564" s="2" t="inlineStr">
+        <is>
+          <t>179.2</t>
+        </is>
+      </c>
+      <c r="F564" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G564" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H564" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I564" s="2" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="B565" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】阿玛尼新款蓝标大师粉底液#1 #2 #3持久遮瑕细腻服帖</t>
+        </is>
+      </c>
+      <c r="C565" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼大师蓝标粉底液2#</t>
+        </is>
+      </c>
+      <c r="D565" s="2" t="inlineStr">
+        <is>
+          <t>289.0</t>
+        </is>
+      </c>
+      <c r="E565" s="2" t="inlineStr">
+        <is>
+          <t>185.0</t>
+        </is>
+      </c>
+      <c r="F565" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G565" s="2" t="inlineStr"/>
+      <c r="H565" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I565" s="2" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="B566" s="2" t="inlineStr">
+        <is>
+          <t>【正品保证】阿玛尼权力PRO粉底液2# 绒雾质感混油肌粉底遮瑕【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C566" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底30ml#2</t>
+        </is>
+      </c>
+      <c r="D566" s="2" t="inlineStr"/>
+      <c r="E566" s="2" t="inlineStr">
+        <is>
+          <t>227.0</t>
+        </is>
+      </c>
+      <c r="F566" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G566" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="H566" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I566" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="B567" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】阿玛尼权力无瑕持妆PRO粉底液(红标)30ml 绒雾感遮瑕</t>
+        </is>
+      </c>
+      <c r="C567" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底30ml#2</t>
+        </is>
+      </c>
+      <c r="D567" s="2" t="inlineStr"/>
+      <c r="E567" s="2" t="inlineStr">
+        <is>
+          <t>255.0</t>
+        </is>
+      </c>
+      <c r="F567" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G567" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="H567" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I567" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="B568" s="2" t="inlineStr">
+        <is>
+          <t>【阿玛尼】权力粉底液 3 号新款 30ml 持妆控油遮瑕油皮亲妈持久</t>
+        </is>
+      </c>
+      <c r="C568" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底30ml#3</t>
+        </is>
+      </c>
+      <c r="D568" s="2" t="inlineStr">
+        <is>
+          <t>299.0</t>
+        </is>
+      </c>
+      <c r="E568" s="2" t="inlineStr">
+        <is>
+          <t>182.6</t>
+        </is>
+      </c>
+      <c r="F568" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G568" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="H568" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I568" s="2" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" s="2" t="n">
+        <v>223</v>
+      </c>
+      <c r="B569" s="2" t="inlineStr">
+        <is>
+          <t>【阿玛尼】蓝标大师粉底液3#新版遮瑕轻薄透气持久30ml</t>
+        </is>
+      </c>
+      <c r="C569" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼「大师」锁光粉底液#3</t>
+        </is>
+      </c>
+      <c r="D569" s="2" t="inlineStr">
+        <is>
+          <t>299.0</t>
+        </is>
+      </c>
+      <c r="E569" s="2" t="inlineStr">
+        <is>
+          <t>193.0</t>
+        </is>
+      </c>
+      <c r="F569" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G569" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="H569" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I569" s="2" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="B570" s="2" t="inlineStr">
+        <is>
+          <t>GIORGIO ARMANI/阿玛尼红气垫替换芯15g#3号色单双个控油持妆新款</t>
+        </is>
+      </c>
+      <c r="C570" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼气垫替换芯3号</t>
+        </is>
+      </c>
+      <c r="D570" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="E570" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="F570" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G570" s="2" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="H570" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I570" s="2" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="B571" s="2" t="inlineStr">
+        <is>
+          <t>【特价清仓】ARMANI阿玛尼红气垫替换芯3号15g新版 遮瑕养肤持久</t>
+        </is>
+      </c>
+      <c r="C571" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼气垫替换芯3号</t>
+        </is>
+      </c>
+      <c r="D571" s="2" t="inlineStr">
+        <is>
+          <t>188.0</t>
+        </is>
+      </c>
+      <c r="E571" s="2" t="inlineStr">
+        <is>
+          <t>108.0</t>
+        </is>
+      </c>
+      <c r="F571" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G571" s="2" t="inlineStr"/>
+      <c r="H571" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I571" s="2" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="B572" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】兰蔻全新菁纯柔雾哑光唇釉  275# 单支礼盒装</t>
+        </is>
+      </c>
+      <c r="C572" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻水唇釉275#</t>
+        </is>
+      </c>
+      <c r="D572" s="2" t="inlineStr">
+        <is>
+          <t>239.0</t>
+        </is>
+      </c>
+      <c r="E572" s="2" t="inlineStr">
+        <is>
+          <t>190.0</t>
+        </is>
+      </c>
+      <c r="F572" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G572" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="H572" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I572" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="B573" s="2" t="inlineStr">
+        <is>
+          <t>【兰蔻】菁纯裸唇釉小蛮腰275 279 313 281 274哑光丝绒柔雾口红正品</t>
+        </is>
+      </c>
+      <c r="C573" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻水唇釉275#</t>
+        </is>
+      </c>
+      <c r="D573" s="2" t="inlineStr"/>
+      <c r="E573" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="F573" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G573" s="2" t="inlineStr"/>
+      <c r="H573" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I573" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="B574" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】Lancome/兰蔻菁纯裸唇釉哑光丝绒轻盈质地显白有气色</t>
+        </is>
+      </c>
+      <c r="C574" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻水唇釉275#</t>
+        </is>
+      </c>
+      <c r="D574" s="2" t="inlineStr"/>
+      <c r="E574" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="F574" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G574" s="2" t="inlineStr"/>
+      <c r="H574" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I574" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="B575" s="2" t="inlineStr">
+        <is>
+          <t>【现货直发】兰蔻菁纯裸唇釉6ml  粉盖柔雾丝滑浓郁口红女生礼物</t>
+        </is>
+      </c>
+      <c r="C575" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻水唇釉275#</t>
+        </is>
+      </c>
+      <c r="D575" s="2" t="inlineStr"/>
+      <c r="E575" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="F575" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G575" s="2" t="inlineStr"/>
+      <c r="H575" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I575" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="2" t="n">
+        <v>226</v>
+      </c>
+      <c r="B576" s="2" t="inlineStr">
+        <is>
+          <t>Gucci古驰绮梦馥栀女士EDP浓香水50ml 25年新品</t>
+        </is>
+      </c>
+      <c r="C576" s="2" t="inlineStr">
+        <is>
+          <t>古驰绮梦栀子花香水50ml浓香型</t>
+        </is>
+      </c>
+      <c r="D576" s="2" t="inlineStr">
+        <is>
+          <t>537.0</t>
+        </is>
+      </c>
+      <c r="E576" s="2" t="inlineStr">
+        <is>
+          <t>338.52</t>
+        </is>
+      </c>
+      <c r="F576" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G576" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="H576" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I576" s="2" t="inlineStr"/>
+    </row>
+    <row r="577">
+      <c r="A577" s="2" t="n">
+        <v>226</v>
+      </c>
+      <c r="B577" s="2" t="inlineStr">
+        <is>
+          <t>【全球购正品】古驰绮梦馥栀香型女士香水50ml</t>
+        </is>
+      </c>
+      <c r="C577" s="2" t="inlineStr">
+        <is>
+          <t>古驰绮梦栀子花香水50ml浓香型</t>
+        </is>
+      </c>
+      <c r="D577" s="2" t="inlineStr">
+        <is>
+          <t>499.0</t>
+        </is>
+      </c>
+      <c r="E577" s="2" t="inlineStr">
+        <is>
+          <t>357.0</t>
+        </is>
+      </c>
+      <c r="F577" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G577" s="2" t="inlineStr"/>
+      <c r="H577" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I577" s="2" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" s="2" t="n">
+        <v>226</v>
+      </c>
+      <c r="B578" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI古驰绮梦馥栀女士香水红瓶馥郁版EDP 50ml</t>
+        </is>
+      </c>
+      <c r="C578" s="2" t="inlineStr">
+        <is>
+          <t>古驰绮梦栀子花香水50ml浓香型</t>
+        </is>
+      </c>
+      <c r="D578" s="2" t="inlineStr"/>
+      <c r="E578" s="2" t="inlineStr">
+        <is>
+          <t>743.0</t>
+        </is>
+      </c>
+      <c r="F578" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G578" s="2" t="inlineStr"/>
+      <c r="H578" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I578" s="2" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="B579" s="2" t="inlineStr">
+        <is>
+          <t>POLA/宝丽第七代洗面奶黑BA控油保湿抗衰老洁面2支</t>
+        </is>
+      </c>
+      <c r="C579" s="2" t="inlineStr">
+        <is>
+          <t>POLA 黑BA洁面</t>
+        </is>
+      </c>
+      <c r="D579" s="2" t="inlineStr">
+        <is>
+          <t>678.0</t>
+        </is>
+      </c>
+      <c r="E579" s="2" t="inlineStr">
+        <is>
+          <t>563.0</t>
+        </is>
+      </c>
+      <c r="F579" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G579" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="H579" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I579" s="2" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="B580" s="2" t="inlineStr">
+        <is>
+          <t>日本本土版第七代POLA/宝丽黑BA抗糖保湿洁面洗面奶</t>
+        </is>
+      </c>
+      <c r="C580" s="2" t="inlineStr">
+        <is>
+          <t>POLA 黑BA洁面</t>
+        </is>
+      </c>
+      <c r="D580" s="2" t="inlineStr">
+        <is>
+          <t>398.0</t>
+        </is>
+      </c>
+      <c r="E580" s="2" t="inlineStr">
+        <is>
+          <t>276.9</t>
+        </is>
+      </c>
+      <c r="F580" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G580" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="H580" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I580" s="2" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="B581" s="2" t="inlineStr">
+        <is>
+          <t>【POLA】宝丽BA深层清洁洗面奶9g*5小样洁面乳温和不紧绷</t>
+        </is>
+      </c>
+      <c r="C581" s="2" t="inlineStr">
+        <is>
+          <t>POLA 黑BA洁面</t>
+        </is>
+      </c>
+      <c r="D581" s="2" t="inlineStr">
+        <is>
+          <t>172.1</t>
+        </is>
+      </c>
+      <c r="E581" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="F581" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G581" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="H581" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I581" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/商品采集汇总.xlsx
+++ b/商品采集汇总.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I581"/>
+  <dimension ref="A1:I737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -20649,175 +20649,171 @@
     </row>
     <row r="553">
       <c r="A553" s="2" t="n">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="B553" s="2" t="inlineStr">
         <is>
-          <t>【特价清仓】资生堂悦薇水乳套装补水保湿清爽亮肤抗衰老滋润正装</t>
+          <t>POLA/宝丽第七代洗面奶黑BA控油保湿抗衰老洁面2支</t>
         </is>
       </c>
       <c r="C553" s="2" t="inlineStr">
         <is>
-          <t>资生堂悦微滋润水150ml（新版）</t>
-        </is>
-      </c>
-      <c r="D553" s="2" t="inlineStr"/>
-      <c r="E553" s="2" t="inlineStr">
-        <is>
-          <t>195.0</t>
-        </is>
+          <t>POLA 黑BA洁面</t>
+        </is>
+      </c>
+      <c r="D553" s="2" t="n">
+        <v>678</v>
+      </c>
+      <c r="E553" s="2" t="n">
+        <v>563</v>
       </c>
       <c r="F553" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G553" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G553" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
       <c r="H553" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I553" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I553" s="2" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" s="2" t="n">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="B554" s="2" t="inlineStr">
         <is>
-          <t>【特价清仓】资生堂悦薇水乳套装补水保湿清爽亮肤抗衰老滋润正装</t>
+          <t>日本本土版第七代POLA/宝丽黑BA抗糖保湿洁面洗面奶</t>
         </is>
       </c>
       <c r="C554" s="2" t="inlineStr">
         <is>
-          <t>资生堂悦微滋润水150ml（新版）</t>
-        </is>
-      </c>
-      <c r="D554" s="2" t="inlineStr"/>
-      <c r="E554" s="2" t="inlineStr">
-        <is>
-          <t>146.0</t>
-        </is>
+          <t>POLA 黑BA洁面</t>
+        </is>
+      </c>
+      <c r="D554" s="2" t="n">
+        <v>398</v>
+      </c>
+      <c r="E554" s="2" t="n">
+        <v>276.9</v>
       </c>
       <c r="F554" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G554" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G554" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
       <c r="H554" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I554" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I554" s="2" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" s="2" t="n">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="B555" s="2" t="inlineStr">
         <is>
-          <t>【全球购正品】资生堂悦薇珀翡紧颜亮肤水(滋润型)150ml</t>
+          <t>【POLA】宝丽BA深层清洁洗面奶9g*5小样洁面乳温和不紧绷</t>
         </is>
       </c>
       <c r="C555" s="2" t="inlineStr">
         <is>
-          <t>资生堂悦微滋润水150ml（新版）</t>
-        </is>
-      </c>
-      <c r="D555" s="2" t="inlineStr"/>
-      <c r="E555" s="2" t="inlineStr">
-        <is>
-          <t>299.0</t>
-        </is>
+          <t>POLA 黑BA洁面</t>
+        </is>
+      </c>
+      <c r="D555" s="2" t="n">
+        <v>172.1</v>
+      </c>
+      <c r="E555" s="2" t="n">
+        <v>105</v>
       </c>
       <c r="F555" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G555" s="2" t="inlineStr"/>
+      <c r="G555" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
       <c r="H555" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I555" s="2" t="inlineStr">
-        <is>
-          <t>品名相似不足(ratio=66.7%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I555" s="2" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" s="2" t="n">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="B556" s="2" t="inlineStr">
         <is>
-          <t>【SHISEIDO】资生堂第二代悦薇智感紧颜亮肤水150ml  补水提亮清爽版</t>
+          <t>HR/赫莲娜绿宝瓶眼霜15ml+小样3ml*5眼部修复淡化黑眼圈【5天内发货】</t>
         </is>
       </c>
       <c r="C556" s="2" t="inlineStr">
         <is>
-          <t>资生堂悦微滋润水150ml（新版）</t>
-        </is>
-      </c>
-      <c r="D556" s="2" t="inlineStr">
-        <is>
-          <t>309.0</t>
-        </is>
-      </c>
-      <c r="E556" s="2" t="inlineStr">
-        <is>
-          <t>200.85</t>
-        </is>
+          <t>HR赫莲娜绿宝瓶眼霜15ml</t>
+        </is>
+      </c>
+      <c r="D556" s="2" t="n">
+        <v>799</v>
+      </c>
+      <c r="E556" s="2" t="n">
+        <v>568</v>
       </c>
       <c r="F556" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G556" s="2" t="inlineStr"/>
+      <c r="G556" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
       <c r="H556" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I556" s="2" t="inlineStr">
-        <is>
-          <t>品名相似不足(ratio=66.7%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I556" s="2" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" s="2" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="B557" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】资生堂悦薇智感视黄醇抗皱霜 20ml 新版小针管眼霜</t>
+          <t>HR/赫莲娜绿宝瓶眼霜15ml眼部修复淡化黑眼圈【5天内发货】</t>
         </is>
       </c>
       <c r="C557" s="2" t="inlineStr">
         <is>
-          <t>资生堂悦薇纯A小针管眼霜20ml</t>
-        </is>
-      </c>
-      <c r="D557" s="2" t="inlineStr"/>
-      <c r="E557" s="2" t="inlineStr">
-        <is>
-          <t>256.0</t>
-        </is>
+          <t>HR赫莲娜绿宝瓶眼霜15ml</t>
+        </is>
+      </c>
+      <c r="D557" s="2" t="n">
+        <v>599</v>
+      </c>
+      <c r="E557" s="2" t="n">
+        <v>419</v>
       </c>
       <c r="F557" s="2" t="inlineStr">
         <is>
@@ -20826,7 +20822,7 @@
       </c>
       <c r="G557" s="2" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="H557" s="2" t="inlineStr">
@@ -20838,23 +20834,23 @@
     </row>
     <row r="558">
       <c r="A558" s="2" t="n">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="B558" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】资生堂二代悦薇智感紧颜亮肤乳 100ml 清爽型</t>
+          <t>【HR】赫莲娜绿宝瓶眼霜15ml淡化黑眼圈护肤品化妆品情人节520礼盒</t>
         </is>
       </c>
       <c r="C558" s="2" t="inlineStr">
         <is>
-          <t>资生堂悦薇滋润乳100ml（新版）</t>
-        </is>
-      </c>
-      <c r="D558" s="2" t="inlineStr"/>
-      <c r="E558" s="2" t="inlineStr">
-        <is>
-          <t>185.0</t>
-        </is>
+          <t>HR赫莲娜绿宝瓶眼霜15ml</t>
+        </is>
+      </c>
+      <c r="D558" s="2" t="n">
+        <v>1220</v>
+      </c>
+      <c r="E558" s="2" t="n">
+        <v>769</v>
       </c>
       <c r="F558" s="2" t="inlineStr">
         <is>
@@ -20863,7 +20859,7 @@
       </c>
       <c r="G558" s="2" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="H558" s="2" t="inlineStr">
@@ -20875,179 +20871,173 @@
     </row>
     <row r="559">
       <c r="A559" s="2" t="n">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="B559" s="2" t="inlineStr">
         <is>
-          <t>【跨境原装】资生堂悦薇水颜亮肤滋润乳液老款滋润亮肤紧颜100ml</t>
+          <t>【旧街场】白咖啡马来西亚进口经典原味榛果咖啡三合一速溶咖啡粉*2袋</t>
         </is>
       </c>
       <c r="C559" s="2" t="inlineStr">
         <is>
-          <t>资生堂悦薇滋润乳100ml（新版）</t>
-        </is>
-      </c>
-      <c r="D559" s="2" t="inlineStr"/>
-      <c r="E559" s="2" t="inlineStr">
-        <is>
-          <t>134.55</t>
-        </is>
+          <t>马来西亚旧街场三合一经典原味白咖啡525g</t>
+        </is>
+      </c>
+      <c r="D559" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="E559" s="2" t="n">
+        <v>51</v>
       </c>
       <c r="F559" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G559" s="2" t="inlineStr">
-        <is>
-          <t>2023-07-01</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G559" s="2" t="inlineStr"/>
       <c r="H559" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I559" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I559" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" s="2" t="n">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="B560" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】资生堂二代悦薇智感紧颜亮肤乳 100ml 清爽型</t>
+          <t>【旧街场】白咖啡马来西亚进口经典原味榛果咖啡三合一速溶咖啡粉*2袋</t>
         </is>
       </c>
       <c r="C560" s="2" t="inlineStr">
         <is>
-          <t>资生堂悦薇清爽乳100ml（新版）</t>
-        </is>
-      </c>
-      <c r="D560" s="2" t="inlineStr"/>
-      <c r="E560" s="2" t="inlineStr">
-        <is>
-          <t>185.0</t>
-        </is>
+          <t>马来西亚旧街场三合一榛果味白咖啡525g</t>
+        </is>
+      </c>
+      <c r="D560" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="E560" s="2" t="n">
+        <v>51</v>
       </c>
       <c r="F560" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G560" s="2" t="inlineStr">
-        <is>
-          <t>2024-05-22</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G560" s="2" t="inlineStr"/>
       <c r="H560" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I560" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I560" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" s="2" t="n">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="B561" s="2" t="inlineStr">
         <is>
-          <t>Jo Malone/祖玛珑蓝风铃100ml清新留香</t>
+          <t>进口马来西亚旧街场经典白咖啡三合一原味榛果少糖特浓15条装袋装</t>
         </is>
       </c>
       <c r="C561" s="2" t="inlineStr">
         <is>
-          <t>祖玛珑 蓝风铃香水100ml</t>
-        </is>
-      </c>
-      <c r="D561" s="2" t="inlineStr"/>
-      <c r="E561" s="2" t="inlineStr">
-        <is>
-          <t>598.0</t>
-        </is>
+          <t>马来西亚旧街场三合一榛果味白咖啡525g</t>
+        </is>
+      </c>
+      <c r="D561" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="E561" s="2" t="n">
+        <v>59.7</v>
       </c>
       <c r="F561" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G561" s="2" t="inlineStr">
-        <is>
-          <t>2024-12-01</t>
-        </is>
-      </c>
+      <c r="G561" s="2" t="inlineStr"/>
       <c r="H561" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I561" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I561" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" s="2" t="n">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="B562" s="2" t="inlineStr">
         <is>
-          <t>祖玛珑鼠尾草与海盐香水30ml清新持久留香</t>
+          <t>【正品保障】马来西亚旧街场咖啡原装进口三合一经典风味速溶榛果</t>
         </is>
       </c>
       <c r="C562" s="2" t="inlineStr">
         <is>
-          <t>祖玛珑鼠尾草与海盐香水30ml</t>
-        </is>
-      </c>
-      <c r="D562" s="2" t="inlineStr">
-        <is>
-          <t>318.0</t>
-        </is>
-      </c>
-      <c r="E562" s="2" t="inlineStr">
-        <is>
-          <t>250.2</t>
-        </is>
+          <t>马来西亚旧街场进口三合一速溶白咖啡低糖醇厚条装525g</t>
+        </is>
+      </c>
+      <c r="D562" s="2" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="E562" s="2" t="n">
+        <v>57.99</v>
       </c>
       <c r="F562" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G562" s="2" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="H562" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I562" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I562" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" s="2" t="n">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="B563" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】JO MALONE/祖.玛珑鼠尾草与海盐30ml清新持久留香</t>
+          <t>【多袋】马来西亚旧街场原装进口三合一原味咖啡袋装榛果速溶经典</t>
         </is>
       </c>
       <c r="C563" s="2" t="inlineStr">
         <is>
-          <t>祖玛珑鼠尾草与海盐香水30ml</t>
-        </is>
-      </c>
-      <c r="D563" s="2" t="inlineStr">
-        <is>
-          <t>390.0</t>
-        </is>
-      </c>
-      <c r="E563" s="2" t="inlineStr">
-        <is>
-          <t>277.5</t>
-        </is>
+          <t>马来西亚旧街场进口三合一速溶白咖啡低糖醇厚条装525g</t>
+        </is>
+      </c>
+      <c r="D563" s="2" t="inlineStr"/>
+      <c r="E563" s="2" t="n">
+        <v>86.8</v>
       </c>
       <c r="F563" s="2" t="inlineStr">
         <is>
@@ -21056,165 +21046,155 @@
       </c>
       <c r="G563" s="2" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="H563" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I563" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I563" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" s="2" t="n">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="B564" s="2" t="inlineStr">
         <is>
-          <t>【阿玛尼】蓝标大师粉底液 2 号 30ml 保湿遮瑕持久干皮</t>
+          <t>【旧街场】白咖啡马来西亚进口经典原味榛果咖啡三合一速溶咖啡粉*2袋</t>
         </is>
       </c>
       <c r="C564" s="2" t="inlineStr">
         <is>
-          <t>阿玛尼大师蓝标粉底液2#</t>
-        </is>
-      </c>
-      <c r="D564" s="2" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="E564" s="2" t="inlineStr">
-        <is>
-          <t>179.2</t>
-        </is>
+          <t>马来西亚进口OldTown旧街场白咖啡特浓浓醇三合一速溶白咖啡15条</t>
+        </is>
+      </c>
+      <c r="D564" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="E564" s="2" t="n">
+        <v>51</v>
       </c>
       <c r="F564" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G564" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
+      <c r="G564" s="2" t="inlineStr"/>
       <c r="H564" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I564" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I564" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" s="2" t="n">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="B565" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】阿玛尼新款蓝标大师粉底液#1 #2 #3持久遮瑕细腻服帖</t>
+          <t>马来西亚进口OLDTOWN旧街场速溶白咖啡粉老街特浓醇香咖啡饮品</t>
         </is>
       </c>
       <c r="C565" s="2" t="inlineStr">
         <is>
-          <t>阿玛尼大师蓝标粉底液2#</t>
-        </is>
-      </c>
-      <c r="D565" s="2" t="inlineStr">
-        <is>
-          <t>289.0</t>
-        </is>
-      </c>
-      <c r="E565" s="2" t="inlineStr">
-        <is>
-          <t>185.0</t>
-        </is>
+          <t>马来西亚进口OldTown旧街场白咖啡特浓浓醇三合一速溶白咖啡15条</t>
+        </is>
+      </c>
+      <c r="D565" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="E565" s="2" t="n">
+        <v>48.17</v>
       </c>
       <c r="F565" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G565" s="2" t="inlineStr"/>
+      <c r="G565" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
       <c r="H565" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I565" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I565" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" s="2" t="n">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="B566" s="2" t="inlineStr">
         <is>
-          <t>【正品保证】阿玛尼权力PRO粉底液2# 绒雾质感混油肌粉底遮瑕【5天内发货】</t>
+          <t>进口马来西亚旧街场经典白咖啡三合一原味榛果少糖特浓15条装袋装</t>
         </is>
       </c>
       <c r="C566" s="2" t="inlineStr">
         <is>
-          <t>阿玛尼权力PR0粉底30ml#2</t>
-        </is>
-      </c>
-      <c r="D566" s="2" t="inlineStr"/>
-      <c r="E566" s="2" t="inlineStr">
-        <is>
-          <t>227.0</t>
-        </is>
+          <t>马来西亚进口OldTown旧街场白咖啡特浓浓醇三合一速溶白咖啡15条</t>
+        </is>
+      </c>
+      <c r="D566" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="E566" s="2" t="n">
+        <v>59.7</v>
       </c>
       <c r="F566" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G566" s="2" t="inlineStr">
-        <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
+      <c r="G566" s="2" t="inlineStr"/>
       <c r="H566" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I566" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I566" s="2" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" s="2" t="n">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="B567" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】阿玛尼权力无瑕持妆PRO粉底液(红标)30ml 绒雾感遮瑕</t>
+          <t>马来西亚进口咖啡粉OLDTOWN旧街场榛果味白咖啡速溶三合一3袋装</t>
         </is>
       </c>
       <c r="C567" s="2" t="inlineStr">
         <is>
-          <t>阿玛尼权力PR0粉底30ml#2</t>
+          <t>马来西亚进口OldTown旧街场白咖啡特浓浓醇三合一速溶白咖啡15条</t>
         </is>
       </c>
       <c r="D567" s="2" t="inlineStr"/>
-      <c r="E567" s="2" t="inlineStr">
-        <is>
-          <t>255.0</t>
-        </is>
+      <c r="E567" s="2" t="n">
+        <v>84.8</v>
       </c>
       <c r="F567" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G567" s="2" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
+      <c r="G567" s="2" t="inlineStr"/>
       <c r="H567" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -21228,68 +21208,60 @@
     </row>
     <row r="568">
       <c r="A568" s="2" t="n">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="B568" s="2" t="inlineStr">
         <is>
-          <t>【阿玛尼】权力粉底液 3 号新款 30ml 持妆控油遮瑕油皮亲妈持久</t>
+          <t>【旧街场】白咖啡马来西亚进口经典原味榛果咖啡三合一速溶咖啡粉*2袋</t>
         </is>
       </c>
       <c r="C568" s="2" t="inlineStr">
         <is>
-          <t>阿玛尼权力PR0粉底30ml#3</t>
-        </is>
-      </c>
-      <c r="D568" s="2" t="inlineStr">
-        <is>
-          <t>299.0</t>
-        </is>
-      </c>
-      <c r="E568" s="2" t="inlineStr">
-        <is>
-          <t>182.6</t>
-        </is>
+          <t>马来西亚进口旧街场白咖啡二合一375g</t>
+        </is>
+      </c>
+      <c r="D568" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="E568" s="2" t="n">
+        <v>51</v>
       </c>
       <c r="F568" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G568" s="2" t="inlineStr">
-        <is>
-          <t>2025-03-01</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G568" s="2" t="inlineStr"/>
       <c r="H568" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I568" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I568" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" s="2" t="n">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B569" s="2" t="inlineStr">
         <is>
-          <t>【阿玛尼】蓝标大师粉底液3#新版遮瑕轻薄透气持久30ml</t>
+          <t>马来西亚进口旧街场咖啡二合一无蔗糖白咖啡速溶咖啡粉30条</t>
         </is>
       </c>
       <c r="C569" s="2" t="inlineStr">
         <is>
-          <t>阿玛尼「大师」锁光粉底液#3</t>
-        </is>
-      </c>
-      <c r="D569" s="2" t="inlineStr">
-        <is>
-          <t>299.0</t>
-        </is>
-      </c>
-      <c r="E569" s="2" t="inlineStr">
-        <is>
-          <t>193.0</t>
-        </is>
+          <t>马来西亚进口旧街场白咖啡二合一375g</t>
+        </is>
+      </c>
+      <c r="D569" s="2" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="E569" s="2" t="n">
+        <v>52.9</v>
       </c>
       <c r="F569" s="2" t="inlineStr">
         <is>
@@ -21298,80 +21270,76 @@
       </c>
       <c r="G569" s="2" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H569" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I569" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I569" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" s="2" t="n">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B570" s="2" t="inlineStr">
         <is>
-          <t>GIORGIO ARMANI/阿玛尼红气垫替换芯15g#3号色单双个控油持妆新款</t>
+          <t>【旧街场】咖啡无蔗糖份二合一速溶白咖啡粉3袋马来西亚进口港版正品</t>
         </is>
       </c>
       <c r="C570" s="2" t="inlineStr">
         <is>
-          <t>阿玛尼气垫替换芯3号</t>
-        </is>
-      </c>
-      <c r="D570" s="2" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="E570" s="2" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
+          <t>马来西亚进口旧街场白咖啡二合一375g</t>
+        </is>
+      </c>
+      <c r="D570" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="E570" s="2" t="n">
+        <v>89.7</v>
       </c>
       <c r="F570" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G570" s="2" t="inlineStr">
-        <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
+      <c r="G570" s="2" t="inlineStr"/>
       <c r="H570" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I570" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I570" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" s="2" t="n">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B571" s="2" t="inlineStr">
         <is>
-          <t>【特价清仓】ARMANI阿玛尼红气垫替换芯3号15g新版 遮瑕养肤持久</t>
+          <t>马来西亚旧街场咖啡无蔗糖二合一速溶白咖啡粉2袋装港版正品</t>
         </is>
       </c>
       <c r="C571" s="2" t="inlineStr">
         <is>
-          <t>阿玛尼气垫替换芯3号</t>
-        </is>
-      </c>
-      <c r="D571" s="2" t="inlineStr">
-        <is>
-          <t>188.0</t>
-        </is>
-      </c>
-      <c r="E571" s="2" t="inlineStr">
-        <is>
-          <t>108.0</t>
-        </is>
+          <t>马来西亚进口旧街场白咖啡二合一375g</t>
+        </is>
+      </c>
+      <c r="D571" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="E571" s="2" t="n">
+        <v>59.4</v>
       </c>
       <c r="F571" s="2" t="inlineStr">
         <is>
@@ -21381,43 +21349,41 @@
       <c r="G571" s="2" t="inlineStr"/>
       <c r="H571" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I571" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I571" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" s="2" t="n">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B572" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】兰蔻全新菁纯柔雾哑光唇釉  275# 单支礼盒装</t>
+          <t>【旧街场】马来西亚进口咖啡港版3合1速溶白咖啡咸焦糖味15条3袋装</t>
         </is>
       </c>
       <c r="C572" s="2" t="inlineStr">
         <is>
-          <t>兰蔻水唇釉275#</t>
-        </is>
-      </c>
-      <c r="D572" s="2" t="inlineStr">
-        <is>
-          <t>239.0</t>
-        </is>
-      </c>
-      <c r="E572" s="2" t="inlineStr">
-        <is>
-          <t>190.0</t>
-        </is>
+          <t>马来西亚旧街场进口白咖啡咸焦糖525g</t>
+        </is>
+      </c>
+      <c r="D572" s="2" t="inlineStr"/>
+      <c r="E572" s="2" t="n">
+        <v>87.90000000000001</v>
       </c>
       <c r="F572" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G572" s="2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H572" s="2" t="inlineStr">
@@ -21427,36 +21393,38 @@
       </c>
       <c r="I572" s="2" t="inlineStr">
         <is>
-          <t>品名相似不足(ratio=66.7%)</t>
+          <t>规格不匹配</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" s="2" t="n">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="B573" s="2" t="inlineStr">
         <is>
-          <t>【兰蔻】菁纯裸唇釉小蛮腰275 279 313 281 274哑光丝绒柔雾口红正品</t>
+          <t>【旧街场】丝滑含微研磨减少糖三合一速溶白咖啡粉375g*3袋装提神防困</t>
         </is>
       </c>
       <c r="C573" s="2" t="inlineStr">
         <is>
-          <t>兰蔻水唇釉275#</t>
+          <t>马来西亚旧街场进口白咖啡微研磨375g</t>
         </is>
       </c>
       <c r="D573" s="2" t="inlineStr"/>
-      <c r="E573" s="2" t="inlineStr">
-        <is>
-          <t>155.0</t>
-        </is>
+      <c r="E573" s="2" t="n">
+        <v>76.09999999999999</v>
       </c>
       <c r="F573" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G573" s="2" t="inlineStr"/>
+      <c r="G573" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
       <c r="H573" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -21464,36 +21432,40 @@
       </c>
       <c r="I573" s="2" t="inlineStr">
         <is>
-          <t>品名相似不足(ratio=66.7%)</t>
+          <t>品名相似不足(ratio=30.0%)</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" s="2" t="n">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="B574" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】Lancome/兰蔻菁纯裸唇釉哑光丝绒轻盈质地显白有气色</t>
+          <t>马来西亚进口旧街场咖啡二合一无蔗糖白咖啡速溶咖啡粉30条</t>
         </is>
       </c>
       <c r="C574" s="2" t="inlineStr">
         <is>
-          <t>兰蔻水唇釉275#</t>
-        </is>
-      </c>
-      <c r="D574" s="2" t="inlineStr"/>
-      <c r="E574" s="2" t="inlineStr">
-        <is>
-          <t>160.0</t>
-        </is>
+          <t>马来西亚旧街场进口白咖啡微研磨375g</t>
+        </is>
+      </c>
+      <c r="D574" s="2" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="E574" s="2" t="n">
+        <v>52.9</v>
       </c>
       <c r="F574" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G574" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G574" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
       <c r="H574" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -21501,33 +21473,33 @@
       </c>
       <c r="I574" s="2" t="inlineStr">
         <is>
-          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
+          <t>规格不匹配</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" s="2" t="n">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="B575" s="2" t="inlineStr">
         <is>
-          <t>【现货直发】兰蔻菁纯裸唇釉6ml  粉盖柔雾丝滑浓郁口红女生礼物</t>
+          <t>【旧街场】白咖啡马来西亚进口经典原味榛果咖啡三合一速溶咖啡粉*2袋</t>
         </is>
       </c>
       <c r="C575" s="2" t="inlineStr">
         <is>
-          <t>兰蔻水唇釉275#</t>
-        </is>
-      </c>
-      <c r="D575" s="2" t="inlineStr"/>
-      <c r="E575" s="2" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
+          <t>马来西亚旧街场进口白咖啡微研磨375g</t>
+        </is>
+      </c>
+      <c r="D575" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="E575" s="2" t="n">
+        <v>51</v>
       </c>
       <c r="F575" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G575" s="2" t="inlineStr"/>
@@ -21538,226 +21510,226 @@
       </c>
       <c r="I575" s="2" t="inlineStr">
         <is>
-          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
+          <t>规格不匹配</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="2" t="n">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="B576" s="2" t="inlineStr">
         <is>
-          <t>Gucci古驰绮梦馥栀女士EDP浓香水50ml 25年新品</t>
+          <t>马来西亚进口速溶咖啡粉OLDTOWN旧街场三合一蔗糖白咖啡3袋装45条</t>
         </is>
       </c>
       <c r="C576" s="2" t="inlineStr">
         <is>
-          <t>古驰绮梦栀子花香水50ml浓香型</t>
-        </is>
-      </c>
-      <c r="D576" s="2" t="inlineStr">
-        <is>
-          <t>537.0</t>
-        </is>
-      </c>
-      <c r="E576" s="2" t="inlineStr">
-        <is>
-          <t>338.52</t>
-        </is>
+          <t>马来西亚旧街场进口白咖啡微研磨375g</t>
+        </is>
+      </c>
+      <c r="D576" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="E576" s="2" t="n">
+        <v>87.7</v>
       </c>
       <c r="F576" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G576" s="2" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H576" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I576" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I576" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" s="2" t="n">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="B577" s="2" t="inlineStr">
         <is>
-          <t>【全球购正品】古驰绮梦馥栀香型女士香水50ml</t>
+          <t>马来西亚进口OLDTOWN旧街场速溶白咖啡粉老街特浓醇香咖啡饮品</t>
         </is>
       </c>
       <c r="C577" s="2" t="inlineStr">
         <is>
-          <t>古驰绮梦栀子花香水50ml浓香型</t>
-        </is>
-      </c>
-      <c r="D577" s="2" t="inlineStr">
-        <is>
-          <t>499.0</t>
-        </is>
-      </c>
-      <c r="E577" s="2" t="inlineStr">
-        <is>
-          <t>357.0</t>
-        </is>
+          <t>马来西亚OLDTOWN进口白咖啡天然庶糖540g</t>
+        </is>
+      </c>
+      <c r="D577" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="E577" s="2" t="n">
+        <v>48.17</v>
       </c>
       <c r="F577" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G577" s="2" t="inlineStr"/>
+      <c r="G577" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
       <c r="H577" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I577" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I577" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" s="2" t="n">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="B578" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】GUCCI古驰绮梦馥栀女士香水红瓶馥郁版EDP 50ml</t>
+          <t>马来西亚进口速溶咖啡粉OLDTOWN旧街场三合一蔗糖白咖啡3袋装45条</t>
         </is>
       </c>
       <c r="C578" s="2" t="inlineStr">
         <is>
-          <t>古驰绮梦栀子花香水50ml浓香型</t>
-        </is>
-      </c>
-      <c r="D578" s="2" t="inlineStr"/>
-      <c r="E578" s="2" t="inlineStr">
-        <is>
-          <t>743.0</t>
-        </is>
+          <t>马来西亚OLDTOWN进口白咖啡天然庶糖540g</t>
+        </is>
+      </c>
+      <c r="D578" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="E578" s="2" t="n">
+        <v>87.7</v>
       </c>
       <c r="F578" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G578" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G578" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
       <c r="H578" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I578" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I578" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" s="2" t="n">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B579" s="2" t="inlineStr">
         <is>
-          <t>POLA/宝丽第七代洗面奶黑BA控油保湿抗衰老洁面2支</t>
+          <t>马来西亚进口咖啡粉OLDTOWN旧街场榛果味白咖啡速溶三合一3袋装</t>
         </is>
       </c>
       <c r="C579" s="2" t="inlineStr">
         <is>
-          <t>POLA 黑BA洁面</t>
-        </is>
-      </c>
-      <c r="D579" s="2" t="inlineStr">
-        <is>
-          <t>678.0</t>
-        </is>
-      </c>
-      <c r="E579" s="2" t="inlineStr">
-        <is>
-          <t>563.0</t>
-        </is>
+          <t>马来西亚OLDTOWN进口白咖啡天然庶糖540g</t>
+        </is>
+      </c>
+      <c r="D579" s="2" t="inlineStr"/>
+      <c r="E579" s="2" t="n">
+        <v>84.8</v>
       </c>
       <c r="F579" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G579" s="2" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G579" s="2" t="inlineStr"/>
       <c r="H579" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I579" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I579" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" s="2" t="n">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B580" s="2" t="inlineStr">
         <is>
-          <t>日本本土版第七代POLA/宝丽黑BA抗糖保湿洁面洗面奶</t>
+          <t>港版丨马来西亚进口咖啡粉OLDTOWN 旧街场榛果白咖啡速溶三合一</t>
         </is>
       </c>
       <c r="C580" s="2" t="inlineStr">
         <is>
-          <t>POLA 黑BA洁面</t>
-        </is>
-      </c>
-      <c r="D580" s="2" t="inlineStr">
-        <is>
-          <t>398.0</t>
-        </is>
-      </c>
-      <c r="E580" s="2" t="inlineStr">
-        <is>
-          <t>276.9</t>
-        </is>
+          <t>马来西亚OLDTOWN进口白咖啡天然庶糖540g</t>
+        </is>
+      </c>
+      <c r="D580" s="2" t="inlineStr"/>
+      <c r="E580" s="2" t="n">
+        <v>86.2</v>
       </c>
       <c r="F580" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G580" s="2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="H580" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I580" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I580" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" s="2" t="n">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="B581" s="2" t="inlineStr">
         <is>
-          <t>【POLA】宝丽BA深层清洁洗面奶9g*5小样洁面乳温和不紧绷</t>
+          <t>SHU UEMURA 植村秀 羽纱持妆喷雾100ml 微光版小黑胶持久控油保湿</t>
         </is>
       </c>
       <c r="C581" s="2" t="inlineStr">
         <is>
-          <t>POLA 黑BA洁面</t>
-        </is>
-      </c>
-      <c r="D581" s="2" t="inlineStr">
-        <is>
-          <t>172.1</t>
-        </is>
-      </c>
-      <c r="E581" s="2" t="inlineStr">
-        <is>
-          <t>105.0</t>
-        </is>
+          <t>植村秀持久保湿定妆喷雾100ml</t>
+        </is>
+      </c>
+      <c r="D581" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="E581" s="2" t="n">
+        <v>111.3</v>
       </c>
       <c r="F581" s="2" t="inlineStr">
         <is>
@@ -21766,15 +21738,5659 @@
       </c>
       <c r="G581" s="2" t="inlineStr">
         <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="H581" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I581" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="2" t="n">
+        <v>237</v>
+      </c>
+      <c r="B582" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】植村秀新品元气小红喷定妆喷雾持久控油保湿100ml</t>
+        </is>
+      </c>
+      <c r="C582" s="2" t="inlineStr">
+        <is>
+          <t>植村秀持久保湿定妆喷雾100ml</t>
+        </is>
+      </c>
+      <c r="D582" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="E582" s="2" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="F582" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G582" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="H582" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I582" s="2" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="B583" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】全新大红瓶面霜80g清爽版+15ml*4补水保湿滋润护肤品【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C583" s="2" t="inlineStr">
+        <is>
+          <t>SK2大红瓶面霜80g滋润</t>
+        </is>
+      </c>
+      <c r="D583" s="2" t="n">
+        <v>1399</v>
+      </c>
+      <c r="E583" s="2" t="n">
+        <v>1248</v>
+      </c>
+      <c r="F583" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G583" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="H583" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I583" s="2" t="inlineStr"/>
+    </row>
+    <row r="584">
+      <c r="A584" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="B584" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】大红瓶面霜80g*2滋润型补水保湿滋润舒缓紧致sk2护肤品【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C584" s="2" t="inlineStr">
+        <is>
+          <t>SK2大红瓶面霜80g滋润</t>
+        </is>
+      </c>
+      <c r="D584" s="2" t="n">
+        <v>1699</v>
+      </c>
+      <c r="E584" s="2" t="n">
+        <v>1450</v>
+      </c>
+      <c r="F584" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G584" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="H584" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I584" s="2" t="inlineStr"/>
+    </row>
+    <row r="585">
+      <c r="A585" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="B585" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】大红瓶面霜80g滋养保湿紧致肌肤清爽款</t>
+        </is>
+      </c>
+      <c r="C585" s="2" t="inlineStr">
+        <is>
+          <t>SK2大红瓶面霜80g滋润</t>
+        </is>
+      </c>
+      <c r="D585" s="2" t="n">
+        <v>868</v>
+      </c>
+      <c r="E585" s="2" t="n">
+        <v>577</v>
+      </c>
+      <c r="F585" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G585" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H585" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I585" s="2" t="inlineStr"/>
+    </row>
+    <row r="586">
+      <c r="A586" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="B586" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】新版大红瓶面霜80g清爽型抗皱紧致滋润保湿【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C586" s="2" t="inlineStr">
+        <is>
+          <t>SK2大红瓶面霜80g滋润</t>
+        </is>
+      </c>
+      <c r="D586" s="2" t="n">
+        <v>999</v>
+      </c>
+      <c r="E586" s="2" t="n">
+        <v>739</v>
+      </c>
+      <c r="F586" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G586" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="H586" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I586" s="2" t="inlineStr"/>
+    </row>
+    <row r="587">
+      <c r="A587" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="B587" s="2" t="inlineStr">
+        <is>
+          <t>【Embryolisse】旗舰店妆前乳隔离补水保湿法国进口深浅蓝</t>
+        </is>
+      </c>
+      <c r="C587" s="2" t="inlineStr">
+        <is>
+          <t>Embryolisse 大宝妆前乳75ml 法国进口</t>
+        </is>
+      </c>
+      <c r="D587" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="E587" s="2" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="F587" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G587" s="2" t="inlineStr"/>
+      <c r="H587" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I587" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="B588" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】石榴洁面乳125ml洗面奶清洁二合一保湿控油</t>
+        </is>
+      </c>
+      <c r="C588" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴洁面125ml</t>
+        </is>
+      </c>
+      <c r="D588" s="2" t="inlineStr"/>
+      <c r="E588" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="F588" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G588" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="H588" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I588" s="2" t="inlineStr"/>
+    </row>
+    <row r="589">
+      <c r="A589" s="2" t="n">
+        <v>241</v>
+      </c>
+      <c r="B589" s="2" t="inlineStr">
+        <is>
+          <t>两瓶 单品 SHISEIDO资生堂第四代红腰子精华75ml</t>
+        </is>
+      </c>
+      <c r="C589" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO红腰子精华（新版）75ml</t>
+        </is>
+      </c>
+      <c r="D589" s="2" t="inlineStr"/>
+      <c r="E589" s="2" t="n">
+        <v>609</v>
+      </c>
+      <c r="F589" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G589" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="H589" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I589" s="2" t="inlineStr"/>
+    </row>
+    <row r="590">
+      <c r="A590" s="2" t="n">
+        <v>241</v>
+      </c>
+      <c r="B590" s="2" t="inlineStr">
+        <is>
+          <t>资生堂红腰子精华液75ml四代补水保湿滋润维稳修护【5月30日发完】</t>
+        </is>
+      </c>
+      <c r="C590" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO红腰子精华（新版）75ml</t>
+        </is>
+      </c>
+      <c r="D590" s="2" t="n">
+        <v>295</v>
+      </c>
+      <c r="E590" s="2" t="n">
+        <v>211.8</v>
+      </c>
+      <c r="F590" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G590" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="H590" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I590" s="2" t="inlineStr"/>
+    </row>
+    <row r="591">
+      <c r="A591" s="2" t="n">
+        <v>242</v>
+      </c>
+      <c r="B591" s="2" t="inlineStr">
+        <is>
+          <t>【SHISEIDO】资生堂时光琉璃御藏柔肤水170ml保湿滋润紧致肌肤爽肤水</t>
+        </is>
+      </c>
+      <c r="C591" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/ SHISEIDO时光大琉璃水（新版）170ml</t>
+        </is>
+      </c>
+      <c r="D591" s="2" t="n">
+        <v>339</v>
+      </c>
+      <c r="E591" s="2" t="n">
+        <v>249.9</v>
+      </c>
+      <c r="F591" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G591" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="H591" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I591" s="2" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" s="2" t="n">
+        <v>243</v>
+      </c>
+      <c r="B592" s="2" t="inlineStr">
+        <is>
+          <t>【SHISEIDO】资生堂悦薇大抗糖滋润面霜50ml补水紧致智感紧塑焕白霜</t>
+        </is>
+      </c>
+      <c r="C592" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO悦薇大抗糖面霜（清爽）50ml</t>
+        </is>
+      </c>
+      <c r="D592" s="2" t="n">
+        <v>329</v>
+      </c>
+      <c r="E592" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="F592" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G592" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="H592" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I592" s="2" t="inlineStr"/>
+    </row>
+    <row r="593">
+      <c r="A593" s="2" t="n">
+        <v>244</v>
+      </c>
+      <c r="B593" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO御藏臻萃奢养时光修护滋养琉璃晚霜15ml滋养 保湿</t>
+        </is>
+      </c>
+      <c r="C593" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO琉璃晚霜15ml（新版）</t>
+        </is>
+      </c>
+      <c r="D593" s="2" t="inlineStr"/>
+      <c r="E593" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="F593" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G593" s="2" t="inlineStr">
+        <is>
+          <t>2024-03-21</t>
+        </is>
+      </c>
+      <c r="H593" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I593" s="2" t="inlineStr"/>
+    </row>
+    <row r="594">
+      <c r="A594" s="2" t="n">
+        <v>244</v>
+      </c>
+      <c r="B594" s="2" t="inlineStr">
+        <is>
+          <t>【资生堂】SHISEIDO新款时光琉璃御藏臻萃奢养晚霜15ml紧致夜霜面霜</t>
+        </is>
+      </c>
+      <c r="C594" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO琉璃晚霜15ml（新版）</t>
+        </is>
+      </c>
+      <c r="D594" s="2" t="inlineStr"/>
+      <c r="E594" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F594" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G594" s="2" t="inlineStr"/>
+      <c r="H594" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I594" s="2" t="inlineStr"/>
+    </row>
+    <row r="595">
+      <c r="A595" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="B595" s="2" t="inlineStr">
+        <is>
+          <t>【资生堂】百优精纯面霜50ml保湿滋润增弹紧致抗衰老乳霜</t>
+        </is>
+      </c>
+      <c r="C595" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO百优面霜50ml</t>
+        </is>
+      </c>
+      <c r="D595" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="E595" s="2" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="F595" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G595" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="H595" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I595" s="2" t="inlineStr"/>
+    </row>
+    <row r="596">
+      <c r="A596" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="B596" s="2" t="inlineStr">
+        <is>
+          <t>【资生堂】百优精纯面霜50ml保湿滋润增弹紧致抗衰老抗皱乳霜</t>
+        </is>
+      </c>
+      <c r="C596" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO百优面霜50ml</t>
+        </is>
+      </c>
+      <c r="D596" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="E596" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="F596" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G596" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="H596" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I596" s="2" t="inlineStr"/>
+    </row>
+    <row r="597">
+      <c r="A597" s="2" t="n">
+        <v>246</v>
+      </c>
+      <c r="B597" s="2" t="inlineStr">
+        <is>
+          <t>【范思哲】爱罗斯爱神之水男士香水 淡香 50ML Eros木质馥奇调</t>
+        </is>
+      </c>
+      <c r="C597" s="2" t="inlineStr">
+        <is>
+          <t>范思哲 爱罗斯爱神男士香水 50ml EDP</t>
+        </is>
+      </c>
+      <c r="D597" s="2" t="inlineStr"/>
+      <c r="E597" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="F597" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G597" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="H597" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I597" s="2" t="inlineStr"/>
+    </row>
+    <row r="598">
+      <c r="A598" s="2" t="n">
+        <v>246</v>
+      </c>
+      <c r="B598" s="2" t="inlineStr">
+        <is>
+          <t>【520礼物】Versace范思哲爱罗斯爱神之水男士淡香水Eros木质正品</t>
+        </is>
+      </c>
+      <c r="C598" s="2" t="inlineStr">
+        <is>
+          <t>范思哲 爱罗斯爱神男士香水 50ml EDP</t>
+        </is>
+      </c>
+      <c r="D598" s="2" t="inlineStr"/>
+      <c r="E598" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="F598" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G598" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="H598" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I598" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="2" t="n">
+        <v>247</v>
+      </c>
+      <c r="B599" s="2" t="inlineStr">
+        <is>
+          <t>【VERSACE】范思哲爱罗斯男士淡香水香氛爱神之水100ml简装EDT</t>
+        </is>
+      </c>
+      <c r="C599" s="2" t="inlineStr">
+        <is>
+          <t>范思哲 爱罗斯爱神男士香水 100ml EDP 简装</t>
+        </is>
+      </c>
+      <c r="D599" s="2" t="n">
+        <v>269</v>
+      </c>
+      <c r="E599" s="2" t="n">
+        <v>230.9</v>
+      </c>
+      <c r="F599" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G599" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="H599" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I599" s="2" t="inlineStr"/>
+    </row>
+    <row r="600">
+      <c r="A600" s="2" t="n">
+        <v>247</v>
+      </c>
+      <c r="B600" s="2" t="inlineStr">
+        <is>
+          <t>【VERSACE】范思哲爱罗斯男士淡香水香氛爱神之水100ml简装EDT</t>
+        </is>
+      </c>
+      <c r="C600" s="2" t="inlineStr">
+        <is>
+          <t>范思哲 爱罗斯爱神男士香水 100ml EDP 简装</t>
+        </is>
+      </c>
+      <c r="D600" s="2" t="inlineStr"/>
+      <c r="E600" s="2" t="n">
+        <v>278</v>
+      </c>
+      <c r="F600" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G600" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="H600" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I600" s="2" t="inlineStr"/>
+    </row>
+    <row r="601">
+      <c r="A601" s="2" t="n">
+        <v>248</v>
+      </c>
+      <c r="B601" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】BURBERRY博柏利伦敦男士香水琥珀木质馥奇调EDT 50ml</t>
+        </is>
+      </c>
+      <c r="C601" s="2" t="inlineStr">
+        <is>
+          <t>burberry新伦敦男士淡香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="D601" s="2" t="inlineStr"/>
+      <c r="E601" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="F601" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G601" s="2" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="H601" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I601" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="2" t="n">
+        <v>248</v>
+      </c>
+      <c r="B602" s="2" t="inlineStr">
+        <is>
+          <t>博柏利(BURBERRY)伦敦男士淡香水EDT 50ML</t>
+        </is>
+      </c>
+      <c r="C602" s="2" t="inlineStr">
+        <is>
+          <t>burberry新伦敦男士淡香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="D602" s="2" t="inlineStr"/>
+      <c r="E602" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="F602" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G602" s="2" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="H602" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I602" s="2" t="inlineStr"/>
+    </row>
+    <row r="603">
+      <c r="A603" s="2" t="n">
+        <v>248</v>
+      </c>
+      <c r="B603" s="2" t="inlineStr">
+        <is>
+          <t>【礼盒礼袋 】BURBERRY博柏利巴宝莉新伦敦男士EDT淡香水送人礼物</t>
+        </is>
+      </c>
+      <c r="C603" s="2" t="inlineStr">
+        <is>
+          <t>burberry新伦敦男士淡香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="D603" s="2" t="inlineStr"/>
+      <c r="E603" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="F603" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G603" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="H603" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I603" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="2" t="n">
+        <v>248</v>
+      </c>
+      <c r="B604" s="2" t="inlineStr">
+        <is>
+          <t>【全球购正品】博柏利伦敦男士淡香水50ml</t>
+        </is>
+      </c>
+      <c r="C604" s="2" t="inlineStr">
+        <is>
+          <t>burberry新伦敦男士淡香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="D604" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="E604" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="F604" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G604" s="2" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="H604" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I604" s="2" t="inlineStr"/>
+    </row>
+    <row r="605">
+      <c r="A605" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="B605" s="2" t="inlineStr">
+        <is>
+          <t>Calvin Klein/CK卡尔文克雷恩 自由男士EDT 50/100ML</t>
+        </is>
+      </c>
+      <c r="C605" s="2" t="inlineStr">
+        <is>
+          <t>CK Man男士香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="D605" s="2" t="inlineStr"/>
+      <c r="E605" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="F605" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G605" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="H605" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I605" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="B606" s="2" t="inlineStr">
+        <is>
+          <t>【50mlCK肆意男士香水EDT50ml</t>
+        </is>
+      </c>
+      <c r="C606" s="2" t="inlineStr">
+        <is>
+          <t>CK Man男士香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="D606" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="E606" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="F606" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G606" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="H606" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I606" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="B607" s="2" t="inlineStr">
+        <is>
+          <t>Calvin Klein/CK凯文克莱 自由男士香水 50/100ML</t>
+        </is>
+      </c>
+      <c r="C607" s="2" t="inlineStr">
+        <is>
+          <t>CK Man男士香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="D607" s="2" t="inlineStr"/>
+      <c r="E607" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="F607" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G607" s="2" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="H607" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I607" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="B608" s="2" t="inlineStr">
+        <is>
+          <t>【50mlCK Man超凡男士淡香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="C608" s="2" t="inlineStr">
+        <is>
+          <t>CK Man男士香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="D608" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="E608" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="F608" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G608" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="H608" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I608" s="2" t="inlineStr"/>
+    </row>
+    <row r="609">
+      <c r="A609" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="B609" s="2" t="inlineStr">
+        <is>
+          <t>【正品】CALVIN KLEIN CK be 男士香水 木质香调 淡香水EDT</t>
+        </is>
+      </c>
+      <c r="C609" s="2" t="inlineStr">
+        <is>
+          <t>CK Man男士香水 50ml EDT</t>
+        </is>
+      </c>
+      <c r="D609" s="2" t="inlineStr"/>
+      <c r="E609" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="F609" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G609" s="2" t="inlineStr"/>
+      <c r="H609" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I609" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="B610" s="2" t="inlineStr">
+        <is>
+          <t>【香港直发】Calvin Klein绝色女士香氛香水 EDP100ml CK女士香水【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C610" s="2" t="inlineStr">
+        <is>
+          <t>CK 绝色美丽女士香水 100ml EDP 黄色</t>
+        </is>
+      </c>
+      <c r="D610" s="2" t="inlineStr"/>
+      <c r="E610" s="2" t="inlineStr"/>
+      <c r="F610" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G610" s="2" t="inlineStr"/>
+      <c r="H610" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I610" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=33.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="B611" s="2" t="inlineStr">
+        <is>
+          <t>【100mlCK绝色美丽女士香水EDP黄色100ml简装无盖</t>
+        </is>
+      </c>
+      <c r="C611" s="2" t="inlineStr">
+        <is>
+          <t>CK 绝色美丽女士香水 100ml EDP 黄色</t>
+        </is>
+      </c>
+      <c r="D611" s="2" t="inlineStr"/>
+      <c r="E611" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="F611" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G611" s="2" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="H611" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I611" s="2" t="inlineStr"/>
+    </row>
+    <row r="612">
+      <c r="A612" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="B612" s="2" t="inlineStr">
+        <is>
+          <t>Calvin Klein/CK凯文克莱 激情女士EDP香水 50/100ml</t>
+        </is>
+      </c>
+      <c r="C612" s="2" t="inlineStr">
+        <is>
+          <t>CK 绝色美丽女士香水 100ml EDP 黄色</t>
+        </is>
+      </c>
+      <c r="D612" s="2" t="inlineStr"/>
+      <c r="E612" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="F612" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G612" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="H612" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I612" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="B613" s="2" t="inlineStr"/>
+      <c r="C613" s="2" t="inlineStr">
+        <is>
+          <t>杜鲁萨迪 雅逸玫瑰女士香水 30ml EDT</t>
+        </is>
+      </c>
+      <c r="D613" s="2" t="inlineStr"/>
+      <c r="E613" s="2" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F613" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G613" s="2" t="inlineStr"/>
+      <c r="H613" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I613" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="B614" s="2" t="inlineStr">
+        <is>
+          <t>【香港直发】TRUSSARDI杜鲁萨迪优雅浪漫玫瑰淡香水EDT 100ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C614" s="2" t="inlineStr">
+        <is>
+          <t>杜鲁萨迪 雅逸玫瑰女士香水 30ml EDT</t>
+        </is>
+      </c>
+      <c r="D614" s="2" t="inlineStr"/>
+      <c r="E614" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="F614" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G614" s="2" t="inlineStr"/>
+      <c r="H614" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I614" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="B615" s="2" t="inlineStr">
+        <is>
+          <t>【大卫杜夫】冷水男士香水海洋调男士淡香水男生节日礼物75ml</t>
+        </is>
+      </c>
+      <c r="C615" s="2" t="inlineStr">
+        <is>
+          <t>大卫杜夫 冷水男士香水 75ml EDP 加强版</t>
+        </is>
+      </c>
+      <c r="D615" s="2" t="n">
+        <v>1391</v>
+      </c>
+      <c r="E615" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="F615" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G615" s="2" t="inlineStr">
+        <is>
+          <t>2022-05-20</t>
+        </is>
+      </c>
+      <c r="H615" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I615" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="B616" s="2" t="inlineStr">
+        <is>
+          <t>【】大卫杜夫(Davidoff)冷水男士淡香水</t>
+        </is>
+      </c>
+      <c r="C616" s="2" t="inlineStr">
+        <is>
+          <t>大卫杜夫 冷水男士香水 75ml EDP 加强版</t>
+        </is>
+      </c>
+      <c r="D616" s="2" t="inlineStr"/>
+      <c r="E616" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="F616" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G616" s="2" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="H616" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I616" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="B617" s="2" t="inlineStr">
+        <is>
+          <t>【Davidoff】大卫杜夫冷水男士淡香水EDT40/75/125ml</t>
+        </is>
+      </c>
+      <c r="C617" s="2" t="inlineStr">
+        <is>
+          <t>大卫杜夫 冷水男士香水 75ml EDP 加强版</t>
+        </is>
+      </c>
+      <c r="D617" s="2" t="inlineStr"/>
+      <c r="E617" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="F617" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G617" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-25</t>
+        </is>
+      </c>
+      <c r="H617" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I617" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="B618" s="2" t="inlineStr">
+        <is>
+          <t>【大卫杜夫】冷水极致版香水喷雾 EDP 125ml/4.2oz【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C618" s="2" t="inlineStr">
+        <is>
+          <t>大卫杜夫 冷水男士香水 75ml EDP 加强版</t>
+        </is>
+      </c>
+      <c r="D618" s="2" t="inlineStr"/>
+      <c r="E618" s="2" t="n">
+        <v>329</v>
+      </c>
+      <c r="F618" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G618" s="2" t="inlineStr"/>
+      <c r="H618" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I618" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="B619" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI古驰竹韵女士浓香水持久花香木质调EDP 50ml</t>
+        </is>
+      </c>
+      <c r="C619" s="2" t="inlineStr">
+        <is>
+          <t>古驰 竹韵女士香水浓香型50ml</t>
+        </is>
+      </c>
+      <c r="D619" s="2" t="n">
+        <v>628</v>
+      </c>
+      <c r="E619" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="F619" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G619" s="2" t="inlineStr"/>
+      <c r="H619" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I619" s="2" t="inlineStr"/>
+    </row>
+    <row r="620">
+      <c r="A620" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="B620" s="2" t="inlineStr">
+        <is>
+          <t>【娇韵诗】双萃精华眼霜20ml紧致淡化细纹</t>
+        </is>
+      </c>
+      <c r="C620" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃眼霜 20ml</t>
+        </is>
+      </c>
+      <c r="D620" s="2" t="inlineStr"/>
+      <c r="E620" s="2" t="n">
+        <v>329</v>
+      </c>
+      <c r="F620" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G620" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="H620" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I620" s="2" t="inlineStr"/>
+    </row>
+    <row r="621">
+      <c r="A621" s="2" t="n">
+        <v>255</v>
+      </c>
+      <c r="B621" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销135.3万+件】新版娇韵诗第九代黄金双萃精华100ml滋润补水抗氧紧致修护护肤</t>
+        </is>
+      </c>
+      <c r="C621" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃新版第9代 75ml</t>
+        </is>
+      </c>
+      <c r="D621" s="2" t="n">
+        <v>999</v>
+      </c>
+      <c r="E621" s="2" t="n">
+        <v>776</v>
+      </c>
+      <c r="F621" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G621" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="H621" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I621" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="2" t="n">
+        <v>255</v>
+      </c>
+      <c r="B622" s="2" t="inlineStr">
+        <is>
+          <t>【正品现货】CLARINS娇韵诗新版第九代黄金双萃精华75ml无盒自用</t>
+        </is>
+      </c>
+      <c r="C622" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃新版第9代 75ml</t>
+        </is>
+      </c>
+      <c r="D622" s="2" t="n">
+        <v>880</v>
+      </c>
+      <c r="E622" s="2" t="n">
+        <v>498</v>
+      </c>
+      <c r="F622" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G622" s="2" t="inlineStr"/>
+      <c r="H622" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I622" s="2" t="inlineStr"/>
+    </row>
+    <row r="623">
+      <c r="A623" s="2" t="n">
+        <v>255</v>
+      </c>
+      <c r="B623" s="2" t="inlineStr">
+        <is>
+          <t>第九代娇韵诗双萃精华液紧致抗皱熬夜修护面部精华护肤轻盈清爽</t>
+        </is>
+      </c>
+      <c r="C623" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃新版第9代 75ml</t>
+        </is>
+      </c>
+      <c r="D623" s="2" t="n">
+        <v>588</v>
+      </c>
+      <c r="E623" s="2" t="n">
+        <v>348</v>
+      </c>
+      <c r="F623" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G623" s="2" t="inlineStr"/>
+      <c r="H623" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I623" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=33.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="2" t="n">
+        <v>255</v>
+      </c>
+      <c r="B624" s="2" t="inlineStr">
+        <is>
+          <t>新版娇韵诗第九代黄金双萃精华100ml滋润补水抗氧</t>
+        </is>
+      </c>
+      <c r="C624" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃新版第9代 75ml</t>
+        </is>
+      </c>
+      <c r="D624" s="2" t="n">
+        <v>959</v>
+      </c>
+      <c r="E624" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F624" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G624" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="H624" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I624" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="B625" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】娇韵诗温和泡沫洁面棉花籽清洁保湿油皮125ml</t>
+        </is>
+      </c>
+      <c r="C625" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 棉花籽洁面 125ml 新版</t>
+        </is>
+      </c>
+      <c r="D625" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="E625" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="F625" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G625" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="H625" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I625" s="2" t="inlineStr"/>
+    </row>
+    <row r="626">
+      <c r="A626" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="B626" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】娇韵诗温和泡沫洁面棉花籽清洁保湿油皮125ml</t>
+        </is>
+      </c>
+      <c r="C626" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 棉花籽洁面 125ml 新版</t>
+        </is>
+      </c>
+      <c r="D626" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="E626" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="F626" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G626" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="H626" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I626" s="2" t="inlineStr"/>
+    </row>
+    <row r="627">
+      <c r="A627" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="B627" s="2" t="inlineStr">
+        <is>
+          <t>Clarins娇韵诗身体护理油抚纹油100ml提拉紧致淡纹滋养【5月28日发完】</t>
+        </is>
+      </c>
+      <c r="C627" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 抚纹油 100ml</t>
+        </is>
+      </c>
+      <c r="D627" s="2" t="n">
+        <v>269</v>
+      </c>
+      <c r="E627" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="F627" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G627" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="H627" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I627" s="2" t="inlineStr"/>
+    </row>
+    <row r="628">
+      <c r="A628" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="B628" s="2" t="inlineStr">
+        <is>
+          <t>【娇韵诗】自然调和身体护理油100ml紧致提拉淡纹滋润</t>
+        </is>
+      </c>
+      <c r="C628" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 抚纹油 100ml</t>
+        </is>
+      </c>
+      <c r="D628" s="2" t="n">
+        <v>318</v>
+      </c>
+      <c r="E628" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="F628" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G628" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H628" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I628" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=33.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="B629" s="2" t="inlineStr">
+        <is>
+          <t>【Clarins】 娇韵诗天然调和身体护理油 抚纹油 100ml</t>
+        </is>
+      </c>
+      <c r="C629" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 抚纹油 100ml</t>
+        </is>
+      </c>
+      <c r="D629" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="E629" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="F629" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G629" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="H629" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I629" s="2" t="inlineStr"/>
+    </row>
+    <row r="630">
+      <c r="A630" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="B630" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】Clarins/娇韵诗双萃精华液紧致面部精华30ml轻盈版</t>
+        </is>
+      </c>
+      <c r="C630" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃新版第9代 30ml</t>
+        </is>
+      </c>
+      <c r="D630" s="2" t="n">
+        <v>412</v>
+      </c>
+      <c r="E630" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="F630" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G630" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="H630" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I630" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=33.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="B631" s="2" t="inlineStr">
+        <is>
+          <t>第九代娇韵诗双萃精华液紧致抗皱熬夜修护面部精华护肤轻盈清爽</t>
+        </is>
+      </c>
+      <c r="C631" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃新版第9代 30ml</t>
+        </is>
+      </c>
+      <c r="D631" s="2" t="n">
+        <v>588</v>
+      </c>
+      <c r="E631" s="2" t="n">
+        <v>348</v>
+      </c>
+      <c r="F631" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G631" s="2" t="inlineStr"/>
+      <c r="H631" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I631" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=33.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="B632" s="2" t="inlineStr">
+        <is>
+          <t>【娇韵诗】第九代双萃精华液抗皱抗衰老紧致淡纹熬夜面部抗皱精华护肤【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C632" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃新版第9代 30ml</t>
+        </is>
+      </c>
+      <c r="D632" s="2" t="n">
+        <v>306</v>
+      </c>
+      <c r="E632" s="2" t="n">
+        <v>305</v>
+      </c>
+      <c r="F632" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G632" s="2" t="inlineStr"/>
+      <c r="H632" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I632" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=33.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="B633" s="2" t="inlineStr">
+        <is>
+          <t>新版 娇韵诗第九代双萃精华经典轻盈双效修护滋润焕亮熬夜精华</t>
+        </is>
+      </c>
+      <c r="C633" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗 双萃新版第9代 30ml</t>
+        </is>
+      </c>
+      <c r="D633" s="2" t="inlineStr"/>
+      <c r="E633" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="F633" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G633" s="2" t="inlineStr"/>
+      <c r="H633" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I633" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=33.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="2" t="n">
+        <v>259</v>
+      </c>
+      <c r="B634" s="2" t="inlineStr">
+        <is>
+          <t>Loccitane 欧舒丹 甜蜜樱花护手霜30ml(新款)</t>
+        </is>
+      </c>
+      <c r="C634" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹樱花护手霜三支装</t>
+        </is>
+      </c>
+      <c r="D634" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="E634" s="2" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F634" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G634" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="H634" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I634" s="2" t="inlineStr"/>
+    </row>
+    <row r="635">
+      <c r="A635" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="B635" s="2" t="inlineStr">
+        <is>
+          <t>法国L'OCCITANE欧舒丹嫩肤沐浴露身体乳全系列</t>
+        </is>
+      </c>
+      <c r="C635" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹乳木果身体乳250ml</t>
+        </is>
+      </c>
+      <c r="D635" s="2" t="inlineStr"/>
+      <c r="E635" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F635" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G635" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="H635" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I635" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="B636" s="2" t="inlineStr">
+        <is>
+          <t>【国内直售】欧舒丹身体乳乳木果身体润肤露滋润保湿250ml滋润</t>
+        </is>
+      </c>
+      <c r="C636" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹乳木果身体乳250ml</t>
+        </is>
+      </c>
+      <c r="D636" s="2" t="inlineStr"/>
+      <c r="E636" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="F636" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G636" s="2" t="inlineStr"/>
+      <c r="H636" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I636" s="2" t="inlineStr"/>
+    </row>
+    <row r="637">
+      <c r="A637" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="B637" s="2" t="inlineStr">
+        <is>
+          <t>【特价】欧舒丹乳木果身体润肤露250ML 滋润保湿身体乳</t>
+        </is>
+      </c>
+      <c r="C637" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹乳木果身体乳250ml</t>
+        </is>
+      </c>
+      <c r="D637" s="2" t="inlineStr"/>
+      <c r="E637" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="F637" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G637" s="2" t="inlineStr"/>
+      <c r="H637" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I637" s="2" t="inlineStr"/>
+    </row>
+    <row r="638">
+      <c r="A638" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="B638" s="2" t="inlineStr">
+        <is>
+          <t>【国内直售】欧舒丹乳木果身体润肤露滋润保湿身体乳250ml滋润</t>
+        </is>
+      </c>
+      <c r="C638" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹乳木果身体乳250ml</t>
+        </is>
+      </c>
+      <c r="D638" s="2" t="inlineStr"/>
+      <c r="E638" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="F638" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G638" s="2" t="inlineStr"/>
+      <c r="H638" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I638" s="2" t="inlineStr"/>
+    </row>
+    <row r="639">
+      <c r="A639" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="B639" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹乳木果身体乳丰凝润肤露250ml舒缓滋润保湿补水正品【6月18日发完】</t>
+        </is>
+      </c>
+      <c r="C639" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹乳木果身体乳250ml</t>
+        </is>
+      </c>
+      <c r="D639" s="2" t="inlineStr"/>
+      <c r="E639" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="F639" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G639" s="2" t="inlineStr"/>
+      <c r="H639" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I639" s="2" t="inlineStr"/>
+    </row>
+    <row r="640">
+      <c r="A640" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="B640" s="2" t="inlineStr">
+        <is>
+          <t>【正品保证】欧舒丹乳木果身体乳250ml润肤露补水保湿滋润保湿霜</t>
+        </is>
+      </c>
+      <c r="C640" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹乳木果身体乳250ml</t>
+        </is>
+      </c>
+      <c r="D640" s="2" t="inlineStr"/>
+      <c r="E640" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="F640" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G640" s="2" t="inlineStr"/>
+      <c r="H640" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I640" s="2" t="inlineStr"/>
+    </row>
+    <row r="641">
+      <c r="A641" s="2" t="n">
+        <v>261</v>
+      </c>
+      <c r="B641" s="2" t="inlineStr">
+        <is>
+          <t>Loccitane 欧舒丹 瑰香之心身体乳250ml 第二代新款</t>
+        </is>
+      </c>
+      <c r="C641" s="2" t="inlineStr">
+        <is>
+          <t>欧舒丹玫瑰身体乳250ml</t>
+        </is>
+      </c>
+      <c r="D641" s="2" t="n">
+        <v>191.8</v>
+      </c>
+      <c r="E641" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="F641" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G641" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="H641" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I641" s="2" t="inlineStr"/>
+    </row>
+    <row r="642">
+      <c r="A642" s="2" t="n">
+        <v>262</v>
+      </c>
+      <c r="B642" s="2" t="inlineStr">
+        <is>
+          <t>【海蓝之谜】洁面125ml清洁焕亮洗面奶</t>
+        </is>
+      </c>
+      <c r="C642" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜洁面125ml</t>
+        </is>
+      </c>
+      <c r="D642" s="2" t="n">
+        <v>599</v>
+      </c>
+      <c r="E642" s="2" t="n">
+        <v>365</v>
+      </c>
+      <c r="F642" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G642" s="2" t="inlineStr"/>
+      <c r="H642" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I642" s="2" t="inlineStr"/>
+    </row>
+    <row r="643">
+      <c r="A643" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="B643" s="2" t="inlineStr">
+        <is>
+          <t>【 正品行货】CPB/肌肤之钥洗面奶125ml光凝润采妆前隔离37ml</t>
+        </is>
+      </c>
+      <c r="C643" s="2" t="inlineStr">
+        <is>
+          <t>CPB滋润洗面奶125ml</t>
+        </is>
+      </c>
+      <c r="D643" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="E643" s="2" t="n">
+        <v>362.51</v>
+      </c>
+      <c r="F643" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G643" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="H643" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I643" s="2" t="inlineStr"/>
+    </row>
+    <row r="644">
+      <c r="A644" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="B644" s="2" t="inlineStr">
+        <is>
+          <t>【CPB】肌肤之钥光采洁面膏洗面奶滋润版125ml</t>
+        </is>
+      </c>
+      <c r="C644" s="2" t="inlineStr">
+        <is>
+          <t>CPB滋润洗面奶125ml</t>
+        </is>
+      </c>
+      <c r="D644" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="E644" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="F644" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G644" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H644" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I644" s="2" t="inlineStr"/>
+    </row>
+    <row r="645">
+      <c r="A645" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="B645" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】肌肤之钥净采洁面膏125ml*2清爽型/湿润型补水保湿</t>
+        </is>
+      </c>
+      <c r="C645" s="2" t="inlineStr">
+        <is>
+          <t>CPB滋润洗面奶125ml</t>
+        </is>
+      </c>
+      <c r="D645" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="E645" s="2" t="n">
+        <v>364</v>
+      </c>
+      <c r="F645" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G645" s="2" t="inlineStr"/>
+      <c r="H645" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I645" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=33.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="2" t="n">
+        <v>264</v>
+      </c>
+      <c r="B646" s="2" t="inlineStr">
+        <is>
+          <t>【CPB】 肌肤之钥 白短管隔离30ml SPF38 高倍防晒</t>
+        </is>
+      </c>
+      <c r="C646" s="2" t="inlineStr">
+        <is>
+          <t>CPB美白短管隔离30ml</t>
+        </is>
+      </c>
+      <c r="D646" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="E646" s="2" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="F646" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G646" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="H646" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I646" s="2" t="inlineStr"/>
+    </row>
+    <row r="647">
+      <c r="A647" s="2" t="n">
+        <v>264</v>
+      </c>
+      <c r="B647" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】CPB肌肤之钥光透白焕采妆前乳防晒短管白隔离 30ml</t>
+        </is>
+      </c>
+      <c r="C647" s="2" t="inlineStr">
+        <is>
+          <t>CPB美白短管隔离30ml</t>
+        </is>
+      </c>
+      <c r="D647" s="2" t="n">
+        <v>255</v>
+      </c>
+      <c r="E647" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="F647" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G647" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H647" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I647" s="2" t="inlineStr"/>
+    </row>
+    <row r="648">
+      <c r="A648" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="B648" s="2" t="inlineStr">
+        <is>
+          <t>【费列罗】巧克力40粒礼盒装榛果威化金球结婚礼喜糖伴手礼情人节礼物</t>
+        </is>
+      </c>
+      <c r="C648" s="2" t="inlineStr">
+        <is>
+          <t>FERRERO ROCHER 费列罗榛果巧克力制品T30</t>
+        </is>
+      </c>
+      <c r="D648" s="2" t="inlineStr"/>
+      <c r="E648" s="2" t="inlineStr"/>
+      <c r="F648" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G648" s="2" t="inlineStr"/>
+      <c r="H648" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I648" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=20.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="B649" s="2" t="inlineStr">
+        <is>
+          <t>Estee Lauder雅诗兰黛红石榴光采能量保湿霜日霜旧版50ml</t>
+        </is>
+      </c>
+      <c r="C649" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴面霜50ml 旧版</t>
+        </is>
+      </c>
+      <c r="D649" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="E649" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="F649" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G649" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="H649" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I649" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="B650" s="2" t="inlineStr">
+        <is>
+          <t>【ESTEE LAUDER雅诗兰黛】红石榴面霜 鲜活亮采日霜50ml保湿补水</t>
+        </is>
+      </c>
+      <c r="C650" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴面霜50ml 旧版</t>
+        </is>
+      </c>
+      <c r="D650" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="E650" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="F650" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G650" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="H650" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I650" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="B651" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】红石榴精华面霜 提亮滋润淡化高保湿补水修护50ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C651" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴面霜50ml 旧版</t>
+        </is>
+      </c>
+      <c r="D651" s="2" t="inlineStr"/>
+      <c r="E651" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="F651" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G651" s="2" t="inlineStr"/>
+      <c r="H651" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I651" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="B652" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】红石榴面霜 晚霜50ml 抗氧化提亮肤色高保湿补水滋润【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C652" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴面霜50ml 旧版</t>
+        </is>
+      </c>
+      <c r="D652" s="2" t="inlineStr"/>
+      <c r="E652" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="F652" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G652" s="2" t="inlineStr"/>
+      <c r="H652" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I652" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="2" t="n">
+        <v>267</v>
+      </c>
+      <c r="B653" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰全新爱心七夕浮雕黑管唇釉610 620 442 443</t>
+        </is>
+      </c>
+      <c r="C653" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰爱心黑管唇釉620</t>
+        </is>
+      </c>
+      <c r="D653" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="E653" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="F653" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G653" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H653" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I653" s="2" t="inlineStr"/>
+    </row>
+    <row r="654">
+      <c r="A654" s="2" t="n">
+        <v>267</v>
+      </c>
+      <c r="B654" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰爱心唇釉442 443 620限定浮雕黑管5.5ml</t>
+        </is>
+      </c>
+      <c r="C654" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰爱心黑管唇釉620</t>
+        </is>
+      </c>
+      <c r="D654" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="E654" s="2" t="n">
+        <v>143.4</v>
+      </c>
+      <c r="F654" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G654" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="H654" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I654" s="2" t="inlineStr"/>
+    </row>
+    <row r="655">
+      <c r="A655" s="2" t="n">
+        <v>268</v>
+      </c>
+      <c r="B655" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰黑皮革气垫羽毛B10白皮B20自然肤色遮瑕</t>
+        </is>
+      </c>
+      <c r="C655" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰黑色皮革气垫B10</t>
+        </is>
+      </c>
+      <c r="D655" s="2" t="n">
+        <v>361</v>
+      </c>
+      <c r="E655" s="2" t="n">
+        <v>223.9</v>
+      </c>
+      <c r="F655" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G655" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="H655" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I655" s="2" t="inlineStr"/>
+    </row>
+    <row r="656">
+      <c r="A656" s="2" t="n">
+        <v>268</v>
+      </c>
+      <c r="B656" s="2" t="inlineStr">
+        <is>
+          <t>【YSL】圣罗兰黑皮革气垫b10# B20# 14g 混油挚爱细腻服帖自然无瑕</t>
+        </is>
+      </c>
+      <c r="C656" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰黑色皮革气垫B10</t>
+        </is>
+      </c>
+      <c r="D656" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="E656" s="2" t="n">
+        <v>235.6</v>
+      </c>
+      <c r="F656" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G656" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H656" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I656" s="2" t="inlineStr"/>
+    </row>
+    <row r="657">
+      <c r="A657" s="2" t="n">
+        <v>270</v>
+      </c>
+      <c r="B657" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】兰蔻新菁纯粉底液均匀肤色隐形毛孔保湿持妆长效持妆</t>
+        </is>
+      </c>
+      <c r="C657" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻菁纯粉底液100</t>
+        </is>
+      </c>
+      <c r="D657" s="2" t="n">
+        <v>674</v>
+      </c>
+      <c r="E657" s="2" t="n">
+        <v>355</v>
+      </c>
+      <c r="F657" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G657" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="H657" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I657" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="2" t="n">
+        <v>270</v>
+      </c>
+      <c r="B658" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】兰蔻菁纯臻颜精华粉底液100#/110#35ml 新版礼物送人</t>
+        </is>
+      </c>
+      <c r="C658" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻菁纯粉底液100</t>
+        </is>
+      </c>
+      <c r="D658" s="2" t="inlineStr"/>
+      <c r="E658" s="2" t="n">
+        <v>640</v>
+      </c>
+      <c r="F658" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G658" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="H658" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I658" s="2" t="inlineStr"/>
+    </row>
+    <row r="659">
+      <c r="A659" s="2" t="n">
+        <v>271</v>
+      </c>
+      <c r="B659" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II骨胶原晶致活肤修护乳液补水保湿抗皱紧致舒缓</t>
+        </is>
+      </c>
+      <c r="C659" s="2" t="inlineStr">
+        <is>
+          <t>SK2骨胶原乳液100g</t>
+        </is>
+      </c>
+      <c r="D659" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="E659" s="2" t="n">
+        <v>432</v>
+      </c>
+      <c r="F659" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G659" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="H659" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I659" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="2" t="n">
+        <v>271</v>
+      </c>
+      <c r="B660" s="2" t="inlineStr">
+        <is>
+          <t>SK2晶致美肤乳液100g 骨胶原修护紧致活肤 保湿不油腻【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C660" s="2" t="inlineStr">
+        <is>
+          <t>SK2骨胶原乳液100g</t>
+        </is>
+      </c>
+      <c r="D660" s="2" t="inlineStr"/>
+      <c r="E660" s="2" t="n">
+        <v>386</v>
+      </c>
+      <c r="F660" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G660" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="H660" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I660" s="2" t="inlineStr"/>
+    </row>
+    <row r="661">
+      <c r="A661" s="2" t="n">
+        <v>271</v>
+      </c>
+      <c r="B661" s="2" t="inlineStr">
+        <is>
+          <t>SK-II/SK2 晶致活肤骨胶原乳液100g(无盒/不满瓶)【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C661" s="2" t="inlineStr">
+        <is>
+          <t>SK2骨胶原乳液100g</t>
+        </is>
+      </c>
+      <c r="D661" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="E661" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="F661" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G661" s="2" t="inlineStr"/>
+      <c r="H661" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I661" s="2" t="inlineStr"/>
+    </row>
+    <row r="662">
+      <c r="A662" s="2" t="n">
+        <v>271</v>
+      </c>
+      <c r="B662" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】 晶致美肤乳液100ml 骨胶原修护活肤乳液紧致提亮保湿抗皱</t>
+        </is>
+      </c>
+      <c r="C662" s="2" t="inlineStr">
+        <is>
+          <t>SK2骨胶原乳液100g</t>
+        </is>
+      </c>
+      <c r="D662" s="2" t="inlineStr"/>
+      <c r="E662" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F662" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G662" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="H662" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I662" s="2" t="inlineStr"/>
+    </row>
+    <row r="663">
+      <c r="A663" s="2" t="n">
+        <v>272</v>
+      </c>
+      <c r="B663" s="2" t="inlineStr">
+        <is>
+          <t>首件19.12大促直降36.2元总售1319件</t>
+        </is>
+      </c>
+      <c r="C663" s="2" t="inlineStr">
+        <is>
+          <t>SK2清莹露230ml</t>
+        </is>
+      </c>
+      <c r="D663" s="2" t="inlineStr"/>
+      <c r="E663" s="2" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="F663" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G663" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="H663" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I663" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="2" t="n">
+        <v>272</v>
+      </c>
+      <c r="B664" s="2" t="inlineStr">
+        <is>
+          <t>【2.13万人评价品牌正品】SK-II/sk2护肤精华露嫩肤清莹露保湿修护抗皱紧致嫩滑230ml化妆水</t>
+        </is>
+      </c>
+      <c r="C664" s="2" t="inlineStr">
+        <is>
+          <t>SK2清莹露230ml</t>
+        </is>
+      </c>
+      <c r="D664" s="2" t="inlineStr"/>
+      <c r="E664" s="2" t="n">
+        <v>418</v>
+      </c>
+      <c r="F664" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G664" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="H664" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I664" s="2" t="inlineStr"/>
+    </row>
+    <row r="665">
+      <c r="A665" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="B665" s="2" t="inlineStr">
+        <is>
+          <t>【专柜行货】SK-II sk2大红瓶微肌因修护焕彩大眼眼霜15g</t>
+        </is>
+      </c>
+      <c r="C665" s="2" t="inlineStr">
+        <is>
+          <t>SK2立体修护眼霜15g两瓶装</t>
+        </is>
+      </c>
+      <c r="D665" s="2" t="inlineStr"/>
+      <c r="E665" s="2" t="n">
+        <v>680</v>
+      </c>
+      <c r="F665" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G665" s="2" t="inlineStr"/>
+      <c r="H665" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I665" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="B666" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】大红瓶眼霜15g赋能焕采大眼眼霜sk2提拉紧致抗皱淡纹正品【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C666" s="2" t="inlineStr">
+        <is>
+          <t>SK2立体修护眼霜15g两瓶装</t>
+        </is>
+      </c>
+      <c r="D666" s="2" t="inlineStr"/>
+      <c r="E666" s="2" t="n">
+        <v>418</v>
+      </c>
+      <c r="F666" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G666" s="2" t="inlineStr"/>
+      <c r="H666" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I666" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="2" t="n">
+        <v>274</v>
+      </c>
+      <c r="B667" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】小灯泡精华50ml#无盒提亮肤色sk2淡斑美白修护面部精华液【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C667" s="2" t="inlineStr">
+        <is>
+          <t>SK2小灯泡50ml两瓶装（25年款）</t>
+        </is>
+      </c>
+      <c r="D667" s="2" t="inlineStr"/>
+      <c r="E667" s="2" t="inlineStr"/>
+      <c r="F667" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G667" s="2" t="inlineStr"/>
+      <c r="H667" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I667" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="2" t="n">
+        <v>274</v>
+      </c>
+      <c r="B668" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】小灯泡精华50ml美白光蕴臻采焕亮精华露sk2紧致淡纹正品【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C668" s="2" t="inlineStr">
+        <is>
+          <t>SK2小灯泡50ml两瓶装（25年款）</t>
+        </is>
+      </c>
+      <c r="D668" s="2" t="inlineStr"/>
+      <c r="E668" s="2" t="n">
+        <v>1299</v>
+      </c>
+      <c r="F668" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G668" s="2" t="inlineStr"/>
+      <c r="H668" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I668" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="B669" s="2" t="inlineStr">
+        <is>
+          <t>【碧欧泉】男士水动力保湿乳液100ml清爽提亮修护礼物【520礼物】</t>
+        </is>
+      </c>
+      <c r="C669" s="2" t="inlineStr">
+        <is>
+          <t>碧欧泉男士水动力乳液100ml</t>
+        </is>
+      </c>
+      <c r="D669" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="E669" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="F669" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G669" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H669" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I669" s="2" t="inlineStr"/>
+    </row>
+    <row r="670">
+      <c r="A670" s="2" t="n">
+        <v>276</v>
+      </c>
+      <c r="B670" s="2" t="inlineStr">
+        <is>
+          <t>【植村秀】绿茶新肌卸妆油450ml温和保湿深层清洁清透毛孔经典洁颜油【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C670" s="2" t="inlineStr">
+        <is>
+          <t>植村秀绿茶卸妆油450ml两瓶装</t>
+        </is>
+      </c>
+      <c r="D670" s="2" t="inlineStr"/>
+      <c r="E670" s="2" t="n">
+        <v>357</v>
+      </c>
+      <c r="F670" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G670" s="2" t="inlineStr"/>
+      <c r="H670" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I670" s="2" t="inlineStr"/>
+    </row>
+    <row r="671">
+      <c r="A671" s="2" t="n">
+        <v>276</v>
+      </c>
+      <c r="B671" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】植村秀绿茶卸妆洁颜油  温和深层清洁彩妆保湿450ml</t>
+        </is>
+      </c>
+      <c r="C671" s="2" t="inlineStr">
+        <is>
+          <t>植村秀绿茶卸妆油450ml两瓶装</t>
+        </is>
+      </c>
+      <c r="D671" s="2" t="n">
+        <v>580</v>
+      </c>
+      <c r="E671" s="2" t="n">
+        <v>365.7</v>
+      </c>
+      <c r="F671" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G671" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="H671" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I671" s="2" t="inlineStr"/>
+    </row>
+    <row r="672">
+      <c r="A672" s="2" t="n">
+        <v>277</v>
+      </c>
+      <c r="B672" s="2" t="inlineStr">
+        <is>
+          <t>【品牌好评229.4万+条】YSL/圣罗兰逆龄女神粉底液#B20持妆遮瑕控油节日礼物</t>
+        </is>
+      </c>
+      <c r="C672" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰女神逆龄粉底液B20</t>
+        </is>
+      </c>
+      <c r="D672" s="2" t="n">
+        <v>589</v>
+      </c>
+      <c r="E672" s="2" t="n">
+        <v>327</v>
+      </c>
+      <c r="F672" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G672" s="2" t="inlineStr"/>
+      <c r="H672" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I672" s="2" t="inlineStr"/>
+    </row>
+    <row r="673">
+      <c r="A673" s="2" t="n">
+        <v>277</v>
+      </c>
+      <c r="B673" s="2" t="inlineStr">
+        <is>
+          <t>【YSL】圣罗兰逆龄女神粉底液恒久B20#遮瑕轻薄控油30ml</t>
+        </is>
+      </c>
+      <c r="C673" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰女神逆龄粉底液B20</t>
+        </is>
+      </c>
+      <c r="D673" s="2" t="inlineStr"/>
+      <c r="E673" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="F673" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G673" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="H673" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I673" s="2" t="inlineStr"/>
+    </row>
+    <row r="674">
+      <c r="A674" s="2" t="n">
+        <v>278</v>
+      </c>
+      <c r="B674" s="2" t="inlineStr">
+        <is>
+          <t>LANCOME/兰蔻新版菁纯眼霜20ml滋润淡眼纹黑眼圈提拉紧致眼周【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C674" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻菁纯眼霜20ml两瓶装</t>
+        </is>
+      </c>
+      <c r="D674" s="2" t="n">
+        <v>459</v>
+      </c>
+      <c r="E674" s="2" t="n">
+        <v>334.4</v>
+      </c>
+      <c r="F674" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G674" s="2" t="inlineStr"/>
+      <c r="H674" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I674" s="2" t="inlineStr"/>
+    </row>
+    <row r="675">
+      <c r="A675" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="B675" s="2" t="inlineStr"/>
+      <c r="C675" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻第三代肌底液100ml</t>
+        </is>
+      </c>
+      <c r="D675" s="2" t="inlineStr"/>
+      <c r="E675" s="2" t="n">
+        <v>855</v>
+      </c>
+      <c r="F675" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G675" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="H675" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I675" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="B676" s="2" t="inlineStr">
+        <is>
+          <t>【兰蔻】小黑瓶第三代肌底液精华水75ml/100ml</t>
+        </is>
+      </c>
+      <c r="C676" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻第三代肌底液100ml</t>
+        </is>
+      </c>
+      <c r="D676" s="2" t="inlineStr"/>
+      <c r="E676" s="2" t="n">
+        <v>327.75</v>
+      </c>
+      <c r="F676" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G676" s="2" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="H676" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I676" s="2" t="inlineStr"/>
+    </row>
+    <row r="677">
+      <c r="A677" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="B677" s="2" t="inlineStr">
+        <is>
+          <t>Urban Decay 牛郎衰败城市ud牛郎眼影单色眼影打底经典牛郎 爆闪【6月18日发完】</t>
+        </is>
+      </c>
+      <c r="C677" s="2" t="inlineStr">
+        <is>
+          <t>衰败城市牛郎眼影</t>
+        </is>
+      </c>
+      <c r="D677" s="2" t="inlineStr"/>
+      <c r="E677" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F677" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G677" s="2" t="inlineStr"/>
+      <c r="H677" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I677" s="2" t="inlineStr"/>
+    </row>
+    <row r="678">
+      <c r="A678" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="B678" s="2" t="inlineStr"/>
+      <c r="C678" s="2" t="inlineStr">
+        <is>
+          <t>衰败城市牛郎眼影</t>
+        </is>
+      </c>
+      <c r="D678" s="2" t="inlineStr"/>
+      <c r="E678" s="2" t="n">
+        <v>241</v>
+      </c>
+      <c r="F678" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G678" s="2" t="inlineStr"/>
+      <c r="H678" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I678" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="B679" s="2" t="inlineStr">
+        <is>
+          <t>【娇兰】第三代帝皇蜂姿复原蜜精华液50ml黄金保湿抗氧提亮</t>
+        </is>
+      </c>
+      <c r="C679" s="2" t="inlineStr">
+        <is>
+          <t>娇兰帝皇蜂姿第三代黄金复原蜜50ML</t>
+        </is>
+      </c>
+      <c r="D679" s="2" t="inlineStr"/>
+      <c r="E679" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F679" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G679" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H679" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I679" s="2" t="inlineStr"/>
+    </row>
+    <row r="680">
+      <c r="A680" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="B680" s="2" t="inlineStr">
+        <is>
+          <t>【娇兰】第三代帝皇蜂姿复原蜜精华液50ml黄金保湿抗氧提亮</t>
+        </is>
+      </c>
+      <c r="C680" s="2" t="inlineStr">
+        <is>
+          <t>娇兰帝皇蜂姿第三代黄金复原蜜50ML</t>
+        </is>
+      </c>
+      <c r="D680" s="2" t="inlineStr"/>
+      <c r="E680" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F680" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G680" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H680" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I680" s="2" t="inlineStr"/>
+    </row>
+    <row r="681">
+      <c r="A681" s="2" t="n">
+        <v>283</v>
+      </c>
+      <c r="B681" s="2" t="inlineStr">
+        <is>
+          <t>【Hermes】爱马仕大地男士淡香水50ml经典淡香木质调正装男士香水</t>
+        </is>
+      </c>
+      <c r="C681" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕大地淡香水50ml</t>
+        </is>
+      </c>
+      <c r="D681" s="2" t="inlineStr"/>
+      <c r="E681" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="F681" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G681" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H681" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I681" s="2" t="inlineStr"/>
+    </row>
+    <row r="682">
+      <c r="A682" s="2" t="n">
+        <v>283</v>
+      </c>
+      <c r="B682" s="2" t="inlineStr">
+        <is>
+          <t>【Hermes】爱马仕大地男士淡香水50ml正装有盒木质调</t>
+        </is>
+      </c>
+      <c r="C682" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕大地淡香水50ml</t>
+        </is>
+      </c>
+      <c r="D682" s="2" t="inlineStr"/>
+      <c r="E682" s="2" t="n">
+        <v>439</v>
+      </c>
+      <c r="F682" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G682" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="H682" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I682" s="2" t="inlineStr"/>
+    </row>
+    <row r="683">
+      <c r="A683" s="2" t="n">
+        <v>283</v>
+      </c>
+      <c r="B683" s="2" t="inlineStr">
+        <is>
+          <t>【Hermes】爱马仕大地男士淡香水50ml经典中性馥郁清新持久留香</t>
+        </is>
+      </c>
+      <c r="C683" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕大地淡香水50ml</t>
+        </is>
+      </c>
+      <c r="D683" s="2" t="inlineStr"/>
+      <c r="E683" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="F683" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G683" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="H683" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I683" s="2" t="inlineStr"/>
+    </row>
+    <row r="684">
+      <c r="A684" s="2" t="n">
+        <v>283</v>
+      </c>
+      <c r="B684" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销59.6万+件】爱马仕(HERMES)大地男士淡香水EDT 30/50/100ML</t>
+        </is>
+      </c>
+      <c r="C684" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕大地淡香水50ml</t>
+        </is>
+      </c>
+      <c r="D684" s="2" t="inlineStr"/>
+      <c r="E684" s="2" t="n">
+        <v>448</v>
+      </c>
+      <c r="F684" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G684" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-20</t>
+        </is>
+      </c>
+      <c r="H684" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I684" s="2" t="inlineStr"/>
+    </row>
+    <row r="685">
+      <c r="A685" s="2" t="n">
+        <v>284</v>
+      </c>
+      <c r="B685" s="2" t="inlineStr"/>
+      <c r="C685" s="2" t="inlineStr">
+        <is>
+          <t>苏秘气垫1号</t>
+        </is>
+      </c>
+      <c r="D685" s="2" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="E685" s="2" t="n">
+        <v>67.43000000000001</v>
+      </c>
+      <c r="F685" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G685" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="H685" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I685" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="2" t="n">
+        <v>284</v>
+      </c>
+      <c r="B686" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销14.3万+件】韩国SUM37°苏秘惊喜气垫BB霜粉底液提亮防晒清透1号色</t>
+        </is>
+      </c>
+      <c r="C686" s="2" t="inlineStr">
+        <is>
+          <t>苏秘气垫1号</t>
+        </is>
+      </c>
+      <c r="D686" s="2" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="E686" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="F686" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G686" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="H686" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I686" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="2" t="n">
+        <v>284</v>
+      </c>
+      <c r="B687" s="2" t="inlineStr">
+        <is>
+          <t>【苏秘】惊喜气垫粉底液CC霜01号色水感妆效提亮防晒遮瑕</t>
+        </is>
+      </c>
+      <c r="C687" s="2" t="inlineStr">
+        <is>
+          <t>苏秘气垫1号</t>
+        </is>
+      </c>
+      <c r="D687" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="E687" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="F687" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G687" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="H687" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I687" s="2" t="inlineStr"/>
+    </row>
+    <row r="688">
+      <c r="A688" s="2" t="n">
+        <v>284</v>
+      </c>
+      <c r="B688" s="2" t="inlineStr">
+        <is>
+          <t>苏秘呼吸孕妇气垫bb霜遮瑕防晒保湿控油提亮镁白轻透气垫BS</t>
+        </is>
+      </c>
+      <c r="C688" s="2" t="inlineStr">
+        <is>
+          <t>苏秘气垫1号</t>
+        </is>
+      </c>
+      <c r="D688" s="2" t="inlineStr"/>
+      <c r="E688" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="F688" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G688" s="2" t="inlineStr"/>
+      <c r="H688" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I688" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="B689" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】红石榴水200ml滋润型 鲜活亮采精华水 补水保湿抗氧提亮</t>
+        </is>
+      </c>
+      <c r="C689" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛 鲜活亮采红石榴倍润水 200ml</t>
+        </is>
+      </c>
+      <c r="D689" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="E689" s="2" t="n">
+        <v>129.2</v>
+      </c>
+      <c r="F689" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G689" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="H689" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I689" s="2" t="inlineStr"/>
+    </row>
+    <row r="690">
+      <c r="A690" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="B690" s="2" t="inlineStr">
+        <is>
+          <t>【YSL】圣罗兰夜皇后面霜50ml轻盈版舒缓淡纹节日礼物</t>
+        </is>
+      </c>
+      <c r="C690" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰夜皇后50ml</t>
+        </is>
+      </c>
+      <c r="D690" s="2" t="n">
+        <v>589</v>
+      </c>
+      <c r="E690" s="2" t="n">
+        <v>436</v>
+      </c>
+      <c r="F690" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G690" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="H690" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I690" s="2" t="inlineStr"/>
+    </row>
+    <row r="691">
+      <c r="A691" s="2" t="n">
+        <v>287</v>
+      </c>
+      <c r="B691" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL/圣罗兰Al Hours 粉盖恒久干皮滋润粉底液LC1 LN4</t>
+        </is>
+      </c>
+      <c r="C691" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC1</t>
+        </is>
+      </c>
+      <c r="D691" s="2" t="inlineStr"/>
+      <c r="E691" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="F691" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G691" s="2" t="inlineStr"/>
+      <c r="H691" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I691" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="2" t="n">
+        <v>287</v>
+      </c>
+      <c r="B692" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL/圣罗兰Al Hours 粉盖恒久干皮滋润粉底液LC1 LN4</t>
+        </is>
+      </c>
+      <c r="C692" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC1</t>
+        </is>
+      </c>
+      <c r="D692" s="2" t="inlineStr"/>
+      <c r="E692" s="2" t="n">
+        <v>456</v>
+      </c>
+      <c r="F692" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G692" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="H692" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I692" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="2" t="n">
+        <v>287</v>
+      </c>
+      <c r="B693" s="2" t="inlineStr">
+        <is>
+          <t>【YSL】圣罗兰恒久粉底液LC1粉盖干皮挚爱超薄雾面长久持妆控油25ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C693" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC1</t>
+        </is>
+      </c>
+      <c r="D693" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="E693" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="F693" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G693" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="H693" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I693" s="2" t="inlineStr"/>
+    </row>
+    <row r="694">
+      <c r="A694" s="2" t="n">
+        <v>287</v>
+      </c>
+      <c r="B694" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL粉底液恒久贴肤衣 遮瑕哑光粉盖LC1 LC2 LN4正品</t>
+        </is>
+      </c>
+      <c r="C694" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC1</t>
+        </is>
+      </c>
+      <c r="D694" s="2" t="inlineStr"/>
+      <c r="E694" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="F694" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G694" s="2" t="inlineStr"/>
+      <c r="H694" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I694" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="B695" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL/圣罗兰粉盖恒久大牌滋润粉底液LC1 LC2滋润正品</t>
+        </is>
+      </c>
+      <c r="C695" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC2</t>
+        </is>
+      </c>
+      <c r="D695" s="2" t="inlineStr"/>
+      <c r="E695" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="F695" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G695" s="2" t="inlineStr"/>
+      <c r="H695" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I695" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="B696" s="2" t="inlineStr">
+        <is>
+          <t>【520礼物】YSL/圣罗兰粉盖恒久大牌滋润粉底液LC1 LC2滋润型正品</t>
+        </is>
+      </c>
+      <c r="C696" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC2</t>
+        </is>
+      </c>
+      <c r="D696" s="2" t="inlineStr"/>
+      <c r="E696" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="F696" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G696" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="H696" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I696" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="B697" s="2" t="inlineStr">
+        <is>
+          <t>【YSL】圣罗兰25年新款贴肤衣粉底液 混干持妆服帖遮瑕粉盖LC1/LC2【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C697" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC2</t>
+        </is>
+      </c>
+      <c r="D697" s="2" t="inlineStr"/>
+      <c r="E697" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="F697" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G697" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="H697" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I697" s="2" t="inlineStr"/>
+    </row>
+    <row r="698">
+      <c r="A698" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="B698" s="2" t="inlineStr">
+        <is>
+          <t>【520礼物】YSL/圣罗兰粉盖恒久大牌滋润粉底液LC1 LC2滋润正品</t>
+        </is>
+      </c>
+      <c r="C698" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰恒久粉底液25年新款粉盖LC2</t>
+        </is>
+      </c>
+      <c r="D698" s="2" t="inlineStr"/>
+      <c r="E698" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="F698" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G698" s="2" t="inlineStr"/>
+      <c r="H698" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I698" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="B699" s="2" t="inlineStr">
+        <is>
+          <t>【】两支 单品 兰蔻新版小白管轻透水漾防晒乳50ml</t>
+        </is>
+      </c>
+      <c r="C699" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻小白管轻适水漾防晒乳 50ml*2</t>
+        </is>
+      </c>
+      <c r="D699" s="2" t="n">
+        <v>659</v>
+      </c>
+      <c r="E699" s="2" t="n">
+        <v>419</v>
+      </c>
+      <c r="F699" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G699" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="H699" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I699" s="2" t="inlineStr"/>
+    </row>
+    <row r="700">
+      <c r="A700" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="B700" s="2" t="inlineStr">
+        <is>
+          <t>【圣罗兰】明彩粉光轻垫粉底液 BR20 #12g 正装粉气垫粉皮革 遮瑕细腻</t>
+        </is>
+      </c>
+      <c r="C700" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰 明彩粉光轻垫粉底液 粉气垫 #B20 CN</t>
+        </is>
+      </c>
+      <c r="D700" s="2" t="inlineStr"/>
+      <c r="E700" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="F700" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G700" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="H700" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I700" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="B701" s="2" t="inlineStr">
+        <is>
+          <t>正品行货 YSL圣罗兰粉气垫B10/B20遮瑕保湿持久养肤干皮挚爱轻薄</t>
+        </is>
+      </c>
+      <c r="C701" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰 明彩粉光轻垫粉底液 粉气垫 #B20 CN</t>
+        </is>
+      </c>
+      <c r="D701" s="2" t="inlineStr"/>
+      <c r="E701" s="2" t="n">
+        <v>385</v>
+      </c>
+      <c r="F701" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G701" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="H701" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I701" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=21.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="B702" s="2" t="inlineStr">
+        <is>
+          <t>【YSL】圣罗兰明彩轻垫粉底液B20 5g 皮气垫 遮瑕提亮 轻薄持妆</t>
+        </is>
+      </c>
+      <c r="C702" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰 明彩粉光轻垫粉底液 粉气垫 #B20 CN</t>
+        </is>
+      </c>
+      <c r="D702" s="2" t="inlineStr"/>
+      <c r="E702" s="2" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="F702" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G702" s="2" t="inlineStr"/>
+      <c r="H702" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I702" s="2" t="inlineStr"/>
+    </row>
+    <row r="703">
+      <c r="A703" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="B703" s="2" t="inlineStr">
+        <is>
+          <t>【清仓特价】圣罗兰明彩气垫轻垫粉底液黑皮革B20#5g 提亮肤色</t>
+        </is>
+      </c>
+      <c r="C703" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰 明彩粉光轻垫粉底液 粉气垫 #B20 CN</t>
+        </is>
+      </c>
+      <c r="D703" s="2" t="inlineStr"/>
+      <c r="E703" s="2" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="F703" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G703" s="2" t="inlineStr"/>
+      <c r="H703" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I703" s="2" t="inlineStr"/>
+    </row>
+    <row r="704">
+      <c r="A704" s="2" t="n">
+        <v>291</v>
+      </c>
+      <c r="B704" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销429.9万+件】2支资生堂新版蓝胖子防晒霜50ml隔离防紫外线</t>
+        </is>
+      </c>
+      <c r="C704" s="2" t="inlineStr">
+        <is>
+          <t>资生堂蓝胖子防晒50ml对装</t>
+        </is>
+      </c>
+      <c r="D704" s="2" t="inlineStr"/>
+      <c r="E704" s="2" t="n">
+        <v>359</v>
+      </c>
+      <c r="F704" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G704" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H704" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I704" s="2" t="inlineStr"/>
+    </row>
+    <row r="705">
+      <c r="A705" s="2" t="n">
+        <v>292</v>
+      </c>
+      <c r="B705" s="2" t="inlineStr">
+        <is>
+          <t>【2.15万人评价品牌正品】Armani 阿玛尼权力PRO粉底液1.5号/2号色红标遮瑕控油滋润</t>
+        </is>
+      </c>
+      <c r="C705" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底1.5 30ml</t>
+        </is>
+      </c>
+      <c r="D705" s="2" t="inlineStr"/>
+      <c r="E705" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="F705" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G705" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H705" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I705" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="2" t="n">
+        <v>292</v>
+      </c>
+      <c r="B706" s="2" t="inlineStr">
+        <is>
+          <t>【阿玛尼】权力持久丝绒哑光粉底液#1.5#30ML红标权力PRO混油</t>
+        </is>
+      </c>
+      <c r="C706" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底1.5 30ml</t>
+        </is>
+      </c>
+      <c r="D706" s="2" t="inlineStr"/>
+      <c r="E706" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="F706" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G706" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="H706" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I706" s="2" t="inlineStr"/>
+    </row>
+    <row r="707">
+      <c r="A707" s="2" t="n">
+        <v>292</v>
+      </c>
+      <c r="B707" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】阿玛尼新款权力PRO权利1.5粉底液(亚洲人混油皮挚爱)</t>
+        </is>
+      </c>
+      <c r="C707" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底1.5 30ml</t>
+        </is>
+      </c>
+      <c r="D707" s="2" t="inlineStr"/>
+      <c r="E707" s="2" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F707" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G707" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="H707" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I707" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="2" t="n">
+        <v>292</v>
+      </c>
+      <c r="B708" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】阿玛尼权力粉底液1.5#权利PRO粉底液1.6# 2# 30ml</t>
+        </is>
+      </c>
+      <c r="C708" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼权力PR0粉底1.5 30ml</t>
+        </is>
+      </c>
+      <c r="D708" s="2" t="inlineStr"/>
+      <c r="E708" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="F708" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G708" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="H708" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I708" s="2" t="inlineStr"/>
+    </row>
+    <row r="709">
+      <c r="A709" s="2" t="n">
+        <v>293</v>
+      </c>
+      <c r="B709" s="2" t="inlineStr">
+        <is>
+          <t>【兰蔻】肌底焕活修护眼霜20ml超修小黑瓶发光眼霜淡化细纹抗氧化修护</t>
+        </is>
+      </c>
+      <c r="C709" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻小黑瓶眼霜20ml</t>
+        </is>
+      </c>
+      <c r="D709" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="E709" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="F709" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G709" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="H709" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I709" s="2" t="inlineStr"/>
+    </row>
+    <row r="710">
+      <c r="A710" s="2" t="n">
+        <v>293</v>
+      </c>
+      <c r="B710" s="2" t="inlineStr">
+        <is>
+          <t>【Lancome】兰蔻小黑瓶发光眼霜20m淡眼圈细纹</t>
+        </is>
+      </c>
+      <c r="C710" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻小黑瓶眼霜20ml</t>
+        </is>
+      </c>
+      <c r="D710" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="E710" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="F710" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G710" s="2" t="inlineStr"/>
+      <c r="H710" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I710" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="2" t="n">
+        <v>293</v>
+      </c>
+      <c r="B711" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】兰蔻肌底焕活修护眼霜20ml超修小黑瓶发光眼霜【5月24日发完】</t>
+        </is>
+      </c>
+      <c r="C711" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻小黑瓶眼霜20ml</t>
+        </is>
+      </c>
+      <c r="D711" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="E711" s="2" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="F711" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G711" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H711" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I711" s="2" t="inlineStr"/>
+    </row>
+    <row r="712">
+      <c r="A712" s="2" t="n">
+        <v>293</v>
+      </c>
+      <c r="B712" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】兰蔻新版超修小黑眼霜20ml淡纹焕亮</t>
+        </is>
+      </c>
+      <c r="C712" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻小黑瓶眼霜20ml</t>
+        </is>
+      </c>
+      <c r="D712" s="2" t="inlineStr"/>
+      <c r="E712" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="F712" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G712" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H712" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I712" s="2" t="inlineStr"/>
+    </row>
+    <row r="713">
+      <c r="A713" s="2" t="n">
+        <v>294</v>
+      </c>
+      <c r="B713" s="2" t="inlineStr">
+        <is>
+          <t>【品牌好评88.8万+条】HR/赫莲娜绿宝瓶眼霜15ml眼部修复淡化黑眼圈【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C713" s="2" t="inlineStr">
+        <is>
+          <t>HR赫莲娜绿眼霜对装</t>
+        </is>
+      </c>
+      <c r="D713" s="2" t="inlineStr"/>
+      <c r="E713" s="2" t="n">
+        <v>599</v>
+      </c>
+      <c r="F713" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G713" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="H713" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I713" s="2" t="inlineStr"/>
+    </row>
+    <row r="714">
+      <c r="A714" s="2" t="n">
+        <v>294</v>
+      </c>
+      <c r="B714" s="2" t="inlineStr">
+        <is>
+          <t>【HR】赫莲娜绿宝瓶眼霜15ml淡化黑眼圈护肤品化妆品情人节520礼盒</t>
+        </is>
+      </c>
+      <c r="C714" s="2" t="inlineStr">
+        <is>
+          <t>HR赫莲娜绿眼霜对装</t>
+        </is>
+      </c>
+      <c r="D714" s="2" t="n">
+        <v>1220</v>
+      </c>
+      <c r="E714" s="2" t="n">
+        <v>730.55</v>
+      </c>
+      <c r="F714" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G714" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="H714" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I714" s="2" t="inlineStr"/>
+    </row>
+    <row r="715">
+      <c r="A715" s="2" t="n">
+        <v>295</v>
+      </c>
+      <c r="B715" s="2" t="inlineStr">
+        <is>
+          <t>【6.5万人回购该品牌】Gucci古驰花悦绽放淡香香水50ml</t>
+        </is>
+      </c>
+      <c r="C715" s="2" t="inlineStr">
+        <is>
+          <t>古驰花悦绽放女士淡香型香水50ml</t>
+        </is>
+      </c>
+      <c r="D715" s="2" t="inlineStr"/>
+      <c r="E715" s="2" t="n">
+        <v>339</v>
+      </c>
+      <c r="F715" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G715" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="H715" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I715" s="2" t="inlineStr"/>
+    </row>
+    <row r="716">
+      <c r="A716" s="2" t="n">
+        <v>295</v>
+      </c>
+      <c r="B716" s="2" t="inlineStr">
+        <is>
+          <t>【6.5万人回购该品牌】GUCCI/古驰花悦绽放女士淡香水EDT50ml芬芳清香送礼</t>
+        </is>
+      </c>
+      <c r="C716" s="2" t="inlineStr">
+        <is>
+          <t>古驰花悦绽放女士淡香型香水50ml</t>
+        </is>
+      </c>
+      <c r="D716" s="2" t="inlineStr"/>
+      <c r="E716" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="F716" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G716" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="H716" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I716" s="2" t="inlineStr"/>
+    </row>
+    <row r="717">
+      <c r="A717" s="2" t="n">
+        <v>295</v>
+      </c>
+      <c r="B717" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销73.8万+件】Gucci 古驰 花悦绽放女士淡香水 50ml 浪漫花香调</t>
+        </is>
+      </c>
+      <c r="C717" s="2" t="inlineStr">
+        <is>
+          <t>古驰花悦绽放女士淡香型香水50ml</t>
+        </is>
+      </c>
+      <c r="D717" s="2" t="n">
+        <v>498</v>
+      </c>
+      <c r="E717" s="2" t="n">
+        <v>317.54</v>
+      </c>
+      <c r="F717" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G717" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-13</t>
+        </is>
+      </c>
+      <c r="H717" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I717" s="2" t="inlineStr"/>
+    </row>
+    <row r="718">
+      <c r="A718" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="B718" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】MAC/魅可新版定制无暇粉底液2.0 持妆控油遮瑕</t>
+        </is>
+      </c>
+      <c r="C718" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液N11 2.0</t>
+        </is>
+      </c>
+      <c r="D718" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="E718" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="F718" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G718" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="H718" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I718" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="B719" s="2" t="inlineStr">
+        <is>
+          <t>正品MAC/魅可定制无暇粉底液2.0#NW11二代30ml持妆油皮控油遮瑕【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C719" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液N11 2.0</t>
+        </is>
+      </c>
+      <c r="D719" s="2" t="inlineStr"/>
+      <c r="E719" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F719" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G719" s="2" t="inlineStr"/>
+      <c r="H719" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I719" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="B720" s="2" t="inlineStr">
+        <is>
+          <t>新版2.0MAC魅可定制无瑕粉底液二代控油持妆遮瑕NM11/N12试色油皮</t>
+        </is>
+      </c>
+      <c r="C720" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液N11 2.0</t>
+        </is>
+      </c>
+      <c r="D720" s="2" t="inlineStr"/>
+      <c r="E720" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="F720" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G720" s="2" t="inlineStr"/>
+      <c r="H720" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I720" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="B721" s="2" t="inlineStr">
+        <is>
+          <t>油皮的神!升级版2.0 Mac魅可定制无暇粉底液30ml 雾面持妆控油</t>
+        </is>
+      </c>
+      <c r="C721" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液N11 2.0</t>
+        </is>
+      </c>
+      <c r="D721" s="2" t="inlineStr"/>
+      <c r="E721" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="F721" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G721" s="2" t="inlineStr"/>
+      <c r="H721" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I721" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="2" t="n">
+        <v>297</v>
+      </c>
+      <c r="B722" s="2" t="inlineStr">
+        <is>
+          <t>不支持7天无理由退换</t>
+        </is>
+      </c>
+      <c r="C722" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液N18 2.0</t>
+        </is>
+      </c>
+      <c r="D722" s="2" t="inlineStr"/>
+      <c r="E722" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="F722" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G722" s="2" t="inlineStr"/>
+      <c r="H722" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I722" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=12.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="2" t="n">
+        <v>297</v>
+      </c>
+      <c r="B723" s="2" t="inlineStr">
+        <is>
+          <t>正品MAC/魅可定制无暇粉底液2.0二代#N18自然色30ml清透遮瑕持妆【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C723" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液N18 2.0</t>
+        </is>
+      </c>
+      <c r="D723" s="2" t="inlineStr"/>
+      <c r="E723" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="F723" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G723" s="2" t="inlineStr"/>
+      <c r="H723" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I723" s="2" t="inlineStr"/>
+    </row>
+    <row r="724">
+      <c r="A724" s="2" t="n">
+        <v>297</v>
+      </c>
+      <c r="B724" s="2" t="inlineStr">
+        <is>
+          <t>【MAC】魅可无瑕粉底液2.0 #N18自然 油皮的神控油持妆遮瑕30ml正品【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C724" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液N18 2.0</t>
+        </is>
+      </c>
+      <c r="D724" s="2" t="inlineStr"/>
+      <c r="E724" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="F724" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G724" s="2" t="inlineStr"/>
+      <c r="H724" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I724" s="2" t="inlineStr"/>
+    </row>
+    <row r="725">
+      <c r="A725" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="B725" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】MAC/魅可新版定制无暇粉底液2.0 持妆控油遮瑕</t>
+        </is>
+      </c>
+      <c r="C725" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液NC11 2.0</t>
+        </is>
+      </c>
+      <c r="D725" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="E725" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="F725" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G725" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="H725" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I725" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="B726" s="2" t="inlineStr">
+        <is>
+          <t>【MAC】魅可定制无暇粉底液2.0二代NW11持妆油皮控油持久</t>
+        </is>
+      </c>
+      <c r="C726" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液NC11 2.0</t>
+        </is>
+      </c>
+      <c r="D726" s="2" t="inlineStr"/>
+      <c r="E726" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="F726" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G726" s="2" t="inlineStr"/>
+      <c r="H726" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I726" s="2" t="inlineStr"/>
+    </row>
+    <row r="727">
+      <c r="A727" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="B727" s="2" t="inlineStr">
+        <is>
+          <t>正品 MAC/魅可无瑕粉底液2.0#NW11 30ml 油皮的神【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C727" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液NC11 2.0</t>
+        </is>
+      </c>
+      <c r="D727" s="2" t="inlineStr"/>
+      <c r="E727" s="2" t="n">
+        <v>134.88</v>
+      </c>
+      <c r="F727" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G727" s="2" t="inlineStr"/>
+      <c r="H727" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I727" s="2" t="inlineStr"/>
+    </row>
+    <row r="728">
+      <c r="A728" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="B728" s="2" t="inlineStr">
+        <is>
+          <t>正品MAC/魅可2.0二代定制无暇粉底液#NW11白皙肤色30ml清透持妆【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C728" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液NC11 2.0</t>
+        </is>
+      </c>
+      <c r="D728" s="2" t="inlineStr"/>
+      <c r="E728" s="2" t="n">
+        <v>134.88</v>
+      </c>
+      <c r="F728" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G728" s="2" t="inlineStr"/>
+      <c r="H728" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I728" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=44.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="B729" s="2" t="inlineStr">
+        <is>
+          <t>【Givenchy】纪梵希 四宫格柔雾散粉0号1号2号3号 12g</t>
+        </is>
+      </c>
+      <c r="C729" s="2" t="inlineStr">
+        <is>
+          <t>纪梵希四宫格散粉1号色（新版）</t>
+        </is>
+      </c>
+      <c r="D729" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="E729" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="F729" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G729" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="H729" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I729" s="2" t="inlineStr"/>
+    </row>
+    <row r="730">
+      <c r="A730" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="B730" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】Givenchy/纪梵希 明星四宫格散粉1号 4*3g</t>
+        </is>
+      </c>
+      <c r="C730" s="2" t="inlineStr">
+        <is>
+          <t>纪梵希四宫格散粉1号色（新版）</t>
+        </is>
+      </c>
+      <c r="D730" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="E730" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="F730" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G730" s="2" t="inlineStr">
+        <is>
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="H581" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I581" s="2" t="inlineStr"/>
+      <c r="H730" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I730" s="2" t="inlineStr"/>
+    </row>
+    <row r="731">
+      <c r="A731" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="B731" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】MAC/魅可新版定制无暇粉底液2.0 持妆控油遮瑕</t>
+        </is>
+      </c>
+      <c r="C731" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液NC11 2.0</t>
+        </is>
+      </c>
+      <c r="D731" s="2" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="E731" s="2" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
+      </c>
+      <c r="F731" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G731" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="H731" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I731" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="B732" s="2" t="inlineStr">
+        <is>
+          <t>【MAC】魅可定制无暇粉底液2.0二代NW11持妆油皮控油持久</t>
+        </is>
+      </c>
+      <c r="C732" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液NC11 2.0</t>
+        </is>
+      </c>
+      <c r="D732" s="2" t="inlineStr"/>
+      <c r="E732" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="F732" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G732" s="2" t="inlineStr"/>
+      <c r="H732" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I732" s="2" t="inlineStr"/>
+    </row>
+    <row r="733">
+      <c r="A733" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="B733" s="2" t="inlineStr">
+        <is>
+          <t>正品 MAC/魅可无瑕粉底液2.0#NW11 30ml 油皮的神【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C733" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液NC11 2.0</t>
+        </is>
+      </c>
+      <c r="D733" s="2" t="inlineStr"/>
+      <c r="E733" s="2" t="inlineStr">
+        <is>
+          <t>134.88</t>
+        </is>
+      </c>
+      <c r="F733" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G733" s="2" t="inlineStr"/>
+      <c r="H733" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I733" s="2" t="inlineStr"/>
+    </row>
+    <row r="734">
+      <c r="A734" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="B734" s="2" t="inlineStr">
+        <is>
+          <t>正品MAC/魅可2.0二代定制无暇粉底液#NW11白皙肤色30ml清透持妆【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C734" s="2" t="inlineStr">
+        <is>
+          <t>MAC无瑕粉底液NC11 2.0</t>
+        </is>
+      </c>
+      <c r="D734" s="2" t="inlineStr"/>
+      <c r="E734" s="2" t="inlineStr">
+        <is>
+          <t>134.88</t>
+        </is>
+      </c>
+      <c r="F734" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G734" s="2" t="inlineStr"/>
+      <c r="H734" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I734" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=44.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="B735" s="2" t="inlineStr">
+        <is>
+          <t>【Givenchy】纪梵希 四宫格柔雾散粉0号1号2号3号 12g</t>
+        </is>
+      </c>
+      <c r="C735" s="2" t="inlineStr">
+        <is>
+          <t>纪梵希四宫格散粉1号色（新版）</t>
+        </is>
+      </c>
+      <c r="D735" s="2" t="inlineStr">
+        <is>
+          <t>298.0</t>
+        </is>
+      </c>
+      <c r="E735" s="2" t="inlineStr">
+        <is>
+          <t>187.0</t>
+        </is>
+      </c>
+      <c r="F735" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G735" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="H735" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I735" s="2" t="inlineStr"/>
+    </row>
+    <row r="736">
+      <c r="A736" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="B736" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】Givenchy/纪梵希 明星四宫格散粉1号 4*3g</t>
+        </is>
+      </c>
+      <c r="C736" s="2" t="inlineStr">
+        <is>
+          <t>纪梵希四宫格散粉1号色（新版）</t>
+        </is>
+      </c>
+      <c r="D736" s="2" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="E736" s="2" t="inlineStr">
+        <is>
+          <t>183.0</t>
+        </is>
+      </c>
+      <c r="F736" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G736" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="H736" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I736" s="2" t="inlineStr"/>
+    </row>
+    <row r="737">
+      <c r="A737" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="B737" s="2" t="inlineStr">
+        <is>
+          <t>DECORTE黛珂 牛油果植萃乳液300ML老版保湿紧致弹润控油持久保湿</t>
+        </is>
+      </c>
+      <c r="C737" s="2" t="inlineStr">
+        <is>
+          <t>黛珂牛油果乳液300ml*2</t>
+        </is>
+      </c>
+      <c r="D737" s="2" t="inlineStr">
+        <is>
+          <t>179.0</t>
+        </is>
+      </c>
+      <c r="E737" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="F737" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G737" s="2" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="H737" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I737" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/商品采集汇总.xlsx
+++ b/商品采集汇总.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I737"/>
+  <dimension ref="A1:I921"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -27123,27 +27123,23 @@
     </row>
     <row r="731">
       <c r="A731" s="2" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B731" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】MAC/魅可新版定制无暇粉底液2.0 持妆控油遮瑕</t>
+          <t>DECORTE黛珂 牛油果植萃乳液300ML老版保湿紧致弹润控油持久保湿</t>
         </is>
       </c>
       <c r="C731" s="2" t="inlineStr">
         <is>
-          <t>MAC无瑕粉底液NC11 2.0</t>
-        </is>
-      </c>
-      <c r="D731" s="2" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="E731" s="2" t="inlineStr">
-        <is>
-          <t>165.0</t>
-        </is>
+          <t>黛珂牛油果乳液300ml*2</t>
+        </is>
+      </c>
+      <c r="D731" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="E731" s="2" t="n">
+        <v>135</v>
       </c>
       <c r="F731" s="2" t="inlineStr">
         <is>
@@ -27152,43 +27148,39 @@
       </c>
       <c r="G731" s="2" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="H731" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I731" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I731" s="2" t="inlineStr"/>
     </row>
     <row r="732">
       <c r="A732" s="2" t="n">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B732" s="2" t="inlineStr">
         <is>
-          <t>【MAC】魅可定制无暇粉底液2.0二代NW11持妆油皮控油持久</t>
+          <t>【正品行货】肌肤之钥净采洁面膏125ml*2清爽型/湿润型补水保湿</t>
         </is>
       </c>
       <c r="C732" s="2" t="inlineStr">
         <is>
-          <t>MAC无瑕粉底液NC11 2.0</t>
-        </is>
-      </c>
-      <c r="D732" s="2" t="inlineStr"/>
-      <c r="E732" s="2" t="inlineStr">
-        <is>
-          <t>158.0</t>
-        </is>
+          <t>CPB肌肤之钥清爽洁面125ML</t>
+        </is>
+      </c>
+      <c r="D732" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="E732" s="2" t="n">
+        <v>364</v>
       </c>
       <c r="F732" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G732" s="2" t="inlineStr"/>
@@ -27201,57 +27193,47 @@
     </row>
     <row r="733">
       <c r="A733" s="2" t="n">
-        <v>298</v>
-      </c>
-      <c r="B733" s="2" t="inlineStr">
-        <is>
-          <t>正品 MAC/魅可无瑕粉底液2.0#NW11 30ml 油皮的神【5天内发货】</t>
-        </is>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="B733" s="2" t="inlineStr"/>
       <c r="C733" s="2" t="inlineStr">
         <is>
-          <t>MAC无瑕粉底液NC11 2.0</t>
+          <t>CPB肌肤之钥清爽洁面125ML</t>
         </is>
       </c>
       <c r="D733" s="2" t="inlineStr"/>
-      <c r="E733" s="2" t="inlineStr">
-        <is>
-          <t>134.88</t>
-        </is>
+      <c r="E733" s="2" t="n">
+        <v>364</v>
       </c>
       <c r="F733" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G733" s="2" t="inlineStr"/>
       <c r="H733" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I733" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I733" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="734">
       <c r="A734" s="2" t="n">
-        <v>298</v>
-      </c>
-      <c r="B734" s="2" t="inlineStr">
-        <is>
-          <t>正品MAC/魅可2.0二代定制无暇粉底液#NW11白皙肤色30ml清透持妆【5天内发货】</t>
-        </is>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="B734" s="2" t="inlineStr"/>
       <c r="C734" s="2" t="inlineStr">
         <is>
-          <t>MAC无瑕粉底液NC11 2.0</t>
+          <t>CPB肌肤之钥清爽洁面125ML</t>
         </is>
       </c>
       <c r="D734" s="2" t="inlineStr"/>
-      <c r="E734" s="2" t="inlineStr">
-        <is>
-          <t>134.88</t>
-        </is>
-      </c>
+      <c r="E734" s="2" t="inlineStr"/>
       <c r="F734" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -27265,33 +27247,29 @@
       </c>
       <c r="I734" s="2" t="inlineStr">
         <is>
-          <t>品名相似不足(ratio=44.4%)</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
     </row>
     <row r="735">
       <c r="A735" s="2" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B735" s="2" t="inlineStr">
         <is>
-          <t>【Givenchy】纪梵希 四宫格柔雾散粉0号1号2号3号 12g</t>
+          <t>【 正品行货】CPB/肌肤之钥洗面奶125ml光凝润采妆前隔离37ml</t>
         </is>
       </c>
       <c r="C735" s="2" t="inlineStr">
         <is>
-          <t>纪梵希四宫格散粉1号色（新版）</t>
-        </is>
-      </c>
-      <c r="D735" s="2" t="inlineStr">
-        <is>
-          <t>298.0</t>
-        </is>
-      </c>
-      <c r="E735" s="2" t="inlineStr">
-        <is>
-          <t>187.0</t>
-        </is>
+          <t>CPB肌肤之钥清爽洁面125ML</t>
+        </is>
+      </c>
+      <c r="D735" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="E735" s="2" t="n">
+        <v>362.51</v>
       </c>
       <c r="F735" s="2" t="inlineStr">
         <is>
@@ -27300,48 +27278,46 @@
       </c>
       <c r="G735" s="2" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="H735" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I735" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I735" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="736">
       <c r="A736" s="2" t="n">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B736" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】Givenchy/纪梵希 明星四宫格散粉1号 4*3g</t>
+          <t>【正品行货】GUCCI古驰绮梦栀子香水爆款花香调简装EDP无盖 100ml</t>
         </is>
       </c>
       <c r="C736" s="2" t="inlineStr">
         <is>
-          <t>纪梵希四宫格散粉1号色（新版）</t>
-        </is>
-      </c>
-      <c r="D736" s="2" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="E736" s="2" t="inlineStr">
-        <is>
-          <t>183.0</t>
-        </is>
+          <t>GUCCI绮梦馥栀100ML</t>
+        </is>
+      </c>
+      <c r="D736" s="2" t="inlineStr"/>
+      <c r="E736" s="2" t="n">
+        <v>712</v>
       </c>
       <c r="F736" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G736" s="2" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="H736" s="2" t="inlineStr">
@@ -27353,27 +27329,23 @@
     </row>
     <row r="737">
       <c r="A737" s="2" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B737" s="2" t="inlineStr">
         <is>
-          <t>DECORTE黛珂 牛油果植萃乳液300ML老版保湿紧致弹润控油持久保湿</t>
+          <t>【正品行货】GUCCI古驰绮梦花园系列馥栀女士香水花香调EDP100ml</t>
         </is>
       </c>
       <c r="C737" s="2" t="inlineStr">
         <is>
-          <t>黛珂牛油果乳液300ml*2</t>
-        </is>
-      </c>
-      <c r="D737" s="2" t="inlineStr">
-        <is>
-          <t>179.0</t>
-        </is>
-      </c>
-      <c r="E737" s="2" t="inlineStr">
-        <is>
-          <t>135.0</t>
-        </is>
+          <t>GUCCI绮梦馥栀100ML</t>
+        </is>
+      </c>
+      <c r="D737" s="2" t="n">
+        <v>922</v>
+      </c>
+      <c r="E737" s="2" t="n">
+        <v>609</v>
       </c>
       <c r="F737" s="2" t="inlineStr">
         <is>
@@ -27382,7 +27354,7 @@
       </c>
       <c r="G737" s="2" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H737" s="2" t="inlineStr">
@@ -27391,6 +27363,6572 @@
         </is>
       </c>
       <c r="I737" s="2" t="inlineStr"/>
+    </row>
+    <row r="738">
+      <c r="A738" s="2" t="n">
+        <v>302</v>
+      </c>
+      <c r="B738" s="2" t="inlineStr">
+        <is>
+          <t>Gucci古驰绮梦馥栀女士EDP浓香水100ml 25年新品</t>
+        </is>
+      </c>
+      <c r="C738" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦馥栀100ML</t>
+        </is>
+      </c>
+      <c r="D738" s="2" t="n">
+        <v>799</v>
+      </c>
+      <c r="E738" s="2" t="n">
+        <v>574</v>
+      </c>
+      <c r="F738" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G738" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="H738" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I738" s="2" t="inlineStr"/>
+    </row>
+    <row r="739">
+      <c r="A739" s="2" t="n">
+        <v>302</v>
+      </c>
+      <c r="B739" s="2" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰绮梦馥栀香水100ml简装正品持久留香节日礼物自用</t>
+        </is>
+      </c>
+      <c r="C739" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦馥栀100ML</t>
+        </is>
+      </c>
+      <c r="D739" s="2" t="n">
+        <v>699</v>
+      </c>
+      <c r="E739" s="2" t="n">
+        <v>471.82</v>
+      </c>
+      <c r="F739" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G739" s="2" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="H739" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I739" s="2" t="inlineStr"/>
+    </row>
+    <row r="740">
+      <c r="A740" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="B740" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI古驰花悦绽放慕意香水女士优雅简装EDP 100ml</t>
+        </is>
+      </c>
+      <c r="C740" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI花悦绽放100ML浓香</t>
+        </is>
+      </c>
+      <c r="D740" s="2" t="inlineStr"/>
+      <c r="E740" s="2" t="n">
+        <v>852</v>
+      </c>
+      <c r="F740" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G740" s="2" t="inlineStr"/>
+      <c r="H740" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I740" s="2" t="inlineStr"/>
+    </row>
+    <row r="741">
+      <c r="A741" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="B741" s="2" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰花悦绽放浓香水100ml简装黑盖女士香氛正品持久留香</t>
+        </is>
+      </c>
+      <c r="C741" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI花悦绽放100ML浓香</t>
+        </is>
+      </c>
+      <c r="D741" s="2" t="n">
+        <v>538</v>
+      </c>
+      <c r="E741" s="2" t="n">
+        <v>339</v>
+      </c>
+      <c r="F741" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G741" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="H741" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I741" s="2" t="inlineStr"/>
+    </row>
+    <row r="742">
+      <c r="A742" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="B742" s="2" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰花悦绽放女士浓香水花香调持久留香送礼100ml</t>
+        </is>
+      </c>
+      <c r="C742" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI花悦绽放100ML浓香</t>
+        </is>
+      </c>
+      <c r="D742" s="2" t="n">
+        <v>447</v>
+      </c>
+      <c r="E742" s="2" t="n">
+        <v>380.82</v>
+      </c>
+      <c r="F742" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G742" s="2" t="inlineStr"/>
+      <c r="H742" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I742" s="2" t="inlineStr"/>
+    </row>
+    <row r="743">
+      <c r="A743" s="2" t="n">
+        <v>304</v>
+      </c>
+      <c r="B743" s="2" t="inlineStr">
+        <is>
+          <t>【全球购正品】古驰绮梦木兰香型女士香水100ml</t>
+        </is>
+      </c>
+      <c r="C743" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦木兰100ML浓香型</t>
+        </is>
+      </c>
+      <c r="D743" s="2" t="n">
+        <v>599</v>
+      </c>
+      <c r="E743" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="F743" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G743" s="2" t="inlineStr"/>
+      <c r="H743" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I743" s="2" t="inlineStr"/>
+    </row>
+    <row r="744">
+      <c r="A744" s="2" t="n">
+        <v>305</v>
+      </c>
+      <c r="B744" s="2" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰绮梦栀子花女士浓香水EDP100ml520节日礼物</t>
+        </is>
+      </c>
+      <c r="C744" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦栀子花100ML浓香型</t>
+        </is>
+      </c>
+      <c r="D744" s="2" t="n">
+        <v>699</v>
+      </c>
+      <c r="E744" s="2" t="n">
+        <v>429.8</v>
+      </c>
+      <c r="F744" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G744" s="2" t="inlineStr"/>
+      <c r="H744" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I744" s="2" t="inlineStr"/>
+    </row>
+    <row r="745">
+      <c r="A745" s="2" t="n">
+        <v>305</v>
+      </c>
+      <c r="B745" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI古驰绮梦栀子香水爆款花香调简装EDP无盖 100ml</t>
+        </is>
+      </c>
+      <c r="C745" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦栀子花100ML浓香型</t>
+        </is>
+      </c>
+      <c r="D745" s="2" t="inlineStr"/>
+      <c r="E745" s="2" t="n">
+        <v>712</v>
+      </c>
+      <c r="F745" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G745" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-12</t>
+        </is>
+      </c>
+      <c r="H745" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I745" s="2" t="inlineStr"/>
+    </row>
+    <row r="746">
+      <c r="A746" s="2" t="n">
+        <v>305</v>
+      </c>
+      <c r="B746" s="2" t="inlineStr">
+        <is>
+          <t>Gucci古驰绮梦馥栀女士EDP浓香水100ml 25年新品</t>
+        </is>
+      </c>
+      <c r="C746" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦栀子花100ML浓香型</t>
+        </is>
+      </c>
+      <c r="D746" s="2" t="n">
+        <v>799</v>
+      </c>
+      <c r="E746" s="2" t="n">
+        <v>574</v>
+      </c>
+      <c r="F746" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G746" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="H746" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I746" s="2" t="inlineStr"/>
+    </row>
+    <row r="747">
+      <c r="A747" s="2" t="n">
+        <v>305</v>
+      </c>
+      <c r="B747" s="2" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰绮梦馥栀香水100ml简装正品持久留香节日礼物自用</t>
+        </is>
+      </c>
+      <c r="C747" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦栀子花100ML浓香型</t>
+        </is>
+      </c>
+      <c r="D747" s="2" t="n">
+        <v>699</v>
+      </c>
+      <c r="E747" s="2" t="n">
+        <v>471.82</v>
+      </c>
+      <c r="F747" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G747" s="2" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="H747" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I747" s="2" t="inlineStr"/>
+    </row>
+    <row r="748">
+      <c r="A748" s="2" t="n">
+        <v>306</v>
+      </c>
+      <c r="B748" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI古驰绮梦香草兰浓香水 甜美水生美食调 EDP30ml</t>
+        </is>
+      </c>
+      <c r="C748" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦香草兰香100ml</t>
+        </is>
+      </c>
+      <c r="D748" s="2" t="inlineStr"/>
+      <c r="E748" s="2" t="n">
+        <v>603</v>
+      </c>
+      <c r="F748" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G748" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="H748" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I748" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="2" t="n">
+        <v>306</v>
+      </c>
+      <c r="B749" s="2" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰绮梦香草兰香型女士浓香水水生调节日礼物【520礼物】</t>
+        </is>
+      </c>
+      <c r="C749" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦香草兰香100ml</t>
+        </is>
+      </c>
+      <c r="D749" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="E749" s="2" t="n">
+        <v>181</v>
+      </c>
+      <c r="F749" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G749" s="2" t="inlineStr"/>
+      <c r="H749" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I749" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="2" t="n">
+        <v>306</v>
+      </c>
+      <c r="B750" s="2" t="inlineStr">
+        <is>
+          <t>【100ml】古驰 绮梦兰花浓香水EDP简装无盖</t>
+        </is>
+      </c>
+      <c r="C750" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦香草兰香100ml</t>
+        </is>
+      </c>
+      <c r="D750" s="2" t="inlineStr"/>
+      <c r="E750" s="2" t="n">
+        <v>888</v>
+      </c>
+      <c r="F750" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G750" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="H750" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I750" s="2" t="inlineStr"/>
+    </row>
+    <row r="751">
+      <c r="A751" s="2" t="n">
+        <v>307</v>
+      </c>
+      <c r="B751" s="2" t="inlineStr">
+        <is>
+          <t>Gucci古驰绮梦馥栀女士EDP浓香水100ml 25年新品</t>
+        </is>
+      </c>
+      <c r="C751" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦香草兰香50ml</t>
+        </is>
+      </c>
+      <c r="D751" s="2" t="n">
+        <v>799</v>
+      </c>
+      <c r="E751" s="2" t="n">
+        <v>574</v>
+      </c>
+      <c r="F751" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G751" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="H751" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I751" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=33.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="2" t="n">
+        <v>307</v>
+      </c>
+      <c r="B752" s="2" t="inlineStr">
+        <is>
+          <t>【正品鉴定】GUCCI古驰 2024年新品 绮梦香草兰浓香水/兰花香草</t>
+        </is>
+      </c>
+      <c r="C752" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦香草兰香50ml</t>
+        </is>
+      </c>
+      <c r="D752" s="2" t="inlineStr"/>
+      <c r="E752" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="F752" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G752" s="2" t="inlineStr"/>
+      <c r="H752" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I752" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="2" t="n">
+        <v>307</v>
+      </c>
+      <c r="B753" s="2" t="inlineStr">
+        <is>
+          <t>【国内直售】GUCCI/古驰香水新品绮梦栀子花香草兰浓香EDP</t>
+        </is>
+      </c>
+      <c r="C753" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦香草兰香50ml</t>
+        </is>
+      </c>
+      <c r="D753" s="2" t="inlineStr"/>
+      <c r="E753" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="F753" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G753" s="2" t="inlineStr"/>
+      <c r="H753" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I753" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="2" t="n">
+        <v>307</v>
+      </c>
+      <c r="B754" s="2" t="inlineStr">
+        <is>
+          <t>【原盒正品】GUCCI古驰 2024年新品 绮梦香草兰浓香水/兰花香草</t>
+        </is>
+      </c>
+      <c r="C754" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI绮梦香草兰香50ml</t>
+        </is>
+      </c>
+      <c r="D754" s="2" t="inlineStr"/>
+      <c r="E754" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="F754" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G754" s="2" t="inlineStr"/>
+      <c r="H754" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I754" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="B755" s="2" t="inlineStr">
+        <is>
+          <t>【卡诗】黑钻钥源洗发水鱼子酱滋养受损干枯毛躁润泽保湿黑金洗发露</t>
+        </is>
+      </c>
+      <c r="C755" s="2" t="inlineStr">
+        <is>
+          <t>Kerastase卡诗黑钻鱼子酱洗发水250ml</t>
+        </is>
+      </c>
+      <c r="D755" s="2" t="inlineStr"/>
+      <c r="E755" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="F755" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G755" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="H755" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I755" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="B756" s="2" t="inlineStr">
+        <is>
+          <t>【卡诗】黑钻钥源凝时鱼子酱洗发水250ml滋养修护柔顺温和清洁 专柜</t>
+        </is>
+      </c>
+      <c r="C756" s="2" t="inlineStr">
+        <is>
+          <t>Kerastase卡诗黑钻鱼子酱洗发水250ml</t>
+        </is>
+      </c>
+      <c r="D756" s="2" t="inlineStr"/>
+      <c r="E756" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="F756" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G756" s="2" t="inlineStr"/>
+      <c r="H756" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I756" s="2" t="inlineStr"/>
+    </row>
+    <row r="757">
+      <c r="A757" s="2" t="n">
+        <v>309</v>
+      </c>
+      <c r="B757" s="2" t="inlineStr">
+        <is>
+          <t>【赫莲娜】赫莲娜HR绿宝瓶新肌水400ml精华爽肤舒缓修护</t>
+        </is>
+      </c>
+      <c r="C757" s="2" t="inlineStr">
+        <is>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水400ml</t>
+        </is>
+      </c>
+      <c r="D757" s="2" t="n">
+        <v>895</v>
+      </c>
+      <c r="E757" s="2" t="n">
+        <v>688</v>
+      </c>
+      <c r="F757" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G757" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="H757" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I757" s="2" t="inlineStr"/>
+    </row>
+    <row r="758">
+      <c r="A758" s="2" t="n">
+        <v>309</v>
+      </c>
+      <c r="B758" s="2" t="inlineStr">
+        <is>
+          <t>【赫莲娜】绿宝瓶新肌水200ml补水保湿精华水</t>
+        </is>
+      </c>
+      <c r="C758" s="2" t="inlineStr">
+        <is>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水400ml</t>
+        </is>
+      </c>
+      <c r="D758" s="2" t="n">
+        <v>699</v>
+      </c>
+      <c r="E758" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="F758" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G758" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H758" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I758" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="2" t="n">
+        <v>309</v>
+      </c>
+      <c r="B759" s="2" t="inlineStr">
+        <is>
+          <t>两瓶 单品 HR赫莲娜绿宝瓶悦活蓄能新肌水400ml</t>
+        </is>
+      </c>
+      <c r="C759" s="2" t="inlineStr">
+        <is>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水400ml</t>
+        </is>
+      </c>
+      <c r="D759" s="2" t="n">
+        <v>1599</v>
+      </c>
+      <c r="E759" s="2" t="n">
+        <v>1291</v>
+      </c>
+      <c r="F759" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G759" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="H759" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I759" s="2" t="inlineStr"/>
+    </row>
+    <row r="760">
+      <c r="A760" s="2" t="n">
+        <v>310</v>
+      </c>
+      <c r="B760" s="2" t="inlineStr">
+        <is>
+          <t>HR/赫莲娜绿宝瓶新肌水200ml*2维稳补水保湿精华水</t>
+        </is>
+      </c>
+      <c r="C760" s="2" t="inlineStr">
+        <is>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水200ml</t>
+        </is>
+      </c>
+      <c r="D760" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="E760" s="2" t="n">
+        <v>954</v>
+      </c>
+      <c r="F760" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G760" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="H760" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I760" s="2" t="inlineStr"/>
+    </row>
+    <row r="761">
+      <c r="A761" s="2" t="n">
+        <v>310</v>
+      </c>
+      <c r="B761" s="2" t="inlineStr">
+        <is>
+          <t>【赫莲娜】绿宝瓶新肌水200ml补水保湿精华水</t>
+        </is>
+      </c>
+      <c r="C761" s="2" t="inlineStr">
+        <is>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水200ml</t>
+        </is>
+      </c>
+      <c r="D761" s="2" t="n">
+        <v>699</v>
+      </c>
+      <c r="E761" s="2" t="n">
+        <v>480</v>
+      </c>
+      <c r="F761" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G761" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H761" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I761" s="2" t="inlineStr"/>
+    </row>
+    <row r="762">
+      <c r="A762" s="2" t="n">
+        <v>310</v>
+      </c>
+      <c r="B762" s="2" t="inlineStr">
+        <is>
+          <t>两瓶 单品 HR赫莲娜绿宝瓶悦活蓄能新肌水400ml</t>
+        </is>
+      </c>
+      <c r="C762" s="2" t="inlineStr">
+        <is>
+          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水200ml</t>
+        </is>
+      </c>
+      <c r="D762" s="2" t="n">
+        <v>1599</v>
+      </c>
+      <c r="E762" s="2" t="n">
+        <v>1291</v>
+      </c>
+      <c r="F762" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G762" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="H762" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I762" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="2" t="n">
+        <v>311</v>
+      </c>
+      <c r="B763" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II光子小灯泡50ml美白护肤精华液淡斑提亮</t>
+        </is>
+      </c>
+      <c r="C763" s="2" t="inlineStr">
+        <is>
+          <t>SK-II光子小灯泡精华露50ml</t>
+        </is>
+      </c>
+      <c r="D763" s="2" t="n">
+        <v>1213</v>
+      </c>
+      <c r="E763" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="F763" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G763" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="H763" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I763" s="2" t="inlineStr"/>
+    </row>
+    <row r="764">
+      <c r="A764" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="B764" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II骨胶原晶致活肤修护乳液补水保湿抗皱紧致舒缓</t>
+        </is>
+      </c>
+      <c r="C764" s="2" t="inlineStr">
+        <is>
+          <t>SK-II晶致美肤乳液100g</t>
+        </is>
+      </c>
+      <c r="D764" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="E764" s="2" t="n">
+        <v>432</v>
+      </c>
+      <c r="F764" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G764" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="H764" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I764" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="B765" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】 晶致美肤乳液100ml 骨胶原修护活肤乳液紧致提亮保湿抗皱</t>
+        </is>
+      </c>
+      <c r="C765" s="2" t="inlineStr">
+        <is>
+          <t>SK-II晶致美肤乳液100g</t>
+        </is>
+      </c>
+      <c r="D765" s="2" t="inlineStr"/>
+      <c r="E765" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F765" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G765" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="H765" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I765" s="2" t="inlineStr"/>
+    </row>
+    <row r="766">
+      <c r="A766" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="B766" s="2" t="inlineStr">
+        <is>
+          <t>SK-II/SK2 晶致活肤骨胶原乳液100g(无盒/不满瓶)【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C766" s="2" t="inlineStr">
+        <is>
+          <t>SK-II晶致美肤乳液100g</t>
+        </is>
+      </c>
+      <c r="D766" s="2" t="inlineStr"/>
+      <c r="E766" s="2" t="n">
+        <v>349</v>
+      </c>
+      <c r="F766" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G766" s="2" t="inlineStr"/>
+      <c r="H766" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I766" s="2" t="inlineStr"/>
+    </row>
+    <row r="767">
+      <c r="A767" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="B767" s="2" t="inlineStr">
+        <is>
+          <t>SK2晶致美肤乳液100g 骨胶原修护紧致活肤 保湿不油腻【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C767" s="2" t="inlineStr">
+        <is>
+          <t>SK-II晶致美肤乳液100g</t>
+        </is>
+      </c>
+      <c r="D767" s="2" t="inlineStr"/>
+      <c r="E767" s="2" t="n">
+        <v>386</v>
+      </c>
+      <c r="F767" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G767" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="H767" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I767" s="2" t="inlineStr"/>
+    </row>
+    <row r="768">
+      <c r="A768" s="2" t="n">
+        <v>313</v>
+      </c>
+      <c r="B768" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II温和护肤洁面霜SK2舒透洗面奶洁净舒缓肌肤skll</t>
+        </is>
+      </c>
+      <c r="C768" s="2" t="inlineStr">
+        <is>
+          <t>SKII女士洗面奶120g/支</t>
+        </is>
+      </c>
+      <c r="D768" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="E768" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="F768" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G768" s="2" t="inlineStr"/>
+      <c r="H768" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I768" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="2" t="n">
+        <v>313</v>
+      </c>
+      <c r="B769" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】 女士氨基酸清洁洁面乳120g/支</t>
+        </is>
+      </c>
+      <c r="C769" s="2" t="inlineStr">
+        <is>
+          <t>SKII女士洗面奶120g/支</t>
+        </is>
+      </c>
+      <c r="D769" s="2" t="n">
+        <v>339</v>
+      </c>
+      <c r="E769" s="2" t="n">
+        <v>244</v>
+      </c>
+      <c r="F769" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G769" s="2" t="inlineStr"/>
+      <c r="H769" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I769" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=33.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="2" t="n">
+        <v>313</v>
+      </c>
+      <c r="B770" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SKII氨基酸洗面奶护肤洁面乳120g两瓶装温和控油清洁</t>
+        </is>
+      </c>
+      <c r="C770" s="2" t="inlineStr">
+        <is>
+          <t>SKII女士洗面奶120g/支</t>
+        </is>
+      </c>
+      <c r="D770" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="E770" s="2" t="n">
+        <v>481</v>
+      </c>
+      <c r="F770" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G770" s="2" t="inlineStr"/>
+      <c r="H770" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I770" s="2" t="inlineStr"/>
+    </row>
+    <row r="771">
+      <c r="A771" s="2" t="n">
+        <v>314</v>
+      </c>
+      <c r="B771" s="2" t="inlineStr">
+        <is>
+          <t>【原装正品】 SK-II/SK2前男友面膜补水保湿急救护肤3/4/6/10片装【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C771" s="2" t="inlineStr">
+        <is>
+          <t>SK-II前男友面膜10片装</t>
+        </is>
+      </c>
+      <c r="D771" s="2" t="n">
+        <v>518</v>
+      </c>
+      <c r="E771" s="2" t="n">
+        <v>410</v>
+      </c>
+      <c r="F771" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G771" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="H771" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I771" s="2" t="inlineStr"/>
+    </row>
+    <row r="772">
+      <c r="A772" s="2" t="n">
+        <v>314</v>
+      </c>
+      <c r="B772" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK2前男友面膜10片装焕润嫩肤贴片女友送礼奢护礼盒</t>
+        </is>
+      </c>
+      <c r="C772" s="2" t="inlineStr">
+        <is>
+          <t>SK-II前男友面膜10片装</t>
+        </is>
+      </c>
+      <c r="D772" s="2" t="n">
+        <v>998</v>
+      </c>
+      <c r="E772" s="2" t="n">
+        <v>695</v>
+      </c>
+      <c r="F772" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G772" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="H772" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I772" s="2" t="inlineStr"/>
+    </row>
+    <row r="773">
+      <c r="A773" s="2" t="n">
+        <v>315</v>
+      </c>
+      <c r="B773" s="2" t="inlineStr">
+        <is>
+          <t>【原装正品】 SK-II/SK2前男友面膜补水保湿急救护肤3/4/6/10片装【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C773" s="2" t="inlineStr">
+        <is>
+          <t>SK-II前男友面膜10片装</t>
+        </is>
+      </c>
+      <c r="D773" s="2" t="n">
+        <v>518</v>
+      </c>
+      <c r="E773" s="2" t="n">
+        <v>410</v>
+      </c>
+      <c r="F773" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G773" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="H773" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I773" s="2" t="inlineStr"/>
+    </row>
+    <row r="774">
+      <c r="A774" s="2" t="n">
+        <v>315</v>
+      </c>
+      <c r="B774" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK2前男友面膜10片装焕润嫩肤贴片女友送礼奢护礼盒</t>
+        </is>
+      </c>
+      <c r="C774" s="2" t="inlineStr">
+        <is>
+          <t>SK-II前男友面膜10片装</t>
+        </is>
+      </c>
+      <c r="D774" s="2" t="n">
+        <v>998</v>
+      </c>
+      <c r="E774" s="2" t="n">
+        <v>695</v>
+      </c>
+      <c r="F774" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G774" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="H774" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I774" s="2" t="inlineStr"/>
+    </row>
+    <row r="775">
+      <c r="A775" s="2" t="n">
+        <v>316</v>
+      </c>
+      <c r="B775" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SKII赋能焕采精华霜大红瓶面霜滋润轻盈保湿紧致养肤</t>
+        </is>
+      </c>
+      <c r="C775" s="2" t="inlineStr">
+        <is>
+          <t>SKII大红瓶面霜80g清爽</t>
+        </is>
+      </c>
+      <c r="D775" s="2" t="n">
+        <v>1048</v>
+      </c>
+      <c r="E775" s="2" t="n">
+        <v>692</v>
+      </c>
+      <c r="F775" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G775" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="H775" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I775" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="2" t="n">
+        <v>316</v>
+      </c>
+      <c r="B776" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】大红瓶面霜80g 滋润版</t>
+        </is>
+      </c>
+      <c r="C776" s="2" t="inlineStr">
+        <is>
+          <t>SKII大红瓶面霜80g清爽</t>
+        </is>
+      </c>
+      <c r="D776" s="2" t="n">
+        <v>879</v>
+      </c>
+      <c r="E776" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="F776" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G776" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="H776" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I776" s="2" t="inlineStr"/>
+    </row>
+    <row r="777">
+      <c r="A777" s="2" t="n">
+        <v>316</v>
+      </c>
+      <c r="B777" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】大红瓶面霜80g滋养保湿紧致肌肤清爽款</t>
+        </is>
+      </c>
+      <c r="C777" s="2" t="inlineStr">
+        <is>
+          <t>SKII大红瓶面霜80g清爽</t>
+        </is>
+      </c>
+      <c r="D777" s="2" t="n">
+        <v>868</v>
+      </c>
+      <c r="E777" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="F777" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G777" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H777" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I777" s="2" t="inlineStr"/>
+    </row>
+    <row r="778">
+      <c r="A778" s="2" t="n">
+        <v>316</v>
+      </c>
+      <c r="B778" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】大红瓶面霜80g滋养保湿紧致肌肤滋润款</t>
+        </is>
+      </c>
+      <c r="C778" s="2" t="inlineStr">
+        <is>
+          <t>SKII大红瓶面霜80g清爽</t>
+        </is>
+      </c>
+      <c r="D778" s="2" t="n">
+        <v>868</v>
+      </c>
+      <c r="E778" s="2" t="n">
+        <v>618</v>
+      </c>
+      <c r="F778" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G778" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="H778" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I778" s="2" t="inlineStr"/>
+    </row>
+    <row r="779">
+      <c r="A779" s="2" t="n">
+        <v>317</v>
+      </c>
+      <c r="B779" s="2" t="inlineStr">
+        <is>
+          <t>【特价清仓】NARS纳斯哑光唇釉空气柔雾唇霜#684 Gipsy吉普赛玫瑰</t>
+        </is>
+      </c>
+      <c r="C779" s="2" t="inlineStr">
+        <is>
+          <t>NARS空气唇釉GIPSY吉普赛</t>
+        </is>
+      </c>
+      <c r="D779" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="E779" s="2" t="n">
+        <v>113.05</v>
+      </c>
+      <c r="F779" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G779" s="2" t="inlineStr"/>
+      <c r="H779" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I779" s="2" t="inlineStr"/>
+    </row>
+    <row r="780">
+      <c r="A780" s="2" t="n">
+        <v>318</v>
+      </c>
+      <c r="B780" s="2" t="inlineStr">
+        <is>
+          <t>宏香记品牌官方正品，100%保障</t>
+        </is>
+      </c>
+      <c r="C780" s="2" t="inlineStr">
+        <is>
+          <t>后Whoo天气丹PRO乳110ML</t>
+        </is>
+      </c>
+      <c r="D780" s="2" t="inlineStr"/>
+      <c r="E780" s="2" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="F780" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G780" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="H780" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I780" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="2" t="n">
+        <v>318</v>
+      </c>
+      <c r="B781" s="2" t="inlineStr">
+        <is>
+          <t>韩国直邮THEWHOO后天气丹PRO光耀焕活紧颜滋养水乳正装提拉抗皱白【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C781" s="2" t="inlineStr">
+        <is>
+          <t>后Whoo天气丹PRO乳110ML</t>
+        </is>
+      </c>
+      <c r="D781" s="2" t="inlineStr"/>
+      <c r="E781" s="2" t="n">
+        <v>448</v>
+      </c>
+      <c r="F781" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G781" s="2" t="inlineStr"/>
+      <c r="H781" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I781" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="2" t="n">
+        <v>318</v>
+      </c>
+      <c r="B782" s="2" t="inlineStr">
+        <is>
+          <t>韩国whoo后天气丹PRO淡纹乳110ml 清透保湿亮肤紧致抗皱滋养乳【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C782" s="2" t="inlineStr">
+        <is>
+          <t>后Whoo天气丹PRO乳110ML</t>
+        </is>
+      </c>
+      <c r="D782" s="2" t="inlineStr"/>
+      <c r="E782" s="2" t="n">
+        <v>223</v>
+      </c>
+      <c r="F782" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G782" s="2" t="inlineStr"/>
+      <c r="H782" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I782" s="2" t="inlineStr"/>
+    </row>
+    <row r="783">
+      <c r="A783" s="2" t="n">
+        <v>318</v>
+      </c>
+      <c r="B783" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】后天气丹PRO光耀焕活紧颜滋养乳50ml/瓶保湿紧致滋润</t>
+        </is>
+      </c>
+      <c r="C783" s="2" t="inlineStr">
+        <is>
+          <t>后Whoo天气丹PRO乳110ML</t>
+        </is>
+      </c>
+      <c r="D783" s="2" t="inlineStr"/>
+      <c r="E783" s="2" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="F783" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G783" s="2" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="H783" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I783" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="2" t="n">
+        <v>319</v>
+      </c>
+      <c r="B784" s="2" t="inlineStr"/>
+      <c r="C784" s="2" t="inlineStr">
+        <is>
+          <t>后拱辰享美黄金气垫13G+替换装13G</t>
+        </is>
+      </c>
+      <c r="D784" s="2" t="inlineStr"/>
+      <c r="E784" s="2" t="n">
+        <v>47.99</v>
+      </c>
+      <c r="F784" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G784" s="2" t="inlineStr"/>
+      <c r="H784" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I784" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="2" t="n">
+        <v>319</v>
+      </c>
+      <c r="B785" s="2" t="inlineStr">
+        <is>
+          <t>新款韩国whoo后拱辰享美奢华黄金气垫套盒粉底修容遮瑕提亮肤色</t>
+        </is>
+      </c>
+      <c r="C785" s="2" t="inlineStr">
+        <is>
+          <t>后拱辰享美黄金气垫13G+替换装13G</t>
+        </is>
+      </c>
+      <c r="D785" s="2" t="inlineStr"/>
+      <c r="E785" s="2" t="n">
+        <v>47.99</v>
+      </c>
+      <c r="F785" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G785" s="2" t="inlineStr"/>
+      <c r="H785" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I785" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="B786" s="2" t="inlineStr"/>
+      <c r="C786" s="2" t="inlineStr">
+        <is>
+          <t>TOMFORD幻魅四色眼影盘 #35 玫瑰晶石</t>
+        </is>
+      </c>
+      <c r="D786" s="2" t="inlineStr"/>
+      <c r="E786" s="2" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="F786" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G786" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="H786" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I786" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="B787" s="2" t="inlineStr">
+        <is>
+          <t>正品TomFord汤姆福特TF幻魅四色眼影盘#35ROSE TOPAZ杏茶盘9g哑光【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C787" s="2" t="inlineStr">
+        <is>
+          <t>TOMFORD幻魅四色眼影盘 #35 玫瑰晶石</t>
+        </is>
+      </c>
+      <c r="D787" s="2" t="inlineStr"/>
+      <c r="E787" s="2" t="n">
+        <v>355</v>
+      </c>
+      <c r="F787" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G787" s="2" t="inlineStr"/>
+      <c r="H787" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I787" s="2" t="inlineStr"/>
+    </row>
+    <row r="788">
+      <c r="A788" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="B788" s="2" t="inlineStr">
+        <is>
+          <t>正品TomFord汤姆福特TF幻魅四色眼影盘#35ROSE TOPAZ杏茶盘9g哑光【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C788" s="2" t="inlineStr">
+        <is>
+          <t>TOMFORD幻魅四色眼影盘 #35 玫瑰晶石</t>
+        </is>
+      </c>
+      <c r="D788" s="2" t="inlineStr"/>
+      <c r="E788" s="2" t="n">
+        <v>378</v>
+      </c>
+      <c r="F788" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G788" s="2" t="inlineStr"/>
+      <c r="H788" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I788" s="2" t="inlineStr"/>
+    </row>
+    <row r="789">
+      <c r="A789" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="B789" s="2" t="inlineStr"/>
+      <c r="C789" s="2" t="inlineStr">
+        <is>
+          <t>TOMFORD幻魅四色眼影盘 #35 玫瑰晶石</t>
+        </is>
+      </c>
+      <c r="D789" s="2" t="inlineStr"/>
+      <c r="E789" s="2" t="n">
+        <v>373</v>
+      </c>
+      <c r="F789" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G789" s="2" t="inlineStr"/>
+      <c r="H789" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I789" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="2" t="n">
+        <v>321</v>
+      </c>
+      <c r="B790" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II光子小灯泡50ml美白护肤精华液淡斑提亮</t>
+        </is>
+      </c>
+      <c r="C790" s="2" t="inlineStr">
+        <is>
+          <t>SK-II小灯泡新版50ml</t>
+        </is>
+      </c>
+      <c r="D790" s="2" t="n">
+        <v>1307</v>
+      </c>
+      <c r="E790" s="2" t="n">
+        <v>902</v>
+      </c>
+      <c r="F790" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G790" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="H790" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I790" s="2" t="inlineStr"/>
+    </row>
+    <row r="791">
+      <c r="A791" s="2" t="n">
+        <v>322</v>
+      </c>
+      <c r="B791" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II光子小灯泡50ml美白护肤精华液淡斑提亮</t>
+        </is>
+      </c>
+      <c r="C791" s="2" t="inlineStr">
+        <is>
+          <t>SKII光子小灯泡75ml</t>
+        </is>
+      </c>
+      <c r="D791" s="2" t="n">
+        <v>1213</v>
+      </c>
+      <c r="E791" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="F791" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G791" s="2" t="inlineStr"/>
+      <c r="H791" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I791" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="2" t="n">
+        <v>322</v>
+      </c>
+      <c r="B792" s="2" t="inlineStr">
+        <is>
+          <t>【正品】SK-II光子小灯泡75ml美白护肤精华液淡斑提亮【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C792" s="2" t="inlineStr">
+        <is>
+          <t>SKII光子小灯泡75ml</t>
+        </is>
+      </c>
+      <c r="D792" s="2" t="inlineStr"/>
+      <c r="E792" s="2" t="n">
+        <v>1258</v>
+      </c>
+      <c r="F792" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G792" s="2" t="inlineStr"/>
+      <c r="H792" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I792" s="2" t="inlineStr"/>
+    </row>
+    <row r="793">
+      <c r="A793" s="2" t="n">
+        <v>322</v>
+      </c>
+      <c r="B793" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II光子小灯泡精华75ml套装礼盒礼物淡斑提亮紧致</t>
+        </is>
+      </c>
+      <c r="C793" s="2" t="inlineStr">
+        <is>
+          <t>SKII光子小灯泡75ml</t>
+        </is>
+      </c>
+      <c r="D793" s="2" t="inlineStr"/>
+      <c r="E793" s="2" t="n">
+        <v>1559</v>
+      </c>
+      <c r="F793" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G793" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="H793" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I793" s="2" t="inlineStr"/>
+    </row>
+    <row r="794">
+      <c r="A794" s="2" t="n">
+        <v>322</v>
+      </c>
+      <c r="B794" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II光子小灯泡新款焕亮精华露75ml 美白淡斑紧致</t>
+        </is>
+      </c>
+      <c r="C794" s="2" t="inlineStr">
+        <is>
+          <t>SKII光子小灯泡75ml</t>
+        </is>
+      </c>
+      <c r="D794" s="2" t="inlineStr"/>
+      <c r="E794" s="2" t="n">
+        <v>1559</v>
+      </c>
+      <c r="F794" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G794" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="H794" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I794" s="2" t="inlineStr"/>
+    </row>
+    <row r="795">
+      <c r="A795" s="2" t="n">
+        <v>323</v>
+      </c>
+      <c r="B795" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】氨基酸洗面奶sk2洁面温和洁净调节肌肤平衡水油护肤嫩肤舒缓【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C795" s="2" t="inlineStr">
+        <is>
+          <t>SKII洁面油250ml</t>
+        </is>
+      </c>
+      <c r="D795" s="2" t="inlineStr"/>
+      <c r="E795" s="2" t="n">
+        <v>325</v>
+      </c>
+      <c r="F795" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G795" s="2" t="inlineStr"/>
+      <c r="H795" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I795" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="2" t="n">
+        <v>323</v>
+      </c>
+      <c r="B796" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】洗面奶深层清洁温和洁面补水控油舒透护肤洁面</t>
+        </is>
+      </c>
+      <c r="C796" s="2" t="inlineStr">
+        <is>
+          <t>SKII洁面油250ml</t>
+        </is>
+      </c>
+      <c r="D796" s="2" t="inlineStr"/>
+      <c r="E796" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="F796" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G796" s="2" t="inlineStr"/>
+      <c r="H796" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I796" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="2" t="n">
+        <v>323</v>
+      </c>
+      <c r="B797" s="2" t="inlineStr">
+        <is>
+          <t>正品SK-II护肤洁面油skll卸妆油250ml深层净透温和清洁【6月18日发完】</t>
+        </is>
+      </c>
+      <c r="C797" s="2" t="inlineStr">
+        <is>
+          <t>SKII洁面油250ml</t>
+        </is>
+      </c>
+      <c r="D797" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="E797" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F797" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G797" s="2" t="inlineStr"/>
+      <c r="H797" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I797" s="2" t="inlineStr"/>
+    </row>
+    <row r="798">
+      <c r="A798" s="2" t="n">
+        <v>323</v>
+      </c>
+      <c r="B798" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】护肤洁面油卸妆油250ml 卸妆洁面二合一深层清洁温和洁净【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C798" s="2" t="inlineStr">
+        <is>
+          <t>SKII洁面油250ml</t>
+        </is>
+      </c>
+      <c r="D798" s="2" t="inlineStr"/>
+      <c r="E798" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="F798" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G798" s="2" t="inlineStr"/>
+      <c r="H798" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I798" s="2" t="inlineStr"/>
+    </row>
+    <row r="799">
+      <c r="A799" s="2" t="n">
+        <v>323</v>
+      </c>
+      <c r="B799" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】护肤洁面油250ml卸妆油温和洁净深层清洁控油【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C799" s="2" t="inlineStr">
+        <is>
+          <t>SKII洁面油250ml</t>
+        </is>
+      </c>
+      <c r="D799" s="2" t="inlineStr"/>
+      <c r="E799" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="F799" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G799" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="H799" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I799" s="2" t="inlineStr"/>
+    </row>
+    <row r="800">
+      <c r="A800" s="2" t="n">
+        <v>324</v>
+      </c>
+      <c r="B800" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】纪梵希口红粉丝绒口红N37小羊皮N319双支口红大牌女</t>
+        </is>
+      </c>
+      <c r="C800" s="2" t="inlineStr">
+        <is>
+          <t>纪梵希粉丝绒N37</t>
+        </is>
+      </c>
+      <c r="D800" s="2" t="inlineStr"/>
+      <c r="E800" s="2" t="n">
+        <v>808</v>
+      </c>
+      <c r="F800" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G800" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="H800" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I800" s="2" t="inlineStr"/>
+    </row>
+    <row r="801">
+      <c r="A801" s="2" t="n">
+        <v>324</v>
+      </c>
+      <c r="B801" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】纪梵希高定粉丝绒唇膏口红N37滋润显白持久大牌正品</t>
+        </is>
+      </c>
+      <c r="C801" s="2" t="inlineStr">
+        <is>
+          <t>纪梵希粉丝绒N37</t>
+        </is>
+      </c>
+      <c r="D801" s="2" t="n">
+        <v>10002</v>
+      </c>
+      <c r="E801" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F801" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G801" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="H801" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I801" s="2" t="inlineStr"/>
+    </row>
+    <row r="802">
+      <c r="A802" s="2" t="n">
+        <v>325</v>
+      </c>
+      <c r="B802" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰全新爱心唇釉440 610 416 622限定浮雕黑管</t>
+        </is>
+      </c>
+      <c r="C802" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰爱心黑管唇釉440</t>
+        </is>
+      </c>
+      <c r="D802" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="E802" s="2" t="n">
+        <v>134.7</v>
+      </c>
+      <c r="F802" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G802" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="H802" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I802" s="2" t="inlineStr"/>
+    </row>
+    <row r="803">
+      <c r="A803" s="2" t="n">
+        <v>326</v>
+      </c>
+      <c r="B803" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销542.3万+件】两支 单品 雅诗兰黛新款红石榴洗面奶125ml</t>
+        </is>
+      </c>
+      <c r="C803" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴洁面125ml两支装</t>
+        </is>
+      </c>
+      <c r="D803" s="2" t="inlineStr"/>
+      <c r="E803" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="F803" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G803" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="H803" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I803" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="2" t="n">
+        <v>326</v>
+      </c>
+      <c r="B804" s="2" t="inlineStr"/>
+      <c r="C804" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴洁面125ml两支装</t>
+        </is>
+      </c>
+      <c r="D804" s="2" t="inlineStr"/>
+      <c r="E804" s="2" t="n">
+        <v>358</v>
+      </c>
+      <c r="F804" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G804" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="H804" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I804" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="2" t="n">
+        <v>326</v>
+      </c>
+      <c r="B805" s="2" t="inlineStr">
+        <is>
+          <t>【】双支雅诗兰黛红石榴洁面新款125ml 清洁保湿洁面乳</t>
+        </is>
+      </c>
+      <c r="C805" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴洁面125ml两支装</t>
+        </is>
+      </c>
+      <c r="D805" s="2" t="inlineStr"/>
+      <c r="E805" s="2" t="n">
+        <v>359</v>
+      </c>
+      <c r="F805" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G805" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="H805" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I805" s="2" t="inlineStr"/>
+    </row>
+    <row r="806">
+      <c r="A806" s="2" t="n">
+        <v>326</v>
+      </c>
+      <c r="B806" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】红石榴洁面新款125ml 清洁保湿洁面乳</t>
+        </is>
+      </c>
+      <c r="C806" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴洁面125ml两支装</t>
+        </is>
+      </c>
+      <c r="D806" s="2" t="inlineStr"/>
+      <c r="E806" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="F806" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G806" s="2" t="inlineStr"/>
+      <c r="H806" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I806" s="2" t="inlineStr"/>
+    </row>
+    <row r="807">
+      <c r="A807" s="2" t="n">
+        <v>327</v>
+      </c>
+      <c r="B807" s="2" t="inlineStr">
+        <is>
+          <t>【ESTEE LAUDER雅诗兰黛】红石榴爽肤水200ml滋润型</t>
+        </is>
+      </c>
+      <c r="C807" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴水200ml两支装</t>
+        </is>
+      </c>
+      <c r="D807" s="2" t="inlineStr"/>
+      <c r="E807" s="2" t="n">
+        <v>137.75</v>
+      </c>
+      <c r="F807" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G807" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="H807" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I807" s="2" t="inlineStr"/>
+    </row>
+    <row r="808">
+      <c r="A808" s="2" t="n">
+        <v>328</v>
+      </c>
+      <c r="B808" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II神仙水补水保湿sk2护肤精华露30ml爽肤水保湿</t>
+        </is>
+      </c>
+      <c r="C808" s="2" t="inlineStr">
+        <is>
+          <t>SK2小银瓶50ml两瓶装</t>
+        </is>
+      </c>
+      <c r="D808" s="2" t="inlineStr"/>
+      <c r="E808" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="F808" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G808" s="2" t="inlineStr"/>
+      <c r="H808" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I808" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="2" t="n">
+        <v>328</v>
+      </c>
+      <c r="B809" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II小银瓶精华50ml淡斑保湿护肤品送女朋友礼物sk2</t>
+        </is>
+      </c>
+      <c r="C809" s="2" t="inlineStr">
+        <is>
+          <t>SK2小银瓶50ml两瓶装</t>
+        </is>
+      </c>
+      <c r="D809" s="2" t="inlineStr"/>
+      <c r="E809" s="2" t="n">
+        <v>2990</v>
+      </c>
+      <c r="F809" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G809" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="H809" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I809" s="2" t="inlineStr"/>
+    </row>
+    <row r="810">
+      <c r="A810" s="2" t="n">
+        <v>328</v>
+      </c>
+      <c r="B810" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II淡斑小银瓶精华50ml美白提亮祛斑sk2护肤品送礼</t>
+        </is>
+      </c>
+      <c r="C810" s="2" t="inlineStr">
+        <is>
+          <t>SK2小银瓶50ml两瓶装</t>
+        </is>
+      </c>
+      <c r="D810" s="2" t="inlineStr"/>
+      <c r="E810" s="2" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F810" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G810" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="H810" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I810" s="2" t="inlineStr"/>
+    </row>
+    <row r="811">
+      <c r="A811" s="2" t="n">
+        <v>328</v>
+      </c>
+      <c r="B811" s="2" t="inlineStr">
+        <is>
+          <t>【送礼佳品】SK-II/sk2小银瓶精华液淡化斑印提亮肤色50ml礼盒款【6月18日发完】</t>
+        </is>
+      </c>
+      <c r="C811" s="2" t="inlineStr">
+        <is>
+          <t>SK2小银瓶50ml两瓶装</t>
+        </is>
+      </c>
+      <c r="D811" s="2" t="inlineStr"/>
+      <c r="E811" s="2" t="n">
+        <v>1380</v>
+      </c>
+      <c r="F811" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G811" s="2" t="inlineStr"/>
+      <c r="H811" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I811" s="2" t="inlineStr"/>
+    </row>
+    <row r="812">
+      <c r="A812" s="2" t="n">
+        <v>329</v>
+      </c>
+      <c r="B812" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】sk2大红瓶面霜50g面部护肤套装礼盒</t>
+        </is>
+      </c>
+      <c r="C812" s="2" t="inlineStr">
+        <is>
+          <t>SK2大红瓶滋润面霜50g</t>
+        </is>
+      </c>
+      <c r="D812" s="2" t="inlineStr"/>
+      <c r="E812" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F812" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G812" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H812" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I812" s="2" t="inlineStr"/>
+    </row>
+    <row r="813">
+      <c r="A813" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="B813" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗西柚/睡莲/小苍兰香皂250g 深层清洁香皂</t>
+        </is>
+      </c>
+      <c r="C813" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗西柚香皂</t>
+        </is>
+      </c>
+      <c r="D813" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="E813" s="2" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F813" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G813" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="H813" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I813" s="2" t="inlineStr"/>
+    </row>
+    <row r="814">
+      <c r="A814" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="B814" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗小苍兰香皂250g 深层清洁香皂</t>
+        </is>
+      </c>
+      <c r="C814" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗西柚香皂</t>
+        </is>
+      </c>
+      <c r="D814" s="2" t="inlineStr"/>
+      <c r="E814" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="F814" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G814" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H814" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I814" s="2" t="inlineStr"/>
+    </row>
+    <row r="815">
+      <c r="A815" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="B815" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗西柚香皂250g 深层清洁香皂</t>
+        </is>
+      </c>
+      <c r="C815" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗西柚香皂</t>
+        </is>
+      </c>
+      <c r="D815" s="2" t="inlineStr"/>
+      <c r="E815" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="F815" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G815" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="H815" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I815" s="2" t="inlineStr"/>
+    </row>
+    <row r="816">
+      <c r="A816" s="2" t="n">
+        <v>331</v>
+      </c>
+      <c r="B816" s="2" t="inlineStr"/>
+      <c r="C816" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
+        </is>
+      </c>
+      <c r="D816" s="2" t="n">
+        <v>435</v>
+      </c>
+      <c r="E816" s="2" t="n">
+        <v>270</v>
+      </c>
+      <c r="F816" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G816" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="H816" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I816" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="2" t="n">
+        <v>331</v>
+      </c>
+      <c r="B817" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗 大马士革玫瑰花瓣润泽密集保湿爽肤水400ml高保湿深层滋润【5月31日发完】</t>
+        </is>
+      </c>
+      <c r="C817" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
+        </is>
+      </c>
+      <c r="D817" s="2" t="inlineStr"/>
+      <c r="E817" s="2" t="n">
+        <v>239.5</v>
+      </c>
+      <c r="F817" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G817" s="2" t="inlineStr"/>
+      <c r="H817" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I817" s="2" t="inlineStr"/>
+    </row>
+    <row r="818">
+      <c r="A818" s="2" t="n">
+        <v>331</v>
+      </c>
+      <c r="B818" s="2" t="inlineStr">
+        <is>
+          <t>【馥蕾诗】 大马士革玫瑰花瓣润泽密集保湿爽肤水400ml高保湿深层滋润【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C818" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
+        </is>
+      </c>
+      <c r="D818" s="2" t="inlineStr"/>
+      <c r="E818" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F818" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G818" s="2" t="inlineStr"/>
+      <c r="H818" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I818" s="2" t="inlineStr"/>
+    </row>
+    <row r="819">
+      <c r="A819" s="2" t="n">
+        <v>331</v>
+      </c>
+      <c r="B819" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗玫瑰花瓣水250ml大马士革玫瑰润泽保湿爽肤水调理肌肤【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C819" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
+        </is>
+      </c>
+      <c r="D819" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="E819" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="F819" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G819" s="2" t="inlineStr"/>
+      <c r="H819" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I819" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="2" t="n">
+        <v>332</v>
+      </c>
+      <c r="B820" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】馥蕾诗红茶凝时焕活面霜50ml淡纹紧致增加光泽</t>
+        </is>
+      </c>
+      <c r="C820" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗红茶紧致面霜50ml</t>
+        </is>
+      </c>
+      <c r="D820" s="2" t="inlineStr"/>
+      <c r="E820" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="F820" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G820" s="2" t="inlineStr"/>
+      <c r="H820" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I820" s="2" t="inlineStr"/>
+    </row>
+    <row r="821">
+      <c r="A821" s="2" t="n">
+        <v>333</v>
+      </c>
+      <c r="B821" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】馥蕾诗睡莲青春赋活面霜50ml修护淡纹柔润光采</t>
+        </is>
+      </c>
+      <c r="C821" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗睡莲日霜50ml</t>
+        </is>
+      </c>
+      <c r="D821" s="2" t="inlineStr"/>
+      <c r="E821" s="2" t="n">
+        <v>482</v>
+      </c>
+      <c r="F821" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G821" s="2" t="inlineStr"/>
+      <c r="H821" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I821" s="2" t="inlineStr"/>
+    </row>
+    <row r="822">
+      <c r="A822" s="2" t="n">
+        <v>334</v>
+      </c>
+      <c r="B822" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗玫瑰保湿面霜50ml  密集保湿舒缓补水</t>
+        </is>
+      </c>
+      <c r="C822" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗玫瑰保湿面霜50ml两瓶装</t>
+        </is>
+      </c>
+      <c r="D822" s="2" t="inlineStr"/>
+      <c r="E822" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="F822" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G822" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="H822" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I822" s="2" t="inlineStr"/>
+    </row>
+    <row r="823">
+      <c r="A823" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="B823" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗小苍兰香皂250g 深层清洁香皂</t>
+        </is>
+      </c>
+      <c r="C823" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗小苍兰香皂</t>
+        </is>
+      </c>
+      <c r="D823" s="2" t="inlineStr"/>
+      <c r="E823" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="F823" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G823" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H823" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I823" s="2" t="inlineStr"/>
+    </row>
+    <row r="824">
+      <c r="A824" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="B824" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗西柚/睡莲/小苍兰香皂250g 深层清洁香皂</t>
+        </is>
+      </c>
+      <c r="C824" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗小苍兰香皂</t>
+        </is>
+      </c>
+      <c r="D824" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="E824" s="2" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F824" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G824" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="H824" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I824" s="2" t="inlineStr"/>
+    </row>
+    <row r="825">
+      <c r="A825" s="2" t="n">
+        <v>336</v>
+      </c>
+      <c r="B825" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛白金级养肤粉底液宝石粉底光感保湿透亮遮瑕</t>
+        </is>
+      </c>
+      <c r="C825" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛白金粉底液1W0</t>
+        </is>
+      </c>
+      <c r="D825" s="2" t="inlineStr"/>
+      <c r="E825" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="F825" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G825" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="H825" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I825" s="2" t="inlineStr"/>
+    </row>
+    <row r="826">
+      <c r="A826" s="2" t="n">
+        <v>336</v>
+      </c>
+      <c r="B826" s="2" t="inlineStr">
+        <is>
+          <t>【专柜行货】雅诗兰黛白金养肤粉底液 持久遮瑕保湿抗氧化服帖</t>
+        </is>
+      </c>
+      <c r="C826" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛白金粉底液1W0</t>
+        </is>
+      </c>
+      <c r="D826" s="2" t="n">
+        <v>980</v>
+      </c>
+      <c r="E826" s="2" t="n">
+        <v>607.6</v>
+      </c>
+      <c r="F826" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G826" s="2" t="inlineStr"/>
+      <c r="H826" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I826" s="2" t="inlineStr"/>
+    </row>
+    <row r="827">
+      <c r="A827" s="2" t="n">
+        <v>337</v>
+      </c>
+      <c r="B827" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗酵母酵萃红茶水250ml保湿补水清爽滋润爽肤水精华水</t>
+        </is>
+      </c>
+      <c r="C827" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗红茶精粹水250ml</t>
+        </is>
+      </c>
+      <c r="D827" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="E827" s="2" t="n">
+        <v>447</v>
+      </c>
+      <c r="F827" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G827" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="H827" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I827" s="2" t="inlineStr"/>
+    </row>
+    <row r="828">
+      <c r="A828" s="2" t="n">
+        <v>338</v>
+      </c>
+      <c r="B828" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】白金粉底液1C0养肤透亮持久保湿遮瑕服帖【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C828" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛白金粉底液1CO</t>
+        </is>
+      </c>
+      <c r="D828" s="2" t="n">
+        <v>599</v>
+      </c>
+      <c r="E828" s="2" t="n">
+        <v>425</v>
+      </c>
+      <c r="F828" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G828" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="H828" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I828" s="2" t="inlineStr"/>
+    </row>
+    <row r="829">
+      <c r="A829" s="2" t="n">
+        <v>339</v>
+      </c>
+      <c r="B829" s="2" t="inlineStr">
+        <is>
+          <t>【娇韵诗】美白三件套(水200ml+乳液100ml+精华50ml)</t>
+        </is>
+      </c>
+      <c r="C829" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗美白滋润水200ml</t>
+        </is>
+      </c>
+      <c r="D829" s="2" t="n">
+        <v>1270</v>
+      </c>
+      <c r="E829" s="2" t="n">
+        <v>728</v>
+      </c>
+      <c r="F829" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G829" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H829" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I829" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="2" t="n">
+        <v>339</v>
+      </c>
+      <c r="B830" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】Clarins/娇韵诗牛奶美白水乳组礼盒装淡斑祛黄提亮</t>
+        </is>
+      </c>
+      <c r="C830" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗美白滋润水200ml</t>
+        </is>
+      </c>
+      <c r="D830" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="E830" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="F830" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G830" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="H830" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I830" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="2" t="n">
+        <v>339</v>
+      </c>
+      <c r="B831" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】娇韵诗牛奶水减黄提亮美白淡斑清爽200ml保湿细腻</t>
+        </is>
+      </c>
+      <c r="C831" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗美白滋润水200ml</t>
+        </is>
+      </c>
+      <c r="D831" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="E831" s="2" t="n">
+        <v>336</v>
+      </c>
+      <c r="F831" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G831" s="2" t="inlineStr"/>
+      <c r="H831" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I831" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="2" t="n">
+        <v>339</v>
+      </c>
+      <c r="B832" s="2" t="inlineStr">
+        <is>
+          <t>【娇韵诗】美白水乳套组牛奶水200ml+乳液75ml+</t>
+        </is>
+      </c>
+      <c r="C832" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗美白滋润水200ml</t>
+        </is>
+      </c>
+      <c r="D832" s="2" t="inlineStr"/>
+      <c r="E832" s="2" t="n">
+        <v>346</v>
+      </c>
+      <c r="F832" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G832" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="H832" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I832" s="2" t="inlineStr"/>
+    </row>
+    <row r="833">
+      <c r="A833" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="B833" s="2" t="inlineStr">
+        <is>
+          <t>Clarins/娇韵诗焕颜弹力元气晚霜滋润型50ml紧致回弹保湿淡纹面霜【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C833" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="D833" s="2" t="inlineStr"/>
+      <c r="E833" s="2" t="n">
+        <v>294</v>
+      </c>
+      <c r="F833" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G833" s="2" t="inlineStr">
+        <is>
+          <t>2023-11-01</t>
+        </is>
+      </c>
+      <c r="H833" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I833" s="2" t="inlineStr"/>
+    </row>
+    <row r="834">
+      <c r="A834" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="B834" s="2" t="inlineStr">
+        <is>
+          <t>CLARINS/娇韵诗焕颜紧致弹簧霜晚霜 50ml修护提亮 娇韵诗弹簧晚霜【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C834" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="D834" s="2" t="inlineStr"/>
+      <c r="E834" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F834" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G834" s="2" t="inlineStr"/>
+      <c r="H834" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I834" s="2" t="inlineStr"/>
+    </row>
+    <row r="835">
+      <c r="A835" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="B835" s="2" t="inlineStr">
+        <is>
+          <t>Clarins/娇韵诗焕颜弹力元气晚霜滋润型50ml紧致回弹保湿淡纹面霜【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C835" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="D835" s="2" t="inlineStr"/>
+      <c r="E835" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="F835" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G835" s="2" t="inlineStr"/>
+      <c r="H835" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I835" s="2" t="inlineStr"/>
+    </row>
+    <row r="836">
+      <c r="A836" s="2" t="n">
+        <v>341</v>
+      </c>
+      <c r="B836" s="2" t="inlineStr">
+        <is>
+          <t>Clarins/娇韵诗焕颜弹力元气晚霜滋润型50ml紧致回弹保湿淡纹面霜【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C836" s="2" t="inlineStr">
+        <is>
+          <t>Clarins娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="D836" s="2" t="inlineStr"/>
+      <c r="E836" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="F836" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G836" s="2" t="inlineStr"/>
+      <c r="H836" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I836" s="2" t="inlineStr"/>
+    </row>
+    <row r="837">
+      <c r="A837" s="2" t="n">
+        <v>341</v>
+      </c>
+      <c r="B837" s="2" t="inlineStr">
+        <is>
+          <t>【Clarins】娇韵诗焕颜弹力晚霜面霜50ml保湿提拉紧致滋润【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C837" s="2" t="inlineStr">
+        <is>
+          <t>Clarins娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="D837" s="2" t="inlineStr"/>
+      <c r="E837" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="F837" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G837" s="2" t="inlineStr"/>
+      <c r="H837" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I837" s="2" t="inlineStr"/>
+    </row>
+    <row r="838">
+      <c r="A838" s="2" t="n">
+        <v>341</v>
+      </c>
+      <c r="B838" s="2" t="inlineStr">
+        <is>
+          <t>【Clarins】娇韵诗焕颜弹力元气晚霜滋润型50ml紧致回弹保湿淡纹面霜【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C838" s="2" t="inlineStr">
+        <is>
+          <t>Clarins娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="D838" s="2" t="inlineStr"/>
+      <c r="E838" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="F838" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G838" s="2" t="inlineStr"/>
+      <c r="H838" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I838" s="2" t="inlineStr"/>
+    </row>
+    <row r="839">
+      <c r="A839" s="2" t="n">
+        <v>342</v>
+      </c>
+      <c r="B839" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】多效智妍面霜75ml 新款清爽款保湿</t>
+        </is>
+      </c>
+      <c r="C839" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛多效智妍乳霜75ml清爽</t>
+        </is>
+      </c>
+      <c r="D839" s="2" t="inlineStr"/>
+      <c r="E839" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="F839" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G839" s="2" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="H839" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I839" s="2" t="inlineStr"/>
+    </row>
+    <row r="840">
+      <c r="A840" s="2" t="n">
+        <v>343</v>
+      </c>
+      <c r="B840" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】梅森马吉拉慵懒周末身体乳50ml*2</t>
+        </is>
+      </c>
+      <c r="C840" s="2" t="inlineStr">
+        <is>
+          <t>马丁马吉拉慵懒周末身体乳200ml</t>
+        </is>
+      </c>
+      <c r="D840" s="2" t="inlineStr"/>
+      <c r="E840" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="F840" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G840" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H840" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I840" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="2" t="n">
+        <v>343</v>
+      </c>
+      <c r="B841" s="2" t="inlineStr">
+        <is>
+          <t>【Maison Margiela】梅森马吉拉 慵懒周末身体乳 滋润芳香200ml/400ml</t>
+        </is>
+      </c>
+      <c r="C841" s="2" t="inlineStr">
+        <is>
+          <t>马丁马吉拉慵懒周末身体乳200ml</t>
+        </is>
+      </c>
+      <c r="D841" s="2" t="inlineStr"/>
+      <c r="E841" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="F841" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G841" s="2" t="inlineStr"/>
+      <c r="H841" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I841" s="2" t="inlineStr"/>
+    </row>
+    <row r="842">
+      <c r="A842" s="2" t="n">
+        <v>343</v>
+      </c>
+      <c r="B842" s="2" t="inlineStr">
+        <is>
+          <t>【原装正品】Maison Margiela/梅森马吉拉慵懒周末身体乳200ml</t>
+        </is>
+      </c>
+      <c r="C842" s="2" t="inlineStr">
+        <is>
+          <t>马丁马吉拉慵懒周末身体乳200ml</t>
+        </is>
+      </c>
+      <c r="D842" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="E842" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="F842" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G842" s="2" t="inlineStr"/>
+      <c r="H842" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I842" s="2" t="inlineStr"/>
+    </row>
+    <row r="843">
+      <c r="A843" s="2" t="n">
+        <v>343</v>
+      </c>
+      <c r="B843" s="2" t="inlineStr">
+        <is>
+          <t>【正品原装】Maison Margiela/梅森马吉拉慵懒周末身体乳200ml</t>
+        </is>
+      </c>
+      <c r="C843" s="2" t="inlineStr">
+        <is>
+          <t>马丁马吉拉慵懒周末身体乳200ml</t>
+        </is>
+      </c>
+      <c r="D843" s="2" t="inlineStr"/>
+      <c r="E843" s="2" t="n">
+        <v>248</v>
+      </c>
+      <c r="F843" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G843" s="2" t="inlineStr"/>
+      <c r="H843" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I843" s="2" t="inlineStr"/>
+    </row>
+    <row r="844">
+      <c r="A844" s="2" t="n">
+        <v>344</v>
+      </c>
+      <c r="B844" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻水粉底 PO01正装30ml养肤柔光新款水润水啵啵【6月18日发完】</t>
+        </is>
+      </c>
+      <c r="C844" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻养肤水粉底液 PO-01 30ml</t>
+        </is>
+      </c>
+      <c r="D844" s="2" t="inlineStr"/>
+      <c r="E844" s="2" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="F844" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G844" s="2" t="inlineStr"/>
+      <c r="H844" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I844" s="2" t="inlineStr"/>
+    </row>
+    <row r="845">
+      <c r="A845" s="2" t="n">
+        <v>344</v>
+      </c>
+      <c r="B845" s="2" t="inlineStr">
+        <is>
+          <t>【兰蔻】水粉底养肤柔光粉底液PO-01#30ml水啵啵干皮持妆遮瑕</t>
+        </is>
+      </c>
+      <c r="C845" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻养肤水粉底液 PO-01 30ml</t>
+        </is>
+      </c>
+      <c r="D845" s="2" t="inlineStr"/>
+      <c r="E845" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="F845" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G845" s="2" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="H845" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I845" s="2" t="inlineStr"/>
+    </row>
+    <row r="846">
+      <c r="A846" s="2" t="n">
+        <v>344</v>
+      </c>
+      <c r="B846" s="2" t="inlineStr">
+        <is>
+          <t>【兰蔻】水粉底养肤柔光粉底液PO-03#30ml正装P01水啵啵PO-01持妆遮瑕</t>
+        </is>
+      </c>
+      <c r="C846" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻养肤水粉底液 PO-01 30ml</t>
+        </is>
+      </c>
+      <c r="D846" s="2" t="inlineStr"/>
+      <c r="E846" s="2" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="F846" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G846" s="2" t="inlineStr"/>
+      <c r="H846" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I846" s="2" t="inlineStr"/>
+    </row>
+    <row r="847">
+      <c r="A847" s="2" t="n">
+        <v>345</v>
+      </c>
+      <c r="B847" s="2" t="inlineStr">
+        <is>
+          <t>【Kiehl's】科颜氏男士保湿乳液125ml活力清爽控油补水收缩毛孔送男友</t>
+        </is>
+      </c>
+      <c r="C847" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏男士乳液125ml</t>
+        </is>
+      </c>
+      <c r="D847" s="2" t="inlineStr"/>
+      <c r="E847" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="F847" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G847" s="2" t="inlineStr"/>
+      <c r="H847" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I847" s="2" t="inlineStr"/>
+    </row>
+    <row r="848">
+      <c r="A848" s="2" t="n">
+        <v>345</v>
+      </c>
+      <c r="B848" s="2" t="inlineStr">
+        <is>
+          <t>【科颜氏】男士保湿乳液125ml补水保湿清爽改善暗沉礼物</t>
+        </is>
+      </c>
+      <c r="C848" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏男士乳液125ml</t>
+        </is>
+      </c>
+      <c r="D848" s="2" t="inlineStr"/>
+      <c r="E848" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="F848" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G848" s="2" t="inlineStr"/>
+      <c r="H848" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I848" s="2" t="inlineStr"/>
+    </row>
+    <row r="849">
+      <c r="A849" s="2" t="n">
+        <v>317</v>
+      </c>
+      <c r="B849" s="2" t="inlineStr">
+        <is>
+          <t>【特价清仓】NARS纳斯哑光唇釉空气柔雾唇霜#684 Gipsy吉普赛玫瑰</t>
+        </is>
+      </c>
+      <c r="C849" s="2" t="inlineStr">
+        <is>
+          <t>NARS空气唇釉GIPSY吉普赛</t>
+        </is>
+      </c>
+      <c r="D849" s="2" t="inlineStr">
+        <is>
+          <t>199.0</t>
+        </is>
+      </c>
+      <c r="E849" s="2" t="inlineStr">
+        <is>
+          <t>113.05</t>
+        </is>
+      </c>
+      <c r="F849" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G849" s="2" t="inlineStr"/>
+      <c r="H849" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I849" s="2" t="inlineStr"/>
+    </row>
+    <row r="850">
+      <c r="A850" s="2" t="n">
+        <v>318</v>
+      </c>
+      <c r="B850" s="2" t="inlineStr">
+        <is>
+          <t>宏香记品牌官方正品，100%保障</t>
+        </is>
+      </c>
+      <c r="C850" s="2" t="inlineStr">
+        <is>
+          <t>后Whoo天气丹PRO乳110ML</t>
+        </is>
+      </c>
+      <c r="D850" s="2" t="inlineStr"/>
+      <c r="E850" s="2" t="inlineStr">
+        <is>
+          <t>19.12</t>
+        </is>
+      </c>
+      <c r="F850" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G850" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="H850" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I850" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="2" t="n">
+        <v>318</v>
+      </c>
+      <c r="B851" s="2" t="inlineStr">
+        <is>
+          <t>韩国直邮THEWHOO后天气丹PRO光耀焕活紧颜滋养水乳正装提拉抗皱白【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C851" s="2" t="inlineStr">
+        <is>
+          <t>后Whoo天气丹PRO乳110ML</t>
+        </is>
+      </c>
+      <c r="D851" s="2" t="inlineStr"/>
+      <c r="E851" s="2" t="inlineStr">
+        <is>
+          <t>448.0</t>
+        </is>
+      </c>
+      <c r="F851" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G851" s="2" t="inlineStr"/>
+      <c r="H851" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I851" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="2" t="n">
+        <v>318</v>
+      </c>
+      <c r="B852" s="2" t="inlineStr">
+        <is>
+          <t>韩国whoo后天气丹PRO淡纹乳110ml 清透保湿亮肤紧致抗皱滋养乳【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C852" s="2" t="inlineStr">
+        <is>
+          <t>后Whoo天气丹PRO乳110ML</t>
+        </is>
+      </c>
+      <c r="D852" s="2" t="inlineStr"/>
+      <c r="E852" s="2" t="inlineStr">
+        <is>
+          <t>223.0</t>
+        </is>
+      </c>
+      <c r="F852" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G852" s="2" t="inlineStr"/>
+      <c r="H852" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I852" s="2" t="inlineStr"/>
+    </row>
+    <row r="853">
+      <c r="A853" s="2" t="n">
+        <v>318</v>
+      </c>
+      <c r="B853" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】后天气丹PRO光耀焕活紧颜滋养乳50ml/瓶保湿紧致滋润</t>
+        </is>
+      </c>
+      <c r="C853" s="2" t="inlineStr">
+        <is>
+          <t>后Whoo天气丹PRO乳110ML</t>
+        </is>
+      </c>
+      <c r="D853" s="2" t="inlineStr"/>
+      <c r="E853" s="2" t="inlineStr">
+        <is>
+          <t>41.9</t>
+        </is>
+      </c>
+      <c r="F853" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G853" s="2" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="H853" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I853" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="2" t="n">
+        <v>319</v>
+      </c>
+      <c r="B854" s="2" t="inlineStr"/>
+      <c r="C854" s="2" t="inlineStr">
+        <is>
+          <t>后拱辰享美黄金气垫13G+替换装13G</t>
+        </is>
+      </c>
+      <c r="D854" s="2" t="inlineStr"/>
+      <c r="E854" s="2" t="inlineStr">
+        <is>
+          <t>47.99</t>
+        </is>
+      </c>
+      <c r="F854" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G854" s="2" t="inlineStr"/>
+      <c r="H854" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I854" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="2" t="n">
+        <v>319</v>
+      </c>
+      <c r="B855" s="2" t="inlineStr">
+        <is>
+          <t>新款韩国whoo后拱辰享美奢华黄金气垫套盒粉底修容遮瑕提亮肤色</t>
+        </is>
+      </c>
+      <c r="C855" s="2" t="inlineStr">
+        <is>
+          <t>后拱辰享美黄金气垫13G+替换装13G</t>
+        </is>
+      </c>
+      <c r="D855" s="2" t="inlineStr"/>
+      <c r="E855" s="2" t="inlineStr">
+        <is>
+          <t>47.99</t>
+        </is>
+      </c>
+      <c r="F855" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G855" s="2" t="inlineStr"/>
+      <c r="H855" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I855" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="B856" s="2" t="inlineStr"/>
+      <c r="C856" s="2" t="inlineStr">
+        <is>
+          <t>TOMFORD幻魅四色眼影盘 #35 玫瑰晶石</t>
+        </is>
+      </c>
+      <c r="D856" s="2" t="inlineStr"/>
+      <c r="E856" s="2" t="inlineStr">
+        <is>
+          <t>19.12</t>
+        </is>
+      </c>
+      <c r="F856" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G856" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="H856" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I856" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="B857" s="2" t="inlineStr">
+        <is>
+          <t>正品TomFord汤姆福特TF幻魅四色眼影盘#35ROSE TOPAZ杏茶盘9g哑光【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C857" s="2" t="inlineStr">
+        <is>
+          <t>TOMFORD幻魅四色眼影盘 #35 玫瑰晶石</t>
+        </is>
+      </c>
+      <c r="D857" s="2" t="inlineStr"/>
+      <c r="E857" s="2" t="inlineStr">
+        <is>
+          <t>355.0</t>
+        </is>
+      </c>
+      <c r="F857" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G857" s="2" t="inlineStr"/>
+      <c r="H857" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I857" s="2" t="inlineStr"/>
+    </row>
+    <row r="858">
+      <c r="A858" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="B858" s="2" t="inlineStr">
+        <is>
+          <t>正品TomFord汤姆福特TF幻魅四色眼影盘#35ROSE TOPAZ杏茶盘9g哑光【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C858" s="2" t="inlineStr">
+        <is>
+          <t>TOMFORD幻魅四色眼影盘 #35 玫瑰晶石</t>
+        </is>
+      </c>
+      <c r="D858" s="2" t="inlineStr"/>
+      <c r="E858" s="2" t="inlineStr">
+        <is>
+          <t>378.0</t>
+        </is>
+      </c>
+      <c r="F858" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G858" s="2" t="inlineStr"/>
+      <c r="H858" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I858" s="2" t="inlineStr"/>
+    </row>
+    <row r="859">
+      <c r="A859" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="B859" s="2" t="inlineStr"/>
+      <c r="C859" s="2" t="inlineStr">
+        <is>
+          <t>TOMFORD幻魅四色眼影盘 #35 玫瑰晶石</t>
+        </is>
+      </c>
+      <c r="D859" s="2" t="inlineStr"/>
+      <c r="E859" s="2" t="inlineStr">
+        <is>
+          <t>373.0</t>
+        </is>
+      </c>
+      <c r="F859" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G859" s="2" t="inlineStr"/>
+      <c r="H859" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I859" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="2" t="n">
+        <v>321</v>
+      </c>
+      <c r="B860" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II光子小灯泡50ml美白护肤精华液淡斑提亮</t>
+        </is>
+      </c>
+      <c r="C860" s="2" t="inlineStr">
+        <is>
+          <t>SK-II小灯泡新版50ml</t>
+        </is>
+      </c>
+      <c r="D860" s="2" t="inlineStr">
+        <is>
+          <t>1307.0</t>
+        </is>
+      </c>
+      <c r="E860" s="2" t="inlineStr">
+        <is>
+          <t>902.0</t>
+        </is>
+      </c>
+      <c r="F860" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G860" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="H860" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I860" s="2" t="inlineStr"/>
+    </row>
+    <row r="861">
+      <c r="A861" s="2" t="n">
+        <v>322</v>
+      </c>
+      <c r="B861" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II光子小灯泡50ml美白护肤精华液淡斑提亮</t>
+        </is>
+      </c>
+      <c r="C861" s="2" t="inlineStr">
+        <is>
+          <t>SKII光子小灯泡75ml</t>
+        </is>
+      </c>
+      <c r="D861" s="2" t="inlineStr">
+        <is>
+          <t>1213.0</t>
+        </is>
+      </c>
+      <c r="E861" s="2" t="inlineStr">
+        <is>
+          <t>825.0</t>
+        </is>
+      </c>
+      <c r="F861" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G861" s="2" t="inlineStr"/>
+      <c r="H861" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I861" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="2" t="n">
+        <v>322</v>
+      </c>
+      <c r="B862" s="2" t="inlineStr">
+        <is>
+          <t>【正品】SK-II光子小灯泡75ml美白护肤精华液淡斑提亮【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C862" s="2" t="inlineStr">
+        <is>
+          <t>SKII光子小灯泡75ml</t>
+        </is>
+      </c>
+      <c r="D862" s="2" t="inlineStr"/>
+      <c r="E862" s="2" t="inlineStr">
+        <is>
+          <t>1258.0</t>
+        </is>
+      </c>
+      <c r="F862" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G862" s="2" t="inlineStr"/>
+      <c r="H862" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I862" s="2" t="inlineStr"/>
+    </row>
+    <row r="863">
+      <c r="A863" s="2" t="n">
+        <v>322</v>
+      </c>
+      <c r="B863" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II光子小灯泡精华75ml套装礼盒礼物淡斑提亮紧致</t>
+        </is>
+      </c>
+      <c r="C863" s="2" t="inlineStr">
+        <is>
+          <t>SKII光子小灯泡75ml</t>
+        </is>
+      </c>
+      <c r="D863" s="2" t="inlineStr"/>
+      <c r="E863" s="2" t="inlineStr">
+        <is>
+          <t>1559.0</t>
+        </is>
+      </c>
+      <c r="F863" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G863" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="H863" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I863" s="2" t="inlineStr"/>
+    </row>
+    <row r="864">
+      <c r="A864" s="2" t="n">
+        <v>322</v>
+      </c>
+      <c r="B864" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II光子小灯泡新款焕亮精华露75ml 美白淡斑紧致</t>
+        </is>
+      </c>
+      <c r="C864" s="2" t="inlineStr">
+        <is>
+          <t>SKII光子小灯泡75ml</t>
+        </is>
+      </c>
+      <c r="D864" s="2" t="inlineStr"/>
+      <c r="E864" s="2" t="inlineStr">
+        <is>
+          <t>1559.0</t>
+        </is>
+      </c>
+      <c r="F864" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G864" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="H864" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I864" s="2" t="inlineStr"/>
+    </row>
+    <row r="865">
+      <c r="A865" s="2" t="n">
+        <v>323</v>
+      </c>
+      <c r="B865" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】氨基酸洗面奶sk2洁面温和洁净调节肌肤平衡水油护肤嫩肤舒缓【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C865" s="2" t="inlineStr">
+        <is>
+          <t>SKII洁面油250ml</t>
+        </is>
+      </c>
+      <c r="D865" s="2" t="inlineStr"/>
+      <c r="E865" s="2" t="inlineStr">
+        <is>
+          <t>325.0</t>
+        </is>
+      </c>
+      <c r="F865" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G865" s="2" t="inlineStr"/>
+      <c r="H865" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I865" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="2" t="n">
+        <v>323</v>
+      </c>
+      <c r="B866" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】洗面奶深层清洁温和洁面补水控油舒透护肤洁面</t>
+        </is>
+      </c>
+      <c r="C866" s="2" t="inlineStr">
+        <is>
+          <t>SKII洁面油250ml</t>
+        </is>
+      </c>
+      <c r="D866" s="2" t="inlineStr"/>
+      <c r="E866" s="2" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
+      </c>
+      <c r="F866" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G866" s="2" t="inlineStr"/>
+      <c r="H866" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I866" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="2" t="n">
+        <v>323</v>
+      </c>
+      <c r="B867" s="2" t="inlineStr">
+        <is>
+          <t>正品SK-II护肤洁面油skll卸妆油250ml深层净透温和清洁【6月18日发完】</t>
+        </is>
+      </c>
+      <c r="C867" s="2" t="inlineStr">
+        <is>
+          <t>SKII洁面油250ml</t>
+        </is>
+      </c>
+      <c r="D867" s="2" t="inlineStr">
+        <is>
+          <t>505.0</t>
+        </is>
+      </c>
+      <c r="E867" s="2" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="F867" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G867" s="2" t="inlineStr"/>
+      <c r="H867" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I867" s="2" t="inlineStr"/>
+    </row>
+    <row r="868">
+      <c r="A868" s="2" t="n">
+        <v>323</v>
+      </c>
+      <c r="B868" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】护肤洁面油卸妆油250ml 卸妆洁面二合一深层清洁温和洁净【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C868" s="2" t="inlineStr">
+        <is>
+          <t>SKII洁面油250ml</t>
+        </is>
+      </c>
+      <c r="D868" s="2" t="inlineStr"/>
+      <c r="E868" s="2" t="inlineStr">
+        <is>
+          <t>299.0</t>
+        </is>
+      </c>
+      <c r="F868" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G868" s="2" t="inlineStr"/>
+      <c r="H868" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I868" s="2" t="inlineStr"/>
+    </row>
+    <row r="869">
+      <c r="A869" s="2" t="n">
+        <v>323</v>
+      </c>
+      <c r="B869" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】护肤洁面油250ml卸妆油温和洁净深层清洁控油【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C869" s="2" t="inlineStr">
+        <is>
+          <t>SKII洁面油250ml</t>
+        </is>
+      </c>
+      <c r="D869" s="2" t="inlineStr"/>
+      <c r="E869" s="2" t="inlineStr">
+        <is>
+          <t>499.0</t>
+        </is>
+      </c>
+      <c r="F869" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G869" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="H869" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I869" s="2" t="inlineStr"/>
+    </row>
+    <row r="870">
+      <c r="A870" s="2" t="n">
+        <v>324</v>
+      </c>
+      <c r="B870" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】纪梵希口红粉丝绒口红N37小羊皮N319双支口红大牌女</t>
+        </is>
+      </c>
+      <c r="C870" s="2" t="inlineStr">
+        <is>
+          <t>纪梵希粉丝绒N37</t>
+        </is>
+      </c>
+      <c r="D870" s="2" t="inlineStr"/>
+      <c r="E870" s="2" t="inlineStr">
+        <is>
+          <t>808.0</t>
+        </is>
+      </c>
+      <c r="F870" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G870" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="H870" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I870" s="2" t="inlineStr"/>
+    </row>
+    <row r="871">
+      <c r="A871" s="2" t="n">
+        <v>324</v>
+      </c>
+      <c r="B871" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】纪梵希高定粉丝绒唇膏口红N37滋润显白持久大牌正品</t>
+        </is>
+      </c>
+      <c r="C871" s="2" t="inlineStr">
+        <is>
+          <t>纪梵希粉丝绒N37</t>
+        </is>
+      </c>
+      <c r="D871" s="2" t="inlineStr">
+        <is>
+          <t>10002.0</t>
+        </is>
+      </c>
+      <c r="E871" s="2" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="F871" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G871" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="H871" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I871" s="2" t="inlineStr"/>
+    </row>
+    <row r="872">
+      <c r="A872" s="2" t="n">
+        <v>325</v>
+      </c>
+      <c r="B872" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰全新爱心唇釉440 610 416 622限定浮雕黑管</t>
+        </is>
+      </c>
+      <c r="C872" s="2" t="inlineStr">
+        <is>
+          <t>圣罗兰爱心黑管唇釉440</t>
+        </is>
+      </c>
+      <c r="D872" s="2" t="inlineStr">
+        <is>
+          <t>220.0</t>
+        </is>
+      </c>
+      <c r="E872" s="2" t="inlineStr">
+        <is>
+          <t>134.7</t>
+        </is>
+      </c>
+      <c r="F872" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G872" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="H872" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I872" s="2" t="inlineStr"/>
+    </row>
+    <row r="873">
+      <c r="A873" s="2" t="n">
+        <v>326</v>
+      </c>
+      <c r="B873" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销542.3万+件】两支 单品 雅诗兰黛新款红石榴洗面奶125ml</t>
+        </is>
+      </c>
+      <c r="C873" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴洁面125ml两支装</t>
+        </is>
+      </c>
+      <c r="D873" s="2" t="inlineStr"/>
+      <c r="E873" s="2" t="inlineStr">
+        <is>
+          <t>299.0</t>
+        </is>
+      </c>
+      <c r="F873" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G873" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="H873" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I873" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=50.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="2" t="n">
+        <v>326</v>
+      </c>
+      <c r="B874" s="2" t="inlineStr"/>
+      <c r="C874" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴洁面125ml两支装</t>
+        </is>
+      </c>
+      <c r="D874" s="2" t="inlineStr"/>
+      <c r="E874" s="2" t="inlineStr">
+        <is>
+          <t>358.0</t>
+        </is>
+      </c>
+      <c r="F874" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G874" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="H874" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I874" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="2" t="n">
+        <v>326</v>
+      </c>
+      <c r="B875" s="2" t="inlineStr">
+        <is>
+          <t>【】双支雅诗兰黛红石榴洁面新款125ml 清洁保湿洁面乳</t>
+        </is>
+      </c>
+      <c r="C875" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴洁面125ml两支装</t>
+        </is>
+      </c>
+      <c r="D875" s="2" t="inlineStr"/>
+      <c r="E875" s="2" t="inlineStr">
+        <is>
+          <t>359.0</t>
+        </is>
+      </c>
+      <c r="F875" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G875" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="H875" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I875" s="2" t="inlineStr"/>
+    </row>
+    <row r="876">
+      <c r="A876" s="2" t="n">
+        <v>326</v>
+      </c>
+      <c r="B876" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】红石榴洁面新款125ml 清洁保湿洁面乳</t>
+        </is>
+      </c>
+      <c r="C876" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴洁面125ml两支装</t>
+        </is>
+      </c>
+      <c r="D876" s="2" t="inlineStr"/>
+      <c r="E876" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="F876" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G876" s="2" t="inlineStr"/>
+      <c r="H876" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I876" s="2" t="inlineStr"/>
+    </row>
+    <row r="877">
+      <c r="A877" s="2" t="n">
+        <v>327</v>
+      </c>
+      <c r="B877" s="2" t="inlineStr">
+        <is>
+          <t>【ESTEE LAUDER雅诗兰黛】红石榴爽肤水200ml滋润型</t>
+        </is>
+      </c>
+      <c r="C877" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛红石榴水200ml两支装</t>
+        </is>
+      </c>
+      <c r="D877" s="2" t="inlineStr"/>
+      <c r="E877" s="2" t="inlineStr">
+        <is>
+          <t>137.75</t>
+        </is>
+      </c>
+      <c r="F877" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G877" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="H877" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I877" s="2" t="inlineStr"/>
+    </row>
+    <row r="878">
+      <c r="A878" s="2" t="n">
+        <v>328</v>
+      </c>
+      <c r="B878" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II神仙水补水保湿sk2护肤精华露30ml爽肤水保湿</t>
+        </is>
+      </c>
+      <c r="C878" s="2" t="inlineStr">
+        <is>
+          <t>SK2小银瓶50ml两瓶装</t>
+        </is>
+      </c>
+      <c r="D878" s="2" t="inlineStr"/>
+      <c r="E878" s="2" t="inlineStr">
+        <is>
+          <t>258.0</t>
+        </is>
+      </c>
+      <c r="F878" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G878" s="2" t="inlineStr"/>
+      <c r="H878" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I878" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="2" t="n">
+        <v>328</v>
+      </c>
+      <c r="B879" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II小银瓶精华50ml淡斑保湿护肤品送女朋友礼物sk2</t>
+        </is>
+      </c>
+      <c r="C879" s="2" t="inlineStr">
+        <is>
+          <t>SK2小银瓶50ml两瓶装</t>
+        </is>
+      </c>
+      <c r="D879" s="2" t="inlineStr"/>
+      <c r="E879" s="2" t="inlineStr">
+        <is>
+          <t>2990.0</t>
+        </is>
+      </c>
+      <c r="F879" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G879" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="H879" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I879" s="2" t="inlineStr"/>
+    </row>
+    <row r="880">
+      <c r="A880" s="2" t="n">
+        <v>328</v>
+      </c>
+      <c r="B880" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SK-II淡斑小银瓶精华50ml美白提亮祛斑sk2护肤品送礼</t>
+        </is>
+      </c>
+      <c r="C880" s="2" t="inlineStr">
+        <is>
+          <t>SK2小银瓶50ml两瓶装</t>
+        </is>
+      </c>
+      <c r="D880" s="2" t="inlineStr"/>
+      <c r="E880" s="2" t="inlineStr">
+        <is>
+          <t>2100.0</t>
+        </is>
+      </c>
+      <c r="F880" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G880" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="H880" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I880" s="2" t="inlineStr"/>
+    </row>
+    <row r="881">
+      <c r="A881" s="2" t="n">
+        <v>328</v>
+      </c>
+      <c r="B881" s="2" t="inlineStr">
+        <is>
+          <t>【送礼佳品】SK-II/sk2小银瓶精华液淡化斑印提亮肤色50ml礼盒款【6月18日发完】</t>
+        </is>
+      </c>
+      <c r="C881" s="2" t="inlineStr">
+        <is>
+          <t>SK2小银瓶50ml两瓶装</t>
+        </is>
+      </c>
+      <c r="D881" s="2" t="inlineStr"/>
+      <c r="E881" s="2" t="inlineStr">
+        <is>
+          <t>1380.0</t>
+        </is>
+      </c>
+      <c r="F881" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G881" s="2" t="inlineStr"/>
+      <c r="H881" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I881" s="2" t="inlineStr"/>
+    </row>
+    <row r="882">
+      <c r="A882" s="2" t="n">
+        <v>329</v>
+      </c>
+      <c r="B882" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】sk2大红瓶面霜50g面部护肤套装礼盒</t>
+        </is>
+      </c>
+      <c r="C882" s="2" t="inlineStr">
+        <is>
+          <t>SK2大红瓶滋润面霜50g</t>
+        </is>
+      </c>
+      <c r="D882" s="2" t="inlineStr"/>
+      <c r="E882" s="2" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="F882" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G882" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H882" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I882" s="2" t="inlineStr"/>
+    </row>
+    <row r="883">
+      <c r="A883" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="B883" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗西柚/睡莲/小苍兰香皂250g 深层清洁香皂</t>
+        </is>
+      </c>
+      <c r="C883" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗西柚香皂</t>
+        </is>
+      </c>
+      <c r="D883" s="2" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="E883" s="2" t="inlineStr">
+        <is>
+          <t>99.5</t>
+        </is>
+      </c>
+      <c r="F883" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G883" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="H883" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I883" s="2" t="inlineStr"/>
+    </row>
+    <row r="884">
+      <c r="A884" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="B884" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗小苍兰香皂250g 深层清洁香皂</t>
+        </is>
+      </c>
+      <c r="C884" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗西柚香皂</t>
+        </is>
+      </c>
+      <c r="D884" s="2" t="inlineStr"/>
+      <c r="E884" s="2" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="F884" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G884" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H884" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I884" s="2" t="inlineStr"/>
+    </row>
+    <row r="885">
+      <c r="A885" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="B885" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗西柚香皂250g 深层清洁香皂</t>
+        </is>
+      </c>
+      <c r="C885" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗西柚香皂</t>
+        </is>
+      </c>
+      <c r="D885" s="2" t="inlineStr"/>
+      <c r="E885" s="2" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="F885" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G885" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="H885" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I885" s="2" t="inlineStr"/>
+    </row>
+    <row r="886">
+      <c r="A886" s="2" t="n">
+        <v>331</v>
+      </c>
+      <c r="B886" s="2" t="inlineStr"/>
+      <c r="C886" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
+        </is>
+      </c>
+      <c r="D886" s="2" t="inlineStr">
+        <is>
+          <t>435.0</t>
+        </is>
+      </c>
+      <c r="E886" s="2" t="inlineStr">
+        <is>
+          <t>270.0</t>
+        </is>
+      </c>
+      <c r="F886" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G886" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="H886" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I886" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="2" t="n">
+        <v>331</v>
+      </c>
+      <c r="B887" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗 大马士革玫瑰花瓣润泽密集保湿爽肤水400ml高保湿深层滋润【5月31日发完】</t>
+        </is>
+      </c>
+      <c r="C887" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
+        </is>
+      </c>
+      <c r="D887" s="2" t="inlineStr"/>
+      <c r="E887" s="2" t="inlineStr">
+        <is>
+          <t>239.5</t>
+        </is>
+      </c>
+      <c r="F887" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G887" s="2" t="inlineStr"/>
+      <c r="H887" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I887" s="2" t="inlineStr"/>
+    </row>
+    <row r="888">
+      <c r="A888" s="2" t="n">
+        <v>331</v>
+      </c>
+      <c r="B888" s="2" t="inlineStr">
+        <is>
+          <t>【馥蕾诗】 大马士革玫瑰花瓣润泽密集保湿爽肤水400ml高保湿深层滋润【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C888" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
+        </is>
+      </c>
+      <c r="D888" s="2" t="inlineStr"/>
+      <c r="E888" s="2" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="F888" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G888" s="2" t="inlineStr"/>
+      <c r="H888" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I888" s="2" t="inlineStr"/>
+    </row>
+    <row r="889">
+      <c r="A889" s="2" t="n">
+        <v>331</v>
+      </c>
+      <c r="B889" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗玫瑰花瓣水250ml大马士革玫瑰润泽保湿爽肤水调理肌肤【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C889" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
+        </is>
+      </c>
+      <c r="D889" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="E889" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
+      <c r="F889" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G889" s="2" t="inlineStr"/>
+      <c r="H889" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I889" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="2" t="n">
+        <v>332</v>
+      </c>
+      <c r="B890" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】馥蕾诗红茶凝时焕活面霜50ml淡纹紧致增加光泽</t>
+        </is>
+      </c>
+      <c r="C890" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗红茶紧致面霜50ml</t>
+        </is>
+      </c>
+      <c r="D890" s="2" t="inlineStr"/>
+      <c r="E890" s="2" t="inlineStr">
+        <is>
+          <t>698.0</t>
+        </is>
+      </c>
+      <c r="F890" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G890" s="2" t="inlineStr"/>
+      <c r="H890" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I890" s="2" t="inlineStr"/>
+    </row>
+    <row r="891">
+      <c r="A891" s="2" t="n">
+        <v>333</v>
+      </c>
+      <c r="B891" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】馥蕾诗睡莲青春赋活面霜50ml修护淡纹柔润光采</t>
+        </is>
+      </c>
+      <c r="C891" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗睡莲日霜50ml</t>
+        </is>
+      </c>
+      <c r="D891" s="2" t="inlineStr"/>
+      <c r="E891" s="2" t="inlineStr">
+        <is>
+          <t>482.0</t>
+        </is>
+      </c>
+      <c r="F891" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G891" s="2" t="inlineStr"/>
+      <c r="H891" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I891" s="2" t="inlineStr"/>
+    </row>
+    <row r="892">
+      <c r="A892" s="2" t="n">
+        <v>334</v>
+      </c>
+      <c r="B892" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗玫瑰保湿面霜50ml  密集保湿舒缓补水</t>
+        </is>
+      </c>
+      <c r="C892" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗玫瑰保湿面霜50ml两瓶装</t>
+        </is>
+      </c>
+      <c r="D892" s="2" t="inlineStr"/>
+      <c r="E892" s="2" t="inlineStr">
+        <is>
+          <t>189.0</t>
+        </is>
+      </c>
+      <c r="F892" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G892" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="H892" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I892" s="2" t="inlineStr"/>
+    </row>
+    <row r="893">
+      <c r="A893" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="B893" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗小苍兰香皂250g 深层清洁香皂</t>
+        </is>
+      </c>
+      <c r="C893" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗小苍兰香皂</t>
+        </is>
+      </c>
+      <c r="D893" s="2" t="inlineStr"/>
+      <c r="E893" s="2" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="F893" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G893" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H893" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I893" s="2" t="inlineStr"/>
+    </row>
+    <row r="894">
+      <c r="A894" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="B894" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗西柚/睡莲/小苍兰香皂250g 深层清洁香皂</t>
+        </is>
+      </c>
+      <c r="C894" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗小苍兰香皂</t>
+        </is>
+      </c>
+      <c r="D894" s="2" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="E894" s="2" t="inlineStr">
+        <is>
+          <t>99.5</t>
+        </is>
+      </c>
+      <c r="F894" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G894" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="H894" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I894" s="2" t="inlineStr"/>
+    </row>
+    <row r="895">
+      <c r="A895" s="2" t="n">
+        <v>336</v>
+      </c>
+      <c r="B895" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】雅诗兰黛白金级养肤粉底液宝石粉底光感保湿透亮遮瑕</t>
+        </is>
+      </c>
+      <c r="C895" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛白金粉底液1W0</t>
+        </is>
+      </c>
+      <c r="D895" s="2" t="inlineStr"/>
+      <c r="E895" s="2" t="inlineStr">
+        <is>
+          <t>559.0</t>
+        </is>
+      </c>
+      <c r="F895" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G895" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="H895" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I895" s="2" t="inlineStr"/>
+    </row>
+    <row r="896">
+      <c r="A896" s="2" t="n">
+        <v>336</v>
+      </c>
+      <c r="B896" s="2" t="inlineStr">
+        <is>
+          <t>【专柜行货】雅诗兰黛白金养肤粉底液 持久遮瑕保湿抗氧化服帖</t>
+        </is>
+      </c>
+      <c r="C896" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛白金粉底液1W0</t>
+        </is>
+      </c>
+      <c r="D896" s="2" t="inlineStr">
+        <is>
+          <t>980.0</t>
+        </is>
+      </c>
+      <c r="E896" s="2" t="inlineStr">
+        <is>
+          <t>607.6</t>
+        </is>
+      </c>
+      <c r="F896" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G896" s="2" t="inlineStr"/>
+      <c r="H896" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I896" s="2" t="inlineStr"/>
+    </row>
+    <row r="897">
+      <c r="A897" s="2" t="n">
+        <v>337</v>
+      </c>
+      <c r="B897" s="2" t="inlineStr">
+        <is>
+          <t>【Fresh】馥蕾诗酵母酵萃红茶水250ml保湿补水清爽滋润爽肤水精华水</t>
+        </is>
+      </c>
+      <c r="C897" s="2" t="inlineStr">
+        <is>
+          <t>馥蕾诗红茶精粹水250ml</t>
+        </is>
+      </c>
+      <c r="D897" s="2" t="inlineStr">
+        <is>
+          <t>550.0</t>
+        </is>
+      </c>
+      <c r="E897" s="2" t="inlineStr">
+        <is>
+          <t>447.0</t>
+        </is>
+      </c>
+      <c r="F897" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G897" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="H897" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I897" s="2" t="inlineStr"/>
+    </row>
+    <row r="898">
+      <c r="A898" s="2" t="n">
+        <v>338</v>
+      </c>
+      <c r="B898" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】白金粉底液1C0养肤透亮持久保湿遮瑕服帖【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C898" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛白金粉底液1CO</t>
+        </is>
+      </c>
+      <c r="D898" s="2" t="inlineStr">
+        <is>
+          <t>599.0</t>
+        </is>
+      </c>
+      <c r="E898" s="2" t="inlineStr">
+        <is>
+          <t>425.0</t>
+        </is>
+      </c>
+      <c r="F898" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G898" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="H898" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I898" s="2" t="inlineStr"/>
+    </row>
+    <row r="899">
+      <c r="A899" s="2" t="n">
+        <v>339</v>
+      </c>
+      <c r="B899" s="2" t="inlineStr">
+        <is>
+          <t>【娇韵诗】美白三件套(水200ml+乳液100ml+精华50ml)</t>
+        </is>
+      </c>
+      <c r="C899" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗美白滋润水200ml</t>
+        </is>
+      </c>
+      <c r="D899" s="2" t="inlineStr">
+        <is>
+          <t>1270.0</t>
+        </is>
+      </c>
+      <c r="E899" s="2" t="inlineStr">
+        <is>
+          <t>728.0</t>
+        </is>
+      </c>
+      <c r="F899" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G899" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H899" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I899" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="2" t="n">
+        <v>339</v>
+      </c>
+      <c r="B900" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】Clarins/娇韵诗牛奶美白水乳组礼盒装淡斑祛黄提亮</t>
+        </is>
+      </c>
+      <c r="C900" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗美白滋润水200ml</t>
+        </is>
+      </c>
+      <c r="D900" s="2" t="inlineStr">
+        <is>
+          <t>499.0</t>
+        </is>
+      </c>
+      <c r="E900" s="2" t="inlineStr">
+        <is>
+          <t>369.0</t>
+        </is>
+      </c>
+      <c r="F900" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G900" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="H900" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I900" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="2" t="n">
+        <v>339</v>
+      </c>
+      <c r="B901" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】娇韵诗牛奶水减黄提亮美白淡斑清爽200ml保湿细腻</t>
+        </is>
+      </c>
+      <c r="C901" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗美白滋润水200ml</t>
+        </is>
+      </c>
+      <c r="D901" s="2" t="inlineStr">
+        <is>
+          <t>420.0</t>
+        </is>
+      </c>
+      <c r="E901" s="2" t="inlineStr">
+        <is>
+          <t>336.0</t>
+        </is>
+      </c>
+      <c r="F901" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G901" s="2" t="inlineStr"/>
+      <c r="H901" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I901" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="2" t="n">
+        <v>339</v>
+      </c>
+      <c r="B902" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】娇韵诗牛奶水清透润白柔肤水清爽滋润型焕亮净白柔嫩【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C902" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗美白滋润水200ml</t>
+        </is>
+      </c>
+      <c r="D902" s="2" t="inlineStr"/>
+      <c r="E902" s="2" t="inlineStr"/>
+      <c r="F902" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G902" s="2" t="inlineStr"/>
+      <c r="H902" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I902" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="2" t="n">
+        <v>339</v>
+      </c>
+      <c r="B903" s="2" t="inlineStr">
+        <is>
+          <t>【澳洲专柜】娇韵诗丰润型牛奶水透亮焕白淡斑美白保湿爽肤水【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C903" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗美白滋润水200ml</t>
+        </is>
+      </c>
+      <c r="D903" s="2" t="inlineStr"/>
+      <c r="E903" s="2" t="inlineStr"/>
+      <c r="F903" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G903" s="2" t="inlineStr"/>
+      <c r="H903" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I903" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="2" t="n">
+        <v>339</v>
+      </c>
+      <c r="B904" s="2" t="inlineStr">
+        <is>
+          <t>【娇韵诗】美白水乳套组牛奶水200ml+乳液75ml+</t>
+        </is>
+      </c>
+      <c r="C904" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗美白滋润水200ml</t>
+        </is>
+      </c>
+      <c r="D904" s="2" t="inlineStr"/>
+      <c r="E904" s="2" t="inlineStr">
+        <is>
+          <t>346.0</t>
+        </is>
+      </c>
+      <c r="F904" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G904" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="H904" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I904" s="2" t="inlineStr"/>
+    </row>
+    <row r="905">
+      <c r="A905" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="B905" s="2" t="inlineStr">
+        <is>
+          <t>Clarins/娇韵诗焕颜弹力元气晚霜滋润型50ml紧致回弹保湿淡纹面霜【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C905" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="D905" s="2" t="inlineStr"/>
+      <c r="E905" s="2" t="inlineStr">
+        <is>
+          <t>294.0</t>
+        </is>
+      </c>
+      <c r="F905" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G905" s="2" t="inlineStr">
+        <is>
+          <t>2023-11-01</t>
+        </is>
+      </c>
+      <c r="H905" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I905" s="2" t="inlineStr"/>
+    </row>
+    <row r="906">
+      <c r="A906" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="B906" s="2" t="inlineStr">
+        <is>
+          <t>CLARINS/娇韵诗焕颜紧致弹簧霜晚霜 50ml修护提亮 娇韵诗弹簧晚霜【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C906" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="D906" s="2" t="inlineStr"/>
+      <c r="E906" s="2" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="F906" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G906" s="2" t="inlineStr"/>
+      <c r="H906" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I906" s="2" t="inlineStr"/>
+    </row>
+    <row r="907">
+      <c r="A907" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="B907" s="2" t="inlineStr">
+        <is>
+          <t>Clarins/娇韵诗焕颜弹力元气晚霜滋润型50ml紧致回弹保湿淡纹面霜【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C907" s="2" t="inlineStr">
+        <is>
+          <t>娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="D907" s="2" t="inlineStr"/>
+      <c r="E907" s="2" t="inlineStr">
+        <is>
+          <t>298.0</t>
+        </is>
+      </c>
+      <c r="F907" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G907" s="2" t="inlineStr"/>
+      <c r="H907" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I907" s="2" t="inlineStr"/>
+    </row>
+    <row r="908">
+      <c r="A908" s="2" t="n">
+        <v>341</v>
+      </c>
+      <c r="B908" s="2" t="inlineStr">
+        <is>
+          <t>Clarins/娇韵诗焕颜弹力元气晚霜滋润型50ml紧致回弹保湿淡纹面霜【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C908" s="2" t="inlineStr">
+        <is>
+          <t>Clarins娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="D908" s="2" t="inlineStr"/>
+      <c r="E908" s="2" t="inlineStr">
+        <is>
+          <t>298.0</t>
+        </is>
+      </c>
+      <c r="F908" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G908" s="2" t="inlineStr"/>
+      <c r="H908" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I908" s="2" t="inlineStr"/>
+    </row>
+    <row r="909">
+      <c r="A909" s="2" t="n">
+        <v>341</v>
+      </c>
+      <c r="B909" s="2" t="inlineStr">
+        <is>
+          <t>【Clarins】娇韵诗焕颜弹力晚霜面霜50ml保湿提拉紧致滋润【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C909" s="2" t="inlineStr">
+        <is>
+          <t>Clarins娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="D909" s="2" t="inlineStr"/>
+      <c r="E909" s="2" t="inlineStr">
+        <is>
+          <t>298.0</t>
+        </is>
+      </c>
+      <c r="F909" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G909" s="2" t="inlineStr"/>
+      <c r="H909" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I909" s="2" t="inlineStr"/>
+    </row>
+    <row r="910">
+      <c r="A910" s="2" t="n">
+        <v>341</v>
+      </c>
+      <c r="B910" s="2" t="inlineStr">
+        <is>
+          <t>【Clarins】娇韵诗焕颜弹力元气晚霜滋润型50ml紧致回弹保湿淡纹面霜【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C910" s="2" t="inlineStr">
+        <is>
+          <t>Clarins娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="D910" s="2" t="inlineStr"/>
+      <c r="E910" s="2" t="inlineStr">
+        <is>
+          <t>298.0</t>
+        </is>
+      </c>
+      <c r="F910" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G910" s="2" t="inlineStr"/>
+      <c r="H910" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I910" s="2" t="inlineStr"/>
+    </row>
+    <row r="911">
+      <c r="A911" s="2" t="n">
+        <v>342</v>
+      </c>
+      <c r="B911" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】多效智妍面霜75ml 新款清爽款保湿</t>
+        </is>
+      </c>
+      <c r="C911" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛多效智妍乳霜75ml清爽</t>
+        </is>
+      </c>
+      <c r="D911" s="2" t="inlineStr"/>
+      <c r="E911" s="2" t="inlineStr">
+        <is>
+          <t>529.0</t>
+        </is>
+      </c>
+      <c r="F911" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G911" s="2" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="H911" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I911" s="2" t="inlineStr"/>
+    </row>
+    <row r="912">
+      <c r="A912" s="2" t="n">
+        <v>343</v>
+      </c>
+      <c r="B912" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】梅森马吉拉慵懒周末身体乳50ml*2</t>
+        </is>
+      </c>
+      <c r="C912" s="2" t="inlineStr">
+        <is>
+          <t>马丁马吉拉慵懒周末身体乳200ml</t>
+        </is>
+      </c>
+      <c r="D912" s="2" t="inlineStr"/>
+      <c r="E912" s="2" t="inlineStr">
+        <is>
+          <t>199.0</t>
+        </is>
+      </c>
+      <c r="F912" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G912" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H912" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I912" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="2" t="n">
+        <v>343</v>
+      </c>
+      <c r="B913" s="2" t="inlineStr">
+        <is>
+          <t>【Maison Margiela】梅森马吉拉 慵懒周末身体乳 滋润芳香200ml/400ml</t>
+        </is>
+      </c>
+      <c r="C913" s="2" t="inlineStr">
+        <is>
+          <t>马丁马吉拉慵懒周末身体乳200ml</t>
+        </is>
+      </c>
+      <c r="D913" s="2" t="inlineStr"/>
+      <c r="E913" s="2" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="F913" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G913" s="2" t="inlineStr"/>
+      <c r="H913" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I913" s="2" t="inlineStr"/>
+    </row>
+    <row r="914">
+      <c r="A914" s="2" t="n">
+        <v>343</v>
+      </c>
+      <c r="B914" s="2" t="inlineStr">
+        <is>
+          <t>【原装正品】Maison Margiela/梅森马吉拉慵懒周末身体乳200ml</t>
+        </is>
+      </c>
+      <c r="C914" s="2" t="inlineStr">
+        <is>
+          <t>马丁马吉拉慵懒周末身体乳200ml</t>
+        </is>
+      </c>
+      <c r="D914" s="2" t="inlineStr">
+        <is>
+          <t>290.0</t>
+        </is>
+      </c>
+      <c r="E914" s="2" t="inlineStr">
+        <is>
+          <t>190.0</t>
+        </is>
+      </c>
+      <c r="F914" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G914" s="2" t="inlineStr"/>
+      <c r="H914" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I914" s="2" t="inlineStr"/>
+    </row>
+    <row r="915">
+      <c r="A915" s="2" t="n">
+        <v>343</v>
+      </c>
+      <c r="B915" s="2" t="inlineStr">
+        <is>
+          <t>【正品原装】Maison Margiela/梅森马吉拉慵懒周末身体乳200ml</t>
+        </is>
+      </c>
+      <c r="C915" s="2" t="inlineStr">
+        <is>
+          <t>马丁马吉拉慵懒周末身体乳200ml</t>
+        </is>
+      </c>
+      <c r="D915" s="2" t="inlineStr"/>
+      <c r="E915" s="2" t="inlineStr">
+        <is>
+          <t>248.0</t>
+        </is>
+      </c>
+      <c r="F915" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G915" s="2" t="inlineStr"/>
+      <c r="H915" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I915" s="2" t="inlineStr"/>
+    </row>
+    <row r="916">
+      <c r="A916" s="2" t="n">
+        <v>344</v>
+      </c>
+      <c r="B916" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻水粉底 PO01正装30ml养肤柔光新款水润水啵啵【6月18日发完】</t>
+        </is>
+      </c>
+      <c r="C916" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻养肤水粉底液 PO-01 30ml</t>
+        </is>
+      </c>
+      <c r="D916" s="2" t="inlineStr"/>
+      <c r="E916" s="2" t="inlineStr">
+        <is>
+          <t>109.9</t>
+        </is>
+      </c>
+      <c r="F916" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G916" s="2" t="inlineStr"/>
+      <c r="H916" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I916" s="2" t="inlineStr"/>
+    </row>
+    <row r="917">
+      <c r="A917" s="2" t="n">
+        <v>344</v>
+      </c>
+      <c r="B917" s="2" t="inlineStr">
+        <is>
+          <t>【兰蔻】水粉底养肤柔光粉底液PO-01#30ml水啵啵干皮持妆遮瑕</t>
+        </is>
+      </c>
+      <c r="C917" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻养肤水粉底液 PO-01 30ml</t>
+        </is>
+      </c>
+      <c r="D917" s="2" t="inlineStr"/>
+      <c r="E917" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="F917" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G917" s="2" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="H917" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I917" s="2" t="inlineStr"/>
+    </row>
+    <row r="918">
+      <c r="A918" s="2" t="n">
+        <v>344</v>
+      </c>
+      <c r="B918" s="2" t="inlineStr">
+        <is>
+          <t>【兰蔻】水粉底养肤柔光粉底液PO-03#30ml正装P01水啵啵PO-01持妆遮瑕</t>
+        </is>
+      </c>
+      <c r="C918" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻养肤水粉底液 PO-01 30ml</t>
+        </is>
+      </c>
+      <c r="D918" s="2" t="inlineStr"/>
+      <c r="E918" s="2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="F918" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G918" s="2" t="inlineStr"/>
+      <c r="H918" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I918" s="2" t="inlineStr"/>
+    </row>
+    <row r="919">
+      <c r="A919" s="2" t="n">
+        <v>345</v>
+      </c>
+      <c r="B919" s="2" t="inlineStr">
+        <is>
+          <t>【Kiehl's】科颜氏男士保湿乳液125ml活力清爽控油补水收缩毛孔送男友</t>
+        </is>
+      </c>
+      <c r="C919" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏男士乳液125ml</t>
+        </is>
+      </c>
+      <c r="D919" s="2" t="inlineStr"/>
+      <c r="E919" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="F919" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G919" s="2" t="inlineStr"/>
+      <c r="H919" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I919" s="2" t="inlineStr"/>
+    </row>
+    <row r="920">
+      <c r="A920" s="2" t="n">
+        <v>345</v>
+      </c>
+      <c r="B920" s="2" t="inlineStr">
+        <is>
+          <t>【科颜氏】男士保湿乳液125ml补水保湿清爽改善暗沉礼物</t>
+        </is>
+      </c>
+      <c r="C920" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏男士乳液125ml</t>
+        </is>
+      </c>
+      <c r="D920" s="2" t="inlineStr"/>
+      <c r="E920" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
+      <c r="F920" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G920" s="2" t="inlineStr"/>
+      <c r="H920" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I920" s="2" t="inlineStr"/>
+    </row>
+    <row r="921">
+      <c r="A921" s="2" t="n">
+        <v>346</v>
+      </c>
+      <c r="B921" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】科颜氏Kiehl高保湿清爽凝霜滋润补水果冻面霜50ml</t>
+        </is>
+      </c>
+      <c r="C921" s="2" t="inlineStr">
+        <is>
+          <t>科颜氏果冻清爽高保湿霜50ml/瓶</t>
+        </is>
+      </c>
+      <c r="D921" s="2" t="inlineStr">
+        <is>
+          <t>199.0</t>
+        </is>
+      </c>
+      <c r="E921" s="2" t="inlineStr">
+        <is>
+          <t>120.8</t>
+        </is>
+      </c>
+      <c r="F921" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G921" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="H921" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I921" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/商品采集汇总.xlsx
+++ b/商品采集汇总.xlsx
@@ -437,18 +437,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K774"/>
+  <dimension ref="A1:K897"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="33" customWidth="1" min="9" max="9"/>
+    <col width="39" customWidth="1" min="9" max="9"/>
     <col width="50" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
   </cols>
@@ -27760,30 +27760,34 @@
     </row>
     <row r="710">
       <c r="A710" s="2" t="n">
-        <v>303</v>
+        <v>330</v>
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】GUCCI古驰花悦绽放慕意香水女士优雅简装EDP 100ml</t>
+          <t>【Fresh】馥蕾诗西柚/睡莲/小苍兰香皂250g 深层清洁香皂</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
         <is>
-          <t>GUCCI花悦绽放100ML浓香</t>
-        </is>
-      </c>
-      <c r="D710" s="2" t="inlineStr"/>
-      <c r="E710" s="2" t="inlineStr">
-        <is>
-          <t>852.0</t>
-        </is>
+          <t>馥蕾诗西柚香皂</t>
+        </is>
+      </c>
+      <c r="D710" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="E710" s="2" t="n">
+        <v>99.5</v>
       </c>
       <c r="F710" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G710" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G710" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
       <c r="H710" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -27795,27 +27799,21 @@
     </row>
     <row r="711">
       <c r="A711" s="2" t="n">
-        <v>303</v>
+        <v>330</v>
       </c>
       <c r="B711" s="2" t="inlineStr">
         <is>
-          <t>【GUCCI】古驰花悦绽放浓香水100ml简装黑盖女士香氛正品持久留香</t>
+          <t>【Fresh】馥蕾诗西柚香皂250g 深层清洁香皂</t>
         </is>
       </c>
       <c r="C711" s="2" t="inlineStr">
         <is>
-          <t>GUCCI花悦绽放100ML浓香</t>
-        </is>
-      </c>
-      <c r="D711" s="2" t="inlineStr">
-        <is>
-          <t>538.0</t>
-        </is>
-      </c>
-      <c r="E711" s="2" t="inlineStr">
-        <is>
-          <t>339.0</t>
-        </is>
+          <t>馥蕾诗西柚香皂</t>
+        </is>
+      </c>
+      <c r="D711" s="2" t="inlineStr"/>
+      <c r="E711" s="2" t="n">
+        <v>115</v>
       </c>
       <c r="F711" s="2" t="inlineStr">
         <is>
@@ -27824,7 +27822,7 @@
       </c>
       <c r="G711" s="2" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H711" s="2" t="inlineStr">
@@ -27838,77 +27836,71 @@
     </row>
     <row r="712">
       <c r="A712" s="2" t="n">
-        <v>304</v>
+        <v>331</v>
       </c>
       <c r="B712" s="2" t="inlineStr">
         <is>
-          <t>【100ml】古驰 绮梦兰花浓香水EDP简装无盖</t>
+          <t>【42.1万人收藏该品牌】FRESH/馥蕾诗玫瑰花瓣水250ml*2瓶</t>
         </is>
       </c>
       <c r="C712" s="2" t="inlineStr">
         <is>
-          <t>GUCCI绮梦木兰100ML浓香型</t>
-        </is>
-      </c>
-      <c r="D712" s="2" t="inlineStr"/>
-      <c r="E712" s="2" t="inlineStr">
-        <is>
-          <t>888.0</t>
-        </is>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
+        </is>
+      </c>
+      <c r="D712" s="2" t="n">
+        <v>435</v>
+      </c>
+      <c r="E712" s="2" t="n">
+        <v>270</v>
       </c>
       <c r="F712" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G712" s="2" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="H712" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I712" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I712" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配</t>
+        </is>
+      </c>
       <c r="J712" s="2" t="inlineStr"/>
       <c r="K712" s="2" t="inlineStr"/>
     </row>
     <row r="713">
       <c r="A713" s="2" t="n">
-        <v>305</v>
+        <v>331</v>
       </c>
       <c r="B713" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】GUCCI古驰绮梦馥栀女士香水花香调简装无盖EDP 100ml</t>
+          <t>超粘超软 JNM GL70Ultra 升级款羽毛球拍手胶吸汗防滑减震</t>
         </is>
       </c>
       <c r="C713" s="2" t="inlineStr">
         <is>
-          <t>GUCCI绮梦栀子花100ML浓香型</t>
-        </is>
-      </c>
-      <c r="D713" s="2" t="inlineStr">
-        <is>
-          <t>771.0</t>
-        </is>
-      </c>
-      <c r="E713" s="2" t="inlineStr">
-        <is>
-          <t>468.7</t>
-        </is>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
+        </is>
+      </c>
+      <c r="D713" s="2" t="inlineStr"/>
+      <c r="E713" s="2" t="n">
+        <v>11.52</v>
       </c>
       <c r="F713" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G713" s="2" t="inlineStr">
-        <is>
-          <t>2025-02-06</t>
-        </is>
-      </c>
+      <c r="G713" s="2" t="inlineStr"/>
       <c r="H713" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -27916,7 +27908,7 @@
       </c>
       <c r="I713" s="2" t="inlineStr">
         <is>
-          <t>品名相似不足(ratio=0.0%)</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)</t>
         </is>
       </c>
       <c r="J713" s="2" t="inlineStr"/>
@@ -27924,85 +27916,63 @@
     </row>
     <row r="714">
       <c r="A714" s="2" t="n">
-        <v>305</v>
+        <v>331</v>
       </c>
       <c r="B714" s="2" t="inlineStr">
         <is>
-          <t>Gucci古驰 绮梦馥栀女士EDP浓香水100ml 25年新品</t>
+          <t>【馥蕾诗】 大马士革玫瑰花瓣润泽密集保湿爽肤水400ml高保湿深层滋润【5天内发货】</t>
         </is>
       </c>
       <c r="C714" s="2" t="inlineStr">
         <is>
-          <t>GUCCI绮梦栀子花100ML浓香型</t>
-        </is>
-      </c>
-      <c r="D714" s="2" t="inlineStr">
-        <is>
-          <t>799.0</t>
-        </is>
-      </c>
-      <c r="E714" s="2" t="inlineStr">
-        <is>
-          <t>531.0</t>
-        </is>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
+        </is>
+      </c>
+      <c r="D714" s="2" t="inlineStr"/>
+      <c r="E714" s="2" t="n">
+        <v>239.5</v>
       </c>
       <c r="F714" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G714" s="2" t="inlineStr">
-        <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G714" s="2" t="inlineStr"/>
       <c r="H714" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I714" s="2" t="inlineStr">
-        <is>
-          <t>品名相似不足(ratio=0.0%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I714" s="2" t="inlineStr"/>
       <c r="J714" s="2" t="inlineStr"/>
       <c r="K714" s="2" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" s="2" t="n">
-        <v>305</v>
+        <v>331</v>
       </c>
       <c r="B715" s="2" t="inlineStr">
         <is>
-          <t>【GUCCI】古驰绮梦馥栀香水100ml简装正品持久留香节日礼物自用</t>
+          <t>【Fresh】馥蕾诗玫瑰花瓣水250ml大马士革玫瑰润泽保湿爽肤水调理肌肤【5天内发货】</t>
         </is>
       </c>
       <c r="C715" s="2" t="inlineStr">
         <is>
-          <t>GUCCI绮梦栀子花100ML浓香型</t>
-        </is>
-      </c>
-      <c r="D715" s="2" t="inlineStr">
-        <is>
-          <t>699.0</t>
-        </is>
-      </c>
-      <c r="E715" s="2" t="inlineStr">
-        <is>
-          <t>467.28</t>
-        </is>
+          <t>馥蕾诗玫瑰花瓣水400ml</t>
+        </is>
+      </c>
+      <c r="D715" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="E715" s="2" t="n">
+        <v>152</v>
       </c>
       <c r="F715" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G715" s="2" t="inlineStr">
-        <is>
-          <t>2023-04-01</t>
-        </is>
-      </c>
+      <c r="G715" s="2" t="inlineStr"/>
       <c r="H715" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -28010,7 +27980,7 @@
       </c>
       <c r="I715" s="2" t="inlineStr">
         <is>
-          <t>品名相似不足(ratio=0.0%)</t>
+          <t>规格不匹配</t>
         </is>
       </c>
       <c r="J715" s="2" t="inlineStr"/>
@@ -28018,34 +27988,34 @@
     </row>
     <row r="716">
       <c r="A716" s="2" t="n">
-        <v>305</v>
+        <v>332</v>
       </c>
       <c r="B716" s="2" t="inlineStr">
         <is>
-          <t>【GUCCI】古驰绮梦栀子花女士浓香水EDP100ml520节日礼物</t>
+          <t>【正品行货】馥蕾诗红茶凝时焕活面霜50ml淡纹紧致增加光泽</t>
         </is>
       </c>
       <c r="C716" s="2" t="inlineStr">
         <is>
-          <t>GUCCI绮梦栀子花100ML浓香型</t>
-        </is>
-      </c>
-      <c r="D716" s="2" t="inlineStr">
-        <is>
-          <t>699.0</t>
-        </is>
-      </c>
-      <c r="E716" s="2" t="inlineStr">
-        <is>
-          <t>432.0</t>
-        </is>
+          <t>馥蕾诗红茶紧致面霜50ml</t>
+        </is>
+      </c>
+      <c r="D716" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="E716" s="2" t="n">
+        <v>447</v>
       </c>
       <c r="F716" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G716" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G716" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
       <c r="H716" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -28057,34 +28027,28 @@
     </row>
     <row r="717">
       <c r="A717" s="2" t="n">
-        <v>306</v>
+        <v>333</v>
       </c>
       <c r="B717" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】GUCCI古驰绮梦香草兰浓香水 甜美水生美食调 EDP30ml</t>
+          <t>【Fresh】馥蕾诗青春赋活面霜日霜紧致肌肤抗皱提亮深度保湿香港仓发【5天内发货】</t>
         </is>
       </c>
       <c r="C717" s="2" t="inlineStr">
         <is>
-          <t>GUCCI绮梦香草兰香100ml</t>
+          <t>馥蕾诗睡莲日霜50ml</t>
         </is>
       </c>
       <c r="D717" s="2" t="inlineStr"/>
-      <c r="E717" s="2" t="inlineStr">
-        <is>
-          <t>603.0</t>
-        </is>
+      <c r="E717" s="2" t="n">
+        <v>27.53</v>
       </c>
       <c r="F717" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G717" s="2" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G717" s="2" t="inlineStr"/>
       <c r="H717" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -28100,202 +28064,176 @@
     </row>
     <row r="718">
       <c r="A718" s="2" t="n">
-        <v>306</v>
+        <v>333</v>
       </c>
       <c r="B718" s="2" t="inlineStr">
         <is>
-          <t>【100ml】古驰 绮梦兰花浓香水EDP简装无盖</t>
+          <t>【Fresh】馥蕾诗睡莲青春赋活面霜Lotus面霜保湿滋养修护提亮肤色50ml【5天内发货】</t>
         </is>
       </c>
       <c r="C718" s="2" t="inlineStr">
         <is>
-          <t>GUCCI绮梦香草兰香100ml</t>
+          <t>馥蕾诗睡莲日霜50ml</t>
         </is>
       </c>
       <c r="D718" s="2" t="inlineStr"/>
-      <c r="E718" s="2" t="inlineStr">
-        <is>
-          <t>888.0</t>
-        </is>
+      <c r="E718" s="2" t="n">
+        <v>292</v>
       </c>
       <c r="F718" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G718" s="2" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
+      <c r="G718" s="2" t="inlineStr"/>
       <c r="H718" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I718" s="2" t="inlineStr">
-        <is>
-          <t>品名相似不足(ratio=25.0%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I718" s="2" t="inlineStr"/>
       <c r="J718" s="2" t="inlineStr"/>
       <c r="K718" s="2" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" s="2" t="n">
-        <v>306</v>
+        <v>334</v>
       </c>
       <c r="B719" s="2" t="inlineStr">
         <is>
-          <t>【正品原装】GUCCI/古驰新品绮梦香草兰浓香EDP香水</t>
+          <t>【Fresh】馥蕾诗玫瑰保湿面霜50ml  密集保湿舒缓补水</t>
         </is>
       </c>
       <c r="C719" s="2" t="inlineStr">
         <is>
-          <t>GUCCI绮梦香草兰香100ml</t>
-        </is>
-      </c>
-      <c r="D719" s="2" t="inlineStr"/>
-      <c r="E719" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
+          <t>馥蕾诗玫瑰保湿面霜50ml两瓶装</t>
+        </is>
+      </c>
+      <c r="D719" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="E719" s="2" t="n">
+        <v>141</v>
       </c>
       <c r="F719" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G719" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G719" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
       <c r="H719" s="2" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
       <c r="I719" s="2" t="inlineStr"/>
-      <c r="J719" s="2" t="inlineStr">
-        <is>
-          <t>已选择： 100mL 绮梦香草兰女士香水 1瓶 古驰绮梦香草兰</t>
-        </is>
-      </c>
-      <c r="K719" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
+      <c r="J719" s="2" t="inlineStr"/>
+      <c r="K719" s="2" t="inlineStr"/>
     </row>
     <row r="720">
       <c r="A720" s="2" t="n">
-        <v>306</v>
+        <v>335</v>
       </c>
       <c r="B720" s="2" t="inlineStr">
         <is>
-          <t>【正品鉴定】GUCCI古驰 2024年新品 绮梦香草兰浓香水/兰花香草</t>
+          <t>【Fresh】馥蕾诗小苍兰香皂250g 深层清洁香皂</t>
         </is>
       </c>
       <c r="C720" s="2" t="inlineStr">
         <is>
-          <t>GUCCI绮梦香草兰香100ml</t>
+          <t>馥蕾诗小苍兰香皂</t>
         </is>
       </c>
       <c r="D720" s="2" t="inlineStr"/>
-      <c r="E720" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
+      <c r="E720" s="2" t="n">
+        <v>115</v>
       </c>
       <c r="F720" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G720" s="2" t="inlineStr"/>
+      <c r="G720" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
       <c r="H720" s="2" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
       <c r="I720" s="2" t="inlineStr"/>
-      <c r="J720" s="2" t="inlineStr">
-        <is>
-          <t>已选择： 100mL 古驰 绮梦香草兰 浓香 个人款</t>
-        </is>
-      </c>
-      <c r="K720" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
+      <c r="J720" s="2" t="inlineStr"/>
+      <c r="K720" s="2" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" s="2" t="n">
-        <v>306</v>
+        <v>335</v>
       </c>
       <c r="B721" s="2" t="inlineStr">
         <is>
-          <t>【原盒正品】GUCCI古驰 2024年新品 绮梦香草兰浓香水/兰花香草</t>
+          <t>【Fresh】馥蕾诗西柚/睡莲/小苍兰香皂250g 深层清洁香皂</t>
         </is>
       </c>
       <c r="C721" s="2" t="inlineStr">
         <is>
-          <t>GUCCI绮梦香草兰香100ml</t>
-        </is>
-      </c>
-      <c r="D721" s="2" t="inlineStr"/>
-      <c r="E721" s="2" t="inlineStr">
-        <is>
-          <t>256.0</t>
-        </is>
+          <t>馥蕾诗小苍兰香皂</t>
+        </is>
+      </c>
+      <c r="D721" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="E721" s="2" t="n">
+        <v>99.5</v>
       </c>
       <c r="F721" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G721" s="2" t="inlineStr"/>
+      <c r="G721" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
       <c r="H721" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I721" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I721" s="2" t="inlineStr"/>
       <c r="J721" s="2" t="inlineStr"/>
       <c r="K721" s="2" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" s="2" t="n">
-        <v>307</v>
+        <v>336</v>
       </c>
       <c r="B722" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】GUCCI古驰绮梦香草兰香型女士香水50ml情人节送女友</t>
+          <t>【正品行货】雅诗兰黛白金级养肤粉底液宝石粉底光感保湿透亮遮瑕</t>
         </is>
       </c>
       <c r="C722" s="2" t="inlineStr">
         <is>
-          <t>GUCCI绮梦香草兰香50ml</t>
+          <t>雅诗兰黛白金粉底液1W0</t>
         </is>
       </c>
       <c r="D722" s="2" t="inlineStr"/>
-      <c r="E722" s="2" t="inlineStr">
-        <is>
-          <t>455.0</t>
-        </is>
+      <c r="E722" s="2" t="n">
+        <v>599</v>
       </c>
       <c r="F722" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G722" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
+      <c r="G722" s="2" t="inlineStr"/>
       <c r="H722" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -28307,27 +28245,23 @@
     </row>
     <row r="723">
       <c r="A723" s="2" t="n">
-        <v>308</v>
+        <v>336</v>
       </c>
       <c r="B723" s="2" t="inlineStr">
         <is>
-          <t>【两瓶装】卡诗洗发水黑钻钥源滋养发毛躁润泽保湿护发卡斯洗发水</t>
+          <t>【专柜行货】雅诗兰黛白金养肤粉底液 持久遮瑕保湿抗氧化服帖</t>
         </is>
       </c>
       <c r="C723" s="2" t="inlineStr">
         <is>
-          <t>Kerastase卡诗黑钻鱼子酱洗发水250ml</t>
-        </is>
-      </c>
-      <c r="D723" s="2" t="inlineStr">
-        <is>
-          <t>318.98</t>
-        </is>
-      </c>
-      <c r="E723" s="2" t="inlineStr">
-        <is>
-          <t>317.98</t>
-        </is>
+          <t>雅诗兰黛白金粉底液1W0</t>
+        </is>
+      </c>
+      <c r="D723" s="2" t="n">
+        <v>980</v>
+      </c>
+      <c r="E723" s="2" t="n">
+        <v>607.6</v>
       </c>
       <c r="F723" s="2" t="inlineStr">
         <is>
@@ -28341,51 +28275,33 @@
         </is>
       </c>
       <c r="I723" s="2" t="inlineStr"/>
-      <c r="J723" s="2" t="inlineStr">
-        <is>
-          <t>已选择： 洗发水250ml  两瓶</t>
-        </is>
-      </c>
-      <c r="K723" s="2" t="inlineStr">
-        <is>
-          <t>317.98</t>
-        </is>
-      </c>
+      <c r="J723" s="2" t="inlineStr"/>
+      <c r="K723" s="2" t="inlineStr"/>
     </row>
     <row r="724">
       <c r="A724" s="2" t="n">
-        <v>309</v>
+        <v>336</v>
       </c>
       <c r="B724" s="2" t="inlineStr">
         <is>
-          <t>【HR】赫莲娜绿宝瓶新肌水400ml保湿修护提亮补水精华水</t>
+          <t>【正品行货】雅诗兰黛白金级养肤粉底液宝石粉底光感保湿透亮遮瑕</t>
         </is>
       </c>
       <c r="C724" s="2" t="inlineStr">
         <is>
-          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水400ml</t>
-        </is>
-      </c>
-      <c r="D724" s="2" t="inlineStr">
-        <is>
-          <t>1099.0</t>
-        </is>
-      </c>
-      <c r="E724" s="2" t="inlineStr">
-        <is>
-          <t>672.0</t>
-        </is>
+          <t>雅诗兰黛白金粉底液1W0</t>
+        </is>
+      </c>
+      <c r="D724" s="2" t="inlineStr"/>
+      <c r="E724" s="2" t="n">
+        <v>559</v>
       </c>
       <c r="F724" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G724" s="2" t="inlineStr">
-        <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
+      <c r="G724" s="2" t="inlineStr"/>
       <c r="H724" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -28397,27 +28313,21 @@
     </row>
     <row r="725">
       <c r="A725" s="2" t="n">
-        <v>309</v>
+        <v>337</v>
       </c>
       <c r="B725" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】HR/赫莲娜绿宝瓶悦活蓄能新肌水400ml</t>
+          <t>【Fresh】馥蕾诗酵母酵萃红茶水250ml保湿补水清爽滋润爽肤水精华水</t>
         </is>
       </c>
       <c r="C725" s="2" t="inlineStr">
         <is>
-          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水400ml</t>
-        </is>
-      </c>
-      <c r="D725" s="2" t="inlineStr">
-        <is>
-          <t>1216.0</t>
-        </is>
-      </c>
-      <c r="E725" s="2" t="inlineStr">
-        <is>
-          <t>749.0</t>
-        </is>
+          <t>馥蕾诗红茶精粹水250ml</t>
+        </is>
+      </c>
+      <c r="D725" s="2" t="inlineStr"/>
+      <c r="E725" s="2" t="n">
+        <v>550</v>
       </c>
       <c r="F725" s="2" t="inlineStr">
         <is>
@@ -28426,7 +28336,7 @@
       </c>
       <c r="G725" s="2" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H725" s="2" t="inlineStr">
@@ -28440,27 +28350,23 @@
     </row>
     <row r="726">
       <c r="A726" s="2" t="n">
-        <v>310</v>
+        <v>338</v>
       </c>
       <c r="B726" s="2" t="inlineStr">
         <is>
-          <t>2支赫莲娜绿宝瓶新肌水200ml补水保湿</t>
+          <t>【雅诗兰黛】白金粉底液1C0养肤透亮持久保湿遮瑕服帖【5天内发货】</t>
         </is>
       </c>
       <c r="C726" s="2" t="inlineStr">
         <is>
-          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水200ml</t>
-        </is>
-      </c>
-      <c r="D726" s="2" t="inlineStr">
-        <is>
-          <t>1359.0</t>
-        </is>
-      </c>
-      <c r="E726" s="2" t="inlineStr">
-        <is>
-          <t>989</t>
-        </is>
+          <t>雅诗兰黛白金粉底液1CO</t>
+        </is>
+      </c>
+      <c r="D726" s="2" t="n">
+        <v>568</v>
+      </c>
+      <c r="E726" s="2" t="n">
+        <v>425</v>
       </c>
       <c r="F726" s="2" t="inlineStr">
         <is>
@@ -28469,7 +28375,7 @@
       </c>
       <c r="G726" s="2" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H726" s="2" t="inlineStr">
@@ -28478,51 +28384,35 @@
         </is>
       </c>
       <c r="I726" s="2" t="inlineStr"/>
-      <c r="J726" s="2" t="inlineStr">
-        <is>
-          <t>已选择： 新肌水200ml*2</t>
-        </is>
-      </c>
-      <c r="K726" s="2" t="inlineStr">
-        <is>
-          <t>989</t>
-        </is>
-      </c>
+      <c r="J726" s="2" t="inlineStr"/>
+      <c r="K726" s="2" t="inlineStr"/>
     </row>
     <row r="727">
       <c r="A727" s="2" t="n">
-        <v>310</v>
+        <v>339</v>
       </c>
       <c r="B727" s="2" t="inlineStr">
         <is>
-          <t>【赫莲娜】绿宝瓶新肌水200ml/瓶补水保湿</t>
+          <t>【正品行货】娇韵诗牛奶水减黄提亮美白淡斑清爽200ml保湿细腻</t>
         </is>
       </c>
       <c r="C727" s="2" t="inlineStr">
         <is>
-          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水200ml</t>
-        </is>
-      </c>
-      <c r="D727" s="2" t="inlineStr">
-        <is>
-          <t>699.0</t>
-        </is>
-      </c>
-      <c r="E727" s="2" t="inlineStr">
-        <is>
-          <t>462.0</t>
-        </is>
+          <t>娇韵诗美白滋润水200ml</t>
+        </is>
+      </c>
+      <c r="D727" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="E727" s="2" t="n">
+        <v>336</v>
       </c>
       <c r="F727" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G727" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G727" s="2" t="inlineStr"/>
       <c r="H727" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -28534,38 +28424,28 @@
     </row>
     <row r="728">
       <c r="A728" s="2" t="n">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="B728" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】HR/赫莲娜绿宝瓶新肌水200ml保湿修护提亮补水精华水</t>
+          <t>CLARINS/娇韵诗焕颜紧致弹簧霜晚霜 50ml修护提亮 娇韵诗弹簧晚霜【5天内发货】</t>
         </is>
       </c>
       <c r="C728" s="2" t="inlineStr">
         <is>
-          <t>Helena Rubinstein 赫莲娜 绿宝瓶新肌水200ml</t>
-        </is>
-      </c>
-      <c r="D728" s="2" t="inlineStr">
-        <is>
-          <t>896.0</t>
-        </is>
-      </c>
-      <c r="E728" s="2" t="inlineStr">
-        <is>
-          <t>556.0</t>
-        </is>
+          <t>娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="D728" s="2" t="inlineStr"/>
+      <c r="E728" s="2" t="n">
+        <v>500</v>
       </c>
       <c r="F728" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G728" s="2" t="inlineStr">
-        <is>
-          <t>2025-05-23</t>
-        </is>
-      </c>
+      <c r="G728" s="2" t="inlineStr"/>
       <c r="H728" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -28577,38 +28457,28 @@
     </row>
     <row r="729">
       <c r="A729" s="2" t="n">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="B729" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】SK-II光子小灯泡50ml美白护肤精华液淡斑提亮</t>
+          <t>【Clarins】娇韵诗焕颜弹力元气晚霜滋润型50ml紧致回弹保湿淡纹面霜【5天内发货】</t>
         </is>
       </c>
       <c r="C729" s="2" t="inlineStr">
         <is>
-          <t>SK-II光子小灯泡精华露50ml</t>
-        </is>
-      </c>
-      <c r="D729" s="2" t="inlineStr">
-        <is>
-          <t>1213.0</t>
-        </is>
-      </c>
-      <c r="E729" s="2" t="inlineStr">
-        <is>
-          <t>825.0</t>
-        </is>
+          <t>娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="D729" s="2" t="inlineStr"/>
+      <c r="E729" s="2" t="n">
+        <v>298</v>
       </c>
       <c r="F729" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G729" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-17</t>
-        </is>
-      </c>
+      <c r="G729" s="2" t="inlineStr"/>
       <c r="H729" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -28620,27 +28490,23 @@
     </row>
     <row r="730">
       <c r="A730" s="2" t="n">
-        <v>312</v>
+        <v>340</v>
       </c>
       <c r="B730" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】SK-II骨胶原晶致活肤修护乳液补水保湿抗皱紧致舒缓</t>
+          <t>【正品】娇韵诗焕颜紧致弹簧晚霜淡纹胶原回弹滋润抗皱面霜女50ml</t>
         </is>
       </c>
       <c r="C730" s="2" t="inlineStr">
         <is>
-          <t>SK-II晶致美肤乳液100g</t>
-        </is>
-      </c>
-      <c r="D730" s="2" t="inlineStr">
-        <is>
-          <t>600.0</t>
-        </is>
-      </c>
-      <c r="E730" s="2" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
+          <t>娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="D730" s="2" t="n">
+        <v>319</v>
+      </c>
+      <c r="E730" s="2" t="n">
+        <v>312.64</v>
       </c>
       <c r="F730" s="2" t="inlineStr">
         <is>
@@ -28649,7 +28515,7 @@
       </c>
       <c r="G730" s="2" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H730" s="2" t="inlineStr">
@@ -28658,40 +28524,26 @@
         </is>
       </c>
       <c r="I730" s="2" t="inlineStr"/>
-      <c r="J730" s="2" t="inlineStr">
-        <is>
-          <t>已选择： 骨胶原乳液100g</t>
-        </is>
-      </c>
-      <c r="K730" s="2" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
+      <c r="J730" s="2" t="inlineStr"/>
+      <c r="K730" s="2" t="inlineStr"/>
     </row>
     <row r="731">
       <c r="A731" s="2" t="n">
-        <v>313</v>
+        <v>341</v>
       </c>
       <c r="B731" s="2" t="inlineStr">
         <is>
-          <t>【SK-II】 女士氨基酸清洁洁面乳120g/支</t>
+          <t>Clarins/娇韵诗焕颜弹力元气晚霜滋润型50ml紧致回弹保湿淡纹面霜【5天内发货】</t>
         </is>
       </c>
       <c r="C731" s="2" t="inlineStr">
         <is>
-          <t>SKII女士洗面奶120g/支</t>
-        </is>
-      </c>
-      <c r="D731" s="2" t="inlineStr">
-        <is>
-          <t>339.0</t>
-        </is>
-      </c>
-      <c r="E731" s="2" t="inlineStr">
-        <is>
-          <t>229.0</t>
-        </is>
+          <t>Clarins娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="D731" s="2" t="inlineStr"/>
+      <c r="E731" s="2" t="n">
+        <v>298</v>
       </c>
       <c r="F731" s="2" t="inlineStr">
         <is>
@@ -28710,27 +28562,21 @@
     </row>
     <row r="732">
       <c r="A732" s="2" t="n">
-        <v>313</v>
+        <v>341</v>
       </c>
       <c r="B732" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】SKII氨基酸洗面奶护肤洁面乳120g温和控油清洁不刺激</t>
+          <t>【Clarins】娇韵诗焕颜弹力元气晚霜滋润型50ml紧致回弹保湿淡纹面霜【5天内发货】</t>
         </is>
       </c>
       <c r="C732" s="2" t="inlineStr">
         <is>
-          <t>SKII女士洗面奶120g/支</t>
-        </is>
-      </c>
-      <c r="D732" s="2" t="inlineStr">
-        <is>
-          <t>393.0</t>
-        </is>
-      </c>
-      <c r="E732" s="2" t="inlineStr">
-        <is>
-          <t>244.0</t>
-        </is>
+          <t>Clarins娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="D732" s="2" t="inlineStr"/>
+      <c r="E732" s="2" t="n">
+        <v>298</v>
       </c>
       <c r="F732" s="2" t="inlineStr">
         <is>
@@ -28749,38 +28595,28 @@
     </row>
     <row r="733">
       <c r="A733" s="2" t="n">
-        <v>313</v>
+        <v>341</v>
       </c>
       <c r="B733" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】SK-II温和护肤洗面奶120g洁面洁净深层清洁控油保湿</t>
+          <t>【Clarins】娇韵诗焕颜弹力晚霜面霜50ml保湿提拉紧致滋润【5天内发货】</t>
         </is>
       </c>
       <c r="C733" s="2" t="inlineStr">
         <is>
-          <t>SKII女士洗面奶120g/支</t>
-        </is>
-      </c>
-      <c r="D733" s="2" t="inlineStr">
-        <is>
-          <t>354.0</t>
-        </is>
-      </c>
-      <c r="E733" s="2" t="inlineStr">
-        <is>
-          <t>220.0</t>
-        </is>
+          <t>Clarins娇韵诗焕颜紧致晚霜50ml</t>
+        </is>
+      </c>
+      <c r="D733" s="2" t="inlineStr"/>
+      <c r="E733" s="2" t="n">
+        <v>298</v>
       </c>
       <c r="F733" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G733" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G733" s="2" t="inlineStr"/>
       <c r="H733" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -28792,27 +28628,23 @@
     </row>
     <row r="734">
       <c r="A734" s="2" t="n">
-        <v>314</v>
+        <v>342</v>
       </c>
       <c r="B734" s="2" t="inlineStr">
         <is>
-          <t>【SK-II】前男友面膜贴片面膜单片*10组合保湿补水修复抗衰老美白【5天内发货】</t>
+          <t>【雅诗兰黛】多效智妍面霜(清爽版)75ml双支</t>
         </is>
       </c>
       <c r="C734" s="2" t="inlineStr">
         <is>
-          <t>SK-II前男友面膜10片装</t>
-        </is>
-      </c>
-      <c r="D734" s="2" t="inlineStr">
-        <is>
-          <t>699.0</t>
-        </is>
-      </c>
-      <c r="E734" s="2" t="inlineStr">
-        <is>
-          <t>494.0</t>
-        </is>
+          <t>雅诗兰黛多效智妍乳霜75ml清爽</t>
+        </is>
+      </c>
+      <c r="D734" s="2" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E734" s="2" t="n">
+        <v>907</v>
       </c>
       <c r="F734" s="2" t="inlineStr">
         <is>
@@ -28821,45 +28653,35 @@
       </c>
       <c r="G734" s="2" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H734" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I734" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I734" s="2" t="inlineStr"/>
       <c r="J734" s="2" t="inlineStr"/>
       <c r="K734" s="2" t="inlineStr"/>
     </row>
     <row r="735">
       <c r="A735" s="2" t="n">
-        <v>314</v>
+        <v>343</v>
       </c>
       <c r="B735" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】SK2前男友面膜10片装焕润嫩肤贴片女友送礼奢护礼盒</t>
+          <t>【梅森马吉拉】慵懒周末身体乳200ml润肤乳保湿补水</t>
         </is>
       </c>
       <c r="C735" s="2" t="inlineStr">
         <is>
-          <t>SK-II前男友面膜10片装</t>
-        </is>
-      </c>
-      <c r="D735" s="2" t="inlineStr">
-        <is>
-          <t>998.0</t>
-        </is>
-      </c>
-      <c r="E735" s="2" t="inlineStr">
-        <is>
-          <t>695.0</t>
-        </is>
+          <t>马丁马吉拉慵懒周末身体乳200ml</t>
+        </is>
+      </c>
+      <c r="D735" s="2" t="inlineStr"/>
+      <c r="E735" s="2" t="n">
+        <v>209</v>
       </c>
       <c r="F735" s="2" t="inlineStr">
         <is>
@@ -28868,7 +28690,7 @@
       </c>
       <c r="G735" s="2" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="H735" s="2" t="inlineStr">
@@ -28882,36 +28704,32 @@
     </row>
     <row r="736">
       <c r="A736" s="2" t="n">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="B736" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】SK2前男友面膜10片装焕润嫩肤贴片女友送礼奢护礼盒</t>
+          <t>【正品行货】兰蔻新款持妆粉底液30ml PO-01</t>
         </is>
       </c>
       <c r="C736" s="2" t="inlineStr">
         <is>
-          <t>SK-II前男友面膜10片装</t>
-        </is>
-      </c>
-      <c r="D736" s="2" t="inlineStr">
-        <is>
-          <t>998.0</t>
-        </is>
-      </c>
-      <c r="E736" s="2" t="inlineStr">
-        <is>
-          <t>695.0</t>
-        </is>
+          <t>兰蔻养肤水粉底液 PO-01 30ml</t>
+        </is>
+      </c>
+      <c r="D736" s="2" t="n">
+        <v>259</v>
+      </c>
+      <c r="E736" s="2" t="n">
+        <v>188</v>
       </c>
       <c r="F736" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G736" s="2" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="H736" s="2" t="inlineStr">
@@ -28925,38 +28743,28 @@
     </row>
     <row r="737">
       <c r="A737" s="2" t="n">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="B737" s="2" t="inlineStr">
         <is>
-          <t>【SK-II】护肤面膜10片/盒 补水舒缓</t>
+          <t>【Kiehl's】科颜氏男士保湿乳液125ml活力清爽控油补水收缩毛孔送男友</t>
         </is>
       </c>
       <c r="C737" s="2" t="inlineStr">
         <is>
-          <t>SK-II前男友面膜10片装</t>
-        </is>
-      </c>
-      <c r="D737" s="2" t="inlineStr">
-        <is>
-          <t>699.0</t>
-        </is>
-      </c>
-      <c r="E737" s="2" t="inlineStr">
-        <is>
-          <t>545.0</t>
-        </is>
+          <t>科颜氏男士乳液125ml</t>
+        </is>
+      </c>
+      <c r="D737" s="2" t="inlineStr"/>
+      <c r="E737" s="2" t="n">
+        <v>106</v>
       </c>
       <c r="F737" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G737" s="2" t="inlineStr">
-        <is>
-          <t>2025-05-01</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G737" s="2" t="inlineStr"/>
       <c r="H737" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -28968,27 +28776,23 @@
     </row>
     <row r="738">
       <c r="A738" s="2" t="n">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="B738" s="2" t="inlineStr">
         <is>
-          <t>【SK-II】前男友面膜贴片面膜单片*10组合保湿补水修复抗衰老美白【5天内发货】</t>
+          <t>【科颜氏】男士保湿乳液125ml补水保湿清爽改善暗沉</t>
         </is>
       </c>
       <c r="C738" s="2" t="inlineStr">
         <is>
-          <t>SK-II前男友面膜10片装</t>
-        </is>
-      </c>
-      <c r="D738" s="2" t="inlineStr">
-        <is>
-          <t>699.0</t>
-        </is>
-      </c>
-      <c r="E738" s="2" t="inlineStr">
-        <is>
-          <t>494.0</t>
-        </is>
+          <t>科颜氏男士乳液125ml</t>
+        </is>
+      </c>
+      <c r="D738" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="E738" s="2" t="n">
+        <v>145</v>
       </c>
       <c r="F738" s="2" t="inlineStr">
         <is>
@@ -28997,105 +28801,77 @@
       </c>
       <c r="G738" s="2" t="inlineStr">
         <is>
-          <t>2024-07-31</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="H738" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I738" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I738" s="2" t="inlineStr"/>
       <c r="J738" s="2" t="inlineStr"/>
       <c r="K738" s="2" t="inlineStr"/>
     </row>
     <row r="739">
       <c r="A739" s="2" t="n">
-        <v>316</v>
+        <v>345</v>
       </c>
       <c r="B739" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】SKII赋能焕采精华霜大红瓶面霜滋润轻盈保湿紧致养肤</t>
+          <t>【科颜氏】男士保湿乳液125ml补水保湿清爽改善暗沉礼物</t>
         </is>
       </c>
       <c r="C739" s="2" t="inlineStr">
         <is>
-          <t>SKII大红瓶面霜80g清爽</t>
-        </is>
-      </c>
-      <c r="D739" s="2" t="inlineStr">
-        <is>
-          <t>1048.0</t>
-        </is>
-      </c>
-      <c r="E739" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
+          <t>科颜氏男士乳液125ml</t>
+        </is>
+      </c>
+      <c r="D739" s="2" t="inlineStr"/>
+      <c r="E739" s="2" t="n">
+        <v>122</v>
       </c>
       <c r="F739" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G739" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-09</t>
-        </is>
-      </c>
+      <c r="G739" s="2" t="inlineStr"/>
       <c r="H739" s="2" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
       <c r="I739" s="2" t="inlineStr"/>
-      <c r="J739" s="2" t="inlineStr">
-        <is>
-          <t>已选择： 大红瓶经典面霜滋润版80g</t>
-        </is>
-      </c>
-      <c r="K739" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
+      <c r="J739" s="2" t="inlineStr"/>
+      <c r="K739" s="2" t="inlineStr"/>
     </row>
     <row r="740">
       <c r="A740" s="2" t="n">
-        <v>316</v>
+        <v>345</v>
       </c>
       <c r="B740" s="2" t="inlineStr">
         <is>
-          <t>【SK-II】大红瓶面霜80g滋养保湿紧致肌肤清爽款</t>
+          <t>【品牌好评322.1万+条】Kiehl's/科颜氏男士活力保湿乳液125ml补水保湿润肤改善干燥</t>
         </is>
       </c>
       <c r="C740" s="2" t="inlineStr">
         <is>
-          <t>SKII大红瓶面霜80g清爽</t>
-        </is>
-      </c>
-      <c r="D740" s="2" t="inlineStr">
-        <is>
-          <t>868.0</t>
-        </is>
-      </c>
-      <c r="E740" s="2" t="inlineStr">
-        <is>
-          <t>577.0</t>
-        </is>
+          <t>科颜氏男士乳液125ml</t>
+        </is>
+      </c>
+      <c r="D740" s="2" t="inlineStr"/>
+      <c r="E740" s="2" t="n">
+        <v>169</v>
       </c>
       <c r="F740" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G740" s="2" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="H740" s="2" t="inlineStr">
@@ -29109,27 +28885,23 @@
     </row>
     <row r="741">
       <c r="A741" s="2" t="n">
-        <v>316</v>
+        <v>346</v>
       </c>
       <c r="B741" s="2" t="inlineStr">
         <is>
-          <t>SKII大红瓶面霜80g滋润版保湿紧致肌肤</t>
+          <t>【正品行货】科颜氏Kiehl高保湿清爽凝霜滋润补水果冻面霜50ml</t>
         </is>
       </c>
       <c r="C741" s="2" t="inlineStr">
         <is>
-          <t>SKII大红瓶面霜80g清爽</t>
-        </is>
-      </c>
-      <c r="D741" s="2" t="inlineStr">
-        <is>
-          <t>870.0</t>
-        </is>
-      </c>
-      <c r="E741" s="2" t="inlineStr">
-        <is>
-          <t>643.0</t>
-        </is>
+          <t>科颜氏果冻清爽高保湿霜50ml/瓶</t>
+        </is>
+      </c>
+      <c r="D741" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="E741" s="2" t="n">
+        <v>120.8</v>
       </c>
       <c r="F741" s="2" t="inlineStr">
         <is>
@@ -29138,7 +28910,7 @@
       </c>
       <c r="G741" s="2" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="H741" s="2" t="inlineStr">
@@ -29152,27 +28924,23 @@
     </row>
     <row r="742">
       <c r="A742" s="2" t="n">
-        <v>316</v>
+        <v>347</v>
       </c>
       <c r="B742" s="2" t="inlineStr">
         <is>
-          <t>【SK-II】大红瓶面霜80g 滋润版</t>
+          <t>【娇韵诗】双萃焕活修护精华露100ml清爽九代补水</t>
         </is>
       </c>
       <c r="C742" s="2" t="inlineStr">
         <is>
-          <t>SKII大红瓶面霜80g清爽</t>
-        </is>
-      </c>
-      <c r="D742" s="2" t="inlineStr">
-        <is>
-          <t>879.0</t>
-        </is>
-      </c>
-      <c r="E742" s="2" t="inlineStr">
-        <is>
-          <t>679.0</t>
-        </is>
+          <t>娇韵诗第九代全新双萃焕活修护精华 100ML</t>
+        </is>
+      </c>
+      <c r="D742" s="2" t="n">
+        <v>899</v>
+      </c>
+      <c r="E742" s="2" t="n">
+        <v>715</v>
       </c>
       <c r="F742" s="2" t="inlineStr">
         <is>
@@ -29181,7 +28949,7 @@
       </c>
       <c r="G742" s="2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="H742" s="2" t="inlineStr">
@@ -29195,23 +28963,21 @@
     </row>
     <row r="743">
       <c r="A743" s="2" t="n">
-        <v>317</v>
+        <v>348</v>
       </c>
       <c r="B743" s="2" t="inlineStr">
         <is>
-          <t>【NARS】空气唇釉#684GIPSY玫瑰豆沙色哑光7.5ml(23.6产</t>
+          <t>【跨境原装】安耐晒防晒霜安热沙隔离小金瓶90ml防水防汗资生堂女</t>
         </is>
       </c>
       <c r="C743" s="2" t="inlineStr">
         <is>
-          <t>NARS空气唇釉GIPSY吉普赛</t>
+          <t>资生堂安耐晒90ml</t>
         </is>
       </c>
       <c r="D743" s="2" t="inlineStr"/>
-      <c r="E743" s="2" t="inlineStr">
-        <is>
-          <t>129.0</t>
-        </is>
+      <c r="E743" s="2" t="n">
+        <v>119</v>
       </c>
       <c r="F743" s="2" t="inlineStr">
         <is>
@@ -29220,7 +28986,7 @@
       </c>
       <c r="G743" s="2" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="H743" s="2" t="inlineStr">
@@ -29234,23 +29000,23 @@
     </row>
     <row r="744">
       <c r="A744" s="2" t="n">
-        <v>317</v>
+        <v>348</v>
       </c>
       <c r="B744" s="2" t="inlineStr">
         <is>
-          <t>【NARS】NARS娜斯空气唇釉#037 #361 #360 #684 7.5ml/支</t>
+          <t>【跨境原装】资生堂安耐晒防晒霜清爽不油面部防紫外线敏感肌正品</t>
         </is>
       </c>
       <c r="C744" s="2" t="inlineStr">
         <is>
-          <t>NARS空气唇釉GIPSY吉普赛</t>
-        </is>
-      </c>
-      <c r="D744" s="2" t="inlineStr"/>
-      <c r="E744" s="2" t="inlineStr">
-        <is>
-          <t>69.8</t>
-        </is>
+          <t>资生堂安耐晒90ml</t>
+        </is>
+      </c>
+      <c r="D744" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="E744" s="2" t="n">
+        <v>127</v>
       </c>
       <c r="F744" s="2" t="inlineStr">
         <is>
@@ -29259,7 +29025,7 @@
       </c>
       <c r="G744" s="2" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="H744" s="2" t="inlineStr">
@@ -29270,41 +29036,41 @@
       <c r="I744" s="2" t="inlineStr"/>
       <c r="J744" s="2" t="inlineStr">
         <is>
-          <t>已选择： 吉普赛GIPSY#684 7.5mL</t>
-        </is>
-      </c>
-      <c r="K744" s="2" t="inlineStr">
-        <is>
-          <t>69.8</t>
-        </is>
+          <t>已选: 软管90ml [盒装版]防晒霜+绵羊乳霜6g</t>
+        </is>
+      </c>
+      <c r="K744" s="2" t="n">
+        <v>127</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" s="2" t="n">
-        <v>317</v>
+        <v>348</v>
       </c>
       <c r="B745" s="2" t="inlineStr">
         <is>
-          <t>【特价清仓】NARS纳斯唇釉空气柔雾唇霜7.5ml#352/360/361/684</t>
+          <t>【保税原装】资生堂安耐晒防晒霜安热沙防晒霜小金瓶防水防汗隔离</t>
         </is>
       </c>
       <c r="C745" s="2" t="inlineStr">
         <is>
-          <t>NARS空气唇釉GIPSY吉普赛</t>
+          <t>资生堂安耐晒90ml</t>
         </is>
       </c>
       <c r="D745" s="2" t="inlineStr"/>
-      <c r="E745" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
+      <c r="E745" s="2" t="n">
+        <v>115</v>
       </c>
       <c r="F745" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G745" s="2" t="inlineStr"/>
+      <c r="G745" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
       <c r="H745" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -29312,132 +29078,130 @@
       </c>
       <c r="I745" s="2" t="inlineStr">
         <is>
-          <t>品名相似不足(ratio=25.0%)</t>
+          <t>规格不匹配；规格匹配失败</t>
         </is>
       </c>
       <c r="J745" s="2" t="inlineStr">
         <is>
-          <t>已选择： 684 Gipsy 吉普赛玫瑰 7.5mL 【23年4月产】国际效期5年</t>
-        </is>
-      </c>
-      <c r="K745" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K745" s="2" t="inlineStr"/>
     </row>
     <row r="746">
       <c r="A746" s="2" t="n">
-        <v>317</v>
+        <v>348</v>
       </c>
       <c r="B746" s="2" t="inlineStr">
         <is>
-          <t>【特价清仓】NARS纳斯哑光唇釉空气柔雾唇霜#684 Gipsy吉普赛玫瑰</t>
+          <t>【保税原装】资生堂安耐晒防晒霜紫外线防水防汗防晒乳隔离霜正品</t>
         </is>
       </c>
       <c r="C746" s="2" t="inlineStr">
         <is>
-          <t>NARS空气唇釉GIPSY吉普赛</t>
-        </is>
-      </c>
-      <c r="D746" s="2" t="inlineStr">
-        <is>
-          <t>199.0</t>
-        </is>
-      </c>
-      <c r="E746" s="2" t="inlineStr">
-        <is>
-          <t>118.99</t>
-        </is>
+          <t>资生堂安耐晒90ml</t>
+        </is>
+      </c>
+      <c r="D746" s="2" t="inlineStr"/>
+      <c r="E746" s="2" t="n">
+        <v>164</v>
       </c>
       <c r="F746" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G746" s="2" t="inlineStr"/>
+      <c r="G746" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
       <c r="H746" s="2" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
       <c r="I746" s="2" t="inlineStr"/>
-      <c r="J746" s="2" t="inlineStr"/>
-      <c r="K746" s="2" t="inlineStr"/>
+      <c r="J746" s="2" t="inlineStr">
+        <is>
+          <t>已选: [原装保税]防晒霜90ml+面霜乳6g</t>
+        </is>
+      </c>
+      <c r="K746" s="2" t="n">
+        <v>164</v>
+      </c>
     </row>
     <row r="747">
       <c r="A747" s="2" t="n">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="B747" s="2" t="inlineStr">
         <is>
-          <t>【跨境原装】韩国whoo后天气丹华泫花献乳液110ml保湿淡纹正品</t>
+          <t>安热沙Anessa安耐晒防晒霜面部防晒男女军训防晒清爽防晒小金软管【6月18日发完】</t>
         </is>
       </c>
       <c r="C747" s="2" t="inlineStr">
         <is>
-          <t>后Whoo天气丹PRO乳110ML</t>
-        </is>
-      </c>
-      <c r="D747" s="2" t="inlineStr">
-        <is>
-          <t>255.0</t>
-        </is>
-      </c>
-      <c r="E747" s="2" t="inlineStr">
-        <is>
-          <t>245.0</t>
-        </is>
+          <t>安耐晒金钻高效防晒90ml</t>
+        </is>
+      </c>
+      <c r="D747" s="2" t="inlineStr"/>
+      <c r="E747" s="2" t="n">
+        <v>112.6</v>
       </c>
       <c r="F747" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G747" s="2" t="inlineStr">
-        <is>
-          <t>2025-02-18</t>
-        </is>
-      </c>
+      <c r="G747" s="2" t="inlineStr"/>
       <c r="H747" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I747" s="2" t="inlineStr"/>
-      <c r="J747" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I747" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J747" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K747" s="2" t="inlineStr"/>
     </row>
     <row r="748">
       <c r="A748" s="2" t="n">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="B748" s="2" t="inlineStr">
         <is>
-          <t>WHOO后天气丹水乳 华泫水150ML乳110ML保湿抗皱</t>
+          <t>【保税原装】安耐晒安热沙防晒霜90ml水润清爽防水防汗户外小金瓶</t>
         </is>
       </c>
       <c r="C748" s="2" t="inlineStr">
         <is>
-          <t>后Whoo天气丹PRO乳110ML</t>
-        </is>
-      </c>
-      <c r="D748" s="2" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="E748" s="2" t="inlineStr">
-        <is>
-          <t>472.9</t>
-        </is>
+          <t>安耐晒金钻高效防晒90ml</t>
+        </is>
+      </c>
+      <c r="D748" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="E748" s="2" t="n">
+        <v>147</v>
       </c>
       <c r="F748" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G748" s="2" t="inlineStr"/>
+      <c r="G748" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
       <c r="H748" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -29449,132 +29213,108 @@
     </row>
     <row r="749">
       <c r="A749" s="2" t="n">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="B749" s="2" t="inlineStr">
         <is>
-          <t>韩国thewhoo后黄金气垫粉底液21号#一正两替换自然遮瑕提亮</t>
+          <t>【20.9万人回购该品牌】ANESSA/安热沙/安耐晒小金瓶防晒霜60ML</t>
         </is>
       </c>
       <c r="C749" s="2" t="inlineStr">
         <is>
-          <t>后拱辰享美黄金气垫13G+替换装13G</t>
-        </is>
-      </c>
-      <c r="D749" s="2" t="inlineStr">
-        <is>
-          <t>222.0</t>
-        </is>
-      </c>
-      <c r="E749" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
+          <t>安耐晒金钻高效防晒90ml</t>
+        </is>
+      </c>
+      <c r="D749" s="2" t="inlineStr"/>
+      <c r="E749" s="2" t="n">
+        <v>130</v>
       </c>
       <c r="F749" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G749" s="2" t="inlineStr"/>
+      <c r="G749" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
       <c r="H749" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I749" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I749" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
       <c r="J749" s="2" t="inlineStr">
         <is>
-          <t>已选择： 后黄金气垫13g*3【21号】</t>
-        </is>
-      </c>
-      <c r="K749" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K749" s="2" t="inlineStr"/>
     </row>
     <row r="750">
       <c r="A750" s="2" t="n">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="B750" s="2" t="inlineStr">
         <is>
-          <t>【618狂欢购】彩棠面部综合盘4.0眼影修容腮红高光多功能一体化妆</t>
+          <t>雅诗兰黛樱花微精华原生液400ml 肌肤赋活保湿滋润提亮修护爽肤水【12天内发货】</t>
         </is>
       </c>
       <c r="C750" s="2" t="inlineStr">
         <is>
-          <t>TOMFORD幻魅四色眼影盘 #35 玫瑰晶石</t>
-        </is>
-      </c>
-      <c r="D750" s="2" t="inlineStr">
-        <is>
-          <t>94.87</t>
-        </is>
-      </c>
-      <c r="E750" s="2" t="inlineStr">
-        <is>
-          <t>72.5</t>
-        </is>
+          <t>雅诗兰黛樱花微精华原生液400ml</t>
+        </is>
+      </c>
+      <c r="D750" s="2" t="n">
+        <v>699</v>
+      </c>
+      <c r="E750" s="2" t="n">
+        <v>439</v>
       </c>
       <c r="F750" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G750" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G750" s="2" t="inlineStr"/>
       <c r="H750" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I750" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=22.2%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I750" s="2" t="inlineStr"/>
       <c r="J750" s="2" t="inlineStr"/>
       <c r="K750" s="2" t="inlineStr"/>
     </row>
     <row r="751">
       <c r="A751" s="2" t="n">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="B751" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】新版TOM FORD汤姆福特TF四色T壳眼影盘35#新色杏茶盘</t>
+          <t>【雅诗兰黛】樱花微精华原生液400ml肌肤赋活保湿滋润提亮修护爽肤水【5天内发货】</t>
         </is>
       </c>
       <c r="C751" s="2" t="inlineStr">
         <is>
-          <t>TOMFORD幻魅四色眼影盘 #35 玫瑰晶石</t>
-        </is>
-      </c>
-      <c r="D751" s="2" t="inlineStr">
-        <is>
-          <t>700.0</t>
-        </is>
-      </c>
-      <c r="E751" s="2" t="inlineStr">
-        <is>
-          <t>440.0</t>
-        </is>
+          <t>雅诗兰黛樱花微精华原生液400ml</t>
+        </is>
+      </c>
+      <c r="D751" s="2" t="inlineStr"/>
+      <c r="E751" s="2" t="n">
+        <v>445</v>
       </c>
       <c r="F751" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G751" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
+      <c r="G751" s="2" t="inlineStr"/>
       <c r="H751" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -29586,36 +29326,30 @@
     </row>
     <row r="752">
       <c r="A752" s="2" t="n">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="B752" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】NARS/娜斯四色眼影盘掌心盘圣保罗绝美温柔清透</t>
+          <t>【雅诗兰黛】樱花水微精华原生液补水保湿提亮肤色收缩毛孔湿敷精华水</t>
         </is>
       </c>
       <c r="C752" s="2" t="inlineStr">
         <is>
-          <t>TOMFORD幻魅四色眼影盘 #35 玫瑰晶石</t>
-        </is>
-      </c>
-      <c r="D752" s="2" t="inlineStr">
-        <is>
-          <t>380.0</t>
-        </is>
-      </c>
-      <c r="E752" s="2" t="inlineStr">
-        <is>
-          <t>236.0</t>
-        </is>
+          <t>雅诗兰黛樱花微精华原生液400ml</t>
+        </is>
+      </c>
+      <c r="D752" s="2" t="inlineStr"/>
+      <c r="E752" s="2" t="n">
+        <v>298</v>
       </c>
       <c r="F752" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G752" s="2" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H752" s="2" t="inlineStr">
@@ -29625,46 +29359,40 @@
       </c>
       <c r="I752" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配</t>
-        </is>
-      </c>
-      <c r="J752" s="2" t="inlineStr"/>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J752" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K752" s="2" t="inlineStr"/>
     </row>
     <row r="753">
       <c r="A753" s="2" t="n">
-        <v>321</v>
+        <v>351</v>
       </c>
       <c r="B753" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】SK-II光子小灯泡50ml美白护肤精华液淡斑提亮</t>
+          <t>【正品行货】YSL/圣罗兰口红小金条21复古红小黑条大牌杨树林哑光</t>
         </is>
       </c>
       <c r="C753" s="2" t="inlineStr">
         <is>
-          <t>SK-II小灯泡新版50ml</t>
-        </is>
-      </c>
-      <c r="D753" s="2" t="inlineStr">
-        <is>
-          <t>1213.0</t>
-        </is>
-      </c>
-      <c r="E753" s="2" t="inlineStr">
-        <is>
-          <t>825.0</t>
-        </is>
+          <t>圣罗兰小金条细管口红21号复古正红色</t>
+        </is>
+      </c>
+      <c r="D753" s="2" t="inlineStr"/>
+      <c r="E753" s="2" t="n">
+        <v>125</v>
       </c>
       <c r="F753" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G753" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-17</t>
-        </is>
-      </c>
+      <c r="G753" s="2" t="inlineStr"/>
       <c r="H753" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -29676,163 +29404,141 @@
     </row>
     <row r="754">
       <c r="A754" s="2" t="n">
-        <v>322</v>
+        <v>351</v>
       </c>
       <c r="B754" s="2" t="inlineStr">
         <is>
-          <t>SK-II/sk2/光蕴恒璨焕亮精华露新版光子小灯泡祛斑美白50ml正品</t>
+          <t>【正品行货】YSL/圣罗兰口红小金条 21复古红显白大牌正品礼盒装</t>
         </is>
       </c>
       <c r="C754" s="2" t="inlineStr">
         <is>
-          <t>SKII光子小灯泡75ml</t>
+          <t>圣罗兰小金条细管口红21号复古正红色</t>
         </is>
       </c>
       <c r="D754" s="2" t="inlineStr"/>
-      <c r="E754" s="2" t="inlineStr">
-        <is>
-          <t>1398</t>
-        </is>
+      <c r="E754" s="2" t="n">
+        <v>125</v>
       </c>
       <c r="F754" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G754" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-17</t>
-        </is>
-      </c>
+      <c r="G754" s="2" t="inlineStr"/>
       <c r="H754" s="2" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
       <c r="I754" s="2" t="inlineStr"/>
-      <c r="J754" s="2" t="inlineStr">
-        <is>
-          <t>已选择： 新版光子小灯泡75ml【正品保证】</t>
-        </is>
-      </c>
-      <c r="K754" s="2" t="inlineStr">
-        <is>
-          <t>1398</t>
-        </is>
-      </c>
+      <c r="J754" s="2" t="inlineStr"/>
+      <c r="K754" s="2" t="inlineStr"/>
     </row>
     <row r="755">
       <c r="A755" s="2" t="n">
-        <v>323</v>
+        <v>352</v>
       </c>
       <c r="B755" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】SKII氨基酸洗面奶护肤洁面乳120g温和控油清洁不刺激</t>
+          <t>芭比布朗清润舒盈新版卸妆油200ml/瓶 温和卸妆</t>
         </is>
       </c>
       <c r="C755" s="2" t="inlineStr">
         <is>
-          <t>SKII洁面油250ml</t>
-        </is>
-      </c>
-      <c r="D755" s="2" t="inlineStr">
-        <is>
-          <t>393.0</t>
-        </is>
-      </c>
-      <c r="E755" s="2" t="inlineStr">
-        <is>
-          <t>244.0</t>
-        </is>
+          <t>芭比布朗舒缓卸妆洁面油200ml</t>
+        </is>
+      </c>
+      <c r="D755" s="2" t="n">
+        <v>2691</v>
+      </c>
+      <c r="E755" s="2" t="n">
+        <v>269</v>
       </c>
       <c r="F755" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G755" s="2" t="inlineStr"/>
+      <c r="G755" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
       <c r="H755" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I755" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I755" s="2" t="inlineStr"/>
       <c r="J755" s="2" t="inlineStr"/>
       <c r="K755" s="2" t="inlineStr"/>
     </row>
     <row r="756">
       <c r="A756" s="2" t="n">
-        <v>323</v>
+        <v>352</v>
       </c>
       <c r="B756" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】SKII男士焕活保湿洁面洗面奶120g深层洁净控油清爽</t>
+          <t>芭比布朗清润舒盈新版卸妆油200ml 温和卸妆</t>
         </is>
       </c>
       <c r="C756" s="2" t="inlineStr">
         <is>
-          <t>SKII洁面油250ml</t>
-        </is>
-      </c>
-      <c r="D756" s="2" t="inlineStr">
-        <is>
-          <t>424.0</t>
-        </is>
-      </c>
-      <c r="E756" s="2" t="inlineStr">
-        <is>
-          <t>263.0</t>
-        </is>
+          <t>芭比布朗舒缓卸妆洁面油200ml</t>
+        </is>
+      </c>
+      <c r="D756" s="2" t="inlineStr"/>
+      <c r="E756" s="2" t="n">
+        <v>269</v>
       </c>
       <c r="F756" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G756" s="2" t="inlineStr"/>
+      <c r="G756" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
       <c r="H756" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I756" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I756" s="2" t="inlineStr"/>
       <c r="J756" s="2" t="inlineStr"/>
       <c r="K756" s="2" t="inlineStr"/>
     </row>
     <row r="757">
       <c r="A757" s="2" t="n">
-        <v>323</v>
+        <v>352</v>
       </c>
       <c r="B757" s="2" t="inlineStr">
         <is>
-          <t>【SK-II】护肤洁面油卸妆油250ml 卸妆洁面二合一深层清洁温和洁净【5天内发货】</t>
+          <t>两瓶 单品 芭比布朗清透舒盈卸妆油200ml/瓶</t>
         </is>
       </c>
       <c r="C757" s="2" t="inlineStr">
         <is>
-          <t>SKII洁面油250ml</t>
+          <t>芭比布朗舒缓卸妆洁面油200ml</t>
         </is>
       </c>
       <c r="D757" s="2" t="inlineStr"/>
-      <c r="E757" s="2" t="inlineStr">
-        <is>
-          <t>299.0</t>
-        </is>
+      <c r="E757" s="2" t="n">
+        <v>517</v>
       </c>
       <c r="F757" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G757" s="2" t="inlineStr"/>
+      <c r="G757" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
       <c r="H757" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -29844,23 +29550,23 @@
     </row>
     <row r="758">
       <c r="A758" s="2" t="n">
-        <v>323</v>
+        <v>353</v>
       </c>
       <c r="B758" s="2" t="inlineStr">
         <is>
-          <t>【SK-II】护肤洁面油250ml卸妆油温和洁净深层清洁控油【5天内发货】</t>
+          <t>【海外直采】顺丰Clarins娇韵诗第九代双萃赋活精华露100ml</t>
         </is>
       </c>
       <c r="C758" s="2" t="inlineStr">
         <is>
-          <t>SKII洁面油250ml</t>
-        </is>
-      </c>
-      <c r="D758" s="2" t="inlineStr"/>
-      <c r="E758" s="2" t="inlineStr">
-        <is>
-          <t>499.0</t>
-        </is>
+          <t>娇韵诗双萃焕活修护精华露100ml</t>
+        </is>
+      </c>
+      <c r="D758" s="2" t="n">
+        <v>999</v>
+      </c>
+      <c r="E758" s="2" t="n">
+        <v>747</v>
       </c>
       <c r="F758" s="2" t="inlineStr">
         <is>
@@ -29869,7 +29575,7 @@
       </c>
       <c r="G758" s="2" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="H758" s="2" t="inlineStr">
@@ -29883,30 +29589,34 @@
     </row>
     <row r="759">
       <c r="A759" s="2" t="n">
-        <v>323</v>
+        <v>353</v>
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>正品SK-II护肤洁面油卸妆油250ml卸妆洁面二合一深层清洁温和洁净【5天内发货】</t>
+          <t>【娇韵诗】双萃焕活修护精华露100ml清爽九代补水</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
         <is>
-          <t>SKII洁面油250ml</t>
-        </is>
-      </c>
-      <c r="D759" s="2" t="inlineStr"/>
-      <c r="E759" s="2" t="inlineStr">
-        <is>
-          <t>298.0</t>
-        </is>
+          <t>娇韵诗双萃焕活修护精华露100ml</t>
+        </is>
+      </c>
+      <c r="D759" s="2" t="n">
+        <v>899</v>
+      </c>
+      <c r="E759" s="2" t="n">
+        <v>715</v>
       </c>
       <c r="F759" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G759" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G759" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
       <c r="H759" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -29918,122 +29628,106 @@
     </row>
     <row r="760">
       <c r="A760" s="2" t="n">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="B760" s="2" t="inlineStr">
         <is>
-          <t>【Givenchy】纪梵希高定丝绒唇釉 N51 N15  N36 N37</t>
+          <t>【阿玛尼】权利红黑管唇膏410瞩目绯红3.1g 显白提气色口红【26年8月</t>
         </is>
       </c>
       <c r="C760" s="2" t="inlineStr">
         <is>
-          <t>纪梵希粉丝绒N37</t>
-        </is>
-      </c>
-      <c r="D760" s="2" t="inlineStr"/>
-      <c r="E760" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
+          <t>阿玛尼权力口红410色</t>
+        </is>
+      </c>
+      <c r="D760" s="2" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="E760" s="2" t="n">
+        <v>61</v>
       </c>
       <c r="F760" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G760" s="2" t="inlineStr">
-        <is>
-          <t>2023-06-01</t>
-        </is>
-      </c>
+      <c r="G760" s="2" t="inlineStr"/>
       <c r="H760" s="2" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
       <c r="I760" s="2" t="inlineStr"/>
-      <c r="J760" s="2" t="inlineStr">
-        <is>
-          <t>已选择： 复古丝绒 N37 6.5mL</t>
-        </is>
-      </c>
-      <c r="K760" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
+      <c r="J760" s="2" t="inlineStr"/>
+      <c r="K760" s="2" t="inlineStr"/>
     </row>
     <row r="761">
       <c r="A761" s="2" t="n">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="B761" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】YSL圣罗兰全新爱心唇釉610 416 622 440限定浮雕黑管</t>
+          <t>【正品行货】YSL圣罗兰黑金浮雕方管大牌口红R1966杨树林唇膏正品</t>
         </is>
       </c>
       <c r="C761" s="2" t="inlineStr">
         <is>
-          <t>圣罗兰爱心黑管唇釉440</t>
+          <t>YSL圣罗兰黑金方管13色</t>
         </is>
       </c>
       <c r="D761" s="2" t="inlineStr"/>
-      <c r="E761" s="2" t="inlineStr">
-        <is>
-          <t>130.4</t>
-        </is>
+      <c r="E761" s="2" t="n">
+        <v>128</v>
       </c>
       <c r="F761" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G761" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
+      <c r="G761" s="2" t="inlineStr"/>
       <c r="H761" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I761" s="2" t="inlineStr"/>
-      <c r="J761" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I761" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J761" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K761" s="2" t="inlineStr"/>
     </row>
     <row r="762">
       <c r="A762" s="2" t="n">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="B762" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】YSL圣罗兰全新爱心唇釉440 610 416 622限定浮雕黑管</t>
+          <t>【正品行货】YSL圣罗兰黑金方管口红 釉光新品10/06/11 裸色温柔</t>
         </is>
       </c>
       <c r="C762" s="2" t="inlineStr">
         <is>
-          <t>圣罗兰爱心黑管唇釉440</t>
-        </is>
-      </c>
-      <c r="D762" s="2" t="inlineStr">
-        <is>
-          <t>235.0</t>
-        </is>
-      </c>
-      <c r="E762" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
+          <t>YSL圣罗兰黑金方管13色</t>
+        </is>
+      </c>
+      <c r="D762" s="2" t="inlineStr"/>
+      <c r="E762" s="2" t="n">
+        <v>367</v>
       </c>
       <c r="F762" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G762" s="2" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2023-12-30</t>
         </is>
       </c>
       <c r="H762" s="2" t="inlineStr">
@@ -30044,77 +29738,73 @@
       <c r="I762" s="2" t="inlineStr"/>
       <c r="J762" s="2" t="inlineStr">
         <is>
-          <t>已选择： 440 野玫瑰 5.5mL</t>
-        </is>
-      </c>
-      <c r="K762" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
+          <t>已选择： 推荐#13-偏执</t>
+        </is>
+      </c>
+      <c r="K762" s="2" t="n">
+        <v>367</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" s="2" t="n">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="B763" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】YSL/圣罗兰全新黑管唇釉440爱心限量版</t>
+          <t>【正品行货】ysl/圣罗兰大牌口红nm裸缪斯黑金浮雕方管大牌礼盒装</t>
         </is>
       </c>
       <c r="C763" s="2" t="inlineStr">
         <is>
-          <t>圣罗兰爱心黑管唇釉440</t>
+          <t>YSL圣罗兰黑金方管13色</t>
         </is>
       </c>
       <c r="D763" s="2" t="inlineStr"/>
-      <c r="E763" s="2" t="inlineStr">
-        <is>
-          <t>143.4</t>
-        </is>
+      <c r="E763" s="2" t="n">
+        <v>128</v>
       </c>
       <c r="F763" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G763" s="2" t="inlineStr">
-        <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
+      <c r="G763" s="2" t="inlineStr"/>
       <c r="H763" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I763" s="2" t="inlineStr"/>
-      <c r="J763" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I763" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J763" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K763" s="2" t="inlineStr"/>
     </row>
     <row r="764">
       <c r="A764" s="2" t="n">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="B764" s="2" t="inlineStr">
         <is>
-          <t>【YSL】圣罗兰爱心唇釉镜面416/622/440/610/620/234口红节日生日礼物【5天内发货】</t>
+          <t>【正品行货】YSL圣罗兰全新爱心唇釉440 610 416 622限定浮雕黑管</t>
         </is>
       </c>
       <c r="C764" s="2" t="inlineStr">
         <is>
-          <t>圣罗兰爱心黑管唇釉440</t>
-        </is>
-      </c>
-      <c r="D764" s="2" t="inlineStr">
-        <is>
-          <t>239.0</t>
-        </is>
-      </c>
-      <c r="E764" s="2" t="inlineStr">
-        <is>
-          <t>146.0</t>
-        </is>
+          <t>YSL圣罗兰黑金方管14色</t>
+        </is>
+      </c>
+      <c r="D764" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="E764" s="2" t="n">
+        <v>143.4</v>
       </c>
       <c r="F764" s="2" t="inlineStr">
         <is>
@@ -30123,213 +29813,215 @@
       </c>
       <c r="G764" s="2" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="H764" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I764" s="2" t="inlineStr"/>
-      <c r="J764" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I764" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J764" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K764" s="2" t="inlineStr"/>
     </row>
     <row r="765">
       <c r="A765" s="2" t="n">
-        <v>326</v>
+        <v>356</v>
       </c>
       <c r="B765" s="2" t="inlineStr">
         <is>
-          <t>两支 单品 雅诗兰黛新款红石榴洗面奶125ml</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="C765" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴洁面125ml两支装</t>
-        </is>
-      </c>
-      <c r="D765" s="2" t="inlineStr">
-        <is>
-          <t>299.0</t>
-        </is>
-      </c>
-      <c r="E765" s="2" t="inlineStr">
-        <is>
-          <t>192.5</t>
-        </is>
+          <t>YSL圣罗兰黑金方管14色</t>
+        </is>
+      </c>
+      <c r="D765" s="2" t="inlineStr"/>
+      <c r="E765" s="2" t="n">
+        <v>59.9</v>
       </c>
       <c r="F765" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G765" s="2" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2023-03-29</t>
         </is>
       </c>
       <c r="H765" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I765" s="2" t="inlineStr"/>
-      <c r="J765" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I765" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J765" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K765" s="2" t="inlineStr"/>
     </row>
     <row r="766">
       <c r="A766" s="2" t="n">
-        <v>326</v>
+        <v>356</v>
       </c>
       <c r="B766" s="2" t="inlineStr">
         <is>
-          <t>【雅诗兰黛】红石榴洁面新款125ml 清洁保湿洁面乳</t>
+          <t>【正品行货】YSL圣罗兰黑金浮雕方管大牌口红R1966杨树林唇膏正品</t>
         </is>
       </c>
       <c r="C766" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴洁面125ml两支装</t>
-        </is>
-      </c>
-      <c r="D766" s="2" t="inlineStr">
-        <is>
-          <t>158.0</t>
-        </is>
-      </c>
-      <c r="E766" s="2" t="inlineStr">
-        <is>
-          <t>98.9</t>
-        </is>
+          <t>YSL圣罗兰黑金方管14色</t>
+        </is>
+      </c>
+      <c r="D766" s="2" t="inlineStr"/>
+      <c r="E766" s="2" t="n">
+        <v>128</v>
       </c>
       <c r="F766" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G766" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G766" s="2" t="inlineStr"/>
       <c r="H766" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I766" s="2" t="inlineStr"/>
-      <c r="J766" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I766" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J766" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K766" s="2" t="inlineStr"/>
     </row>
     <row r="767">
       <c r="A767" s="2" t="n">
-        <v>327</v>
+        <v>356</v>
       </c>
       <c r="B767" s="2" t="inlineStr">
         <is>
-          <t>【雅诗兰黛】新款红石榴滋润精华水200ml保湿补水</t>
+          <t>【正品行货】YSL圣罗兰全新黑金方管口红 缎光质地显白</t>
         </is>
       </c>
       <c r="C767" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴水200ml两支装</t>
-        </is>
-      </c>
-      <c r="D767" s="2" t="inlineStr">
-        <is>
-          <t>259.0</t>
-        </is>
-      </c>
-      <c r="E767" s="2" t="inlineStr">
-        <is>
-          <t>158.84</t>
-        </is>
+          <t>YSL圣罗兰黑金方管14色</t>
+        </is>
+      </c>
+      <c r="D767" s="2" t="n">
+        <v>410</v>
+      </c>
+      <c r="E767" s="2" t="n">
+        <v>295.2</v>
       </c>
       <c r="F767" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G767" s="2" t="inlineStr">
-        <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
+      <c r="G767" s="2" t="inlineStr"/>
       <c r="H767" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I767" s="2" t="inlineStr"/>
-      <c r="J767" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I767" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J767" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K767" s="2" t="inlineStr"/>
     </row>
     <row r="768">
       <c r="A768" s="2" t="n">
-        <v>327</v>
+        <v>356</v>
       </c>
       <c r="B768" s="2" t="inlineStr">
         <is>
-          <t>【雅诗兰黛】新款红石榴滋润精华水200ml保湿补水</t>
+          <t>【正品行货】圣罗兰/YSL方管口红黑金浮雕NM裸缪斯大牌正品礼盒装</t>
         </is>
       </c>
       <c r="C768" s="2" t="inlineStr">
         <is>
-          <t>雅诗兰黛红石榴水200ml两支装</t>
-        </is>
-      </c>
-      <c r="D768" s="2" t="inlineStr">
-        <is>
-          <t>234.0</t>
-        </is>
-      </c>
-      <c r="E768" s="2" t="inlineStr">
-        <is>
-          <t>143.15</t>
-        </is>
+          <t>YSL圣罗兰黑金方管14色</t>
+        </is>
+      </c>
+      <c r="D768" s="2" t="inlineStr"/>
+      <c r="E768" s="2" t="n">
+        <v>128</v>
       </c>
       <c r="F768" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G768" s="2" t="inlineStr">
-        <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G768" s="2" t="inlineStr"/>
       <c r="H768" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I768" s="2" t="inlineStr"/>
-      <c r="J768" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I768" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J768" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K768" s="2" t="inlineStr"/>
     </row>
     <row r="769">
       <c r="A769" s="2" t="n">
-        <v>328</v>
+        <v>357</v>
       </c>
       <c r="B769" s="2" t="inlineStr">
         <is>
-          <t>【SK-II】小银瓶精华液50ml美白淡斑精华露护肤品送女友生日礼物【5天内发货】</t>
+          <t>【正品行货】YSL圣罗兰全新爱心唇釉440 610 416 622限定浮雕黑管</t>
         </is>
       </c>
       <c r="C769" s="2" t="inlineStr">
         <is>
-          <t>SK2小银瓶50ml两瓶装</t>
-        </is>
-      </c>
-      <c r="D769" s="2" t="inlineStr">
-        <is>
-          <t>1218.0</t>
-        </is>
-      </c>
-      <c r="E769" s="2" t="inlineStr">
-        <is>
-          <t>775.0</t>
-        </is>
+          <t>YSL圣罗兰黑金方管1968</t>
+        </is>
+      </c>
+      <c r="D769" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="E769" s="2" t="n">
+        <v>143.4</v>
       </c>
       <c r="F769" s="2" t="inlineStr">
         <is>
@@ -30338,84 +30030,92 @@
       </c>
       <c r="G769" s="2" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="H769" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I769" s="2" t="inlineStr"/>
-      <c r="J769" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I769" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J769" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K769" s="2" t="inlineStr"/>
     </row>
     <row r="770">
       <c r="A770" s="2" t="n">
-        <v>328</v>
+        <v>357</v>
       </c>
       <c r="B770" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】SKII小银瓶肌因光蕴淡斑精华露50ml提亮淡斑淡痘印</t>
+          <t>【正品行货】YSL/圣罗兰全新黑管唇釉610 416 442 443爱心限量版</t>
         </is>
       </c>
       <c r="C770" s="2" t="inlineStr">
         <is>
-          <t>SK2小银瓶50ml两瓶装</t>
-        </is>
-      </c>
-      <c r="D770" s="2" t="inlineStr">
-        <is>
-          <t>1300.0</t>
-        </is>
-      </c>
-      <c r="E770" s="2" t="inlineStr">
-        <is>
-          <t>782.0</t>
-        </is>
+          <t>YSL圣罗兰黑金方管1968</t>
+        </is>
+      </c>
+      <c r="D770" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="E770" s="2" t="n">
+        <v>146.2</v>
       </c>
       <c r="F770" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G770" s="2" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="H770" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I770" s="2" t="inlineStr"/>
-      <c r="J770" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I770" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J770" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K770" s="2" t="inlineStr"/>
     </row>
     <row r="771">
       <c r="A771" s="2" t="n">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="B771" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】SKII赋能焕采精华霜大红瓶面霜滋润轻盈保湿紧致养肤</t>
+          <t>【正品行货】YSL圣罗兰口红1966小金条314小黑条杨树林大牌正品</t>
         </is>
       </c>
       <c r="C771" s="2" t="inlineStr">
         <is>
-          <t>SK2大红瓶滋润面霜50g</t>
-        </is>
-      </c>
-      <c r="D771" s="2" t="inlineStr">
-        <is>
-          <t>1048.0</t>
-        </is>
-      </c>
-      <c r="E771" s="2" t="inlineStr">
-        <is>
-          <t>692.0</t>
-        </is>
+          <t>YSL圣罗兰黑金方管1968</t>
+        </is>
+      </c>
+      <c r="D771" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="E771" s="2" t="n">
+        <v>170.8</v>
       </c>
       <c r="F771" s="2" t="inlineStr">
         <is>
@@ -30424,7 +30124,7 @@
       </c>
       <c r="G771" s="2" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H771" s="2" t="inlineStr">
@@ -30434,35 +30134,35 @@
       </c>
       <c r="I771" s="2" t="inlineStr">
         <is>
-          <t>规格不匹配</t>
-        </is>
-      </c>
-      <c r="J771" s="2" t="inlineStr"/>
+          <t>规格不匹配；品名相似不足(ratio=25.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J771" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K771" s="2" t="inlineStr"/>
     </row>
     <row r="772">
       <c r="A772" s="2" t="n">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="B772" s="2" t="inlineStr">
         <is>
-          <t>【520礼物】SK-II大红瓶面霜50g限定礼盒紧致上扬保湿润提亮紧致</t>
+          <t>【正品行货】GUCCI古驰口红碎花25金管哑光滋润505大牌正品礼物</t>
         </is>
       </c>
       <c r="C772" s="2" t="inlineStr">
         <is>
-          <t>SK2大红瓶滋润面霜50g</t>
-        </is>
-      </c>
-      <c r="D772" s="2" t="inlineStr">
-        <is>
-          <t>998.0</t>
-        </is>
-      </c>
-      <c r="E772" s="2" t="inlineStr">
-        <is>
-          <t>860.0</t>
-        </is>
+          <t>YSL圣罗兰黑金方管1968</t>
+        </is>
+      </c>
+      <c r="D772" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="E772" s="2" t="n">
+        <v>119</v>
       </c>
       <c r="F772" s="2" t="inlineStr">
         <is>
@@ -30471,99 +30171,5168 @@
       </c>
       <c r="G772" s="2" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="H772" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I772" s="2" t="inlineStr"/>
-      <c r="J772" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I772" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J772" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K772" s="2" t="inlineStr"/>
     </row>
     <row r="773">
       <c r="A773" s="2" t="n">
-        <v>330</v>
+        <v>357</v>
       </c>
       <c r="B773" s="2" t="inlineStr">
         <is>
-          <t>【Fresh】馥蕾诗西柚/睡莲/小苍兰香皂250g 深层清洁香皂</t>
+          <t>YSL/圣罗兰黑金浮雕方管釉光滋润质感唇膏口红06偏见高定礼盒包装</t>
         </is>
       </c>
       <c r="C773" s="2" t="inlineStr">
         <is>
-          <t>馥蕾诗西柚香皂</t>
-        </is>
-      </c>
-      <c r="D773" s="2" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="E773" s="2" t="inlineStr">
-        <is>
-          <t>99.5</t>
-        </is>
+          <t>YSL圣罗兰黑金方管1968</t>
+        </is>
+      </c>
+      <c r="D773" s="2" t="inlineStr"/>
+      <c r="E773" s="2" t="n">
+        <v>158</v>
       </c>
       <c r="F773" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G773" s="2" t="inlineStr">
-        <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
+      <c r="G773" s="2" t="inlineStr"/>
       <c r="H773" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I773" s="2" t="inlineStr"/>
-      <c r="J773" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I773" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J773" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K773" s="2" t="inlineStr"/>
     </row>
     <row r="774">
       <c r="A774" s="2" t="n">
-        <v>330</v>
+        <v>357</v>
       </c>
       <c r="B774" s="2" t="inlineStr">
         <is>
-          <t>【Fresh】馥蕾诗西柚香皂250g 深层清洁香皂</t>
+          <t>【YSL】圣罗兰黑金浮雕方管唇膏口红1968透视1971 14 11礼盒装520礼物</t>
         </is>
       </c>
       <c r="C774" s="2" t="inlineStr">
         <is>
-          <t>馥蕾诗西柚香皂</t>
+          <t>YSL圣罗兰黑金方管1968</t>
         </is>
       </c>
       <c r="D774" s="2" t="inlineStr"/>
-      <c r="E774" s="2" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
+      <c r="E774" s="2" t="n">
+        <v>158</v>
       </c>
       <c r="F774" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G774" s="2" t="inlineStr">
+      <c r="G774" s="2" t="inlineStr"/>
+      <c r="H774" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I774" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J774" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K774" s="2" t="inlineStr"/>
+    </row>
+    <row r="775">
+      <c r="A775" s="2" t="n">
+        <v>357</v>
+      </c>
+      <c r="B775" s="2" t="inlineStr">
+        <is>
+          <t>YSL/圣罗兰黑金浮雕方管釉光唇膏口红1971流言06裸缪斯NM1968正品</t>
+        </is>
+      </c>
+      <c r="C775" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰黑金方管1968</t>
+        </is>
+      </c>
+      <c r="D775" s="2" t="inlineStr"/>
+      <c r="E775" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="F775" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G775" s="2" t="inlineStr"/>
+      <c r="H775" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I775" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J775" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K775" s="2" t="inlineStr"/>
+    </row>
+    <row r="776">
+      <c r="A776" s="2" t="n">
+        <v>358</v>
+      </c>
+      <c r="B776" s="2" t="inlineStr">
+        <is>
+          <t>【YSL】圣罗兰啵啵丰盈唇冻光耀丰盈唇釉银盖日常通勤提升气色6ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C776" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰银管02色</t>
+        </is>
+      </c>
+      <c r="D776" s="2" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="E776" s="2" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="F776" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G776" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="H776" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I776" s="2" t="inlineStr"/>
+      <c r="J776" s="2" t="inlineStr">
+        <is>
+          <t>已选择： YSL啵啵唇冻#02 霜冻粉色 6mL</t>
+        </is>
+      </c>
+      <c r="K776" s="2" t="n">
+        <v>112.1</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="2" t="n">
+        <v>359</v>
+      </c>
+      <c r="B777" s="2" t="inlineStr">
+        <is>
+          <t>【Clinique】倩碧黄油滋润(有油)125ml</t>
+        </is>
+      </c>
+      <c r="C777" s="2" t="inlineStr">
+        <is>
+          <t>倩碧有油润肤乳125ml</t>
+        </is>
+      </c>
+      <c r="D777" s="2" t="n">
+        <v>121.3</v>
+      </c>
+      <c r="E777" s="2" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="F777" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G777" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="H777" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I777" s="2" t="inlineStr"/>
+      <c r="J777" s="2" t="inlineStr"/>
+      <c r="K777" s="2" t="inlineStr"/>
+    </row>
+    <row r="778">
+      <c r="A778" s="2" t="n">
+        <v>359</v>
+      </c>
+      <c r="B778" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】Clinique/倩碧黄油无油有油乳液保湿滋润滋养</t>
+        </is>
+      </c>
+      <c r="C778" s="2" t="inlineStr">
+        <is>
+          <t>倩碧有油润肤乳125ml</t>
+        </is>
+      </c>
+      <c r="D778" s="2" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="E778" s="2" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="F778" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G778" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="H778" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I778" s="2" t="inlineStr"/>
+      <c r="J778" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 倩碧黄油125ml无油</t>
+        </is>
+      </c>
+      <c r="K778" s="2" t="n">
+        <v>84.5</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="2" t="n">
+        <v>359</v>
+      </c>
+      <c r="B779" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】Clinique/倩碧黄油无油有油乳液保湿滋润滋养125ml*2</t>
+        </is>
+      </c>
+      <c r="C779" s="2" t="inlineStr">
+        <is>
+          <t>倩碧有油润肤乳125ml</t>
+        </is>
+      </c>
+      <c r="D779" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="E779" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="F779" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G779" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="H779" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I779" s="2" t="inlineStr"/>
+      <c r="J779" s="2" t="inlineStr"/>
+      <c r="K779" s="2" t="inlineStr"/>
+    </row>
+    <row r="780">
+      <c r="A780" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="B780" s="2" t="inlineStr">
+        <is>
+          <t>LA MER/海蓝之谜臻璨焕活精华油30ml抗老淡纹</t>
+        </is>
+      </c>
+      <c r="C780" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜 臻璨焕活精华油30ml （万能油）</t>
+        </is>
+      </c>
+      <c r="D780" s="2" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E780" s="2" t="n">
+        <v>999</v>
+      </c>
+      <c r="F780" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G780" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="H780" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I780" s="2" t="inlineStr"/>
+      <c r="J780" s="2" t="inlineStr"/>
+      <c r="K780" s="2" t="inlineStr"/>
+    </row>
+    <row r="781">
+      <c r="A781" s="2" t="n">
+        <v>361</v>
+      </c>
+      <c r="B781" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】大红瓶面霜80g滋养保湿紧致肌肤清爽款</t>
+        </is>
+      </c>
+      <c r="C781" s="2" t="inlineStr">
+        <is>
+          <t>SK2大红瓶清爽版80g</t>
+        </is>
+      </c>
+      <c r="D781" s="2" t="n">
+        <v>868</v>
+      </c>
+      <c r="E781" s="2" t="n">
+        <v>607</v>
+      </c>
+      <c r="F781" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G781" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H781" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I781" s="2" t="inlineStr"/>
+      <c r="J781" s="2" t="inlineStr"/>
+      <c r="K781" s="2" t="inlineStr"/>
+    </row>
+    <row r="782">
+      <c r="A782" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="B782" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】大红瓶面霜80g 滋润版</t>
+        </is>
+      </c>
+      <c r="C782" s="2" t="inlineStr">
+        <is>
+          <t>SK2大红瓶滋润版80g</t>
+        </is>
+      </c>
+      <c r="D782" s="2" t="n">
+        <v>879</v>
+      </c>
+      <c r="E782" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="F782" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G782" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="H782" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I782" s="2" t="inlineStr"/>
+      <c r="J782" s="2" t="inlineStr"/>
+      <c r="K782" s="2" t="inlineStr"/>
+    </row>
+    <row r="783">
+      <c r="A783" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="B783" s="2" t="inlineStr">
+        <is>
+          <t>SKII大红瓶面霜80g滋润版保湿紧致肌肤</t>
+        </is>
+      </c>
+      <c r="C783" s="2" t="inlineStr">
+        <is>
+          <t>SK2大红瓶滋润版80g</t>
+        </is>
+      </c>
+      <c r="D783" s="2" t="n">
+        <v>870</v>
+      </c>
+      <c r="E783" s="2" t="n">
+        <v>643</v>
+      </c>
+      <c r="F783" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G783" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="H783" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I783" s="2" t="inlineStr"/>
+      <c r="J783" s="2" t="inlineStr"/>
+      <c r="K783" s="2" t="inlineStr"/>
+    </row>
+    <row r="784">
+      <c r="A784" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="B784" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】大红瓶面霜80g滋养保湿紧致肌肤清爽款</t>
+        </is>
+      </c>
+      <c r="C784" s="2" t="inlineStr">
+        <is>
+          <t>SK2大红瓶滋润版80g</t>
+        </is>
+      </c>
+      <c r="D784" s="2" t="n">
+        <v>868</v>
+      </c>
+      <c r="E784" s="2" t="n">
+        <v>607</v>
+      </c>
+      <c r="F784" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G784" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H784" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I784" s="2" t="inlineStr"/>
+      <c r="J784" s="2" t="inlineStr"/>
+      <c r="K784" s="2" t="inlineStr"/>
+    </row>
+    <row r="785">
+      <c r="A785" s="2" t="n">
+        <v>363</v>
+      </c>
+      <c r="B785" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】新款红石榴滋润精华水200ml保湿补水</t>
+        </is>
+      </c>
+      <c r="C785" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛ESTEE LAUDER新版红石榴能量水清爽型 200ML</t>
+        </is>
+      </c>
+      <c r="D785" s="2" t="n">
+        <v>234</v>
+      </c>
+      <c r="E785" s="2" t="n">
+        <v>143.15</v>
+      </c>
+      <c r="F785" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G785" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="H785" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I785" s="2" t="inlineStr"/>
+      <c r="J785" s="2" t="inlineStr"/>
+      <c r="K785" s="2" t="inlineStr"/>
+    </row>
+    <row r="786">
+      <c r="A786" s="2" t="n">
+        <v>363</v>
+      </c>
+      <c r="B786" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】新款红石榴滋润精华水200ml保湿补水</t>
+        </is>
+      </c>
+      <c r="C786" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛ESTEE LAUDER新版红石榴能量水清爽型 200ML</t>
+        </is>
+      </c>
+      <c r="D786" s="2" t="n">
+        <v>259</v>
+      </c>
+      <c r="E786" s="2" t="n">
+        <v>158.84</v>
+      </c>
+      <c r="F786" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G786" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="H786" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I786" s="2" t="inlineStr"/>
+      <c r="J786" s="2" t="inlineStr"/>
+      <c r="K786" s="2" t="inlineStr"/>
+    </row>
+    <row r="787">
+      <c r="A787" s="2" t="n">
+        <v>364</v>
+      </c>
+      <c r="B787" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】SKII小银瓶肌因光蕴淡斑精华露50ml提亮淡斑淡痘印</t>
+        </is>
+      </c>
+      <c r="C787" s="2" t="inlineStr">
+        <is>
+          <t>SK-II 小银瓶精华50ML</t>
+        </is>
+      </c>
+      <c r="D787" s="2" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E787" s="2" t="n">
+        <v>782</v>
+      </c>
+      <c r="F787" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G787" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="H787" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I787" s="2" t="inlineStr"/>
+      <c r="J787" s="2" t="inlineStr"/>
+      <c r="K787" s="2" t="inlineStr"/>
+    </row>
+    <row r="788">
+      <c r="A788" s="2" t="n">
+        <v>364</v>
+      </c>
+      <c r="B788" s="2" t="inlineStr">
+        <is>
+          <t>【SK-II】小银瓶精华液50ml美白淡斑精华露护肤品送女友生日礼物【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C788" s="2" t="inlineStr">
+        <is>
+          <t>SK-II 小银瓶精华50ML</t>
+        </is>
+      </c>
+      <c r="D788" s="2" t="n">
+        <v>1218</v>
+      </c>
+      <c r="E788" s="2" t="n">
+        <v>775</v>
+      </c>
+      <c r="F788" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G788" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="H788" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I788" s="2" t="inlineStr"/>
+      <c r="J788" s="2" t="inlineStr"/>
+      <c r="K788" s="2" t="inlineStr"/>
+    </row>
+    <row r="789">
+      <c r="A789" s="2" t="n">
+        <v>365</v>
+      </c>
+      <c r="B789" s="2" t="inlineStr">
+        <is>
+          <t>正品行货|新版阿玛尼粉底液大师蓝标遮瑕持久不脱妆滋润干皮</t>
+        </is>
+      </c>
+      <c r="C789" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼大师粉底液2号</t>
+        </is>
+      </c>
+      <c r="D789" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="E789" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="F789" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G789" s="2" t="inlineStr">
         <is>
           <t>2024-07-01</t>
         </is>
       </c>
-      <c r="H774" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I774" s="2" t="inlineStr"/>
-      <c r="J774" s="2" t="inlineStr"/>
-      <c r="K774" s="2" t="inlineStr"/>
+      <c r="H789" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I789" s="2" t="inlineStr"/>
+      <c r="J789" s="2" t="inlineStr"/>
+      <c r="K789" s="2" t="inlineStr"/>
+    </row>
+    <row r="790">
+      <c r="A790" s="2" t="n">
+        <v>365</v>
+      </c>
+      <c r="B790" s="2" t="inlineStr">
+        <is>
+          <t>ARMANI阿玛尼蓝标大师造型紧颜粉底液2号色30ml持久遮瑕</t>
+        </is>
+      </c>
+      <c r="C790" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼大师粉底液2号</t>
+        </is>
+      </c>
+      <c r="D790" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="E790" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="F790" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G790" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="H790" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I790" s="2" t="inlineStr"/>
+      <c r="J790" s="2" t="inlineStr"/>
+      <c r="K790" s="2" t="inlineStr"/>
+    </row>
+    <row r="791">
+      <c r="A791" s="2" t="n">
+        <v>365</v>
+      </c>
+      <c r="B791" s="2" t="inlineStr">
+        <is>
+          <t>ARMANII阿玛尼大师蓝标粉底液2号30ml/瓶</t>
+        </is>
+      </c>
+      <c r="C791" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼大师粉底液2号</t>
+        </is>
+      </c>
+      <c r="D791" s="2" t="n">
+        <v>269</v>
+      </c>
+      <c r="E791" s="2" t="n">
+        <v>161.8</v>
+      </c>
+      <c r="F791" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G791" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="H791" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I791" s="2" t="inlineStr"/>
+      <c r="J791" s="2" t="inlineStr"/>
+      <c r="K791" s="2" t="inlineStr"/>
+    </row>
+    <row r="792">
+      <c r="A792" s="2" t="n">
+        <v>366</v>
+      </c>
+      <c r="B792" s="2" t="inlineStr">
+        <is>
+          <t>【Lancome】 兰蔻 美丽人生女士香水EDP 30/100ML</t>
+        </is>
+      </c>
+      <c r="C792" s="2" t="inlineStr">
+        <is>
+          <t>Lancome兰蔻美丽人生馥郁版100ml</t>
+        </is>
+      </c>
+      <c r="D792" s="2" t="inlineStr"/>
+      <c r="E792" s="2" t="n">
+        <v>305</v>
+      </c>
+      <c r="F792" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G792" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="H792" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I792" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J792" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K792" s="2" t="inlineStr"/>
+    </row>
+    <row r="793">
+      <c r="A793" s="2" t="n">
+        <v>367</v>
+      </c>
+      <c r="B793" s="2" t="inlineStr">
+        <is>
+          <t>【专柜行货】兰蔻新品美丽人生香水50ml 浓香版EDP 女士香水</t>
+        </is>
+      </c>
+      <c r="C793" s="2" t="inlineStr">
+        <is>
+          <t>Lancome兰蔻美丽人生馥郁版50ml</t>
+        </is>
+      </c>
+      <c r="D793" s="2" t="n">
+        <v>1060</v>
+      </c>
+      <c r="E793" s="2" t="n">
+        <v>879.8</v>
+      </c>
+      <c r="F793" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G793" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="H793" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I793" s="2" t="inlineStr"/>
+      <c r="J793" s="2" t="inlineStr"/>
+      <c r="K793" s="2" t="inlineStr"/>
+    </row>
+    <row r="794">
+      <c r="A794" s="2" t="n">
+        <v>367</v>
+      </c>
+      <c r="B794" s="2" t="inlineStr">
+        <is>
+          <t>【Lancome】兰蔻美丽人生馥郁版女士浓香香水EDP 30-100ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C794" s="2" t="inlineStr">
+        <is>
+          <t>Lancome兰蔻美丽人生馥郁版50ml</t>
+        </is>
+      </c>
+      <c r="D794" s="2" t="n">
+        <v>459</v>
+      </c>
+      <c r="E794" s="2" t="n">
+        <v>649</v>
+      </c>
+      <c r="F794" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G794" s="2" t="inlineStr"/>
+      <c r="H794" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I794" s="2" t="inlineStr"/>
+      <c r="J794" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 50ml</t>
+        </is>
+      </c>
+      <c r="K794" s="2" t="n">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="2" t="n">
+        <v>367</v>
+      </c>
+      <c r="B795" s="2" t="inlineStr">
+        <is>
+          <t>【Lancome】兰蔻美丽人生馥郁版女士浓香EDP 30-50-100ml【法国直发】【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C795" s="2" t="inlineStr">
+        <is>
+          <t>Lancome兰蔻美丽人生馥郁版50ml</t>
+        </is>
+      </c>
+      <c r="D795" s="2" t="inlineStr"/>
+      <c r="E795" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="F795" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G795" s="2" t="inlineStr"/>
+      <c r="H795" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I795" s="2" t="inlineStr"/>
+      <c r="J795" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 50ml</t>
+        </is>
+      </c>
+      <c r="K795" s="2" t="n">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="2" t="n">
+        <v>368</v>
+      </c>
+      <c r="B796" s="2" t="inlineStr">
+        <is>
+          <t>【Lancome】兰蔻美丽人生馥郁版女浓香EDP 30-100ml【法国直发【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C796" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻 美丽人生香氛精华香水 50ml</t>
+        </is>
+      </c>
+      <c r="D796" s="2" t="inlineStr"/>
+      <c r="E796" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="F796" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G796" s="2" t="inlineStr"/>
+      <c r="H796" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I796" s="2" t="inlineStr"/>
+      <c r="J796" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 50mL</t>
+        </is>
+      </c>
+      <c r="K796" s="2" t="n">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="2" t="n">
+        <v>368</v>
+      </c>
+      <c r="B797" s="2" t="inlineStr">
+        <is>
+          <t>LANCOME兰蔻美丽人生女士淡香精EDP30/50/100ML精装</t>
+        </is>
+      </c>
+      <c r="C797" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻 美丽人生香氛精华香水 50ml</t>
+        </is>
+      </c>
+      <c r="D797" s="2" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="E797" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="F797" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G797" s="2" t="inlineStr"/>
+      <c r="H797" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I797" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J797" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K797" s="2" t="inlineStr"/>
+    </row>
+    <row r="798">
+      <c r="A798" s="2" t="n">
+        <v>368</v>
+      </c>
+      <c r="B798" s="2" t="inlineStr">
+        <is>
+          <t>【Lancome】兰蔻 美丽人生女士浓香水 30/50/100ml【法国直发】【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C798" s="2" t="inlineStr">
+        <is>
+          <t>兰蔻 美丽人生香氛精华香水 50ml</t>
+        </is>
+      </c>
+      <c r="D798" s="2" t="inlineStr"/>
+      <c r="E798" s="2" t="n">
+        <v>697</v>
+      </c>
+      <c r="F798" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G798" s="2" t="inlineStr"/>
+      <c r="H798" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I798" s="2" t="inlineStr"/>
+      <c r="J798" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 50ml</t>
+        </is>
+      </c>
+      <c r="K798" s="2" t="n">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="B799" s="2" t="inlineStr">
+        <is>
+          <t>【Lancome】兰蔻idole偶像是我淡香水50ml留香清新约会高级礼物</t>
+        </is>
+      </c>
+      <c r="C799" s="2" t="inlineStr">
+        <is>
+          <t>Lancome/兰蔻是我IDOLE偶像香水 50ml</t>
+        </is>
+      </c>
+      <c r="D799" s="2" t="n">
+        <v>449</v>
+      </c>
+      <c r="E799" s="2" t="n">
+        <v>398</v>
+      </c>
+      <c r="F799" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G799" s="2" t="inlineStr"/>
+      <c r="H799" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I799" s="2" t="inlineStr"/>
+      <c r="J799" s="2" t="inlineStr"/>
+      <c r="K799" s="2" t="inlineStr"/>
+    </row>
+    <row r="800">
+      <c r="A800" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="B800" s="2" t="inlineStr">
+        <is>
+          <t>【兰蔻】唯我浓香水100ml花果香调清新持久馥郁迷人节日礼物</t>
+        </is>
+      </c>
+      <c r="C800" s="2" t="inlineStr">
+        <is>
+          <t>Lancome 兰蔻是我 浓情版 100ml</t>
+        </is>
+      </c>
+      <c r="D800" s="2" t="n">
+        <v>789</v>
+      </c>
+      <c r="E800" s="2" t="n">
+        <v>508.8</v>
+      </c>
+      <c r="F800" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G800" s="2" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="H800" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I800" s="2" t="inlineStr"/>
+      <c r="J800" s="2" t="inlineStr"/>
+      <c r="K800" s="2" t="inlineStr"/>
+    </row>
+    <row r="801">
+      <c r="A801" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="B801" s="2" t="inlineStr">
+        <is>
+          <t>【兰蔻】是我偶像经典浓香水EDP100ML补充装花香调新版</t>
+        </is>
+      </c>
+      <c r="C801" s="2" t="inlineStr">
+        <is>
+          <t>Lancome 兰蔻是我 浓情版 100ml</t>
+        </is>
+      </c>
+      <c r="D801" s="2" t="n">
+        <v>699</v>
+      </c>
+      <c r="E801" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="F801" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G801" s="2" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="H801" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I801" s="2" t="inlineStr"/>
+      <c r="J801" s="2" t="inlineStr"/>
+      <c r="K801" s="2" t="inlineStr"/>
+    </row>
+    <row r="802">
+      <c r="A802" s="2" t="n">
+        <v>371</v>
+      </c>
+      <c r="B802" s="2" t="inlineStr">
+        <is>
+          <t>古驰(GUCCI)绮梦茉莉女士香水EDP 30/50/100ML</t>
+        </is>
+      </c>
+      <c r="C802" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI 香水 茉莉100ML</t>
+        </is>
+      </c>
+      <c r="D802" s="2" t="inlineStr"/>
+      <c r="E802" s="2" t="n">
+        <v>355</v>
+      </c>
+      <c r="F802" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G802" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="H802" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I802" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J802" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K802" s="2" t="inlineStr"/>
+    </row>
+    <row r="803">
+      <c r="A803" s="2" t="n">
+        <v>372</v>
+      </c>
+      <c r="B803" s="2" t="inlineStr">
+        <is>
+          <t>【Hermes】爱马仕李先生的花园淡香水EDT100ml</t>
+        </is>
+      </c>
+      <c r="C803" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕李先生的花园淡香水100ml</t>
+        </is>
+      </c>
+      <c r="D803" s="2" t="n">
+        <v>589</v>
+      </c>
+      <c r="E803" s="2" t="n">
+        <v>358.5</v>
+      </c>
+      <c r="F803" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G803" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="H803" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I803" s="2" t="inlineStr"/>
+      <c r="J803" s="2" t="inlineStr"/>
+      <c r="K803" s="2" t="inlineStr"/>
+    </row>
+    <row r="804">
+      <c r="A804" s="2" t="n">
+        <v>373</v>
+      </c>
+      <c r="B804" s="2" t="inlineStr">
+        <is>
+          <t>【Hermes】爱马仕绯红火参/血色大黄古龙水香水节日礼物</t>
+        </is>
+      </c>
+      <c r="C804" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕绯红火参古龙水100ml</t>
+        </is>
+      </c>
+      <c r="D804" s="2" t="n">
+        <v>461</v>
+      </c>
+      <c r="E804" s="2" t="n">
+        <v>308.03</v>
+      </c>
+      <c r="F804" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G804" s="2" t="inlineStr"/>
+      <c r="H804" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I804" s="2" t="inlineStr"/>
+      <c r="J804" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 100mL 血色大黄 EDC 古龙水</t>
+        </is>
+      </c>
+      <c r="K804" s="2" t="n">
+        <v>308.03</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="2" t="n">
+        <v>373</v>
+      </c>
+      <c r="B805" s="2" t="inlineStr">
+        <is>
+          <t>【Hermes】爱马仕绯红火参/血色大黄古龙水香水简装礼物</t>
+        </is>
+      </c>
+      <c r="C805" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕绯红火参古龙水100ml</t>
+        </is>
+      </c>
+      <c r="D805" s="2" t="n">
+        <v>440</v>
+      </c>
+      <c r="E805" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="F805" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G805" s="2" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="H805" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I805" s="2" t="inlineStr"/>
+      <c r="J805" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 100mL 血色大黄 EDC 古龙水【简装】</t>
+        </is>
+      </c>
+      <c r="K805" s="2" t="n">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="2" t="n">
+        <v>374</v>
+      </c>
+      <c r="B806" s="2" t="inlineStr">
+        <is>
+          <t>纳斯小粉金口红321TURNED ON#透茶玫瑰1.5g节日礼物</t>
+        </is>
+      </c>
+      <c r="C806" s="2" t="inlineStr">
+        <is>
+          <t>NARS小粉金细管唇膏1.5G #321 Turned on</t>
+        </is>
+      </c>
+      <c r="D806" s="2" t="inlineStr"/>
+      <c r="E806" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="F806" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G806" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="H806" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I806" s="2" t="inlineStr"/>
+      <c r="J806" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 1.5g #321 Turned On 透茶玫瑰</t>
+        </is>
+      </c>
+      <c r="K806" s="2" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="2" t="n">
+        <v>374</v>
+      </c>
+      <c r="B807" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】氛围娜斯小粉唇膏#321透茶玫瑰丝滑显色保湿滋润水感通透1.5g</t>
+        </is>
+      </c>
+      <c r="C807" s="2" t="inlineStr">
+        <is>
+          <t>NARS小粉金细管唇膏1.5G #321 Turned on</t>
+        </is>
+      </c>
+      <c r="D807" s="2" t="inlineStr"/>
+      <c r="E807" s="2" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="F807" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G807" s="2" t="inlineStr"/>
+      <c r="H807" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I807" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=20.0%)</t>
+        </is>
+      </c>
+      <c r="J807" s="2" t="inlineStr"/>
+      <c r="K807" s="2" t="inlineStr"/>
+    </row>
+    <row r="808">
+      <c r="A808" s="2" t="n">
+        <v>375</v>
+      </c>
+      <c r="B808" s="2" t="inlineStr">
+        <is>
+          <t>MAC/魅可大子弹头口红唇膏#646   3.5g</t>
+        </is>
+      </c>
+      <c r="C808" s="2" t="inlineStr">
+        <is>
+          <t>MAC 丝柔哑光唇膏 #646 MARRAKESH 肉桂红茶</t>
+        </is>
+      </c>
+      <c r="D808" s="2" t="n">
+        <v>137.6</v>
+      </c>
+      <c r="E808" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F808" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G808" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H808" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I808" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=11.8%)</t>
+        </is>
+      </c>
+      <c r="J808" s="2" t="inlineStr"/>
+      <c r="K808" s="2" t="inlineStr"/>
+    </row>
+    <row r="809">
+      <c r="A809" s="2" t="n">
+        <v>375</v>
+      </c>
+      <c r="B809" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】MAC/魅可大子弹头口红 662大辣椒唇膏 显色哑光滋润</t>
+        </is>
+      </c>
+      <c r="C809" s="2" t="inlineStr">
+        <is>
+          <t>MAC 丝柔哑光唇膏 #646 MARRAKESH 肉桂红茶</t>
+        </is>
+      </c>
+      <c r="D809" s="2" t="inlineStr"/>
+      <c r="E809" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="F809" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G809" s="2" t="inlineStr"/>
+      <c r="H809" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I809" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=11.8%)</t>
+        </is>
+      </c>
+      <c r="J809" s="2" t="inlineStr">
+        <is>
+          <t>已选择： #646*大女主+专柜礼盒 正品行货-送礼好物-可代写祝福贺卡</t>
+        </is>
+      </c>
+      <c r="K809" s="2" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="2" t="n">
+        <v>375</v>
+      </c>
+      <c r="B810" s="2" t="inlineStr">
+        <is>
+          <t>【MAC】魅可新品哑光大子弹头唇膏口红666大宠粉 683大玩咖 682 646【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C810" s="2" t="inlineStr">
+        <is>
+          <t>MAC 丝柔哑光唇膏 #646 MARRAKESH 肉桂红茶</t>
+        </is>
+      </c>
+      <c r="D810" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="E810" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="F810" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G810" s="2" t="inlineStr"/>
+      <c r="H810" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I810" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=29.4%)</t>
+        </is>
+      </c>
+      <c r="J810" s="2" t="inlineStr">
+        <is>
+          <t>已选择： #646MARRAKESH 大女主</t>
+        </is>
+      </c>
+      <c r="K810" s="2" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="2" t="n">
+        <v>375</v>
+      </c>
+      <c r="B811" s="2" t="inlineStr">
+        <is>
+          <t>【鉴定正品】MAC/魅可新经典哑光唇膏 柔雾 气色 3.5g 大子弹头</t>
+        </is>
+      </c>
+      <c r="C811" s="2" t="inlineStr">
+        <is>
+          <t>MAC 丝柔哑光唇膏 #646 MARRAKESH 肉桂红茶</t>
+        </is>
+      </c>
+      <c r="D811" s="2" t="inlineStr"/>
+      <c r="E811" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="F811" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G811" s="2" t="inlineStr"/>
+      <c r="H811" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I811" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=23.5%)</t>
+        </is>
+      </c>
+      <c r="J811" s="2" t="inlineStr">
+        <is>
+          <t>已选择：#646 3.5g MAC 经典大子弹头</t>
+        </is>
+      </c>
+      <c r="K811" s="2" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="2" t="n">
+        <v>376</v>
+      </c>
+      <c r="B812" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】Lamer海蓝之谜修护焕新精萃水100ml 修护舒缓精华水</t>
+        </is>
+      </c>
+      <c r="C812" s="2" t="inlineStr">
+        <is>
+          <t>LAMER海蓝之谜调理焕肤液100ml</t>
+        </is>
+      </c>
+      <c r="D812" s="2" t="n">
+        <v>650</v>
+      </c>
+      <c r="E812" s="2" t="n">
+        <v>426</v>
+      </c>
+      <c r="F812" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G812" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="H812" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I812" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=20.0%)</t>
+        </is>
+      </c>
+      <c r="J812" s="2" t="inlineStr"/>
+      <c r="K812" s="2" t="inlineStr"/>
+    </row>
+    <row r="813">
+      <c r="A813" s="2" t="n">
+        <v>376</v>
+      </c>
+      <c r="B813" s="2" t="inlineStr">
+        <is>
+          <t>【LA MER】 海蓝之谜焕肤水100ML 舒缓提亮滋润【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C813" s="2" t="inlineStr">
+        <is>
+          <t>LAMER海蓝之谜调理焕肤液100ml</t>
+        </is>
+      </c>
+      <c r="D813" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="E813" s="2" t="n">
+        <v>292.99</v>
+      </c>
+      <c r="F813" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G813" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="H813" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I813" s="2" t="inlineStr"/>
+      <c r="J813" s="2" t="inlineStr"/>
+      <c r="K813" s="2" t="inlineStr"/>
+    </row>
+    <row r="814">
+      <c r="A814" s="2" t="n">
+        <v>376</v>
+      </c>
+      <c r="B814" s="2" t="inlineStr">
+        <is>
+          <t>【海蓝之谜】精粹柔酸水肌底液精华换肤调理液100ml 控油保湿改善闭口【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C814" s="2" t="inlineStr">
+        <is>
+          <t>LAMER海蓝之谜调理焕肤液100ml</t>
+        </is>
+      </c>
+      <c r="D814" s="2" t="n">
+        <v>565</v>
+      </c>
+      <c r="E814" s="2" t="n">
+        <v>564</v>
+      </c>
+      <c r="F814" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G814" s="2" t="inlineStr"/>
+      <c r="H814" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I814" s="2" t="inlineStr"/>
+      <c r="J814" s="2" t="inlineStr"/>
+      <c r="K814" s="2" t="inlineStr"/>
+    </row>
+    <row r="815">
+      <c r="A815" s="2" t="n">
+        <v>376</v>
+      </c>
+      <c r="B815" s="2" t="inlineStr">
+        <is>
+          <t>【LA MER】海蓝之谜鞣酸水柔酸肌底液100ml复合精华细致毛孔调理焕肤【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C815" s="2" t="inlineStr">
+        <is>
+          <t>LAMER海蓝之谜调理焕肤液100ml</t>
+        </is>
+      </c>
+      <c r="D815" s="2" t="inlineStr"/>
+      <c r="E815" s="2" t="n">
+        <v>576</v>
+      </c>
+      <c r="F815" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G815" s="2" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="H815" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I815" s="2" t="inlineStr"/>
+      <c r="J815" s="2" t="inlineStr"/>
+      <c r="K815" s="2" t="inlineStr"/>
+    </row>
+    <row r="816">
+      <c r="A816" s="2" t="n">
+        <v>377</v>
+      </c>
+      <c r="B816" s="2" t="inlineStr">
+        <is>
+          <t>【MAC】魅可定妆保湿喷雾白瓶100ml补水控油持久干皮油皮滋养清爽正品</t>
+        </is>
+      </c>
+      <c r="C816" s="2" t="inlineStr">
+        <is>
+          <t>MAC魅可保湿定妆喷雾Fix+100mL</t>
+        </is>
+      </c>
+      <c r="D816" s="2" t="inlineStr"/>
+      <c r="E816" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="F816" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G816" s="2" t="inlineStr"/>
+      <c r="H816" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I816" s="2" t="inlineStr"/>
+      <c r="J816" s="2" t="inlineStr"/>
+      <c r="K816" s="2" t="inlineStr"/>
+    </row>
+    <row r="817">
+      <c r="A817" s="2" t="n">
+        <v>378</v>
+      </c>
+      <c r="B817" s="2" t="inlineStr">
+        <is>
+          <t>宏香记品牌官方正品，100%保障</t>
+        </is>
+      </c>
+      <c r="C817" s="2" t="inlineStr">
+        <is>
+          <t>MAC妆前瞬间定妆喷雾100ML</t>
+        </is>
+      </c>
+      <c r="D817" s="2" t="inlineStr"/>
+      <c r="E817" s="2" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="F817" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G817" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="H817" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I817" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J817" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K817" s="2" t="inlineStr"/>
+    </row>
+    <row r="818">
+      <c r="A818" s="2" t="n">
+        <v>378</v>
+      </c>
+      <c r="B818" s="2" t="inlineStr">
+        <is>
+          <t>【MAC】魅可定妆紫喷喷雾持久锁妆防水保湿控油不拔干不刺激干皮100ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C818" s="2" t="inlineStr">
+        <is>
+          <t>MAC妆前瞬间定妆喷雾100ML</t>
+        </is>
+      </c>
+      <c r="D818" s="2" t="inlineStr"/>
+      <c r="E818" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="F818" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G818" s="2" t="inlineStr"/>
+      <c r="H818" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I818" s="2" t="inlineStr"/>
+      <c r="J818" s="2" t="inlineStr"/>
+      <c r="K818" s="2" t="inlineStr"/>
+    </row>
+    <row r="819">
+      <c r="A819" s="2" t="n">
+        <v>378</v>
+      </c>
+      <c r="B819" s="2" t="inlineStr">
+        <is>
+          <t>MAC/魅可定妆妆前保湿喷雾原味长效定妆防水不黏腻</t>
+        </is>
+      </c>
+      <c r="C819" s="2" t="inlineStr">
+        <is>
+          <t>MAC妆前瞬间定妆喷雾100ML</t>
+        </is>
+      </c>
+      <c r="D819" s="2" t="inlineStr"/>
+      <c r="E819" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="F819" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G819" s="2" t="inlineStr"/>
+      <c r="H819" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I819" s="2" t="inlineStr"/>
+      <c r="J819" s="2" t="inlineStr">
+        <is>
+          <t>已选: 100mL 妆前保湿喷雾[24.1产]</t>
+        </is>
+      </c>
+      <c r="K819" s="2" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="2" t="n">
+        <v>378</v>
+      </c>
+      <c r="B820" s="2" t="inlineStr">
+        <is>
+          <t>【MAC】魅可定妆紫喷喷雾持久锁妆防水保湿控油不拔干不刺激干皮100ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C820" s="2" t="inlineStr">
+        <is>
+          <t>MAC妆前瞬间定妆喷雾100ML</t>
+        </is>
+      </c>
+      <c r="D820" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="E820" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="F820" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G820" s="2" t="inlineStr"/>
+      <c r="H820" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I820" s="2" t="inlineStr"/>
+      <c r="J820" s="2" t="inlineStr"/>
+      <c r="K820" s="2" t="inlineStr"/>
+    </row>
+    <row r="821">
+      <c r="A821" s="2" t="n">
+        <v>379</v>
+      </c>
+      <c r="B821" s="2" t="inlineStr">
+        <is>
+          <t>【MAC】魅可 新升级定制无瑕粉底液NC12#30ml</t>
+        </is>
+      </c>
+      <c r="C821" s="2" t="inlineStr">
+        <is>
+          <t>MAC 无暇粉底液NC12 30ML</t>
+        </is>
+      </c>
+      <c r="D821" s="2" t="inlineStr"/>
+      <c r="E821" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="F821" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G821" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="H821" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I821" s="2" t="inlineStr"/>
+      <c r="J821" s="2" t="inlineStr">
+        <is>
+          <t>已选: NC12 黄二白</t>
+        </is>
+      </c>
+      <c r="K821" s="2" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="B822" s="2" t="inlineStr">
+        <is>
+          <t>【ESTEE LAUDER雅诗兰黛】红石榴面霜 鲜活亮采日霜50ml保湿补水</t>
+        </is>
+      </c>
+      <c r="C822" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛 红石榴面霜50ml</t>
+        </is>
+      </c>
+      <c r="D822" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="E822" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="F822" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G822" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="H822" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I822" s="2" t="inlineStr"/>
+      <c r="J822" s="2" t="inlineStr"/>
+      <c r="K822" s="2" t="inlineStr"/>
+    </row>
+    <row r="823">
+      <c r="A823" s="2" t="n">
+        <v>381</v>
+      </c>
+      <c r="B823" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】红石榴洁面新款125ml 清洁保湿洁面乳</t>
+        </is>
+      </c>
+      <c r="C823" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛 红石榴洁面125ml</t>
+        </is>
+      </c>
+      <c r="D823" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="E823" s="2" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="F823" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G823" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H823" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I823" s="2" t="inlineStr"/>
+      <c r="J823" s="2" t="inlineStr"/>
+      <c r="K823" s="2" t="inlineStr"/>
+    </row>
+    <row r="824">
+      <c r="A824" s="2" t="n">
+        <v>381</v>
+      </c>
+      <c r="B824" s="2" t="inlineStr">
+        <is>
+          <t>【861.8万人收藏该品牌】双支 单品 雅诗兰黛新款红石榴洗面奶125ml</t>
+        </is>
+      </c>
+      <c r="C824" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛 红石榴洁面125ml</t>
+        </is>
+      </c>
+      <c r="D824" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="E824" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="F824" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G824" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="H824" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I824" s="2" t="inlineStr"/>
+      <c r="J824" s="2" t="inlineStr"/>
+      <c r="K824" s="2" t="inlineStr"/>
+    </row>
+    <row r="825">
+      <c r="A825" s="2" t="n">
+        <v>382</v>
+      </c>
+      <c r="B825" s="2" t="inlineStr">
+        <is>
+          <t>【跨境原装】资生堂红腰子洗面奶女洁面乳膏氨基酸清洁保湿旗舰店</t>
+        </is>
+      </c>
+      <c r="C825" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO红腰子洁面125ml</t>
+        </is>
+      </c>
+      <c r="D825" s="2" t="inlineStr"/>
+      <c r="E825" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="F825" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G825" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="H825" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I825" s="2" t="inlineStr"/>
+      <c r="J825" s="2" t="inlineStr">
+        <is>
+          <t>已选: 125ml [温和保湿]红腰子洁面乳+嫩白洇色蛋</t>
+        </is>
+      </c>
+      <c r="K825" s="2" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="2" t="n">
+        <v>382</v>
+      </c>
+      <c r="B826" s="2" t="inlineStr">
+        <is>
+          <t>【跨境原装】资生堂洁面膏红腰子洗面奶深层清洁保湿去黄黑头提亮</t>
+        </is>
+      </c>
+      <c r="C826" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO红腰子洁面125ml</t>
+        </is>
+      </c>
+      <c r="D826" s="2" t="inlineStr"/>
+      <c r="E826" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="F826" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G826" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="H826" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I826" s="2" t="inlineStr"/>
+      <c r="J826" s="2" t="inlineStr">
+        <is>
+          <t>已选: 175ml[正装125ml+中样50ml]洁面膏+滴形妆蛋球1</t>
+        </is>
+      </c>
+      <c r="K826" s="2" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="2" t="n">
+        <v>383</v>
+      </c>
+      <c r="B827" s="2" t="inlineStr">
+        <is>
+          <t>【特价清仓】资生堂悦薇智感紧塑焕白眼霜15ml 紧致淡纹提亮眼周</t>
+        </is>
+      </c>
+      <c r="C827" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO悦薇抗糖眼霜（新版）15ml</t>
+        </is>
+      </c>
+      <c r="D827" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="E827" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="F827" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G827" s="2" t="inlineStr"/>
+      <c r="H827" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I827" s="2" t="inlineStr"/>
+      <c r="J827" s="2" t="inlineStr"/>
+      <c r="K827" s="2" t="inlineStr"/>
+    </row>
+    <row r="828">
+      <c r="A828" s="2" t="n">
+        <v>384</v>
+      </c>
+      <c r="B828" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂盼丽风姿智感抚纹眼霜15ml小雷达抗皱紧致礼物</t>
+        </is>
+      </c>
+      <c r="C828" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO盼丽风姿眼霜（新款）15ml</t>
+        </is>
+      </c>
+      <c r="D828" s="2" t="n">
+        <v>193.4</v>
+      </c>
+      <c r="E828" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="F828" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G828" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="H828" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I828" s="2" t="inlineStr"/>
+      <c r="J828" s="2" t="inlineStr"/>
+      <c r="K828" s="2" t="inlineStr"/>
+    </row>
+    <row r="829">
+      <c r="A829" s="2" t="n">
+        <v>385</v>
+      </c>
+      <c r="B829" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】DW持妆粉底液1C1 66#瓷白色 30ml</t>
+        </is>
+      </c>
+      <c r="C829" s="2" t="inlineStr">
+        <is>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1C1 30ML 新版 2026年</t>
+        </is>
+      </c>
+      <c r="D829" s="2" t="inlineStr"/>
+      <c r="E829" s="2" t="n">
+        <v>293</v>
+      </c>
+      <c r="F829" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G829" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="H829" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I829" s="2" t="inlineStr"/>
+      <c r="J829" s="2" t="inlineStr"/>
+      <c r="K829" s="2" t="inlineStr"/>
+    </row>
+    <row r="830">
+      <c r="A830" s="2" t="n">
+        <v>386</v>
+      </c>
+      <c r="B830" s="2" t="inlineStr">
+        <is>
+          <t>Estee Lauder/雅诗兰黛 DW持妆粉底液30ml#1N2 柔光遮瑕【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C830" s="2" t="inlineStr">
+        <is>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N2 30ML 新版 2026</t>
+        </is>
+      </c>
+      <c r="D830" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="E830" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="F830" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G830" s="2" t="inlineStr"/>
+      <c r="H830" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I830" s="2" t="inlineStr"/>
+      <c r="J830" s="2" t="inlineStr"/>
+      <c r="K830" s="2" t="inlineStr"/>
+    </row>
+    <row r="831">
+      <c r="A831" s="2" t="n">
+        <v>386</v>
+      </c>
+      <c r="B831" s="2" t="inlineStr">
+        <is>
+          <t>Estee Lauder/雅诗兰黛dw持粉底液#1N2油皮亲妈持妆粉底液30ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C831" s="2" t="inlineStr">
+        <is>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N2 30ML 新版 2026</t>
+        </is>
+      </c>
+      <c r="D831" s="2" t="inlineStr"/>
+      <c r="E831" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="F831" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G831" s="2" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="H831" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I831" s="2" t="inlineStr"/>
+      <c r="J831" s="2" t="inlineStr"/>
+      <c r="K831" s="2" t="inlineStr"/>
+    </row>
+    <row r="832">
+      <c r="A832" s="2" t="n">
+        <v>386</v>
+      </c>
+      <c r="B832" s="2" t="inlineStr">
+        <is>
+          <t>【原装正品】雅诗兰黛DW持妆粉底液 油皮亲妈持久不脱妆遮瑕控油</t>
+        </is>
+      </c>
+      <c r="C832" s="2" t="inlineStr">
+        <is>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N2 30ML 新版 2026</t>
+        </is>
+      </c>
+      <c r="D832" s="2" t="inlineStr"/>
+      <c r="E832" s="2" t="n">
+        <v>212</v>
+      </c>
+      <c r="F832" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G832" s="2" t="inlineStr"/>
+      <c r="H832" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I832" s="2" t="inlineStr"/>
+      <c r="J832" s="2" t="inlineStr">
+        <is>
+          <t>已选: 1W2 自然色（全新原装） 30mL 个人 DW-粉底液 赠彩妆蛋 压头[新旧版随机]</t>
+        </is>
+      </c>
+      <c r="K832" s="2" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="2" t="n">
+        <v>387</v>
+      </c>
+      <c r="B833" s="2" t="inlineStr">
+        <is>
+          <t>Estee Lauder/雅诗兰黛 DW持妆粉底液30ml#1N2 柔光遮瑕【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C833" s="2" t="inlineStr">
+        <is>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N1 30ML 新版 2026</t>
+        </is>
+      </c>
+      <c r="D833" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="E833" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="F833" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G833" s="2" t="inlineStr"/>
+      <c r="H833" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I833" s="2" t="inlineStr"/>
+      <c r="J833" s="2" t="inlineStr">
+        <is>
+          <t>已选: 30mL 1N2</t>
+        </is>
+      </c>
+      <c r="K833" s="2" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="2" t="n">
+        <v>388</v>
+      </c>
+      <c r="B834" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】MAC/魅可大子弹头口红哑光柔雾666大宠粉602大辣椒</t>
+        </is>
+      </c>
+      <c r="C834" s="2" t="inlineStr">
+        <is>
+          <t>MAC魅可 丝柔哑光唇膏 大子弹口红#666 Sweet Deal 玫瑰冷萃</t>
+        </is>
+      </c>
+      <c r="D834" s="2" t="inlineStr"/>
+      <c r="E834" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="F834" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G834" s="2" t="inlineStr"/>
+      <c r="H834" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I834" s="2" t="inlineStr"/>
+      <c r="J834" s="2" t="inlineStr">
+        <is>
+          <t>已选: 大宠粉[666] 赠专柜礼盒+正品保障+假一赔十</t>
+        </is>
+      </c>
+      <c r="K834" s="2" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="B835" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销401万+件】韩国兰芝新款马卡龙防晒隔离霜30ml遮瑕妆前乳打底</t>
+        </is>
+      </c>
+      <c r="C835" s="2" t="inlineStr">
+        <is>
+          <t>兰芝马卡龙隔离30ml紫色</t>
+        </is>
+      </c>
+      <c r="D835" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="E835" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="F835" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G835" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="H835" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I835" s="2" t="inlineStr"/>
+      <c r="J835" s="2" t="inlineStr"/>
+      <c r="K835" s="2" t="inlineStr"/>
+    </row>
+    <row r="836">
+      <c r="A836" s="2" t="n">
+        <v>390</v>
+      </c>
+      <c r="B836" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销401万+件】韩国LANEIGE兰芝新款马卡龙防晒隔离霜遮瑕三合一妆前乳打底</t>
+        </is>
+      </c>
+      <c r="C836" s="2" t="inlineStr">
+        <is>
+          <t>兰芝马卡龙隔离30ml绿色</t>
+        </is>
+      </c>
+      <c r="D836" s="2" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="E836" s="2" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="F836" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G836" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="H836" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I836" s="2" t="inlineStr"/>
+      <c r="J836" s="2" t="inlineStr">
+        <is>
+          <t>已选: 兰芝紫隔离30ml[新版马卡龙]</t>
+        </is>
+      </c>
+      <c r="K836" s="2" t="n">
+        <v>68.90000000000001</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="2" t="n">
+        <v>391</v>
+      </c>
+      <c r="B837" s="2" t="inlineStr">
+        <is>
+          <t>【资生堂】悦薇抗糖面霜智感塑颜抗皱霜焕白清爽资生堂面霜50ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C837" s="2" t="inlineStr">
+        <is>
+          <t>资生堂 悦薇大抗糖滋润面霜（新款）50mL</t>
+        </is>
+      </c>
+      <c r="D837" s="2" t="inlineStr"/>
+      <c r="E837" s="2" t="n">
+        <v>309</v>
+      </c>
+      <c r="F837" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G837" s="2" t="inlineStr"/>
+      <c r="H837" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I837" s="2" t="inlineStr"/>
+      <c r="J837" s="2" t="inlineStr"/>
+      <c r="K837" s="2" t="inlineStr"/>
+    </row>
+    <row r="838">
+      <c r="A838" s="2" t="n">
+        <v>391</v>
+      </c>
+      <c r="B838" s="2" t="inlineStr">
+        <is>
+          <t>【资生堂】悦薇面霜抗糖抗初老补水紧致智感紧塑焕白霜</t>
+        </is>
+      </c>
+      <c r="C838" s="2" t="inlineStr">
+        <is>
+          <t>资生堂 悦薇大抗糖滋润面霜（新款）50mL</t>
+        </is>
+      </c>
+      <c r="D838" s="2" t="n">
+        <v>359</v>
+      </c>
+      <c r="E838" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="F838" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G838" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="H838" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I838" s="2" t="inlineStr"/>
+      <c r="J838" s="2" t="inlineStr">
+        <is>
+          <t>已选: 50mL [滋润型]悦薇面霜</t>
+        </is>
+      </c>
+      <c r="K838" s="2" t="n">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="2" t="n">
+        <v>392</v>
+      </c>
+      <c r="B839" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】娜斯5894大白饼粉饼控油磨皮持妆蜜粉饼【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C839" s="2" t="inlineStr">
+        <is>
+          <t>NARS蜜粉饼5894 效期24年</t>
+        </is>
+      </c>
+      <c r="D839" s="2" t="inlineStr"/>
+      <c r="E839" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="F839" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G839" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="H839" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I839" s="2" t="inlineStr"/>
+      <c r="J839" s="2" t="inlineStr"/>
+      <c r="K839" s="2" t="inlineStr"/>
+    </row>
+    <row r="840">
+      <c r="A840" s="2" t="n">
+        <v>392</v>
+      </c>
+      <c r="B840" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】娜斯 流光美肌轻透蜜粉饼5894大白饼粉饼10g【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C840" s="2" t="inlineStr">
+        <is>
+          <t>NARS蜜粉饼5894 效期24年</t>
+        </is>
+      </c>
+      <c r="D840" s="2" t="inlineStr"/>
+      <c r="E840" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="F840" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G840" s="2" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="H840" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I840" s="2" t="inlineStr"/>
+      <c r="J840" s="2" t="inlineStr"/>
+      <c r="K840" s="2" t="inlineStr"/>
+    </row>
+    <row r="841">
+      <c r="A841" s="2" t="n">
+        <v>392</v>
+      </c>
+      <c r="B841" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】娜斯5894大白饼粉饼控油磨皮持妆蜜粉饼【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C841" s="2" t="inlineStr">
+        <is>
+          <t>NARS蜜粉饼5894 效期24年</t>
+        </is>
+      </c>
+      <c r="D841" s="2" t="inlineStr"/>
+      <c r="E841" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="F841" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G841" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="H841" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I841" s="2" t="inlineStr"/>
+      <c r="J841" s="2" t="inlineStr"/>
+      <c r="K841" s="2" t="inlineStr"/>
+    </row>
+    <row r="842">
+      <c r="A842" s="2" t="n">
+        <v>393</v>
+      </c>
+      <c r="B842" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销248.5万+件】whoo后拱辰享泡沫洗面奶水妍津率享深层清洁控油洁面女</t>
+        </is>
+      </c>
+      <c r="C842" s="2" t="inlineStr">
+        <is>
+          <t>WHOO/后拱辰享洁面泡沫180ml/支 （新条码）</t>
+        </is>
+      </c>
+      <c r="D842" s="2" t="inlineStr"/>
+      <c r="E842" s="2" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="F842" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G842" s="2" t="inlineStr"/>
+      <c r="H842" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I842" s="2" t="inlineStr"/>
+      <c r="J842" s="2" t="inlineStr">
+        <is>
+          <t>已选: 美白洁面套180ML+洁面40ML</t>
+        </is>
+      </c>
+      <c r="K842" s="2" t="n">
+        <v>119.9</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="2" t="n">
+        <v>394</v>
+      </c>
+      <c r="B843" s="2" t="inlineStr">
+        <is>
+          <t>【资生堂】红腰子精华液4.0紧致抗皱面部护肤抗初老120ml</t>
+        </is>
+      </c>
+      <c r="C843" s="2" t="inlineStr">
+        <is>
+          <t>SHISEIDO资生堂红腰子精华100ml</t>
+        </is>
+      </c>
+      <c r="D843" s="2" t="n">
+        <v>599</v>
+      </c>
+      <c r="E843" s="2" t="n">
+        <v>368</v>
+      </c>
+      <c r="F843" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G843" s="2" t="inlineStr"/>
+      <c r="H843" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I843" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J843" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K843" s="2" t="inlineStr"/>
+    </row>
+    <row r="844">
+      <c r="A844" s="2" t="n">
+        <v>395</v>
+      </c>
+      <c r="B844" s="2" t="inlineStr">
+        <is>
+          <t>【1.37万人评价品牌正品】GUCCI/古驰炼金士花园系列香水100ML正品香氛送礼</t>
+        </is>
+      </c>
+      <c r="C844" s="2" t="inlineStr">
+        <is>
+          <t>古驰炼金师花园香草颂香水100ML</t>
+        </is>
+      </c>
+      <c r="D844" s="2" t="n">
+        <v>1099</v>
+      </c>
+      <c r="E844" s="2" t="n">
+        <v>736.36</v>
+      </c>
+      <c r="F844" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G844" s="2" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="H844" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I844" s="2" t="inlineStr"/>
+      <c r="J844" s="2" t="inlineStr"/>
+      <c r="K844" s="2" t="inlineStr"/>
+    </row>
+    <row r="845">
+      <c r="A845" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="B845" s="2" t="inlineStr">
+        <is>
+          <t>【百补品牌热销40.6万件】GUCCI/古驰炼金士花园系列香水150ML简装持久留香</t>
+        </is>
+      </c>
+      <c r="C845" s="2" t="inlineStr">
+        <is>
+          <t>古驰炼金师花园沐光橙香水100ML</t>
+        </is>
+      </c>
+      <c r="D845" s="2" t="n">
+        <v>845</v>
+      </c>
+      <c r="E845" s="2" t="n">
+        <v>549.49</v>
+      </c>
+      <c r="F845" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G845" s="2" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="H845" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I845" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J845" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K845" s="2" t="inlineStr"/>
+    </row>
+    <row r="846">
+      <c r="A846" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="B846" s="2" t="inlineStr">
+        <is>
+          <t>【百补品牌热销40.6万件】GUCCI/古驰炼金士花园系列香水100ML正品香氛送礼</t>
+        </is>
+      </c>
+      <c r="C846" s="2" t="inlineStr">
+        <is>
+          <t>古驰炼金师花园沐光橙香水100ML</t>
+        </is>
+      </c>
+      <c r="D846" s="2" t="n">
+        <v>1099</v>
+      </c>
+      <c r="E846" s="2" t="n">
+        <v>736.36</v>
+      </c>
+      <c r="F846" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G846" s="2" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="H846" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I846" s="2" t="inlineStr"/>
+      <c r="J846" s="2" t="inlineStr"/>
+      <c r="K846" s="2" t="inlineStr"/>
+    </row>
+    <row r="847">
+      <c r="A847" s="2" t="n">
+        <v>397</v>
+      </c>
+      <c r="B847" s="2" t="inlineStr">
+        <is>
+          <t>Maison Margiela 梅森马吉拉马丁马吉拉香水 慵懒周末/沙滩漫步【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C847" s="2" t="inlineStr">
+        <is>
+          <t>马丁马吉拉-爵士酒廊淡香100ml</t>
+        </is>
+      </c>
+      <c r="D847" s="2" t="inlineStr"/>
+      <c r="E847" s="2" t="n">
+        <v>585</v>
+      </c>
+      <c r="F847" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G847" s="2" t="inlineStr"/>
+      <c r="H847" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I847" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+      <c r="J847" s="2" t="inlineStr">
+        <is>
+          <t>已选: 温暖壁炉/壁炉火光100ml</t>
+        </is>
+      </c>
+      <c r="K847" s="2" t="n">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="2" t="n">
+        <v>398</v>
+      </c>
+      <c r="B848" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰全新爱心唇釉610 416 622 440限定浮雕黑管</t>
+        </is>
+      </c>
+      <c r="C848" s="2" t="inlineStr">
+        <is>
+          <t>YSL新款爱心唇釉610#</t>
+        </is>
+      </c>
+      <c r="D848" s="2" t="inlineStr"/>
+      <c r="E848" s="2" t="n">
+        <v>154.7</v>
+      </c>
+      <c r="F848" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G848" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H848" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I848" s="2" t="inlineStr"/>
+      <c r="J848" s="2" t="inlineStr">
+        <is>
+          <t>已选: 610 冰乌龙</t>
+        </is>
+      </c>
+      <c r="K848" s="2" t="n">
+        <v>154.7</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="B849" s="2" t="inlineStr">
+        <is>
+          <t>【BVLGARI】宝格丽 白茶 香水 茶香系列 淡香水EDT 75ml/150ml</t>
+        </is>
+      </c>
+      <c r="C849" s="2" t="inlineStr">
+        <is>
+          <t>宝格丽白茶淡香150ml</t>
+        </is>
+      </c>
+      <c r="D849" s="2" t="inlineStr"/>
+      <c r="E849" s="2" t="n">
+        <v>899</v>
+      </c>
+      <c r="F849" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G849" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="H849" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I849" s="2" t="inlineStr"/>
+      <c r="J849" s="2" t="inlineStr">
+        <is>
+          <t>已选: 150mL 宝格丽白茶</t>
+        </is>
+      </c>
+      <c r="K849" s="2" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="B850" s="2" t="inlineStr">
+        <is>
+          <t>【宝格丽】悠境白茶淡香75ml正装新款白茶清新茶香木质花香</t>
+        </is>
+      </c>
+      <c r="C850" s="2" t="inlineStr">
+        <is>
+          <t>宝格丽白茶淡香150ml</t>
+        </is>
+      </c>
+      <c r="D850" s="2" t="n">
+        <v>6991</v>
+      </c>
+      <c r="E850" s="2" t="n">
+        <v>699</v>
+      </c>
+      <c r="F850" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G850" s="2" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="H850" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I850" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J850" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K850" s="2" t="inlineStr"/>
+    </row>
+    <row r="851">
+      <c r="A851" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="B851" s="2" t="inlineStr">
+        <is>
+          <t>【宝格丽】宝格丽白茶香水 淡香水 150ml/5oz【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C851" s="2" t="inlineStr">
+        <is>
+          <t>宝格丽白茶淡香150ml</t>
+        </is>
+      </c>
+      <c r="D851" s="2" t="inlineStr"/>
+      <c r="E851" s="2" t="n">
+        <v>1026</v>
+      </c>
+      <c r="F851" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G851" s="2" t="inlineStr"/>
+      <c r="H851" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I851" s="2" t="inlineStr"/>
+      <c r="J851" s="2" t="inlineStr">
+        <is>
+          <t>已选: 150mL</t>
+        </is>
+      </c>
+      <c r="K851" s="2" t="n">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="B852" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】植村秀绿茶卸妆洁颜油  温和深层清洁彩妆保湿</t>
+        </is>
+      </c>
+      <c r="C852" s="2" t="inlineStr">
+        <is>
+          <t>植村秀绿茶卸妆油150ml</t>
+        </is>
+      </c>
+      <c r="D852" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="E852" s="2" t="n">
+        <v>304</v>
+      </c>
+      <c r="F852" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G852" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="H852" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I852" s="2" t="inlineStr"/>
+      <c r="J852" s="2" t="inlineStr">
+        <is>
+          <t>已选: 150mL</t>
+        </is>
+      </c>
+      <c r="K852" s="2" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="B853" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】植村秀绿茶新肌洁颜油卸妆油150ml 去黄抗氧化</t>
+        </is>
+      </c>
+      <c r="C853" s="2" t="inlineStr">
+        <is>
+          <t>植村秀绿茶卸妆油150ml</t>
+        </is>
+      </c>
+      <c r="D853" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="E853" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F853" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G853" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="H853" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I853" s="2" t="inlineStr"/>
+      <c r="J853" s="2" t="inlineStr"/>
+      <c r="K853" s="2" t="inlineStr"/>
+    </row>
+    <row r="854">
+      <c r="A854" s="2" t="n">
+        <v>377</v>
+      </c>
+      <c r="B854" s="2" t="inlineStr">
+        <is>
+          <t>【MAC】魅可定妆保湿喷雾白瓶100ml补水控油持久干皮油皮滋养清爽正品</t>
+        </is>
+      </c>
+      <c r="C854" s="2" t="inlineStr">
+        <is>
+          <t>MAC魅可保湿定妆喷雾Fix+100mL</t>
+        </is>
+      </c>
+      <c r="D854" s="2" t="inlineStr"/>
+      <c r="E854" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="F854" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G854" s="2" t="inlineStr"/>
+      <c r="H854" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I854" s="2" t="inlineStr"/>
+      <c r="J854" s="2" t="inlineStr"/>
+      <c r="K854" s="2" t="inlineStr"/>
+    </row>
+    <row r="855">
+      <c r="A855" s="2" t="n">
+        <v>378</v>
+      </c>
+      <c r="B855" s="2" t="inlineStr">
+        <is>
+          <t>宏香记品牌官方正品，100%保障</t>
+        </is>
+      </c>
+      <c r="C855" s="2" t="inlineStr">
+        <is>
+          <t>MAC妆前瞬间定妆喷雾100ML</t>
+        </is>
+      </c>
+      <c r="D855" s="2" t="inlineStr"/>
+      <c r="E855" s="2" t="inlineStr">
+        <is>
+          <t>24.57</t>
+        </is>
+      </c>
+      <c r="F855" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G855" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="H855" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I855" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J855" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K855" s="2" t="inlineStr"/>
+    </row>
+    <row r="856">
+      <c r="A856" s="2" t="n">
+        <v>378</v>
+      </c>
+      <c r="B856" s="2" t="inlineStr">
+        <is>
+          <t>【MAC】魅可定妆紫喷喷雾持久锁妆防水保湿控油不拔干不刺激干皮100ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C856" s="2" t="inlineStr">
+        <is>
+          <t>MAC妆前瞬间定妆喷雾100ML</t>
+        </is>
+      </c>
+      <c r="D856" s="2" t="inlineStr"/>
+      <c r="E856" s="2" t="inlineStr">
+        <is>
+          <t>218.0</t>
+        </is>
+      </c>
+      <c r="F856" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G856" s="2" t="inlineStr"/>
+      <c r="H856" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I856" s="2" t="inlineStr"/>
+      <c r="J856" s="2" t="inlineStr"/>
+      <c r="K856" s="2" t="inlineStr"/>
+    </row>
+    <row r="857">
+      <c r="A857" s="2" t="n">
+        <v>378</v>
+      </c>
+      <c r="B857" s="2" t="inlineStr">
+        <is>
+          <t>MAC/魅可定妆妆前保湿喷雾原味长效定妆防水不黏腻</t>
+        </is>
+      </c>
+      <c r="C857" s="2" t="inlineStr">
+        <is>
+          <t>MAC妆前瞬间定妆喷雾100ML</t>
+        </is>
+      </c>
+      <c r="D857" s="2" t="inlineStr"/>
+      <c r="E857" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="F857" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G857" s="2" t="inlineStr"/>
+      <c r="H857" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I857" s="2" t="inlineStr"/>
+      <c r="J857" s="2" t="inlineStr">
+        <is>
+          <t>已选: 100mL 妆前保湿喷雾[24.1产]</t>
+        </is>
+      </c>
+      <c r="K857" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="2" t="n">
+        <v>378</v>
+      </c>
+      <c r="B858" s="2" t="inlineStr">
+        <is>
+          <t>【MAC】魅可定妆紫喷喷雾持久锁妆防水保湿控油不拔干不刺激干皮100ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C858" s="2" t="inlineStr">
+        <is>
+          <t>MAC妆前瞬间定妆喷雾100ML</t>
+        </is>
+      </c>
+      <c r="D858" s="2" t="inlineStr">
+        <is>
+          <t>232.0</t>
+        </is>
+      </c>
+      <c r="E858" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
+      <c r="F858" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G858" s="2" t="inlineStr"/>
+      <c r="H858" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I858" s="2" t="inlineStr"/>
+      <c r="J858" s="2" t="inlineStr"/>
+      <c r="K858" s="2" t="inlineStr"/>
+    </row>
+    <row r="859">
+      <c r="A859" s="2" t="n">
+        <v>379</v>
+      </c>
+      <c r="B859" s="2" t="inlineStr">
+        <is>
+          <t>【MAC】魅可 新升级定制无瑕粉底液NC12#30ml</t>
+        </is>
+      </c>
+      <c r="C859" s="2" t="inlineStr">
+        <is>
+          <t>MAC 无暇粉底液NC12 30ML</t>
+        </is>
+      </c>
+      <c r="D859" s="2" t="inlineStr"/>
+      <c r="E859" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="F859" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G859" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="H859" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I859" s="2" t="inlineStr"/>
+      <c r="J859" s="2" t="inlineStr">
+        <is>
+          <t>已选: NC12 黄二白</t>
+        </is>
+      </c>
+      <c r="K859" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="B860" s="2" t="inlineStr">
+        <is>
+          <t>【ESTEE LAUDER雅诗兰黛】红石榴面霜 鲜活亮采日霜50ml保湿补水</t>
+        </is>
+      </c>
+      <c r="C860" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛 红石榴面霜50ml</t>
+        </is>
+      </c>
+      <c r="D860" s="2" t="inlineStr">
+        <is>
+          <t>195.0</t>
+        </is>
+      </c>
+      <c r="E860" s="2" t="inlineStr">
+        <is>
+          <t>119.0</t>
+        </is>
+      </c>
+      <c r="F860" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G860" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="H860" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I860" s="2" t="inlineStr"/>
+      <c r="J860" s="2" t="inlineStr"/>
+      <c r="K860" s="2" t="inlineStr"/>
+    </row>
+    <row r="861">
+      <c r="A861" s="2" t="n">
+        <v>381</v>
+      </c>
+      <c r="B861" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】红石榴洁面新款125ml 清洁保湿洁面乳</t>
+        </is>
+      </c>
+      <c r="C861" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛 红石榴洁面125ml</t>
+        </is>
+      </c>
+      <c r="D861" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="E861" s="2" t="inlineStr">
+        <is>
+          <t>98.9</t>
+        </is>
+      </c>
+      <c r="F861" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G861" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H861" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I861" s="2" t="inlineStr"/>
+      <c r="J861" s="2" t="inlineStr"/>
+      <c r="K861" s="2" t="inlineStr"/>
+    </row>
+    <row r="862">
+      <c r="A862" s="2" t="n">
+        <v>381</v>
+      </c>
+      <c r="B862" s="2" t="inlineStr">
+        <is>
+          <t>【861.8万人收藏该品牌】双支 单品 雅诗兰黛新款红石榴洗面奶125ml</t>
+        </is>
+      </c>
+      <c r="C862" s="2" t="inlineStr">
+        <is>
+          <t>雅诗兰黛 红石榴洁面125ml</t>
+        </is>
+      </c>
+      <c r="D862" s="2" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="E862" s="2" t="inlineStr">
+        <is>
+          <t>183.0</t>
+        </is>
+      </c>
+      <c r="F862" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G862" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="H862" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I862" s="2" t="inlineStr"/>
+      <c r="J862" s="2" t="inlineStr"/>
+      <c r="K862" s="2" t="inlineStr"/>
+    </row>
+    <row r="863">
+      <c r="A863" s="2" t="n">
+        <v>382</v>
+      </c>
+      <c r="B863" s="2" t="inlineStr">
+        <is>
+          <t>【跨境原装】资生堂红腰子洗面奶女洁面乳膏氨基酸清洁保湿旗舰店</t>
+        </is>
+      </c>
+      <c r="C863" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO红腰子洁面125ml</t>
+        </is>
+      </c>
+      <c r="D863" s="2" t="inlineStr"/>
+      <c r="E863" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="F863" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G863" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="H863" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I863" s="2" t="inlineStr"/>
+      <c r="J863" s="2" t="inlineStr">
+        <is>
+          <t>已选: 125ml [温和保湿]红腰子洁面乳+嫩白洇色蛋</t>
+        </is>
+      </c>
+      <c r="K863" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="2" t="n">
+        <v>382</v>
+      </c>
+      <c r="B864" s="2" t="inlineStr">
+        <is>
+          <t>【跨境原装】资生堂洁面膏红腰子洗面奶深层清洁保湿去黄黑头提亮</t>
+        </is>
+      </c>
+      <c r="C864" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO红腰子洁面125ml</t>
+        </is>
+      </c>
+      <c r="D864" s="2" t="inlineStr"/>
+      <c r="E864" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="F864" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G864" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="H864" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I864" s="2" t="inlineStr"/>
+      <c r="J864" s="2" t="inlineStr">
+        <is>
+          <t>已选: 175ml[正装125ml+中样50ml]洁面膏+滴形妆蛋球1</t>
+        </is>
+      </c>
+      <c r="K864" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="2" t="n">
+        <v>383</v>
+      </c>
+      <c r="B865" s="2" t="inlineStr">
+        <is>
+          <t>【特价清仓】资生堂悦薇智感紧塑焕白眼霜15ml 紧致淡纹提亮眼周</t>
+        </is>
+      </c>
+      <c r="C865" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO悦薇抗糖眼霜（新版）15ml</t>
+        </is>
+      </c>
+      <c r="D865" s="2" t="inlineStr">
+        <is>
+          <t>258.0</t>
+        </is>
+      </c>
+      <c r="E865" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="F865" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G865" s="2" t="inlineStr"/>
+      <c r="H865" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I865" s="2" t="inlineStr"/>
+      <c r="J865" s="2" t="inlineStr"/>
+      <c r="K865" s="2" t="inlineStr"/>
+    </row>
+    <row r="866">
+      <c r="A866" s="2" t="n">
+        <v>384</v>
+      </c>
+      <c r="B866" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】资生堂盼丽风姿智感抚纹眼霜15ml小雷达抗皱紧致礼物</t>
+        </is>
+      </c>
+      <c r="C866" s="2" t="inlineStr">
+        <is>
+          <t>资生堂/SHISEIDO盼丽风姿眼霜（新款）15ml</t>
+        </is>
+      </c>
+      <c r="D866" s="2" t="inlineStr">
+        <is>
+          <t>193.4</t>
+        </is>
+      </c>
+      <c r="E866" s="2" t="inlineStr">
+        <is>
+          <t>118.0</t>
+        </is>
+      </c>
+      <c r="F866" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G866" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="H866" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I866" s="2" t="inlineStr"/>
+      <c r="J866" s="2" t="inlineStr"/>
+      <c r="K866" s="2" t="inlineStr"/>
+    </row>
+    <row r="867">
+      <c r="A867" s="2" t="n">
+        <v>385</v>
+      </c>
+      <c r="B867" s="2" t="inlineStr">
+        <is>
+          <t>【雅诗兰黛】DW持妆粉底液1C1 66#瓷白色 30ml</t>
+        </is>
+      </c>
+      <c r="C867" s="2" t="inlineStr">
+        <is>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1C1 30ML 新版 2026年</t>
+        </is>
+      </c>
+      <c r="D867" s="2" t="inlineStr"/>
+      <c r="E867" s="2" t="inlineStr">
+        <is>
+          <t>293.0</t>
+        </is>
+      </c>
+      <c r="F867" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G867" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="H867" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I867" s="2" t="inlineStr"/>
+      <c r="J867" s="2" t="inlineStr"/>
+      <c r="K867" s="2" t="inlineStr"/>
+    </row>
+    <row r="868">
+      <c r="A868" s="2" t="n">
+        <v>386</v>
+      </c>
+      <c r="B868" s="2" t="inlineStr">
+        <is>
+          <t>Estee Lauder/雅诗兰黛 DW持妆粉底液30ml#1N2 柔光遮瑕【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C868" s="2" t="inlineStr">
+        <is>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N2 30ML 新版 2026</t>
+        </is>
+      </c>
+      <c r="D868" s="2" t="inlineStr">
+        <is>
+          <t>399.0</t>
+        </is>
+      </c>
+      <c r="E868" s="2" t="inlineStr">
+        <is>
+          <t>224.0</t>
+        </is>
+      </c>
+      <c r="F868" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G868" s="2" t="inlineStr"/>
+      <c r="H868" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I868" s="2" t="inlineStr"/>
+      <c r="J868" s="2" t="inlineStr"/>
+      <c r="K868" s="2" t="inlineStr"/>
+    </row>
+    <row r="869">
+      <c r="A869" s="2" t="n">
+        <v>386</v>
+      </c>
+      <c r="B869" s="2" t="inlineStr">
+        <is>
+          <t>Estee Lauder/雅诗兰黛dw持粉底液#1N2油皮亲妈持妆粉底液30ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C869" s="2" t="inlineStr">
+        <is>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N2 30ML 新版 2026</t>
+        </is>
+      </c>
+      <c r="D869" s="2" t="inlineStr"/>
+      <c r="E869" s="2" t="inlineStr">
+        <is>
+          <t>249.0</t>
+        </is>
+      </c>
+      <c r="F869" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G869" s="2" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="H869" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I869" s="2" t="inlineStr"/>
+      <c r="J869" s="2" t="inlineStr"/>
+      <c r="K869" s="2" t="inlineStr"/>
+    </row>
+    <row r="870">
+      <c r="A870" s="2" t="n">
+        <v>386</v>
+      </c>
+      <c r="B870" s="2" t="inlineStr">
+        <is>
+          <t>【原装正品】雅诗兰黛DW持妆粉底液 油皮亲妈持久不脱妆遮瑕控油</t>
+        </is>
+      </c>
+      <c r="C870" s="2" t="inlineStr">
+        <is>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N2 30ML 新版 2026</t>
+        </is>
+      </c>
+      <c r="D870" s="2" t="inlineStr"/>
+      <c r="E870" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="F870" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G870" s="2" t="inlineStr"/>
+      <c r="H870" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I870" s="2" t="inlineStr"/>
+      <c r="J870" s="2" t="inlineStr">
+        <is>
+          <t>已选: 1W2 自然色（全新原装） 30mL 个人 DW-粉底液 赠彩妆蛋 压头[新旧版随机]</t>
+        </is>
+      </c>
+      <c r="K870" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="2" t="n">
+        <v>387</v>
+      </c>
+      <c r="B871" s="2" t="inlineStr">
+        <is>
+          <t>Estee Lauder/雅诗兰黛 DW持妆粉底液30ml#1N2 柔光遮瑕【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C871" s="2" t="inlineStr">
+        <is>
+          <t>ESTEE LAUDER /雅诗兰黛 DW持妆粉底液 #1N1 30ML 新版 2026</t>
+        </is>
+      </c>
+      <c r="D871" s="2" t="inlineStr">
+        <is>
+          <t>399.0</t>
+        </is>
+      </c>
+      <c r="E871" s="2" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="F871" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G871" s="2" t="inlineStr"/>
+      <c r="H871" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I871" s="2" t="inlineStr"/>
+      <c r="J871" s="2" t="inlineStr">
+        <is>
+          <t>已选: 30mL 1N2</t>
+        </is>
+      </c>
+      <c r="K871" s="2" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="2" t="n">
+        <v>388</v>
+      </c>
+      <c r="B872" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】MAC/魅可大子弹头口红哑光柔雾666大宠粉602大辣椒</t>
+        </is>
+      </c>
+      <c r="C872" s="2" t="inlineStr">
+        <is>
+          <t>MAC魅可 丝柔哑光唇膏 大子弹口红#666 Sweet Deal 玫瑰冷萃</t>
+        </is>
+      </c>
+      <c r="D872" s="2" t="inlineStr"/>
+      <c r="E872" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="F872" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G872" s="2" t="inlineStr"/>
+      <c r="H872" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I872" s="2" t="inlineStr"/>
+      <c r="J872" s="2" t="inlineStr">
+        <is>
+          <t>已选: 大宠粉[666] 赠专柜礼盒+正品保障+假一赔十</t>
+        </is>
+      </c>
+      <c r="K872" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="B873" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销401万+件】韩国兰芝新款马卡龙防晒隔离霜30ml遮瑕妆前乳打底</t>
+        </is>
+      </c>
+      <c r="C873" s="2" t="inlineStr">
+        <is>
+          <t>兰芝马卡龙隔离30ml紫色</t>
+        </is>
+      </c>
+      <c r="D873" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="E873" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="F873" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G873" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="H873" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I873" s="2" t="inlineStr"/>
+      <c r="J873" s="2" t="inlineStr"/>
+      <c r="K873" s="2" t="inlineStr"/>
+    </row>
+    <row r="874">
+      <c r="A874" s="2" t="n">
+        <v>390</v>
+      </c>
+      <c r="B874" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销401万+件】韩国LANEIGE兰芝新款马卡龙防晒隔离霜遮瑕三合一妆前乳打底</t>
+        </is>
+      </c>
+      <c r="C874" s="2" t="inlineStr">
+        <is>
+          <t>兰芝马卡龙隔离30ml绿色</t>
+        </is>
+      </c>
+      <c r="D874" s="2" t="inlineStr">
+        <is>
+          <t>68.9</t>
+        </is>
+      </c>
+      <c r="E874" s="2" t="inlineStr">
+        <is>
+          <t>68.9</t>
+        </is>
+      </c>
+      <c r="F874" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G874" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="H874" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I874" s="2" t="inlineStr"/>
+      <c r="J874" s="2" t="inlineStr">
+        <is>
+          <t>已选: 兰芝紫隔离30ml[新版马卡龙]</t>
+        </is>
+      </c>
+      <c r="K874" s="2" t="inlineStr">
+        <is>
+          <t>68.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="2" t="n">
+        <v>391</v>
+      </c>
+      <c r="B875" s="2" t="inlineStr">
+        <is>
+          <t>【资生堂】悦薇抗糖面霜智感塑颜抗皱霜焕白清爽资生堂面霜50ml【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C875" s="2" t="inlineStr">
+        <is>
+          <t>资生堂 悦薇大抗糖滋润面霜（新款）50mL</t>
+        </is>
+      </c>
+      <c r="D875" s="2" t="inlineStr"/>
+      <c r="E875" s="2" t="inlineStr">
+        <is>
+          <t>309.0</t>
+        </is>
+      </c>
+      <c r="F875" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G875" s="2" t="inlineStr"/>
+      <c r="H875" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I875" s="2" t="inlineStr"/>
+      <c r="J875" s="2" t="inlineStr"/>
+      <c r="K875" s="2" t="inlineStr"/>
+    </row>
+    <row r="876">
+      <c r="A876" s="2" t="n">
+        <v>391</v>
+      </c>
+      <c r="B876" s="2" t="inlineStr">
+        <is>
+          <t>【资生堂】悦薇面霜抗糖抗初老补水紧致智感紧塑焕白霜</t>
+        </is>
+      </c>
+      <c r="C876" s="2" t="inlineStr">
+        <is>
+          <t>资生堂 悦薇大抗糖滋润面霜（新款）50mL</t>
+        </is>
+      </c>
+      <c r="D876" s="2" t="inlineStr">
+        <is>
+          <t>359.0</t>
+        </is>
+      </c>
+      <c r="E876" s="2" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="F876" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G876" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="H876" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I876" s="2" t="inlineStr"/>
+      <c r="J876" s="2" t="inlineStr">
+        <is>
+          <t>已选: 50mL [滋润型]悦薇面霜</t>
+        </is>
+      </c>
+      <c r="K876" s="2" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="2" t="n">
+        <v>392</v>
+      </c>
+      <c r="B877" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】娜斯5894大白饼粉饼控油磨皮持妆蜜粉饼【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C877" s="2" t="inlineStr">
+        <is>
+          <t>NARS蜜粉饼5894 效期24年</t>
+        </is>
+      </c>
+      <c r="D877" s="2" t="inlineStr"/>
+      <c r="E877" s="2" t="inlineStr">
+        <is>
+          <t>299.0</t>
+        </is>
+      </c>
+      <c r="F877" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G877" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="H877" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I877" s="2" t="inlineStr"/>
+      <c r="J877" s="2" t="inlineStr"/>
+      <c r="K877" s="2" t="inlineStr"/>
+    </row>
+    <row r="878">
+      <c r="A878" s="2" t="n">
+        <v>392</v>
+      </c>
+      <c r="B878" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】娜斯 流光美肌轻透蜜粉饼5894大白饼粉饼10g【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C878" s="2" t="inlineStr">
+        <is>
+          <t>NARS蜜粉饼5894 效期24年</t>
+        </is>
+      </c>
+      <c r="D878" s="2" t="inlineStr"/>
+      <c r="E878" s="2" t="inlineStr">
+        <is>
+          <t>169.0</t>
+        </is>
+      </c>
+      <c r="F878" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G878" s="2" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="H878" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I878" s="2" t="inlineStr"/>
+      <c r="J878" s="2" t="inlineStr"/>
+      <c r="K878" s="2" t="inlineStr"/>
+    </row>
+    <row r="879">
+      <c r="A879" s="2" t="n">
+        <v>392</v>
+      </c>
+      <c r="B879" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】娜斯5894大白饼粉饼控油磨皮持妆蜜粉饼【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C879" s="2" t="inlineStr">
+        <is>
+          <t>NARS蜜粉饼5894 效期24年</t>
+        </is>
+      </c>
+      <c r="D879" s="2" t="inlineStr"/>
+      <c r="E879" s="2" t="inlineStr">
+        <is>
+          <t>169.0</t>
+        </is>
+      </c>
+      <c r="F879" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G879" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="H879" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I879" s="2" t="inlineStr"/>
+      <c r="J879" s="2" t="inlineStr"/>
+      <c r="K879" s="2" t="inlineStr"/>
+    </row>
+    <row r="880">
+      <c r="A880" s="2" t="n">
+        <v>393</v>
+      </c>
+      <c r="B880" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销248.5万+件】whoo后拱辰享泡沫洗面奶水妍津率享深层清洁控油洁面女</t>
+        </is>
+      </c>
+      <c r="C880" s="2" t="inlineStr">
+        <is>
+          <t>WHOO/后拱辰享洁面泡沫180ml/支 （新条码）</t>
+        </is>
+      </c>
+      <c r="D880" s="2" t="inlineStr"/>
+      <c r="E880" s="2" t="inlineStr">
+        <is>
+          <t>119.9</t>
+        </is>
+      </c>
+      <c r="F880" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G880" s="2" t="inlineStr"/>
+      <c r="H880" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I880" s="2" t="inlineStr"/>
+      <c r="J880" s="2" t="inlineStr">
+        <is>
+          <t>已选: 美白洁面套180ML+洁面40ML</t>
+        </is>
+      </c>
+      <c r="K880" s="2" t="inlineStr">
+        <is>
+          <t>119.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="2" t="n">
+        <v>394</v>
+      </c>
+      <c r="B881" s="2" t="inlineStr">
+        <is>
+          <t>【资生堂】红腰子精华液4.0紧致抗皱面部护肤抗初老120ml</t>
+        </is>
+      </c>
+      <c r="C881" s="2" t="inlineStr">
+        <is>
+          <t>SHISEIDO资生堂红腰子精华100ml</t>
+        </is>
+      </c>
+      <c r="D881" s="2" t="inlineStr">
+        <is>
+          <t>599.0</t>
+        </is>
+      </c>
+      <c r="E881" s="2" t="inlineStr">
+        <is>
+          <t>368.0</t>
+        </is>
+      </c>
+      <c r="F881" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G881" s="2" t="inlineStr"/>
+      <c r="H881" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I881" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J881" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K881" s="2" t="inlineStr"/>
+    </row>
+    <row r="882">
+      <c r="A882" s="2" t="n">
+        <v>394</v>
+      </c>
+      <c r="B882" s="2" t="inlineStr">
+        <is>
+          <t>同城用户刚刚拼成&amp;#10;可参与拼单马上拼</t>
+        </is>
+      </c>
+      <c r="C882" s="2" t="inlineStr">
+        <is>
+          <t>SHISEIDO资生堂红腰子精华100ml</t>
+        </is>
+      </c>
+      <c r="D882" s="2" t="inlineStr"/>
+      <c r="E882" s="2" t="inlineStr"/>
+      <c r="F882" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G882" s="2" t="inlineStr"/>
+      <c r="H882" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I882" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J882" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K882" s="2" t="inlineStr"/>
+    </row>
+    <row r="883">
+      <c r="A883" s="2" t="n">
+        <v>394</v>
+      </c>
+      <c r="B883" s="2" t="inlineStr">
+        <is>
+          <t>【6671人收藏】服装店袋子塑料袋购物袋礼品袋包装袋网红手提袋子服装店袋子批发</t>
+        </is>
+      </c>
+      <c r="C883" s="2" t="inlineStr">
+        <is>
+          <t>SHISEIDO资生堂红腰子精华100ml</t>
+        </is>
+      </c>
+      <c r="D883" s="2" t="inlineStr"/>
+      <c r="E883" s="2" t="inlineStr"/>
+      <c r="F883" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G883" s="2" t="inlineStr"/>
+      <c r="H883" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I883" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J883" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K883" s="2" t="inlineStr"/>
+    </row>
+    <row r="884">
+      <c r="A884" s="2" t="n">
+        <v>394</v>
+      </c>
+      <c r="B884" s="2" t="inlineStr">
+        <is>
+          <t>【清仓】筋膜球足底按摩球腰背部肌肉放松瑜伽肩颈腿膜健身筋膜球</t>
+        </is>
+      </c>
+      <c r="C884" s="2" t="inlineStr">
+        <is>
+          <t>SHISEIDO资生堂红腰子精华100ml</t>
+        </is>
+      </c>
+      <c r="D884" s="2" t="inlineStr"/>
+      <c r="E884" s="2" t="inlineStr"/>
+      <c r="F884" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G884" s="2" t="inlineStr"/>
+      <c r="H884" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I884" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J884" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K884" s="2" t="inlineStr"/>
+    </row>
+    <row r="885">
+      <c r="A885" s="2" t="n">
+        <v>395</v>
+      </c>
+      <c r="B885" s="2" t="inlineStr">
+        <is>
+          <t>【1.37万人评价品牌正品】GUCCI/古驰炼金士花园系列香水100ML正品香氛送礼</t>
+        </is>
+      </c>
+      <c r="C885" s="2" t="inlineStr">
+        <is>
+          <t>古驰炼金师花园香草颂香水100ML</t>
+        </is>
+      </c>
+      <c r="D885" s="2" t="inlineStr">
+        <is>
+          <t>1099.0</t>
+        </is>
+      </c>
+      <c r="E885" s="2" t="inlineStr">
+        <is>
+          <t>736.36</t>
+        </is>
+      </c>
+      <c r="F885" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G885" s="2" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="H885" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I885" s="2" t="inlineStr"/>
+      <c r="J885" s="2" t="inlineStr"/>
+      <c r="K885" s="2" t="inlineStr"/>
+    </row>
+    <row r="886">
+      <c r="A886" s="2" t="n">
+        <v>395</v>
+      </c>
+      <c r="B886" s="2" t="inlineStr">
+        <is>
+          <t>同城用户刚刚拼成&amp;#10;可参与拼单马上拼</t>
+        </is>
+      </c>
+      <c r="C886" s="2" t="inlineStr">
+        <is>
+          <t>古驰炼金师花园香草颂香水100ML</t>
+        </is>
+      </c>
+      <c r="D886" s="2" t="inlineStr"/>
+      <c r="E886" s="2" t="inlineStr"/>
+      <c r="F886" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G886" s="2" t="inlineStr"/>
+      <c r="H886" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I886" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J886" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K886" s="2" t="inlineStr"/>
+    </row>
+    <row r="887">
+      <c r="A887" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="B887" s="2" t="inlineStr">
+        <is>
+          <t>【百补品牌热销40.6万件】GUCCI/古驰炼金士花园系列香水150ML简装持久留香</t>
+        </is>
+      </c>
+      <c r="C887" s="2" t="inlineStr">
+        <is>
+          <t>古驰炼金师花园沐光橙香水100ML</t>
+        </is>
+      </c>
+      <c r="D887" s="2" t="inlineStr">
+        <is>
+          <t>845.0</t>
+        </is>
+      </c>
+      <c r="E887" s="2" t="inlineStr">
+        <is>
+          <t>549.49</t>
+        </is>
+      </c>
+      <c r="F887" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G887" s="2" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="H887" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I887" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J887" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K887" s="2" t="inlineStr"/>
+    </row>
+    <row r="888">
+      <c r="A888" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="B888" s="2" t="inlineStr">
+        <is>
+          <t>【百补品牌热销40.6万件】GUCCI/古驰炼金士花园系列香水100ML正品香氛送礼</t>
+        </is>
+      </c>
+      <c r="C888" s="2" t="inlineStr">
+        <is>
+          <t>古驰炼金师花园沐光橙香水100ML</t>
+        </is>
+      </c>
+      <c r="D888" s="2" t="inlineStr">
+        <is>
+          <t>1099.0</t>
+        </is>
+      </c>
+      <c r="E888" s="2" t="inlineStr">
+        <is>
+          <t>736.36</t>
+        </is>
+      </c>
+      <c r="F888" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G888" s="2" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="H888" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I888" s="2" t="inlineStr"/>
+      <c r="J888" s="2" t="inlineStr"/>
+      <c r="K888" s="2" t="inlineStr"/>
+    </row>
+    <row r="889">
+      <c r="A889" s="2" t="n">
+        <v>397</v>
+      </c>
+      <c r="B889" s="2" t="inlineStr">
+        <is>
+          <t>Maison Margiela 梅森马吉拉马丁马吉拉香水 慵懒周末/沙滩漫步【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C889" s="2" t="inlineStr">
+        <is>
+          <t>马丁马吉拉-爵士酒廊淡香100ml</t>
+        </is>
+      </c>
+      <c r="D889" s="2" t="inlineStr"/>
+      <c r="E889" s="2" t="inlineStr">
+        <is>
+          <t>585</t>
+        </is>
+      </c>
+      <c r="F889" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G889" s="2" t="inlineStr"/>
+      <c r="H889" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I889" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=0.0%)</t>
+        </is>
+      </c>
+      <c r="J889" s="2" t="inlineStr">
+        <is>
+          <t>已选: 温暖壁炉/壁炉火光100ml</t>
+        </is>
+      </c>
+      <c r="K889" s="2" t="inlineStr">
+        <is>
+          <t>585</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="2" t="n">
+        <v>398</v>
+      </c>
+      <c r="B890" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰全新爱心唇釉610 416 622 440限定浮雕黑管</t>
+        </is>
+      </c>
+      <c r="C890" s="2" t="inlineStr">
+        <is>
+          <t>YSL新款爱心唇釉610#</t>
+        </is>
+      </c>
+      <c r="D890" s="2" t="inlineStr"/>
+      <c r="E890" s="2" t="inlineStr">
+        <is>
+          <t>154.7</t>
+        </is>
+      </c>
+      <c r="F890" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G890" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H890" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I890" s="2" t="inlineStr"/>
+      <c r="J890" s="2" t="inlineStr">
+        <is>
+          <t>已选: 610 冰乌龙</t>
+        </is>
+      </c>
+      <c r="K890" s="2" t="inlineStr">
+        <is>
+          <t>154.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="B891" s="2" t="inlineStr">
+        <is>
+          <t>已优惠5元券后6.98已拼45.5万+件</t>
+        </is>
+      </c>
+      <c r="C891" s="2" t="inlineStr">
+        <is>
+          <t>宝格丽白茶淡香150ml</t>
+        </is>
+      </c>
+      <c r="D891" s="2" t="inlineStr"/>
+      <c r="E891" s="2" t="inlineStr"/>
+      <c r="F891" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G891" s="2" t="inlineStr"/>
+      <c r="H891" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I891" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J891" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K891" s="2" t="inlineStr"/>
+    </row>
+    <row r="892">
+      <c r="A892" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="B892" s="2" t="inlineStr">
+        <is>
+          <t>【BVLGARI】宝格丽 白茶 香水 茶香系列 淡香水EDT 75ml/150ml</t>
+        </is>
+      </c>
+      <c r="C892" s="2" t="inlineStr">
+        <is>
+          <t>宝格丽白茶淡香150ml</t>
+        </is>
+      </c>
+      <c r="D892" s="2" t="inlineStr"/>
+      <c r="E892" s="2" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="F892" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G892" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="H892" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I892" s="2" t="inlineStr"/>
+      <c r="J892" s="2" t="inlineStr">
+        <is>
+          <t>已选: 150mL 宝格丽白茶</t>
+        </is>
+      </c>
+      <c r="K892" s="2" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="B893" s="2" t="inlineStr">
+        <is>
+          <t>【宝格丽】悠境白茶淡香75ml正装新款白茶清新茶香木质花香</t>
+        </is>
+      </c>
+      <c r="C893" s="2" t="inlineStr">
+        <is>
+          <t>宝格丽白茶淡香150ml</t>
+        </is>
+      </c>
+      <c r="D893" s="2" t="inlineStr">
+        <is>
+          <t>6991.0</t>
+        </is>
+      </c>
+      <c r="E893" s="2" t="inlineStr">
+        <is>
+          <t>699.0</t>
+        </is>
+      </c>
+      <c r="F893" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G893" s="2" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="H893" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I893" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J893" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K893" s="2" t="inlineStr"/>
+    </row>
+    <row r="894">
+      <c r="A894" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="B894" s="2" t="inlineStr">
+        <is>
+          <t>【宝格丽】宝格丽白茶香水 淡香水 150ml/5oz【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C894" s="2" t="inlineStr">
+        <is>
+          <t>宝格丽白茶淡香150ml</t>
+        </is>
+      </c>
+      <c r="D894" s="2" t="inlineStr"/>
+      <c r="E894" s="2" t="inlineStr">
+        <is>
+          <t>1026</t>
+        </is>
+      </c>
+      <c r="F894" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G894" s="2" t="inlineStr"/>
+      <c r="H894" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I894" s="2" t="inlineStr"/>
+      <c r="J894" s="2" t="inlineStr">
+        <is>
+          <t>已选: 150mL</t>
+        </is>
+      </c>
+      <c r="K894" s="2" t="inlineStr">
+        <is>
+          <t>1026</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="B895" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】植村秀绿茶卸妆洁颜油  温和深层清洁彩妆保湿</t>
+        </is>
+      </c>
+      <c r="C895" s="2" t="inlineStr">
+        <is>
+          <t>植村秀绿茶卸妆油150ml</t>
+        </is>
+      </c>
+      <c r="D895" s="2" t="inlineStr">
+        <is>
+          <t>380.0</t>
+        </is>
+      </c>
+      <c r="E895" s="2" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="F895" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G895" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="H895" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I895" s="2" t="inlineStr"/>
+      <c r="J895" s="2" t="inlineStr">
+        <is>
+          <t>已选: 150mL</t>
+        </is>
+      </c>
+      <c r="K895" s="2" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="B896" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】植村秀绿茶新肌洁颜油卸妆油150ml 去黄抗氧化</t>
+        </is>
+      </c>
+      <c r="C896" s="2" t="inlineStr">
+        <is>
+          <t>植村秀绿茶卸妆油150ml</t>
+        </is>
+      </c>
+      <c r="D896" s="2" t="inlineStr">
+        <is>
+          <t>380.0</t>
+        </is>
+      </c>
+      <c r="E896" s="2" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="F896" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G896" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="H896" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I896" s="2" t="inlineStr"/>
+      <c r="J896" s="2" t="inlineStr"/>
+      <c r="K896" s="2" t="inlineStr"/>
+    </row>
+    <row r="897">
+      <c r="A897" s="2" t="n">
+        <v>401</v>
+      </c>
+      <c r="B897" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】纳斯液体腮红BRAZEN西柚奶桃元气清透提气色易上色服帖持妆</t>
+        </is>
+      </c>
+      <c r="C897" s="2" t="inlineStr">
+        <is>
+          <t>NARS 水光绚色液体腮红 西柚奶桃 BRAZEN 7ml</t>
+        </is>
+      </c>
+      <c r="D897" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="E897" s="2" t="inlineStr">
+        <is>
+          <t>89.9</t>
+        </is>
+      </c>
+      <c r="F897" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G897" s="2" t="inlineStr"/>
+      <c r="H897" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I897" s="2" t="inlineStr"/>
+      <c r="J897" s="2" t="inlineStr">
+        <is>
+          <t>已选: 7mL （24年4月批次） NARS液体腮红BRAZEN 西柚奶桃</t>
+        </is>
+      </c>
+      <c r="K897" s="2" t="inlineStr">
+        <is>
+          <t>89.9</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/商品采集汇总.xlsx
+++ b/商品采集汇总.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3139,27 +3139,27 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>408</v>
-      </c>
-      <c r="B67" s="2" t="inlineStr"/>
+        <v>421</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>【超值囤货装】伊丽莎白雅顿经典润泽SPF15唇膏8小时保湿滋润防晒</t>
+        </is>
+      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>NARS液体腮红 INSATIABLE</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>10.46</t>
-        </is>
+          <t>伊丽莎白雅顿经典唇膏13g</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>119.98</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr"/>
@@ -3170,66 +3170,78 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；品名相似不足(ratio=0.0%)</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr"/>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>NARS/纳斯 小粉金液体腮红 #INSATIABLE 酒渍樱桃【5天内发货】</t>
+          <t>【官方正品】伊丽莎白雅顿唇膏经典润泽唇膏雅顿八小时润唇膏</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>NARS液体腮红 INSATIABLE</t>
+          <t>伊丽莎白雅顿经典唇膏13g</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
+      <c r="E68" s="2" t="n">
+        <v>119</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>408</v>
+        <v>6</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Nars纳斯夏季新品液体腮红小粉金管自然服帖显示牛奶粉紫杏茶玫瑰【5天内发货】</t>
+          <t>MAC/魅可 热吻棒唇膏口红 显色显白哑光滋润不掉色67狂野棕【5天内发货】</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>NARS液体腮红 INSATIABLE</t>
+          <t>MAC热吻棒67</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>175.0</t>
-        </is>
+      <c r="E69" s="2" t="n">
+        <v>72</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -3248,23 +3260,21 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>408</v>
+        <v>9</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>【NARS】纳斯全新小粉金液体腮红 腮紫牛奶粉紫色显嫩自然膨胀收缩色【5天内发货】</t>
+          <t>【NARS】超方瓶粉底液持妆持久养肤轻薄轻透奶油肌新年礼物送女友</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>NARS液体腮红 INSATIABLE</t>
+          <t>NARS超方瓶粉底液L4</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>165.0</t>
-        </is>
+      <c r="E70" s="2" t="n">
+        <v>228</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -3274,36 +3284,38 @@
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>421</v>
+        <v>9</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>【超值囤货装】伊丽莎白雅顿经典润泽SPF15唇膏8小时保湿滋润防晒</t>
+          <t>【正品行货】娜斯/纳斯全新超方瓶粉底液L02流光美肌养肤遮瑕持久</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>伊丽莎白雅顿经典唇膏13g</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>199.0</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>119.98</t>
-        </is>
+          <t>NARS超方瓶粉底液L4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="n">
+        <v>238</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -3330,34 +3342,28 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>421</v>
+        <v>9</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>【官方正品】伊丽莎白雅顿唇膏经典润泽唇膏雅顿八小时润唇膏</t>
+          <t>【正品行货】娜斯/纳斯NARS超方瓶粉底液L02流光美肌养肤遮瑕持久</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>伊丽莎白雅顿经典唇膏13g</t>
+          <t>NARS超方瓶粉底液L4</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>119.0</t>
-        </is>
+      <c r="E72" s="2" t="n">
+        <v>256</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
+      <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -3374,6 +3380,244 @@
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】纳斯超方瓶粉底液新款小方瓶L0L2持久不脱妆养肤保湿遮瑕正品</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>NARS超方瓶粉底液L4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="n">
+        <v>338</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 【L4】黄二白 +  美妆蛋</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】纳斯 超方瓶流光美肌粉底液 L1 30ml提亮肤色</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>NARS 超方瓶粉底液#L1</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>【NARS】纳斯 超方瓶流光美肌粉底液 L1 30ml提亮肤色</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>NARS 超方瓶粉底液#L1</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>289.0</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>【拉夫劳伦】Ralph Lauren POLO俱乐部Ralph'sClub男士浓淡香水木质调【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>拉夫劳伦俱乐部香水淡香型 100ML</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>【拉夫劳伦】俱乐部小熊限定香水l肖战同款馥奇木质香男士持久淡香</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>拉夫劳伦俱乐部香水淡香型 100ML</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>255.9</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>【拉夫劳伦】俱乐部男士香水100ml 木质调持久留香 秋冬氛围感渣男香</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>拉夫劳伦俱乐部香水淡香型 100ML</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>255.9</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/商品采集汇总.xlsx
+++ b/商品采集汇总.xlsx
@@ -437,20 +437,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="42" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -512,97 +512,97 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>【520礼物】MAC/魅可热吻棒银管细管口红67 狂野棕约会礼物礼盒装</t>
+          <t>【正品行货】CPB肌肤之钥御龄防晒霜50ml 防晒乳</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>MAC热吻棒67</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
+          <t>CPB防晒霜50g</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>400</v>
+      </c>
       <c r="E2" s="2" t="n">
-        <v>82</v>
+        <v>312.8</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>已选: 简装款*可代写贺卡 [67]狂野棕 Meticulous +mac热吻棒</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>82</v>
-      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>双支CPB肌肤之钥洁面滋润型125ml温和清洁</t>
+        </is>
+      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>NARS超方瓶粉底液L4</t>
+          <t>CPB滋润洁面125ml</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="n">
-        <v>11.9</v>
+        <v>352</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】NARS纳斯超方瓶粉底液流光美肌轻薄润贴不脱妆不卡粉</t>
+          <t>【CPB】肌肤之钥滋润洗面奶125ml洁面乳深层清洁滋润温和控油【5天内发货】</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>NARS超方瓶粉底液L4</t>
+          <t>CPB滋润洁面125ml</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="n">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -612,120 +612,106 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；规格匹配失败</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>【NARS】纳斯超方瓶持妆粉底液流光美肌养肤遮瑕</t>
+          <t>【CPB】肌肤之钥滋润洗面奶125ml洁面乳深层清洁滋润温和控油【5天内发货】</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>NARS超方瓶粉底液L4</t>
+          <t>CPB滋润洁面125ml</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="n">
-        <v>256</v>
+        <v>189</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；规格匹配失败</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>【5097人收藏】NARS/纳斯超方瓶娜斯粉底液新品流光美肌养肤遮瑕持久不脱妆干皮</t>
+          <t>【正品行货】CPB/肌肤之钥隔离霜保湿长管哑光清爽妆前乳38ml</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>NARS超方瓶粉底液L4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>368</v>
-      </c>
+          <t>CPB长管隔离38ml 清爽</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="n">
-        <v>338</v>
+        <v>380</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>已选: [L4] DEAUVILLE黄二白</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>338</v>
-      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>【Healthy Care】澳洲进口木瓜膏正品100g万能保湿滋润止痒润唇膏护臀</t>
+          <t>【正品行货】 CPB长管隔离37ml 光凝润采妆前霜 防晒保湿</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>澳洲木瓜膏16g</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr"/>
+          <t>CPB长管隔离新款37ml滋润</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>225</v>
+      </c>
       <c r="E7" s="2" t="n">
-        <v>58</v>
+        <v>198</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -734,84 +720,76 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；规格匹配失败</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Nature BOBO/漾然澳洲番木瓜膏16g*1瓶润唇膏保湿女唇膜霜油</t>
+          <t>【正品行货】 CPB长管隔离37ml 光凝润采妆前霜 防晒保湿</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>澳洲木瓜膏16g</t>
+          <t>CPB长管隔离新款37ml滋润</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>28.69</v>
+        <v>252</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>17.89</v>
+        <v>195</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>已选: BOBO澳洲木瓜膏 16g*1瓶</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>17.89</v>
-      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Nature BOBO澳洲番木瓜膏16g*2支润唇膏保湿女唇膜霜油滋润保湿</t>
+          <t>MAC/魅可经典子弹头口红#923 滋润唇膏哑光持久【5天内发货】</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>澳洲木瓜膏16g</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr"/>
+          <t>MAC 子弹头口红 923# STAY CURIOUS</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>122</v>
+      </c>
       <c r="E9" s="2" t="n">
-        <v>25.1</v>
+        <v>120.7</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -825,77 +803,59 @@
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>已选: 16g*2支</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>25.1</v>
-      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>【三只松鼠】生椰脆100g*1袋即食薄脆椰果休闲果干蜜饯零食</t>
+          <t>MAC/魅可口红 923 Stay Curious  3g【6月26日发完】</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>TF白麝香 100ml</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>12.4</v>
-      </c>
+          <t>MAC 子弹头口红 923# STAY CURIOUS</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="n">
-        <v>10.4</v>
+        <v>125</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；品名相似不足(ratio=0.0%)；规格匹配失败</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>TOMFORD 汤姆福特 TF白麝香护手霜100ML 日本专柜版【5天内发货】</t>
+          <t>316魅可MAC口红916 930 549 543小辣椒646情人节544礼物 热吻棒67</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>TF白麝香 100ml</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>385</v>
-      </c>
+          <t>MAC 子弹头口红 923# STAY CURIOUS</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="n">
-        <v>364</v>
+        <v>119</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -909,26 +869,32 @@
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 923# stay curious</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>【TOM FORD】 汤姆福特 TF 白麝香身体喷雾150ML【5天内发货】</t>
+          <t>魅可/MAC热吻棒银管哑光口红锁色细管唇膏67 69 79持久显色【5天内发货】</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>TF白麝香 100ml</t>
+          <t>MAC热吻棒67</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="n">
-        <v>495</v>
+        <v>72</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -938,90 +904,80 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；规格匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr"/>
+          <t>已选择： 67#狂野棕 1.8g</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>TF白麝香身体止汗喷雾150ml柔和留香持久</t>
+          <t>【专柜礼盒】MAC魅可热吻棒银管细管口红哑光锁色唇膏67正品行货</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>TF白麝香 100ml</t>
+          <t>MAC热吻棒67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="n">
-        <v>405</v>
+        <v>83</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2025-10-04</t>
-        </is>
-      </c>
+      <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；规格匹配失败</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>【南国】100g椰子角海南特产椰果生椰脆块袋装零食肉块椰果片果干零食</t>
+          <t>【520情人节】MAC/魅可热吻棒银管细管67 69 任性莓哑光口红正品</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>黛珂AQ舒活白檀美白乳液200ml</t>
+          <t>MAC热吻棒67</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="n">
-        <v>11.9</v>
+        <v>81</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-05</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -1029,7 +985,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+          <t>规格匹配失败</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1041,156 +997,130 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>川崎品牌官方正品，100%保障</t>
+          <t>【MAC】魅可新品紫白饼粉饼双色去黄提亮柔焦控油轻薄【5天内发货】</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>黛珂牛油果乳液 300ml</t>
+          <t>MAC紫白饼</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>12.5</v>
+        <v>190</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>10</v>
+        <v>135</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】黛珂牛油果植萃乳液祛痘控油保湿紧致150ml</t>
+          <t>MiuMiu缪缪女士EDP淡香精 50ML 经典同名红盖浓香水 花香调</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>黛珂牛油果乳液 300ml</t>
+          <t>MiuMiu紅蓋同名女士濃香水50ml</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="n">
-        <v>103.7</v>
+        <v>599</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；规格匹配失败</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】黛珂牛油果植萃乳液祛痘控油保湿紧致150ml</t>
+          <t>MIUMIU缪缪同名女士香水EDP50ml</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>黛珂牛油果乳液 300ml</t>
+          <t>MiuMiu紅蓋同名女士濃香水50ml</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="n">
-        <v>94</v>
+        <v>479</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；规格匹配失败</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>【黛珂】牛油果乳天然植物乳液保湿平衡水油300ml大容量</t>
+          <t>【NARS】超方瓶粉底液持妆持久养肤轻薄轻透奶油肌新年礼物送女友</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>黛珂牛油果乳液 300ml</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>288</v>
-      </c>
+          <t>NARS超方瓶粉底液L4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="n">
-        <v>159</v>
+        <v>228</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1200,32 +1130,38 @@
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>【黛珂】牛油果植物乳液控油保湿滋润补水嫩白300ml【5天内发货】</t>
+          <t>【正品行货】娜斯/纳斯全新超方瓶粉底液L02流光美肌养肤遮瑕持久</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>黛珂牛油果乳液 300ml</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>205</v>
-      </c>
+          <t>NARS超方瓶粉底液L4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="n">
-        <v>134</v>
+        <v>256</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1235,149 +1171,163 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>【黛珂】2024新版心悦容光幻纱丝柔蜜粉细腻柔滑持久定妆</t>
+          <t>【NARS】超方瓶粉底液持妆持久养肤轻薄轻透奶油肌新年礼物送女友</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>黛珂散粉01 24年新版</t>
+          <t>NARS超方瓶粉底液L4</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>169</v>
+        <v>883</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>128</v>
+        <v>358</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；规格匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
+          <t>已选择： 超方瓶*L4 黄二白+专柜礼盒</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>358</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>【黛珂】2024新版心悦容光幻纱丝柔蜜粉细腻柔滑持久定妆#01【5天内发货】</t>
+          <t>【NARS】纳斯超方瓶粉底液新款小方瓶L0L2持久不脱妆养肤保湿遮瑕正品</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>黛珂散粉01 24年新版</t>
+          <t>NARS超方瓶粉底液L4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="n">
-        <v>146</v>
+        <v>338</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>2024-06-01</t>
-        </is>
-      </c>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 【L4】黄二白 +  美妆蛋</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>338</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>【黛珂】2024新版心悦容光幻纱丝柔蜜粉细腻柔滑持久定妆【5天内发货】</t>
+          <t>【NARS】纳斯/娜斯超方瓶粉底液L0/L1/L2持妆遮瑕30ml</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>黛珂散粉01 24年新版</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr"/>
+          <t>NARS 超方瓶粉底液 L3#</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>289</v>
+      </c>
       <c r="E22" s="2" t="n">
-        <v>151</v>
+        <v>210</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>已选: 101#幻纱四色</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="n">
-        <v>151</v>
-      </c>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Decorte/黛珂散粉定妆粉10持久隐形白檀舞蝶丝绒蜜粉11 80 00正品</t>
+          <t>【NARS】超方瓶流光美肌粉底液#L1持久遮瑕水润30ml</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>黛珂散粉01 24年新版</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>303</v>
-      </c>
+          <t>NARS 超方瓶粉底液#L1</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="n">
         <v>178</v>
       </c>
@@ -1386,52 +1336,46 @@
           <t>否</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；规格匹配失败</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>【10.2万人回购该品牌】CosmeDecorte黛珂清爽护肤三件套(白泥洁面+牛油果乳液+紫苏水)</t>
+          <t>NARS/纳斯超方瓶粉底液美肌遮瑕粉底液l0/l1/l2/l3干皮本命持久</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>黛珂紫苏水 300ml</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>355</v>
-      </c>
+          <t>NARS 超方瓶粉底液#L2</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="n">
-        <v>303.87</v>
+        <v>279</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1441,7 +1385,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+          <t>规格匹配失败</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1453,23 +1397,21 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>【黛珂】DECORTE 紫苏水300ml+牛油果乳液300ml 水乳套装</t>
+          <t>【NARS】纳斯自然亮采持久超雾瓶粉底液 #L1 OSLO哑光长效持妆</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>黛珂紫苏水 300ml</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>459</v>
-      </c>
+          <t>NARS 粉底液 LO色</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="n">
-        <v>348</v>
+        <v>210</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1478,7 +1420,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1492,69 +1434,71 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>【三只松鼠】生椰脆100g*1袋即食薄脆椰果休闲果干蜜饯零食</t>
+          <t>【正品行货】NARS纳斯新版定妆散粉控油定妆持久隐形毛孔提亮11g</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>费列罗榛果巧克力制品T24</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr"/>
+          <t>NARS纳斯定妆散粉</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>206</v>
+      </c>
       <c r="E26" s="2" t="n">
-        <v>12.4</v>
+        <v>153</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-05</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=11.1%)；规格匹配失败</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>144</v>
+        <v>15</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>【南国】生椰脆椰子肉干50g袋装海南特产香烤椰子脆片椰子块休闲零食</t>
+          <t>Nars/纳斯自然亮采持久粉底液L1/L2/L4.5/M2持妆遮瑕哑光雾面30ml</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>蔻依北国雪松浓香水50ml</t>
+          <t>NARS 柔哑净瑕持妆粉底液45ml L3 GOBI</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="n">
-        <v>11.9</v>
+        <v>499</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -1562,76 +1506,74 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；品名相似不足(ratio=0.0%)</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr"/>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>144</v>
+        <v>15</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>【蔻依】仙境花园系列北国雪松香水150ml浓香持久留香</t>
+          <t>..Ꭿི྆sじ!ℳ࿆Ꭿི྆..618大促刚下单还差1人拼成现在拼</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>蔻依北国雪松浓香水50ml</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>859</v>
-      </c>
+          <t>NARS 柔哑净瑕持妆粉底液45ml L3 GOBI</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="n">
-        <v>739</v>
+        <v>11.6</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>已选: 150mL 1瓶 蔻依北国雪松香水EDP</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="n">
-        <v>739</v>
-      </c>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>144</v>
+        <v>16</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>【累计热销16.4万+件】Chloe/蔻依香水北国雪松50ml木质香调淡雅沉稳</t>
+          <t>【NARS】纳斯遮瑕膏圆罐香草肉桂卡仕达奶油痘印斑黑眼圈提亮泪沟正品</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>蔻依北国雪松浓香水50ml</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>719</v>
-      </c>
+          <t>NARS 遮瑕膏 VANILLA色号</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="n">
-        <v>455</v>
+        <v>188</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1640,76 +1582,74 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-01-05</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=10.0%)</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>152</v>
+        <v>16</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>【三只松鼠】生椰脆100g*1袋即食薄脆椰果休闲果干蜜饯零食</t>
+          <t>【NARS】遮瑕蜜纳斯遮暇膏遮斑点黑眼圈痘印卡仕达提亮液vanilla香草【5天内发货】</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>拉夫劳伦地球系列香氛 澳洲檀木 100ml</t>
+          <t>NARS 遮瑕膏 VANILLA色号</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="n">
-        <v>12.4</v>
+        <v>156</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；品名相似不足(ratio=0.0%)；规格匹配失败</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>152</v>
+        <v>16</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Ralph Lauren/拉夫劳伦地球系列经典地球淡香氛香水100ml持久留香【5天内发货】</t>
+          <t>原装正品NARS娜斯遮瑕蜜#1232Vanilla香草粉遮斑点痘印遮瑕膏6ml【5天内发货】</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>拉夫劳伦地球系列香氛 澳洲檀木 100ml</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr"/>
+          <t>NARS 遮瑕膏 VANILLA色号</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>138</v>
+      </c>
       <c r="E31" s="2" t="n">
-        <v>279</v>
+        <v>13</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -1719,29 +1659,39 @@
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=10.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>152</v>
+        <v>16</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>【Ralph Lauren】拉夫劳伦 地球系列淡香水EDT男女100ml清新持久【5天内发货】</t>
+          <t>原装正品NARS娜斯遮瑕蜜#1232Vanilla香草粉遮斑点痘印遮瑕膏6ml【5天内发货】</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>拉夫劳伦地球系列香氛 澳洲檀木 100ml</t>
+          <t>NARS 遮瑕膏 VANILLA色号</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="n">
+        <v>138</v>
+      </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -1750,32 +1700,40 @@
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>品名相似不足(ratio=10.0%)</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 6mL NARS遮瑕蜜#1232Vanilla香草粉</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>138</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>【拉夫劳伦】地球香水清新木质调中性淡香男女通用持久留香夏季清新</t>
+          <t>【原装正品】Nars/娜斯光透感蜜粉5894大白粉饼10g正品【5天内发货】</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>拉夫劳伦地球系列香氛 澳洲檀木 100ml</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>399</v>
-      </c>
+          <t>NARS5894蜜粉饼10G</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="n">
-        <v>279</v>
+        <v>170</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -1785,84 +1743,78 @@
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；品名相似不足(ratio=25.0%)</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>已选: 100mL （22年6月批次） 拉夫劳伦地球香水 EDT 淡香</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>279</v>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>175</v>
+        <v>17</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>【8.7万人收藏该品牌】LAURA MERCIER/罗拉玛斯亚 柔光透明蜜粉罗拉29g定妆</t>
+          <t>【NARS】娜斯 流光美肌轻透蜜粉饼5894大白饼粉饼10g【5天内发货】</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>罗拉散粉经典款29G</t>
+          <t>NARS5894蜜粉饼10G</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="n">
-        <v>109</v>
+        <v>220</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>品名相似不足(ratio=25.0%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>175</v>
+        <v>17</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Laura Mercier罗拉散粉新版Translucent柔光透明哑光控油定妆29g【5天内发货】</t>
+          <t>【NARS】娜斯 流光美肌轻透蜜粉饼5894大白饼粉饼10g【5天内发货】</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>罗拉散粉经典款29G</t>
+          <t>NARS5894蜜粉饼10G</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="n">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -1874,28 +1826,32 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>177</v>
+        <v>18</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>【三只松鼠】生椰脆100g*1袋即食薄脆椰果休闲果干蜜饯零食</t>
+          <t>【NARS】空气唇釉#684GIPSY玫瑰豆沙色哑光7.5ml(23.6产</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>慕拉得塑颜修复A醇精华30ml</t>
+          <t>NARS空气唇釉686 lose control</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="n">
-        <v>12.4</v>
+        <v>129</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -1903,7 +1859,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+          <t>规格不匹配；规格匹配失败</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -1915,67 +1871,73 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>【百补品牌热销1.2万件】骆王宇推荐Murad慕拉得视黄醇A醇精华30ml/支</t>
+          <t>【特价清仓】NARS纳斯唇釉空气柔雾唇霜352#Thrust 奶咖玫瑰7.5ml</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>慕拉得塑颜修复A醇精华30ml</t>
+          <t>NARS空气唇釉thrust</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>359</v>
+        <v>179</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>251.09</v>
+        <v>99</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>2025-06-13</t>
-        </is>
-      </c>
+      <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 7.5mL 【23年5月 产】 #352（原037）Thrust 奶咖玫瑰</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>191</v>
+        <v>19</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>【三只松鼠】生椰脆100g*1袋即食薄脆椰果休闲果干蜜饯零食</t>
+          <t>【NARS】NARS娜斯空气唇釉#037 #361 #360 #684 7.5ml/支</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
+          <t>NARS空气唇釉thrust</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="n">
-        <v>12.4</v>
+        <v>53.9</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -1983,7 +1945,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+          <t>规格匹配失败</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -1995,60 +1957,62 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>191</v>
+        <v>20</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>伟博 强效氨糖软骨素180粒硫酸中老年成维骨力D3促吸收强效补软骨【5天内发货】</t>
+          <t>【特价清仓】NARS纳斯口红细管哑光唇膏101#No Angel奶咖土棕1.5g</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
+          <t>NARS细管101 NO ANGEL</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>298</v>
+        <v>148</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>167</v>
+        <v>79.8</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
+      <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 1.5g 【23年8月 产】国际效期5年 细管口红101#No Angel 奶咖土棕</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>79.8</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>191</v>
+        <v>20</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>加拿大伟博硫酸氨糖软骨素中老年成人维骨力D3关节健康180粒【5天内发货】</t>
+          <t>【NARS】NARS娜斯细管口红#102 #116  #135 #133 #1011.5g/支</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
+          <t>NARS细管101 NO ANGEL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="n">
-        <v>167</v>
+        <v>54.9</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2057,48 +2021,52 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2023-03-29</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>伟博硫酸氨糖软骨素 中老年成人维骨力D3促吸收 加拿大进口 180粒【5天内发货】</t>
+          <t>【特价清仓】NARS纳斯细管口红哑光唇膏1.5g#116烟杏START ME UP</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>伟博天然氨糖D3维骨力胶囊300粒</t>
+          <t>NARS细管116 START ME UP</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>548</v>
+        <v>188</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>328</v>
+        <v>108.98</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>2025-09-12</t>
-        </is>
-      </c>
+      <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -2110,200 +2078,184 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>269</v>
+        <v>21</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>【YSL】 圣罗兰新款皮革气垫 B10 14g哑光遮瑕持妆ysl气垫控油正装</t>
+          <t>【NARS】NARS娜斯细管口红#102 #116  #135 #133 #1011.5g/支</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>圣罗兰黑色皮革气垫B10</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>399</v>
-      </c>
+          <t>NARS细管116 START ME UP</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="n">
-        <v>244</v>
+        <v>54.9</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2023-03-29</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>已选: 14g YSL皮革气垫B10新款</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="n">
-        <v>244</v>
-      </c>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>293</v>
+        <v>22</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】阿玛尼新款权力PRO权利1.5粉底液(亚洲人混油皮挚爱)</t>
+          <t>【特价清仓】NARS纳斯细管口红#133日烧赤粽TOO HOT TO HOLD 1.5g</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>阿玛尼权力PR0粉底1.5 30ml</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr"/>
+          <t>NARS细管133 TOO HOT TO HOLD</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>148</v>
+      </c>
       <c r="E43" s="2" t="n">
-        <v>25.5</v>
+        <v>79.8</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
+      <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>已选: 片装1ml*5（推荐） 红标PRO丝绒哑光粉一白#1.5 中性白</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="n">
-        <v>25.5</v>
-      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>293</v>
+        <v>22</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】阿玛尼权力粉底液1.5#权利PRO粉底液1.6# 2# 30ml</t>
+          <t>【NARS】纳斯细管口红哑光唇膏磨砂雾感133 清仓</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>阿玛尼权力PR0粉底1.5 30ml</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>279</v>
-      </c>
+          <t>NARS细管133 TOO HOT TO HOLD</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="n">
-        <v>205</v>
+        <v>59</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>已选: #1.5 中性一白 30ml</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>205</v>
-      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>304</v>
+        <v>23</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>【GUCCI】古驰花悦绽放浓香水100ml简装黑盖女士香氛正品持久留香</t>
+          <t>Nature BOBO澳洲番木瓜膏16g*2支润唇膏保湿女唇膜霜油滋润保湿</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>GUCCI花悦绽放100ML浓香</t>
+          <t>Nature BOBO澳洲木瓜膏唇膜润唇1</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="n">
-        <v>339</v>
+        <v>25.1</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>2023-09-01</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>310</v>
+        <v>24</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>【HR】赫莲娜绿宝瓶悦活蓄能新肌水200ml</t>
+          <t>【正品行货】SKII男士神仙水精华露护肤补水紧致抗皱晶透保湿舒缓</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>赫莲娜绿宝瓶新肌水400ml</t>
+          <t>SK2 神仙水230ml</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="n">
-        <v>484</v>
+        <v>847</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2325,32 +2277,32 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>310</v>
+        <v>25</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>【12.6万人回购该品牌】两瓶 单品 HR赫莲娜绿宝瓶悦活蓄能新肌水400ml</t>
+          <t>【正品行货】SK-II赋能焕彩精华霜100g全新大红瓶滋润紧致保湿sk2</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>赫莲娜绿宝瓶新肌水400ml</t>
+          <t>SK2大红瓶滋润面霜100g</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>1599</v>
+        <v>949</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>1314</v>
+        <v>858</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2359,34 +2311,28 @@
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>已选: 400mL 2瓶</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="n">
-        <v>1314</v>
-      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>310</v>
+        <v>26</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>【2.47万人评价品牌正品】HR/赫莲娜绿宝瓶新肌水200ml*2瓶 精华爽肤水</t>
+          <t>【正品行货】SK-II神仙水330ml抗皱精华液 SK2护肤精华露专柜单品</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>赫莲娜绿宝瓶新肌水400ml</t>
+          <t>SK2神仙水330ML</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>1200</v>
+        <v>1098</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>988</v>
+        <v>948</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2395,45 +2341,35 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；规格匹配失败</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>310</v>
+        <v>27</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>【HR】赫莲娜绿宝瓶悦活蓄能新肌水400ml</t>
+          <t>国内专柜 SK-II男士焕活保湿洁面霜120g 氨基酸清洁洗面奶sk2skll</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>赫莲娜绿宝瓶新肌水400ml</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="n">
-        <v>819</v>
-      </c>
+          <t>SK-II 男士保湿焕活洁面霜120g</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="n">
-        <v>658</v>
+        <v>315</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -2442,7 +2378,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2456,79 +2392,63 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>311</v>
+        <v>28</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>【HR】赫莲娜绿宝瓶悦活蓄能新肌水400ml</t>
+          <t>【SK-II】 男士焕活护肤精华露230ml 补水保湿 提亮肤色【5天内发货】</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>赫莲娜绿宝瓶新肌水200ml</t>
+          <t>SK-II 男士焕活护肤精华露 230ml</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>819</v>
+        <v>888</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>642</v>
+        <v>760</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>2025-02-01</t>
-        </is>
-      </c>
+      <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；规格匹配失败</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>311</v>
+        <v>28</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>【12.6万人回购该品牌】双支 单品 HR赫莲娜绿宝瓶悦活蓄能新肌水200ml</t>
+          <t>SK-II 男士焕活护肤精华露230ml 补水保湿 提亮肤色【7月4日发完】</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>赫莲娜绿宝瓶新肌水200ml</t>
+          <t>SK-II 男士焕活护肤精华露 230ml</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" s="2" t="n">
-        <v>960</v>
+        <v>840</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>2025-03-01</t>
-        </is>
-      </c>
+      <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -2540,21 +2460,23 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>311</v>
+        <v>29</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>【HR】赫莲娜绿宝瓶悦活蓄能新肌水200ml</t>
+          <t>【正品行货】SKII小银瓶肌因光蕴淡斑精华露50ml提亮淡斑淡痘印</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>赫莲娜绿宝瓶新肌水200ml</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr"/>
+          <t>SK-II 小银瓶淡斑精华露75ml</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>1300</v>
+      </c>
       <c r="E52" s="2" t="n">
-        <v>484</v>
+        <v>782</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -2563,35 +2485,43 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>311</v>
+        <v>30</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】HR/赫莲娜绿宝瓶新肌水200ml保湿修护提亮补水精华水</t>
+          <t>【正品行货】SKII小银瓶肌因光蕴淡斑精华露50ml提亮淡斑淡痘印</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>赫莲娜绿宝瓶新肌水200ml</t>
+          <t>SK-II 小银瓶淡斑精华露75ml</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="2" t="n">
-        <v>533</v>
+        <v>1380</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -2600,129 +2530,113 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>354</v>
+        <v>31</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>【娇韵诗】双萃焕活修护精华露75ml清爽九代补水</t>
+          <t>【SK-II】小灯泡精华50ml美白光蕴臻采焕亮精华露sk2紧致淡纹正品【5天内发货】</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>娇韵诗双萃焕活修护精华露100ml</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="n">
-        <v>699</v>
-      </c>
+          <t>SK-II光蕴臻采焕亮精华露双瓶装</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="n">
-        <v>570</v>
+        <v>1299</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；规格匹配失败</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>354</v>
+        <v>31</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>【娇韵诗】双萃焕活修护精华露75ml清爽轻盈九代补水</t>
+          <t>【正品行货】SK-II小灯泡SK2光蕴臻采焕亮精华露美白淡斑精华30ml</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>娇韵诗双萃焕活修护精华露100ml</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="n">
-        <v>699</v>
-      </c>
+          <t>SK-II光蕴臻采焕亮精华露双瓶装</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr"/>
       <c r="E55" s="2" t="n">
-        <v>572.8</v>
+        <v>759</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；规格匹配失败</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>354</v>
+        <v>31</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>【娇韵诗】双萃焕活修护精华露100ml清爽九代补水</t>
+          <t>【SK-II】小灯泡精华50ml美白光蕴臻采焕亮精华露祛斑提亮肤色【5天内发货】</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>娇韵诗双萃焕活修护精华露100ml</t>
+          <t>SK-II光蕴臻采焕亮精华露双瓶装</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="n">
-        <v>899</v>
+        <v>1664</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -2731,7 +2645,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2745,21 +2659,21 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>354</v>
+        <v>32</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>【娇韵诗】双萃焕活修护精华露50ml清爽九代补水</t>
+          <t>Tom Ford/汤姆福特tf白麝香香水100ml持久体香留香礼物浓香【5天内发货】</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>娇韵诗双萃焕活修护精华露100ml</t>
+          <t>TF白麝香 100ml</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" s="2" t="n">
-        <v>569</v>
+        <v>1430</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -2768,95 +2682,79 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；规格匹配失败</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>358</v>
+        <v>32</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>三只松鼠品牌官方正品，100%保障</t>
+          <t>TF汤姆福特白麝香香水(新暗麝心魄香型)100ML浓香木质花香</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>YSL圣罗兰黑金方管1968</t>
+          <t>TF白麝香 100ml</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="n">
-        <v>12.4</v>
+        <v>2299</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；品名相似不足(ratio=25.0%)；规格匹配失败</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>358</v>
+        <v>32</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>YSL/圣罗兰黑金浮雕方管口红NM裸缪斯RM红缪斯丝绒哑光持久正品</t>
+          <t>正品TOM FORD汤姆福特TF限量暗麝心魄浓香水EDP白麝香30/50/100ml【5天内发货】</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>YSL圣罗兰黑金方管1968</t>
+          <t>TF白麝香 100ml</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="2" t="n">
-        <v>386</v>
+        <v>988</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>2023-11-17</t>
-        </is>
-      </c>
+      <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -2864,7 +2762,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>规格不匹配；规格匹配失败</t>
+          <t>规格匹配失败</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -2876,62 +2774,60 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>358</v>
+        <v>33</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>【YSL】圣罗兰黑金浮雕方管唇膏口红1968透视1971 14 11礼盒装520礼物</t>
+          <t>【TOM FORD】 汤姆福特 黑管#16 哑光</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>YSL圣罗兰黑金方管1968</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr"/>
+          <t>TF黑管哑光16</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>270</v>
+      </c>
       <c r="E60" s="2" t="n">
-        <v>158</v>
+        <v>245</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>规格匹配失败</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>358</v>
+        <v>34</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>YSL/圣罗兰黑金浮雕方管釉光唇膏口红1971流言06裸缪斯NM1968正品</t>
+          <t>【正品】TomFord汤姆福特tf黑金哑光丝绒唇釉123 欲火6ml</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>YSL圣罗兰黑金方管1968</t>
+          <t>TF黑金唇釉123</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="2" t="n">
-        <v>118</v>
+        <v>85.3</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -2941,193 +2837,207 @@
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>规格匹配失败</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>398</v>
+        <v>35</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>正品马吉拉香水爵士酒廊中性淡香水木质香水30ml</t>
+          <t>正品TomFord/汤姆福特四色眼影41#PeachDawnTF桃色晨曦盘哑光显色【5天内发货】</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>马丁马吉拉-爵士酒廊淡香100ml</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="n">
-        <v>178</v>
-      </c>
+          <t>TF幻魅四色眼影盘#41 Peach Dawn桃色晨曦盘</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr"/>
       <c r="E62" s="2" t="n">
-        <v>94.81999999999999</v>
+        <v>298</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
+      <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；规格不匹配；规格匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr"/>
+          <t>已选择： +原包装盒+TF眼影#41</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>298</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>408</v>
-      </c>
-      <c r="B63" s="2" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>TOMFORD 汤姆福特 幻魅四色眼影41珠光光大地色烟熏日常百搭正品【5天内发货】</t>
+        </is>
+      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>NARS液体腮红 INSATIABLE</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="n">
-        <v>18.9</v>
-      </c>
+          <t>TF幻魅四色眼影盘#41 Peach Dawn桃色晨曦盘</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr"/>
       <c r="E63" s="2" t="n">
-        <v>10.46</v>
+        <v>589</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>品牌不一致；品名相似不足(ratio=0.0%)</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>408</v>
+        <v>36</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>NARS/纳斯 小粉金液体腮红 #INSATIABLE 酒渍樱桃【5天内发货】</t>
+          <t>【正品行货】TF幻魅四色眼影 2025汤姆福特璀璨流光限定01#9g</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>NARS液体腮红 INSATIABLE</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr"/>
+          <t>TF幻魅四色眼影盘#GOLDEN MINK</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>800</v>
+      </c>
       <c r="E64" s="2" t="n">
-        <v>86</v>
+        <v>523</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>408</v>
+        <v>37</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Nars纳斯夏季新品液体腮红小粉金管自然服帖显示牛奶粉紫杏茶玫瑰【5天内发货】</t>
+          <t>【正品行货】TOM FORD汤姆福特镜面唇蜜 新色唇釉 雪映流光 03 N3</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>NARS液体腮红 INSATIABLE</t>
+          <t>TF镜面唇蜜17</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
       <c r="E65" s="2" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>408</v>
+        <v>38</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>【NARS】纳斯全新小粉金液体腮红 腮紫牛奶粉紫色显嫩自然膨胀收缩色【5天内发货】</t>
+          <t>Tom Ford 汤姆福特 珍华乌木香水 EDP 100ml檀香沉木</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>NARS液体腮红 INSATIABLE</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr"/>
+          <t>TF汤姆福特 乌木沉香 100ml</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>17992</v>
+      </c>
       <c r="E66" s="2" t="n">
-        <v>165</v>
+        <v>1799</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -3139,73 +3049,69 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>421</v>
+        <v>39</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>【超值囤货装】伊丽莎白雅顿经典润泽SPF15唇膏8小时保湿滋润防晒</t>
+          <t>Tom Ford汤姆福特TF细黑管口红52#裸玫瑰3.3g丝缎哑光【5天内发货】</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>伊丽莎白雅顿经典唇膏13g</t>
+          <t>TF细黑管52</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>199</v>
+        <v>299</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>119.98</v>
+        <v>213</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；规格匹配失败</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>421</v>
+        <v>40</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>【官方正品】伊丽莎白雅顿唇膏经典润泽唇膏雅顿八小时润唇膏</t>
+          <t>【两瓶装】日本未来vape驱蚊水喷雾孕妇儿童驱蚊液宝宝婴儿防蚊</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>伊丽莎白雅顿经典唇膏13g</t>
+          <t>VAPE未来驱蚊液 海蓝柑橘喷雾 200ml</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="2" t="n">
-        <v>119</v>
+        <v>44.44</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3227,28 +3133,32 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>MAC/魅可 热吻棒唇膏口红 显色显白哑光滋润不掉色67狂野棕【5天内发货】</t>
+          <t>【跨境原装】YSL圣罗兰小黑条316口红滋润显色送礼物国际彩妆5年</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>MAC热吻棒67</t>
+          <t>YSL 细管丝绒纯口红 小黑条 316#</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
       <c r="E69" s="2" t="n">
-        <v>72</v>
+        <v>125.58</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -3260,22 +3170,20 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>【NARS】超方瓶粉底液持妆持久养肤轻薄轻透奶油肌新年礼物送女友</t>
+          <t>【YSL】圣罗兰唇釉416  爱心限定黑管 镜面水光口红 正品保真</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>NARS超方瓶粉底液L4</t>
+          <t>YSL黑管唇釉416</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
-      <c r="E70" s="2" t="n">
-        <v>228</v>
-      </c>
+      <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -3284,39 +3192,29 @@
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；规格匹配失败</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】娜斯/纳斯全新超方瓶粉底液L02流光美肌养肤遮瑕持久</t>
+          <t>【YSL】圣罗兰唇釉416  爱心限定黑管 镜面水光口红 正品保真</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>NARS超方瓶粉底液L4</t>
+          <t>YSL黑管唇釉416</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
-      <c r="E71" s="2" t="n">
-        <v>238</v>
-      </c>
+      <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -3325,163 +3223,155 @@
       <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；规格匹配失败</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>【正品行货】娜斯/纳斯NARS超方瓶粉底液L02流光美肌养肤遮瑕持久</t>
+          <t>【YSL】圣罗兰反转巴黎浓香水EDP 50ml 果香西普调礼物</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>NARS超方瓶粉底液L4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr"/>
+          <t>YSL反转巴黎浓香香水50ml</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>4982</v>
+      </c>
       <c r="E72" s="2" t="n">
-        <v>256</v>
+        <v>498</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>规格不匹配；规格匹配失败</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>【NARS】纳斯超方瓶粉底液新款小方瓶L0L2持久不脱妆养肤保湿遮瑕正品</t>
+          <t>【专柜正品】YSL圣罗兰粉气垫B10替换芯 持久遮瑕细腻干皮挚爱</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>NARS超方瓶粉底液L4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr"/>
+          <t>YSL粉气垫替换芯B10</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>450</v>
+      </c>
       <c r="E73" s="2" t="n">
-        <v>338</v>
+        <v>292.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>2024-01-04</t>
+        </is>
+      </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>已选择： 【L4】黄二白 +  美妆蛋</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="n">
-        <v>338</v>
-      </c>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>【NARS】纳斯 超方瓶流光美肌粉底液 L1 30ml提亮肤色</t>
+          <t>光辉岁月618大促刚下单还差1人拼成现在拼</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>NARS 超方瓶粉底液#L1</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="n">
-        <v>289</v>
-      </c>
-      <c r="E74" s="2" t="n">
-        <v>165</v>
-      </c>
+          <t>YSL粉气垫替换芯B10</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>2024-06-29</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>【NARS】纳斯 超方瓶流光美肌粉底液 L1 30ml提亮肤色</t>
+          <t>【专柜正品】YSL圣罗兰粉气垫B10遮瑕细腻粉质轻薄干皮挚爱</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>NARS 超方瓶粉底液#L1</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>289.0</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>165.0</t>
-        </is>
+          <t>YSL粉气垫B10</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="n">
+        <v>696</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -3490,40 +3380,54 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
       <c r="K75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>【拉夫劳伦】Ralph Lauren POLO俱乐部Ralph'sClub男士浓淡香水木质调【5天内发货】</t>
+          <t>【专柜正品】YSL/圣罗兰粉气垫BR20替换芯遮瑕持久不脱妆干皮挚爱</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>拉夫劳伦俱乐部香水淡香型 100ML</t>
+          <t>YSL粉气垫替换芯br20</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
-      <c r="E76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="n">
+        <v>450</v>
+      </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>2024-01-04</t>
+        </is>
+      </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
           <t>❌</t>
@@ -3531,7 +3435,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>规格不匹配；规格匹配失败</t>
+          <t>规格匹配失败</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -3543,24 +3447,20 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>【拉夫劳伦】俱乐部小熊限定香水l肖战同款馥奇木质香男士持久淡香</t>
+          <t>电动车防水防晒坐垫套电瓶车电动自行车全包皮革坐套四季通用款</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>拉夫劳伦俱乐部香水淡香型 100ML</t>
+          <t>YSL粉气垫替换芯br20</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>255.9</t>
-        </is>
-      </c>
+      <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr">
         <is>
           <t>否</t>
@@ -3574,7 +3474,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>规格不匹配；规格匹配失败</t>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=12.5%)；规格匹配失败</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -3586,30 +3486,34 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>【拉夫劳伦】俱乐部男士香水100ml 木质调持久留香 秋冬氛围感渣男香</t>
+          <t>YSL圣罗兰黑鸦片女士香水EDP50ml浓香咖啡花香【6月27日发完】</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>拉夫劳伦俱乐部香水淡香型 100ML</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr"/>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>255.9</t>
-        </is>
+          <t>YSL黑鸦片浓香50ml</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>479</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>393</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
           <t>✅</t>
@@ -3618,6 +3522,4167 @@
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL/圣罗兰粉圆管大牌润唇膏口红水光晶莹正品礼盒装</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>YSL口红8B</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>已选择： 粉管 YSL 【8B】  透光杏茶 #原装正品 【自用选我】    *    支持鉴定</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL粉色皮革气垫轻薄水光肌BR10/B10/B20 替换芯正品</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>YSL皮革气垫B20替换芯新款</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="n">
+        <v>305</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>已选择： YSL黑皮革气垫#B20 + 【专柜礼袋礼盒】 14g 【粉色12g  黑色14g】</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>【圣罗兰】明彩粉光轻垫粉底液 B20 #12g 正装粉气垫粉皮革 遮瑕细腻</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰皮气垫新明彩亮润轻垫粉底液 #B20</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr"/>
+      <c r="E81" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>【圣罗兰】明彩粉光轻垫粉底液 B20 #12g 正装粉气垫粉皮革 遮瑕细腻</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>YSL圣罗兰皮气垫新明彩亮润轻垫粉底液 #B20</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>【YSL】圣罗兰小金条细管口红哑光易上色持久1966/2024</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>YSL细管小金条 #1966</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr"/>
+      <c r="E83" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰新品自由之水30ml上瘾浆果持久香水EDP浓香</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>YSL自由之水浓香型30ml</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="n">
+        <v>495.87</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】YSL圣罗兰香水自由之水浓香50ML杨树林正品大牌</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>YSL自由之水浓香50ml</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>568</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>492</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>【YSL】圣罗兰自由之水浓香EDP50ml 持久留香</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>YSL自由之水浓香50ml</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>458</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>【YSL】圣罗兰自由之水浓香EDP50ml 持久留香</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>YSL自由之水浓香90ml</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>458</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>7天无理由退货</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>YSL自由之水浓香90ml</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=25.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>【9.3万人收藏】芍福堂正宗桂花酸梅粉酸梅汤饮料酸梅晶商用独立包装泡水喝的东西</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>YSL自由之水浓香90ml</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr"/>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=25.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>【农夫山泉】东方树叶335ml小瓶装迷你乌龙茶茉莉花茶无糖零卡零脂肪</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>YSL自由之水浓香90ml</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr"/>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>【GIORGIO ARMANI】 阿玛尼寄情男士EDT淡香水30ml 水生调</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼 寄情男士淡香水100ml 新版</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>259</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼 寄情男士淡香水100ml 新版</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr"/>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>川崎品牌官方正品，100%保障</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼 寄情男士淡香水100ml 新版</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr"/>
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>【农夫山泉】水溶C100柠檬西柚250ml*5瓶装饮料 mini装出游便携装</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼大师蓝标粉底液1.5</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr"/>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>【2.25万人评价品牌正品】ARMANI阿玛尼红管唇釉#206红棕色丝绒复古哑光滋润提升气色【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼红管唇釉206#</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>154.3</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>【专柜正品】阿玛尼红管丝绒唇釉显白口红405passion燃情红</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼红管唇釉405-24年</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr"/>
+      <c r="E96" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>2024-01-02</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>【品牌好评109.3万+条】GIORGIO ARMANI/阿玛尼红气垫替换芯15g#2号色单双个控油持妆新款</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼红气垫替换芯2#-24年</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr"/>
+      <c r="E97" s="2" t="n">
+        <v>98.98999999999999</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>【阿玛尼】权力粉底液 3 号新款 30ml 持妆控油遮瑕油皮亲妈持久</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼权力粉底液3号</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>【9.4万人收藏】ARMANI 阿玛尼 权利权力粉底液长效遮瑕 30mI 3#</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼权力粉底液3号</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr"/>
+      <c r="E99" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】阿玛尼唇釉405烂番茄红管214丝绒哑光水唇釉206口红</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼臻致丝绒哑光唇釉#214</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr"/>
+      <c r="E100" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>【原装正品】阿玛尼红管丝绒唇釉显白保湿口红214奶杏色哑光持久【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼臻致丝绒哑光唇釉#214</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr"/>
+      <c r="E101" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>ARMANI/阿玛尼 红管丝绒哑光唇釉 #214暖昧奶杏【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼臻致丝绒哑光唇釉#214</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr"/>
+      <c r="E102" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】阿玛尼唇釉405烂番茄红管214丝绒哑光水唇釉206口红</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼臻致丝绒哑光唇釉#214</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr"/>
+      <c r="E103" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>【正品】阿玛尼口红挚爱哑光唇膏红黑管#400复古红 正装4g</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>阿玛尼挚爱哑光唇膏#400</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>【百补品牌热销45.2万件】双支爱马仕尼罗河花园淡香EDT30ml持久留香正装</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕尼罗河淡香30ml</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr"/>
+      <c r="E105" s="2" t="n">
+        <v>336.5</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>【1.35万人评价品牌正品】双支爱马仕尼罗河花园淡香EDT30ml持久留香正装</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕尼罗河淡香30ml</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>599</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>345</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>【爱马仕】尼罗河花园香水淡香EDT30ml持久留香正装</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>爱马仕尼罗河淡香30ml</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>【4.9万人回购该品牌】BobbiBrown芭比波朗密集奢采精华妆前隔离乳40ml妆前乳水润轻薄</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>芭比波朗 密集修护菁华妆前乳 40ml</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr"/>
+      <c r="E108" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>【芭比波朗】橘子面霜维他命妆前隔离柔润底霜50ml</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>芭比波朗 维他命橘子面霜 50ml</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>295</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>【百补品牌热销39.3万件】Bobbi Brown芭比波朗月光石眼影爆闪亮片moonstone提亮卧蚕高光【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>芭比波朗月光石眼影</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>176.43</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>【74.1万人收藏该品牌】Bobbi Brown 芭比波朗 月光石眼影#Moon stone</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>芭比波朗月光石眼影</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】BYREDO柏芮朵百瑞德无人区玫瑰典藏版EDP浓香50ml</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>百瑞德无人区玫瑰50ML</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>1970</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>1399</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>【BYREDO】百瑞德无人之境EDP浓香水50ml 无人区玫瑰</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>百瑞德无人区玫瑰50ML</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>999</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>【城野医生】377美白精华18g淡斑提亮紧致保湿淡化痘印精华液护肤品</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>城野医生美白淡斑精华18g</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】黛珂多重亮护素颜乳35g妆前防晒保湿润色修颜</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>黛珂多重修颜素颜霜35</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>【黛珂】防晒霜多重防晒乳耐水型55ml 防水防汗水润养肤</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>黛珂 防晒防水版60g</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr"/>
+      <c r="E116" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>日本黛珂多重防晒乳防晒霜60g防水款【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>黛珂 防晒防水版60g</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr"/>
+      <c r="E117" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr"/>
+      <c r="K117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>【黛珂】防晒霜多重防晒乳防水版58ml防水防汗水润养肤</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>黛珂 防晒防水版60g</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr"/>
+      <c r="E118" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>【黛珂】植物韵律乳液200ml女保湿化妆水补水收缩毛孔提亮去黄清爽型K</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>黛珂 植物韵律清爽乳200ml</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr"/>
+      <c r="E119" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr"/>
+      <c r="K119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>【黛珂】植物韵律清爽型水乳套装200ml 平衡水油细致毛孔</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>黛珂 植物韵律清爽乳200ml</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>【黛珂】水乳植物韵律水乳套装200ml(清爽型) 清爽保湿</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>黛珂 植物韵律清爽水200ml</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr"/>
+      <c r="K121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】黛珂AQ舒活耀白水乳200mL白檀祛斑美白新升级套装</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>黛珂AQ白檀乳液200ml清爽型</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>699</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>580</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>【特价清仓】黛珂AQ白檀舒活修复化妆水爽肤水清爽型200ml抗衰老</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>黛珂AQ白檀水200ml清爽型</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr"/>
+      <c r="E123" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr"/>
+      <c r="K123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>【特价清仓】黛珂AQ白檀舒活化妆水保湿修护爽肤水清爽型200ml</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>黛珂AQ白檀水200ml清爽型</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr"/>
+      <c r="E124" s="2" t="n">
+        <v>218.99</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】黛珂AQ舒活耀白水乳200mL白檀祛斑美白新升级套装</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>黛珂AQ舒活白檀美白乳液200ml</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>699</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>580</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Decorte黛珂AQ舒活凝光化妆水II滋润型 200ml 【法国直发】【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>黛珂AQ舒活滋润化妆水200ml</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr"/>
+      <c r="E126" s="2" t="n">
+        <v>395</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】黛珂AQ舒活耀白水乳200mL白檀祛斑美白新升级套装</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>黛珂AQ舒活滋润乳液200ml</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>699</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>580</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】黛珂牛油果植萃乳液祛痘控油保湿紧致150ml</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>黛珂牛油果乳液 300ml</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr"/>
+      <c r="E128" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr"/>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>黛珂牛油果乳液 300ml</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr"/>
+      <c r="E129" s="2" t="inlineStr"/>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>【一周内2600+人拼单】361度硅胶握力圈手指训练康复专业男女握力器儿童学生练臂训练器</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>黛珂牛油果乳液 300ml</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr"/>
+      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>【三只松鼠】生椰脆100g*1袋即食薄脆椰果休闲果干蜜饯零食</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>黛珂牛油果乳液150ml</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr"/>
+      <c r="E131" s="2" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=20.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】黛珂牛油草本水乳套装150ml+150ml保湿控油官方正品</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>黛珂牛油果乳液150ml</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>2023-07-29</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr"/>
+      <c r="K132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】黛珂牛油果植萃乳液祛痘控油保湿紧致150ml</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>黛珂牛油果乳液150ml</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr"/>
+      <c r="E133" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="2" t="inlineStr"/>
+      <c r="K133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>【三只松鼠】生椰脆100g*1袋即食薄脆椰果休闲果干蜜饯零食</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>黛珂沁活晶澈润肤精华水200ml</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr"/>
+      <c r="E134" s="2" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>【官方授权】黛珂沁活晶澈精华水换季补水保湿滋润紧致明亮200ml</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>黛珂沁活晶澈润肤精华水200ml</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr"/>
+      <c r="E135" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>2023-03-15</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr"/>
+      <c r="K135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>【黛珂】心悦容光幻纱丝柔蜜粉#01细腻柔滑持久调光师定妆散粉</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>黛珂散粉01 24年新版</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>【黛珂】2024新版心悦容光幻纱丝柔蜜粉细腻柔滑持久定妆</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>黛珂散粉光肌00 24年新版</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr"/>
+      <c r="E137" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>【黛珂】DECORTE 紫苏水300ml+牛油果乳液300ml 水乳套装</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>黛珂紫苏水 300ml</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>459</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>348</v>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="2" t="inlineStr"/>
+      <c r="K138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>【品牌好评67万+条】Decorte黛珂植萃牛油果紫苏水乳150ml*2支护肤品组合</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>黛珂紫苏水150ml</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr"/>
+      <c r="E139" s="2" t="n">
+        <v>310</v>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>【德美乐嘉】多维面膜10ml滋养修护保湿紧致熬夜救急胡萝卜涂抹面膜</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>德美乐嘉多维面膜涂抹面膜75ml</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr"/>
+      <c r="E140" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>【三只松鼠】生椰脆100g*1袋即食薄脆椰果休闲果干蜜饯零食</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>费列罗榛果巧克力制品T24</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr"/>
+      <c r="E141" s="2" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=11.1%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>【308.1万人收藏该品牌】WHOO 后 拱辰享净澈洁面膏180ml 小云朵洗面奶 焕肤净透</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>拱辰享洁面180ml</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr"/>
+      <c r="E142" s="2" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>【6.7万人回购该品牌】Gucci/古驰花悦绽放女士浓香水50mlEDP  BLOOM茉莉香</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>古驰花悦绽放女士浓香50ml</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr"/>
+      <c r="E143" s="2" t="n">
+        <v>388</v>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>2023-01-21</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI古驰口红217金管倾色绒雾哑光礼盒装 生日礼物</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>古驰金管217哑光</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr"/>
+      <c r="E144" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰 倾色绒雾唇膏#208 情倾阿根廷 蜜桃奶茶 金管哑光口红</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>古驰金管哑光口红208#</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" s="2" t="inlineStr"/>
+      <c r="K145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰 绮梦香草兰香型女士浓香水30ML 水生美食调</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>古驰绮梦香草兰香型30ml</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr"/>
+      <c r="E146" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】Gucci/古驰绮梦木兰女士浓香水持久留香大牌节日礼物</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>古驰绮梦香草兰香型30ml</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr"/>
+      <c r="E147" s="2" t="n">
+        <v>384</v>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；品名相似不足(ratio=25.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>同城用户刚刚拼成&amp;#10;可参与拼单马上拼</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>古驰绮梦香草兰香型30ml</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr"/>
+      <c r="E148" s="2" t="inlineStr"/>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>品牌不一致；规格不匹配；品名相似不足(ratio=0.0%)；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI古驰倾色琉光唇膏25口红细管滋润节日礼物女士</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>古驰细管口红#25*</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr"/>
+      <c r="E149" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI古驰倾色琉光唇膏25细管口红显白送女友礼盒装</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>古驰细管口红#25*</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>【专柜礼盒】GUCCI古驰口红碎花25金管哑光滋润505大牌专柜礼盒</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>古驰细管口红#25*</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr"/>
+      <c r="E151" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】Gucci古驰口红505金管绒雾哑光口红礼盒装 生日礼物</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>古驰倾色绒雾唇膏505（金色短管）</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>309</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI古驰金管倾色绒雾哑光505口红唇膏节日礼物女生</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>古驰倾色绒雾唇膏505（金色短管）</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>229</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr"/>
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI/古驰倾色云雾哑光锁色持久唇釉203 505 208</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>古驰倾色云雾唇釉505（红色长管）</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr"/>
+      <c r="E154" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI/古驰倾色云雾哑光锁色持久唇釉208 505 203 25【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>古驰倾色云雾唇釉505（红色长管）</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI/古驰 倾色云雾哑光锁色持久唇釉25# 208# 505#【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>古驰倾色云雾唇釉505（红色长管）</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>已选: 505#复古红棕</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI古驰倾色云雾唇釉208哑光505易上色217送女友</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>古驰倾色云雾唇釉505（红色长管）</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr"/>
+      <c r="E157" s="2" t="n">
+        <v>229</v>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰竹韵女士EDT淡香水50ml木质花香调送礼礼物</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>古驰竹韵淡香50ml</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr"/>
+      <c r="E158" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>【全球购正品】古驰竹韵女性淡香氛50ml</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>古驰竹韵淡香50ml</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr"/>
+      <c r="E159" s="2" t="n">
+        <v>464</v>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr"/>
+      <c r="K159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>【品牌好评58.4万+条】Gucci/古驰竹韵女士淡香水50ml花香木质清新持久礼物</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>古驰竹韵淡香50ml</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr"/>
+      <c r="E160" s="2" t="n">
+        <v>329</v>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI古驰罪爱男士浓香水经典系列男神雪松EDP 50ml</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>古驰罪爱男香50ml</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr"/>
+      <c r="E161" s="2" t="n">
+        <v>311.99</v>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="2" t="inlineStr"/>
+      <c r="K161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>【古驰】罪爱惹火男士淡香水精粹版EDT50/90ml 清新淡雅</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>古驰罪爱男香50ml</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰罪爱男士EDT淡香水50ML 木质香调 经典礼物</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>古驰罪爱男香50ml</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>201.9</v>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" s="2" t="inlineStr"/>
+      <c r="K163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销136.5万+件】LA MER/海蓝之谜润唇膏唇蜜唇膜唇霜品牌礼盒装送人淡化唇纹正品</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜唇膜9g</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr"/>
+      <c r="E164" s="2" t="n">
+        <v>488</v>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-05</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>LA MER海蓝之谜润唇膜9g唇膏保湿滋润舒缓修护淡化唇纹【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜唇膜9g</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr"/>
+      <c r="E165" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" s="2" t="inlineStr"/>
+      <c r="K165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>LA MER海蓝之谜润唇膜9g唇膏保湿滋润舒缓修护淡化唇纹无盒自用【6月26日发完】</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜唇膜9g</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr"/>
+      <c r="E166" s="2" t="n">
+        <v>330</v>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" s="2" t="inlineStr"/>
+      <c r="K166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI/古驰倾色云雾哑光锁色持久唇釉203 505 208</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>古驰倾色云雾唇釉505（红色长管）</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr"/>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI/古驰倾色云雾哑光锁色持久唇釉208 505 203 25【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>古驰倾色云雾唇釉505（红色长管）</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>GUCCI/古驰 倾色云雾哑光锁色持久唇釉25# 208# 505#【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>古驰倾色云雾唇釉505（红色长管）</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>119.0</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>已选: 505#复古红棕</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI古驰倾色云雾唇釉208哑光505易上色217送女友</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>古驰倾色云雾唇釉505（红色长管）</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr"/>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>229.0</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰竹韵女士EDT淡香水50ml木质花香调送礼礼物</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>古驰竹韵淡香50ml</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr"/>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>273.0</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr"/>
+      <c r="J171" s="2" t="inlineStr"/>
+      <c r="K171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>【全球购正品】古驰竹韵女性淡香氛50ml</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>古驰竹韵淡香50ml</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr"/>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>464.0</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>【品牌好评58.4万+条】Gucci/古驰竹韵女士淡香水50ml花香木质清新持久礼物</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>古驰竹韵淡香50ml</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr"/>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>329.0</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr"/>
+      <c r="J173" s="2" t="inlineStr"/>
+      <c r="K173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>【正品行货】GUCCI古驰罪爱男士浓香水经典系列男神雪松EDP 50ml</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>古驰罪爱男香50ml</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr"/>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>311.99</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr"/>
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>【古驰】罪爱惹火男士淡香水精粹版EDT50/90ml 清新淡雅</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>古驰罪爱男香50ml</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>389.0</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>【GUCCI】古驰罪爱男士EDT淡香水50ML 木质香调 经典礼物</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>古驰罪爱男香50ml</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>201.9</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销136.5万+件】LA MER/海蓝之谜润唇膏唇蜜唇膜唇霜品牌礼盒装送人淡化唇纹正品</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜唇膜9g</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr"/>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>488.0</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-05</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>【国内直售】LAMER唇膏9g 护唇膏唇部护理海蓝之谜唇膜</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜唇膜9g</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr"/>
+      <c r="E178" s="2" t="inlineStr"/>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>LA MER海蓝之谜润唇膜9g唇膏保湿滋润舒缓修护淡化唇纹【5天内发货】</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜唇膜9g</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr"/>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="inlineStr"/>
+      <c r="K179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>LA MER海蓝之谜润唇膜9g唇膏保湿滋润舒缓修护淡化唇纹无盒自用【6月26日发完】</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜唇膜9g</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr"/>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>330.0</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr"/>
+      <c r="K180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>【累计热销136.5万+件】LAMER海蓝之谜精萃水乳套装礼盒紧致舒缓抗皱护肤情人节限定礼盒</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜精粹水 150ml 新版</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>2988.0</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>1850.0</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>【LA MER】 海蓝之谜 清爽版精粹水150ml 25年新版</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜精粹水 150ml 新版</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>1109.0</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr"/>
+      <c r="K182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>【品牌好评115.2万+条】LAMER海蓝之谜精粹水15ML(新版) 油皮版痘痘闭口保湿细肤</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>海蓝之谜精粹水 150ml 新版</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr"/>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>规格不匹配；规格匹配失败</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>匹配失败</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
